--- a/test/TestExecutionReport.xlsx
+++ b/test/TestExecutionReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITI_Courses\QA\QA-project-tool\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\9Months\QA\Project\QA-project-tool\QA-project-tool\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A73AA9-2204-4F3A-98B1-7FF4807F63C8}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C83A4B1-BE40-4E4E-9DF5-A0D1CD117CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Execution " sheetId="1" r:id="rId1"/>
@@ -20,15 +20,23 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="402">
   <si>
     <t>TesTCASE ID</t>
   </si>
@@ -1405,6 +1413,9 @@
   <si>
     <t>email:ali@gmail.com
 password:  ali123456</t>
+  </si>
+  <si>
+    <t>blocked</t>
   </si>
 </sst>
 </file>
@@ -1670,12 +1681,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1695,6 +1700,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1750,44 +1761,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
         <right/>
         <top style="thin">
           <color indexed="64"/>
@@ -1826,6 +1799,44 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1862,10 +1873,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="C86:D90" headerRowCount="0" headerRowDxfId="7" dataDxfId="10" totalsRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="C86:D90" headerRowCount="0" headerRowDxfId="10" dataDxfId="9" totalsRowDxfId="8">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Test Execution -style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2073,25 +2084,25 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC1083"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="22.88671875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="85" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="31.21875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="33.88671875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="39" style="3" customWidth="1"/>
-    <col min="9" max="9" width="30.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="80.77734375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="51.6640625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="29.21875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="24.44140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="30.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="80.7109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="51.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="29.28515625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="24.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="3" customWidth="1"/>
     <col min="16" max="16" width="23" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="12.6640625" style="3"/>
+    <col min="17" max="16384" width="12.7109375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="42">
@@ -2159,7 +2170,7 @@
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
     </row>
-    <row r="2" spans="1:29" ht="92.4">
+    <row r="2" spans="1:29" ht="89.25">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -2181,7 +2192,7 @@
       <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="25" t="s">
         <v>360</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -2218,7 +2229,7 @@
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
     </row>
-    <row r="3" spans="1:29" ht="26.4">
+    <row r="3" spans="1:29" ht="25.5">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -2231,7 +2242,7 @@
       <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -2273,7 +2284,7 @@
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
     </row>
-    <row r="4" spans="1:29" ht="92.4">
+    <row r="4" spans="1:29" ht="89.25">
       <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
@@ -2286,7 +2297,7 @@
       <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -2330,7 +2341,7 @@
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
     </row>
-    <row r="5" spans="1:29" ht="105.6">
+    <row r="5" spans="1:29" ht="102">
       <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
@@ -2343,7 +2354,7 @@
       <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2387,7 +2398,7 @@
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
     </row>
-    <row r="6" spans="1:29" ht="92.4">
+    <row r="6" spans="1:29" ht="89.25">
       <c r="A6" s="4" t="s">
         <v>37</v>
       </c>
@@ -2400,7 +2411,7 @@
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2444,7 +2455,7 @@
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
     </row>
-    <row r="7" spans="1:29" ht="92.4">
+    <row r="7" spans="1:29" ht="89.25">
       <c r="A7" s="4" t="s">
         <v>39</v>
       </c>
@@ -2457,7 +2468,7 @@
       <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -2466,7 +2477,7 @@
       <c r="G7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="26" t="s">
         <v>368</v>
       </c>
       <c r="I7" s="4" t="s">
@@ -2501,7 +2512,7 @@
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
     </row>
-    <row r="8" spans="1:29" ht="92.4">
+    <row r="8" spans="1:29" ht="89.25">
       <c r="A8" s="4" t="s">
         <v>42</v>
       </c>
@@ -2514,7 +2525,7 @@
       <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -2558,7 +2569,7 @@
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
     </row>
-    <row r="9" spans="1:29" ht="66">
+    <row r="9" spans="1:29" ht="63.75">
       <c r="A9" s="4" t="s">
         <v>44</v>
       </c>
@@ -2571,7 +2582,7 @@
       <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -2615,7 +2626,7 @@
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
     </row>
-    <row r="10" spans="1:29" ht="92.4">
+    <row r="10" spans="1:29" ht="89.25">
       <c r="A10" s="4" t="s">
         <v>49</v>
       </c>
@@ -2628,7 +2639,7 @@
       <c r="D10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -2672,7 +2683,7 @@
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
     </row>
-    <row r="11" spans="1:29" ht="66">
+    <row r="11" spans="1:29" ht="63.75">
       <c r="A11" s="4" t="s">
         <v>51</v>
       </c>
@@ -2685,7 +2696,7 @@
       <c r="D11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -2729,7 +2740,7 @@
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
     </row>
-    <row r="12" spans="1:29" ht="92.4">
+    <row r="12" spans="1:29" ht="89.25">
       <c r="A12" s="4" t="s">
         <v>54</v>
       </c>
@@ -2742,7 +2753,7 @@
       <c r="D12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F12" s="4" t="s">
@@ -2786,7 +2797,7 @@
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
     </row>
-    <row r="13" spans="1:29" ht="66">
+    <row r="13" spans="1:29" ht="63.75">
       <c r="A13" s="4" t="s">
         <v>56</v>
       </c>
@@ -2799,7 +2810,7 @@
       <c r="D13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F13" s="4" t="s">
@@ -2843,7 +2854,7 @@
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
     </row>
-    <row r="14" spans="1:29" ht="66">
+    <row r="14" spans="1:29" ht="63.75">
       <c r="A14" s="4" t="s">
         <v>61</v>
       </c>
@@ -2856,7 +2867,7 @@
       <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -2900,7 +2911,7 @@
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
     </row>
-    <row r="15" spans="1:29" ht="66">
+    <row r="15" spans="1:29" ht="63.75">
       <c r="A15" s="4" t="s">
         <v>65</v>
       </c>
@@ -2913,7 +2924,7 @@
       <c r="D15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -2957,11 +2968,11 @@
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
     </row>
-    <row r="16" spans="1:29" ht="66">
+    <row r="16" spans="1:29" ht="63.75">
       <c r="A16" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="26" t="s">
         <v>364</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2970,7 +2981,7 @@
       <c r="D16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -3014,7 +3025,7 @@
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
     </row>
-    <row r="17" spans="1:29" ht="66">
+    <row r="17" spans="1:29" ht="63.75">
       <c r="A17" s="4" t="s">
         <v>69</v>
       </c>
@@ -3027,7 +3038,7 @@
       <c r="D17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -3071,7 +3082,7 @@
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
     </row>
-    <row r="18" spans="1:29" ht="66">
+    <row r="18" spans="1:29" ht="63.75">
       <c r="A18" s="4" t="s">
         <v>71</v>
       </c>
@@ -3084,7 +3095,7 @@
       <c r="D18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -3128,7 +3139,7 @@
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
     </row>
-    <row r="19" spans="1:29" ht="66">
+    <row r="19" spans="1:29" ht="63.75">
       <c r="A19" s="4" t="s">
         <v>76</v>
       </c>
@@ -3141,7 +3152,7 @@
       <c r="D19" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -3185,7 +3196,7 @@
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
     </row>
-    <row r="20" spans="1:29" ht="66">
+    <row r="20" spans="1:29" ht="63.75">
       <c r="A20" s="4" t="s">
         <v>81</v>
       </c>
@@ -3198,7 +3209,7 @@
       <c r="D20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -3242,7 +3253,7 @@
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
     </row>
-    <row r="21" spans="1:29" ht="66">
+    <row r="21" spans="1:29" ht="63.75">
       <c r="A21" s="4" t="s">
         <v>83</v>
       </c>
@@ -3255,7 +3266,7 @@
       <c r="D21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F21" s="4" t="s">
@@ -3299,7 +3310,7 @@
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
     </row>
-    <row r="22" spans="1:29" ht="66">
+    <row r="22" spans="1:29" ht="63.75">
       <c r="A22" s="4" t="s">
         <v>85</v>
       </c>
@@ -3312,7 +3323,7 @@
       <c r="D22" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F22" s="4" t="s">
@@ -3356,7 +3367,7 @@
       <c r="AB22" s="4"/>
       <c r="AC22" s="4"/>
     </row>
-    <row r="23" spans="1:29" ht="66">
+    <row r="23" spans="1:29" ht="63.75">
       <c r="A23" s="4" t="s">
         <v>90</v>
       </c>
@@ -3369,7 +3380,7 @@
       <c r="D23" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F23" s="4" t="s">
@@ -3413,7 +3424,7 @@
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
     </row>
-    <row r="24" spans="1:29" ht="66">
+    <row r="24" spans="1:29" ht="63.75">
       <c r="A24" s="4" t="s">
         <v>92</v>
       </c>
@@ -3426,7 +3437,7 @@
       <c r="D24" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F24" s="4" t="s">
@@ -3470,7 +3481,7 @@
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
     </row>
-    <row r="25" spans="1:29" ht="66">
+    <row r="25" spans="1:29" ht="63.75">
       <c r="A25" s="4" t="s">
         <v>95</v>
       </c>
@@ -3483,7 +3494,7 @@
       <c r="D25" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F25" s="4" t="s">
@@ -3527,7 +3538,7 @@
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
     </row>
-    <row r="26" spans="1:29" ht="92.4">
+    <row r="26" spans="1:29" ht="89.25">
       <c r="A26" s="4" t="s">
         <v>97</v>
       </c>
@@ -3540,7 +3551,7 @@
       <c r="D26" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -3584,7 +3595,7 @@
       <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
     </row>
-    <row r="27" spans="1:29" ht="79.2">
+    <row r="27" spans="1:29" ht="76.5">
       <c r="A27" s="4" t="s">
         <v>102</v>
       </c>
@@ -3597,7 +3608,7 @@
       <c r="D27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -3641,7 +3652,7 @@
       <c r="AB27" s="4"/>
       <c r="AC27" s="4"/>
     </row>
-    <row r="28" spans="1:29" ht="79.2">
+    <row r="28" spans="1:29" ht="76.5">
       <c r="A28" s="4" t="s">
         <v>107</v>
       </c>
@@ -3654,7 +3665,7 @@
       <c r="D28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="27" t="s">
+      <c r="E28" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -3698,7 +3709,7 @@
       <c r="AB28" s="4"/>
       <c r="AC28" s="4"/>
     </row>
-    <row r="29" spans="1:29" ht="79.2">
+    <row r="29" spans="1:29" ht="76.5">
       <c r="A29" s="4" t="s">
         <v>111</v>
       </c>
@@ -3711,7 +3722,7 @@
       <c r="D29" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="27" t="s">
+      <c r="E29" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -3755,7 +3766,7 @@
       <c r="AB29" s="4"/>
       <c r="AC29" s="4"/>
     </row>
-    <row r="30" spans="1:29" ht="79.2">
+    <row r="30" spans="1:29" ht="76.5">
       <c r="A30" s="4" t="s">
         <v>115</v>
       </c>
@@ -3768,7 +3779,7 @@
       <c r="D30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -3812,7 +3823,7 @@
       <c r="AB30" s="4"/>
       <c r="AC30" s="4"/>
     </row>
-    <row r="31" spans="1:29" ht="66">
+    <row r="31" spans="1:29" ht="63.75">
       <c r="A31" s="4" t="s">
         <v>119</v>
       </c>
@@ -3825,7 +3836,7 @@
       <c r="D31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -3869,7 +3880,7 @@
       <c r="AB31" s="4"/>
       <c r="AC31" s="4"/>
     </row>
-    <row r="32" spans="1:29" ht="13.2">
+    <row r="32" spans="1:29" ht="12.75">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="8"/>
@@ -3902,7 +3913,7 @@
       <c r="AB32" s="8"/>
       <c r="AC32" s="8"/>
     </row>
-    <row r="33" spans="1:29" ht="39.6">
+    <row r="33" spans="1:29" ht="38.25">
       <c r="A33" s="4" t="s">
         <v>123</v>
       </c>
@@ -3954,7 +3965,7 @@
       <c r="AB33" s="4"/>
       <c r="AC33" s="4"/>
     </row>
-    <row r="34" spans="1:29" ht="39.6">
+    <row r="34" spans="1:29" ht="38.25">
       <c r="A34" s="4" t="s">
         <v>128</v>
       </c>
@@ -4006,7 +4017,7 @@
       <c r="AB34" s="4"/>
       <c r="AC34" s="4"/>
     </row>
-    <row r="35" spans="1:29" ht="28.8">
+    <row r="35" spans="1:29" ht="28.5">
       <c r="A35" s="4" t="s">
         <v>131</v>
       </c>
@@ -4058,7 +4069,7 @@
       <c r="AB35" s="4"/>
       <c r="AC35" s="4"/>
     </row>
-    <row r="36" spans="1:29" ht="39.6">
+    <row r="36" spans="1:29" ht="38.25">
       <c r="A36" s="4" t="s">
         <v>134</v>
       </c>
@@ -4110,7 +4121,7 @@
       <c r="AB36" s="4"/>
       <c r="AC36" s="4"/>
     </row>
-    <row r="37" spans="1:29" ht="28.8">
+    <row r="37" spans="1:29" ht="28.5">
       <c r="A37" s="4" t="s">
         <v>137</v>
       </c>
@@ -4161,7 +4172,7 @@
       <c r="AB37" s="4"/>
       <c r="AC37" s="4"/>
     </row>
-    <row r="38" spans="1:29" ht="28.8">
+    <row r="38" spans="1:29" ht="38.25">
       <c r="A38" s="4" t="s">
         <v>141</v>
       </c>
@@ -4212,7 +4223,7 @@
       <c r="AB38" s="4"/>
       <c r="AC38" s="4"/>
     </row>
-    <row r="39" spans="1:29" ht="28.8">
+    <row r="39" spans="1:29" ht="28.5">
       <c r="A39" s="4" t="s">
         <v>145</v>
       </c>
@@ -4263,7 +4274,7 @@
       <c r="AB39" s="4"/>
       <c r="AC39" s="4"/>
     </row>
-    <row r="40" spans="1:29" ht="39.6">
+    <row r="40" spans="1:29" ht="38.25">
       <c r="A40" s="4" t="s">
         <v>149</v>
       </c>
@@ -4313,7 +4324,7 @@
       <c r="AB40" s="4"/>
       <c r="AC40" s="4"/>
     </row>
-    <row r="41" spans="1:29" ht="13.2">
+    <row r="41" spans="1:29" ht="12.75">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="8"/>
@@ -4346,7 +4357,7 @@
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
     </row>
-    <row r="42" spans="1:29" ht="52.8">
+    <row r="42" spans="1:29" ht="51">
       <c r="A42" s="4" t="s">
         <v>153</v>
       </c>
@@ -4395,7 +4406,7 @@
       <c r="AB42" s="4"/>
       <c r="AC42" s="4"/>
     </row>
-    <row r="43" spans="1:29" ht="13.2">
+    <row r="43" spans="1:29" ht="12.75">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="8"/>
@@ -4428,12 +4439,12 @@
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
     </row>
-    <row r="44" spans="1:29" ht="26.4">
+    <row r="44" spans="1:29" ht="25.5">
       <c r="A44" s="4" t="s">
         <v>158</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>159</v>
@@ -4481,12 +4492,12 @@
       <c r="AB44" s="2"/>
       <c r="AC44" s="2"/>
     </row>
-    <row r="45" spans="1:29" ht="26.4">
+    <row r="45" spans="1:29" ht="25.5">
       <c r="A45" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>166</v>
@@ -4534,12 +4545,12 @@
       <c r="AB45" s="2"/>
       <c r="AC45" s="2"/>
     </row>
-    <row r="46" spans="1:29" ht="26.4">
+    <row r="46" spans="1:29" ht="25.5">
       <c r="A46" s="4" t="s">
         <v>170</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>171</v>
@@ -4587,12 +4598,12 @@
       <c r="AB46" s="2"/>
       <c r="AC46" s="2"/>
     </row>
-    <row r="47" spans="1:29" ht="26.4">
+    <row r="47" spans="1:29" ht="25.5">
       <c r="A47" s="4" t="s">
         <v>175</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>176</v>
@@ -4640,12 +4651,12 @@
       <c r="AB47" s="2"/>
       <c r="AC47" s="2"/>
     </row>
-    <row r="48" spans="1:29" ht="13.2">
+    <row r="48" spans="1:29" ht="12.75">
       <c r="A48" s="4" t="s">
         <v>180</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>181</v>
@@ -4693,12 +4704,12 @@
       <c r="AB48" s="2"/>
       <c r="AC48" s="2"/>
     </row>
-    <row r="49" spans="1:29" ht="13.2">
+    <row r="49" spans="1:29" ht="12.75">
       <c r="A49" s="4" t="s">
         <v>185</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>186</v>
@@ -4746,12 +4757,12 @@
       <c r="AB49" s="2"/>
       <c r="AC49" s="2"/>
     </row>
-    <row r="50" spans="1:29" ht="13.2">
+    <row r="50" spans="1:29" ht="12.75">
       <c r="A50" s="4" t="s">
         <v>187</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>188</v>
@@ -4799,12 +4810,12 @@
       <c r="AB50" s="2"/>
       <c r="AC50" s="2"/>
     </row>
-    <row r="51" spans="1:29" ht="13.2">
+    <row r="51" spans="1:29" ht="12.75">
       <c r="A51" s="4" t="s">
         <v>191</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>192</v>
@@ -4852,12 +4863,12 @@
       <c r="AB51" s="2"/>
       <c r="AC51" s="2"/>
     </row>
-    <row r="52" spans="1:29" ht="13.2">
+    <row r="52" spans="1:29" ht="12.75">
       <c r="A52" s="4" t="s">
         <v>194</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>195</v>
@@ -4905,12 +4916,12 @@
       <c r="AB52" s="2"/>
       <c r="AC52" s="2"/>
     </row>
-    <row r="53" spans="1:29" ht="13.2">
+    <row r="53" spans="1:29" ht="12.75">
       <c r="A53" s="4" t="s">
         <v>198</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>199</v>
@@ -4958,12 +4969,12 @@
       <c r="AB53" s="2"/>
       <c r="AC53" s="2"/>
     </row>
-    <row r="54" spans="1:29" ht="13.2">
+    <row r="54" spans="1:29" ht="12.75">
       <c r="A54" s="4" t="s">
         <v>202</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>203</v>
@@ -5011,7 +5022,7 @@
       <c r="AB54" s="2"/>
       <c r="AC54" s="2"/>
     </row>
-    <row r="55" spans="1:29" ht="13.2">
+    <row r="55" spans="1:29" ht="12.75">
       <c r="A55" s="8"/>
       <c r="B55" s="9"/>
       <c r="C55" s="8"/>
@@ -5044,12 +5055,12 @@
       <c r="AB55" s="9"/>
       <c r="AC55" s="9"/>
     </row>
-    <row r="56" spans="1:29" ht="26.4">
+    <row r="56" spans="1:29" ht="25.5">
       <c r="A56" s="4" t="s">
         <v>206</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>207</v>
@@ -5097,12 +5108,12 @@
       <c r="AB56" s="2"/>
       <c r="AC56" s="2"/>
     </row>
-    <row r="57" spans="1:29" ht="26.4">
+    <row r="57" spans="1:29" ht="25.5">
       <c r="A57" s="4" t="s">
         <v>212</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>213</v>
@@ -5150,12 +5161,12 @@
       <c r="AB57" s="2"/>
       <c r="AC57" s="2"/>
     </row>
-    <row r="58" spans="1:29" ht="26.4">
+    <row r="58" spans="1:29" ht="25.5">
       <c r="A58" s="4" t="s">
         <v>217</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>218</v>
@@ -5203,12 +5214,12 @@
       <c r="AB58" s="2"/>
       <c r="AC58" s="2"/>
     </row>
-    <row r="59" spans="1:29" ht="26.4">
+    <row r="59" spans="1:29" ht="25.5">
       <c r="A59" s="4" t="s">
         <v>221</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>222</v>
@@ -5256,12 +5267,12 @@
       <c r="AB59" s="2"/>
       <c r="AC59" s="2"/>
     </row>
-    <row r="60" spans="1:29" ht="26.4">
+    <row r="60" spans="1:29" ht="25.5">
       <c r="A60" s="4" t="s">
         <v>225</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>226</v>
@@ -5309,12 +5320,12 @@
       <c r="AB60" s="2"/>
       <c r="AC60" s="2"/>
     </row>
-    <row r="61" spans="1:29" ht="13.2">
+    <row r="61" spans="1:29" ht="12.75">
       <c r="A61" s="4" t="s">
         <v>229</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>230</v>
@@ -5362,12 +5373,12 @@
       <c r="AB61" s="2"/>
       <c r="AC61" s="2"/>
     </row>
-    <row r="62" spans="1:29" ht="26.4">
+    <row r="62" spans="1:29" ht="25.5">
       <c r="A62" s="4" t="s">
         <v>235</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>236</v>
@@ -5415,12 +5426,12 @@
       <c r="AB62" s="2"/>
       <c r="AC62" s="2"/>
     </row>
-    <row r="63" spans="1:29" ht="26.4">
+    <row r="63" spans="1:29" ht="25.5">
       <c r="A63" s="4" t="s">
         <v>241</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>242</v>
@@ -5468,12 +5479,12 @@
       <c r="AB63" s="2"/>
       <c r="AC63" s="2"/>
     </row>
-    <row r="64" spans="1:29" ht="26.4">
+    <row r="64" spans="1:29" ht="25.5">
       <c r="A64" s="4" t="s">
         <v>247</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>248</v>
@@ -5521,7 +5532,7 @@
       <c r="AB64" s="2"/>
       <c r="AC64" s="2"/>
     </row>
-    <row r="65" spans="1:29" ht="13.2">
+    <row r="65" spans="1:29" ht="12.75">
       <c r="A65" s="8"/>
       <c r="B65" s="9"/>
       <c r="C65" s="8"/>
@@ -5554,12 +5565,12 @@
       <c r="AB65" s="9"/>
       <c r="AC65" s="9"/>
     </row>
-    <row r="66" spans="1:29" ht="13.2">
+    <row r="66" spans="1:29" ht="12.75">
       <c r="A66" s="4" t="s">
         <v>251</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>252</v>
@@ -5607,12 +5618,12 @@
       <c r="AB66" s="2"/>
       <c r="AC66" s="2"/>
     </row>
-    <row r="67" spans="1:29" ht="13.2">
+    <row r="67" spans="1:29" ht="12.75">
       <c r="A67" s="4" t="s">
         <v>257</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>258</v>
@@ -5665,7 +5676,7 @@
         <v>263</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>264</v>
@@ -5680,7 +5691,7 @@
       <c r="G68" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="H68" s="29"/>
+      <c r="H68" s="27"/>
       <c r="I68" s="4" t="s">
         <v>267</v>
       </c>
@@ -5713,12 +5724,12 @@
       <c r="AB68" s="11"/>
       <c r="AC68" s="11"/>
     </row>
-    <row r="69" spans="1:29" ht="13.2">
+    <row r="69" spans="1:29" ht="12.75">
       <c r="A69" s="4" t="s">
         <v>269</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>270</v>
@@ -5750,12 +5761,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="13.2">
+    <row r="70" spans="1:29" ht="12.75">
       <c r="A70" s="4" t="s">
         <v>275</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>276</v>
@@ -5787,9 +5798,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="13.2">
+    <row r="71" spans="1:29" ht="12.75">
       <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
+      <c r="B71" s="8"/>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
@@ -5820,12 +5831,12 @@
       <c r="AB71" s="8"/>
       <c r="AC71" s="8"/>
     </row>
-    <row r="72" spans="1:29" ht="13.2">
+    <row r="72" spans="1:29" ht="12.75">
       <c r="A72" s="4" t="s">
         <v>279</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>280</v>
@@ -5857,12 +5868,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="13.2">
+    <row r="73" spans="1:29" ht="12.75">
       <c r="A73" s="4" t="s">
         <v>284</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>285</v>
@@ -5894,12 +5905,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="13.2">
+    <row r="74" spans="1:29" ht="12.75">
       <c r="A74" s="4" t="s">
         <v>290</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>291</v>
@@ -5931,12 +5942,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="13.2">
+    <row r="75" spans="1:29" ht="12.75">
       <c r="A75" s="4" t="s">
         <v>295</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>296</v>
@@ -5968,12 +5979,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="13.2">
+    <row r="76" spans="1:29" ht="12.75">
       <c r="A76" s="4" t="s">
         <v>300</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>301</v>
@@ -6005,7 +6016,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="13.2">
+    <row r="77" spans="1:29" ht="12.75">
       <c r="A77" s="8"/>
       <c r="B77" s="9"/>
       <c r="C77" s="8"/>
@@ -6038,7 +6049,7 @@
       <c r="AB77" s="8"/>
       <c r="AC77" s="8"/>
     </row>
-    <row r="78" spans="1:29" ht="72">
+    <row r="78" spans="1:29" ht="71.25">
       <c r="A78" s="4" t="s">
         <v>304</v>
       </c>
@@ -6071,7 +6082,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="14.4">
+    <row r="79" spans="1:29" ht="14.25">
       <c r="A79" s="4" t="s">
         <v>309</v>
       </c>
@@ -6137,7 +6148,7 @@
       <c r="AB80" s="8"/>
       <c r="AC80" s="8"/>
     </row>
-    <row r="81" spans="1:29" ht="39.6">
+    <row r="81" spans="1:29" ht="38.25">
       <c r="A81" s="4" t="s">
         <v>312</v>
       </c>
@@ -6157,7 +6168,7 @@
       <c r="G81" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="H81" s="32" t="s">
+      <c r="H81" s="30" t="s">
         <v>393</v>
       </c>
       <c r="I81" s="4" t="s">
@@ -6177,7 +6188,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="39.6">
+    <row r="82" spans="1:29" ht="38.25">
       <c r="A82" s="4" t="s">
         <v>318</v>
       </c>
@@ -6215,7 +6226,7 @@
       </c>
       <c r="P82" s="4"/>
     </row>
-    <row r="83" spans="1:29" ht="26.4">
+    <row r="83" spans="1:29" ht="25.5">
       <c r="A83" s="4" t="s">
         <v>323</v>
       </c>
@@ -6252,7 +6263,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="52.8">
+    <row r="84" spans="1:29" ht="51">
       <c r="A84" s="4" t="s">
         <v>329</v>
       </c>
@@ -6292,7 +6303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="52.8">
+    <row r="85" spans="1:29" ht="51">
       <c r="A85" s="4" t="s">
         <v>334</v>
       </c>
@@ -6346,7 +6357,7 @@
       <c r="AB85" s="12"/>
       <c r="AC85" s="12"/>
     </row>
-    <row r="86" spans="1:29" ht="39.6">
+    <row r="86" spans="1:29" ht="38.25">
       <c r="A86" s="4" t="s">
         <v>339</v>
       </c>
@@ -6386,7 +6397,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="39.6">
+    <row r="87" spans="1:29" ht="38.25">
       <c r="A87" s="4" t="s">
         <v>344</v>
       </c>
@@ -6426,7 +6437,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="39.6">
+    <row r="88" spans="1:29" ht="38.25">
       <c r="A88" s="4" t="s">
         <v>346</v>
       </c>
@@ -6466,7 +6477,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="39.6">
+    <row r="89" spans="1:29" ht="38.25">
       <c r="A89" s="4" t="s">
         <v>348</v>
       </c>
@@ -6559,7 +6570,7 @@
       <c r="G91" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H91" s="31"/>
+      <c r="H91" s="29"/>
       <c r="I91" s="4" t="s">
         <v>356</v>
       </c>
@@ -6592,7 +6603,7 @@
       <c r="AB91" s="14"/>
       <c r="AC91" s="14"/>
     </row>
-    <row r="92" spans="1:29" ht="14.4">
+    <row r="92" spans="1:29" ht="15">
       <c r="A92" s="4"/>
       <c r="B92" s="2"/>
       <c r="C92" s="15"/>
@@ -6608,7 +6619,7 @@
       <c r="O92" s="15"/>
       <c r="P92" s="4"/>
     </row>
-    <row r="93" spans="1:29" ht="14.4">
+    <row r="93" spans="1:29" ht="15">
       <c r="A93" s="4"/>
       <c r="B93" s="2"/>
       <c r="C93" s="15"/>
@@ -6624,7 +6635,7 @@
       <c r="O93" s="15"/>
       <c r="P93" s="4"/>
     </row>
-    <row r="94" spans="1:29" ht="14.4">
+    <row r="94" spans="1:29" ht="15">
       <c r="A94" s="4"/>
       <c r="B94" s="2"/>
       <c r="C94" s="15"/>
@@ -6640,7 +6651,7 @@
       <c r="O94" s="15"/>
       <c r="P94" s="4"/>
     </row>
-    <row r="95" spans="1:29" ht="14.4">
+    <row r="95" spans="1:29" ht="15">
       <c r="A95" s="4"/>
       <c r="B95" s="2"/>
       <c r="C95" s="15"/>
@@ -6656,7 +6667,7 @@
       <c r="O95" s="15"/>
       <c r="P95" s="4"/>
     </row>
-    <row r="96" spans="1:29" ht="14.4">
+    <row r="96" spans="1:29" ht="15">
       <c r="A96" s="4"/>
       <c r="B96" s="2"/>
       <c r="C96" s="15"/>
@@ -6680,7 +6691,7 @@
       <c r="E97" s="16"/>
       <c r="F97" s="15"/>
       <c r="G97" s="15"/>
-      <c r="H97" s="30"/>
+      <c r="H97" s="28"/>
       <c r="I97" s="15"/>
       <c r="J97" s="17"/>
       <c r="K97" s="17"/>
@@ -6705,7 +6716,7 @@
       <c r="AB97" s="17"/>
       <c r="AC97" s="17"/>
     </row>
-    <row r="98" spans="1:29" ht="14.4">
+    <row r="98" spans="1:29" ht="15">
       <c r="A98" s="4"/>
       <c r="B98" s="2"/>
       <c r="C98" s="15"/>
@@ -6722,7 +6733,7 @@
       <c r="O98" s="15"/>
       <c r="P98" s="4"/>
     </row>
-    <row r="99" spans="1:29" ht="14.4">
+    <row r="99" spans="1:29" ht="15">
       <c r="A99" s="4"/>
       <c r="B99" s="2"/>
       <c r="C99" s="15"/>
@@ -6739,7 +6750,7 @@
       <c r="O99" s="15"/>
       <c r="P99" s="4"/>
     </row>
-    <row r="100" spans="1:29" ht="14.4">
+    <row r="100" spans="1:29" ht="15">
       <c r="A100" s="4"/>
       <c r="B100" s="2"/>
       <c r="C100" s="15"/>
@@ -6756,7 +6767,7 @@
       <c r="O100" s="15"/>
       <c r="P100" s="4"/>
     </row>
-    <row r="101" spans="1:29" ht="14.4">
+    <row r="101" spans="1:29" ht="15">
       <c r="A101" s="4"/>
       <c r="B101" s="2"/>
       <c r="C101" s="15"/>
@@ -6773,7 +6784,7 @@
       <c r="O101" s="15"/>
       <c r="P101" s="4"/>
     </row>
-    <row r="102" spans="1:29" ht="14.4">
+    <row r="102" spans="1:29" ht="15">
       <c r="A102" s="4"/>
       <c r="B102" s="2"/>
       <c r="C102" s="15"/>
@@ -6789,7 +6800,7 @@
       <c r="O102" s="15"/>
       <c r="P102" s="4"/>
     </row>
-    <row r="103" spans="1:29" ht="14.4">
+    <row r="103" spans="1:29" ht="15">
       <c r="A103" s="4"/>
       <c r="B103" s="2"/>
       <c r="C103" s="15"/>
@@ -6806,7 +6817,7 @@
       <c r="O103" s="15"/>
       <c r="P103" s="4"/>
     </row>
-    <row r="104" spans="1:29" ht="14.4">
+    <row r="104" spans="1:29" ht="15">
       <c r="A104" s="4"/>
       <c r="B104" s="2"/>
       <c r="C104" s="15"/>
@@ -6822,7 +6833,7 @@
       <c r="O104" s="15"/>
       <c r="P104" s="4"/>
     </row>
-    <row r="105" spans="1:29" ht="14.4">
+    <row r="105" spans="1:29" ht="15">
       <c r="A105" s="4"/>
       <c r="B105" s="2"/>
       <c r="C105" s="15"/>
@@ -6839,7 +6850,7 @@
       <c r="O105" s="15"/>
       <c r="P105" s="4"/>
     </row>
-    <row r="106" spans="1:29" ht="14.4">
+    <row r="106" spans="1:29" ht="15">
       <c r="A106" s="4"/>
       <c r="B106" s="2"/>
       <c r="C106" s="15"/>
@@ -6856,7 +6867,7 @@
       <c r="O106" s="15"/>
       <c r="P106" s="4"/>
     </row>
-    <row r="107" spans="1:29" ht="14.4">
+    <row r="107" spans="1:29" ht="15">
       <c r="A107" s="4"/>
       <c r="B107" s="2"/>
       <c r="C107" s="15"/>
@@ -6873,7 +6884,7 @@
       <c r="O107" s="15"/>
       <c r="P107" s="4"/>
     </row>
-    <row r="108" spans="1:29" ht="14.4">
+    <row r="108" spans="1:29" ht="15">
       <c r="A108" s="4"/>
       <c r="B108" s="2"/>
       <c r="C108" s="15"/>
@@ -6922,7 +6933,7 @@
       <c r="AB109" s="17"/>
       <c r="AC109" s="17"/>
     </row>
-    <row r="110" spans="1:29" ht="14.4">
+    <row r="110" spans="1:29" ht="15">
       <c r="A110" s="4"/>
       <c r="B110" s="2"/>
       <c r="C110" s="15"/>
@@ -6940,7 +6951,7 @@
       <c r="O110" s="15"/>
       <c r="P110" s="4"/>
     </row>
-    <row r="111" spans="1:29" ht="14.4">
+    <row r="111" spans="1:29" ht="15">
       <c r="A111" s="4"/>
       <c r="B111" s="2"/>
       <c r="C111" s="15"/>
@@ -6958,7 +6969,7 @@
       <c r="O111" s="15"/>
       <c r="P111" s="4"/>
     </row>
-    <row r="112" spans="1:29" ht="13.2">
+    <row r="112" spans="1:29" ht="12.75">
       <c r="A112" s="4"/>
       <c r="B112" s="2"/>
       <c r="C112" s="4"/>
@@ -7343,7 +7354,7 @@
       <c r="O139" s="4"/>
       <c r="P139" s="4"/>
     </row>
-    <row r="140" spans="1:16" ht="13.2">
+    <row r="140" spans="1:16" ht="12.75">
       <c r="A140" s="4"/>
       <c r="B140" s="2"/>
       <c r="C140" s="4"/>
@@ -7354,7 +7365,7 @@
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
     </row>
-    <row r="141" spans="1:16" ht="13.2">
+    <row r="141" spans="1:16" ht="12.75">
       <c r="B141" s="2"/>
       <c r="C141" s="4"/>
       <c r="E141" s="4"/>
@@ -7365,7 +7376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="13.2">
+    <row r="142" spans="1:16" ht="12.75">
       <c r="B142" s="2"/>
       <c r="C142" s="4"/>
       <c r="E142" s="4"/>
@@ -7748,7 +7759,7 @@
       <c r="AB170" s="11"/>
       <c r="AC170" s="11"/>
     </row>
-    <row r="171" spans="2:29" ht="13.2">
+    <row r="171" spans="2:29" ht="12.75">
       <c r="B171" s="2"/>
       <c r="C171" s="4"/>
       <c r="E171" s="2"/>
@@ -7774,7 +7785,7 @@
       <c r="AB171" s="2"/>
       <c r="AC171" s="2"/>
     </row>
-    <row r="172" spans="2:29" ht="13.2">
+    <row r="172" spans="2:29" ht="12.75">
       <c r="B172" s="2"/>
       <c r="C172" s="4"/>
       <c r="E172" s="2"/>
@@ -7800,7 +7811,7 @@
       <c r="AB172" s="2"/>
       <c r="AC172" s="2"/>
     </row>
-    <row r="173" spans="2:29" ht="13.2">
+    <row r="173" spans="2:29" ht="12.75">
       <c r="B173" s="2"/>
       <c r="C173" s="4"/>
       <c r="E173" s="2"/>
@@ -7826,7 +7837,7 @@
       <c r="AB173" s="2"/>
       <c r="AC173" s="2"/>
     </row>
-    <row r="174" spans="2:29" ht="13.2">
+    <row r="174" spans="2:29" ht="12.75">
       <c r="B174" s="2"/>
       <c r="C174" s="4"/>
       <c r="E174" s="2"/>
@@ -7852,7 +7863,7 @@
       <c r="AB174" s="2"/>
       <c r="AC174" s="2"/>
     </row>
-    <row r="175" spans="2:29" ht="13.2">
+    <row r="175" spans="2:29" ht="12.75">
       <c r="B175" s="2"/>
       <c r="C175" s="4"/>
       <c r="E175" s="2"/>
@@ -7878,7 +7889,7 @@
       <c r="AB175" s="2"/>
       <c r="AC175" s="2"/>
     </row>
-    <row r="176" spans="2:29" ht="13.2">
+    <row r="176" spans="2:29" ht="12.75">
       <c r="B176" s="2"/>
       <c r="C176" s="4"/>
       <c r="E176" s="2"/>
@@ -7904,7 +7915,7 @@
       <c r="AB176" s="2"/>
       <c r="AC176" s="2"/>
     </row>
-    <row r="177" spans="2:29" ht="13.2">
+    <row r="177" spans="2:29" ht="12.75">
       <c r="B177" s="2"/>
       <c r="C177" s="4"/>
       <c r="E177" s="2"/>
@@ -7930,7 +7941,7 @@
       <c r="AB177" s="2"/>
       <c r="AC177" s="2"/>
     </row>
-    <row r="178" spans="2:29" ht="13.2">
+    <row r="178" spans="2:29" ht="12.75">
       <c r="B178" s="2"/>
       <c r="C178" s="4"/>
       <c r="E178" s="2"/>
@@ -7956,7 +7967,7 @@
       <c r="AB178" s="2"/>
       <c r="AC178" s="2"/>
     </row>
-    <row r="179" spans="2:29" ht="13.2">
+    <row r="179" spans="2:29" ht="12.75">
       <c r="B179" s="2"/>
       <c r="C179" s="4"/>
       <c r="E179" s="2"/>
@@ -7982,7 +7993,7 @@
       <c r="AB179" s="2"/>
       <c r="AC179" s="2"/>
     </row>
-    <row r="180" spans="2:29" ht="13.2">
+    <row r="180" spans="2:29" ht="12.75">
       <c r="B180" s="2"/>
       <c r="C180" s="4"/>
       <c r="E180" s="2"/>
@@ -8008,7 +8019,7 @@
       <c r="AB180" s="2"/>
       <c r="AC180" s="2"/>
     </row>
-    <row r="181" spans="2:29" ht="13.2">
+    <row r="181" spans="2:29" ht="12.75">
       <c r="B181" s="2"/>
       <c r="C181" s="4"/>
       <c r="E181" s="2"/>
@@ -8034,7 +8045,7 @@
       <c r="AB181" s="2"/>
       <c r="AC181" s="2"/>
     </row>
-    <row r="182" spans="2:29" ht="13.2">
+    <row r="182" spans="2:29" ht="12.75">
       <c r="B182" s="2"/>
       <c r="C182" s="4"/>
       <c r="E182" s="2"/>
@@ -8060,7 +8071,7 @@
       <c r="AB182" s="2"/>
       <c r="AC182" s="2"/>
     </row>
-    <row r="183" spans="2:29" ht="13.2">
+    <row r="183" spans="2:29" ht="12.75">
       <c r="B183" s="2"/>
       <c r="C183" s="4"/>
       <c r="E183" s="2"/>
@@ -8086,7 +8097,7 @@
       <c r="AB183" s="2"/>
       <c r="AC183" s="2"/>
     </row>
-    <row r="184" spans="2:29" ht="13.2">
+    <row r="184" spans="2:29" ht="12.75">
       <c r="B184" s="2"/>
       <c r="C184" s="4"/>
       <c r="E184" s="2"/>
@@ -8112,7 +8123,7 @@
       <c r="AB184" s="2"/>
       <c r="AC184" s="2"/>
     </row>
-    <row r="185" spans="2:29" ht="13.2">
+    <row r="185" spans="2:29" ht="12.75">
       <c r="B185" s="2"/>
       <c r="C185" s="4"/>
       <c r="E185" s="2"/>
@@ -8138,7 +8149,7 @@
       <c r="AB185" s="2"/>
       <c r="AC185" s="2"/>
     </row>
-    <row r="186" spans="2:29" ht="13.2">
+    <row r="186" spans="2:29" ht="12.75">
       <c r="B186" s="2"/>
       <c r="C186" s="4"/>
       <c r="E186" s="2"/>
@@ -8164,7 +8175,7 @@
       <c r="AB186" s="2"/>
       <c r="AC186" s="2"/>
     </row>
-    <row r="187" spans="2:29" ht="13.2">
+    <row r="187" spans="2:29" ht="12.75">
       <c r="B187" s="2"/>
       <c r="C187" s="4"/>
       <c r="E187" s="2"/>
@@ -8190,7 +8201,7 @@
       <c r="AB187" s="2"/>
       <c r="AC187" s="2"/>
     </row>
-    <row r="188" spans="2:29" ht="13.2">
+    <row r="188" spans="2:29" ht="12.75">
       <c r="B188" s="2"/>
       <c r="C188" s="4"/>
       <c r="E188" s="2"/>
@@ -8216,7 +8227,7 @@
       <c r="AB188" s="2"/>
       <c r="AC188" s="2"/>
     </row>
-    <row r="189" spans="2:29" ht="13.2">
+    <row r="189" spans="2:29" ht="12.75">
       <c r="B189" s="2"/>
       <c r="C189" s="4"/>
       <c r="E189" s="2"/>
@@ -8242,7 +8253,7 @@
       <c r="AB189" s="2"/>
       <c r="AC189" s="2"/>
     </row>
-    <row r="190" spans="2:29" ht="13.2">
+    <row r="190" spans="2:29" ht="12.75">
       <c r="B190" s="2"/>
       <c r="C190" s="4"/>
       <c r="E190" s="2"/>
@@ -8268,7 +8279,7 @@
       <c r="AB190" s="2"/>
       <c r="AC190" s="2"/>
     </row>
-    <row r="191" spans="2:29" ht="13.2">
+    <row r="191" spans="2:29" ht="12.75">
       <c r="B191" s="2"/>
       <c r="C191" s="4"/>
       <c r="E191" s="2"/>
@@ -8294,7 +8305,7 @@
       <c r="AB191" s="2"/>
       <c r="AC191" s="2"/>
     </row>
-    <row r="192" spans="2:29" ht="13.2">
+    <row r="192" spans="2:29" ht="12.75">
       <c r="B192" s="2"/>
       <c r="C192" s="4"/>
       <c r="E192" s="2"/>
@@ -8346,7 +8357,7 @@
       <c r="AB193" s="21"/>
       <c r="AC193" s="21"/>
     </row>
-    <row r="194" spans="2:29" ht="13.2">
+    <row r="194" spans="2:29" ht="12.75">
       <c r="B194" s="2"/>
       <c r="C194" s="4"/>
       <c r="E194" s="4"/>
@@ -8357,7 +8368,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="2:29" ht="13.2">
+    <row r="195" spans="2:29" ht="12.75">
       <c r="B195" s="2"/>
       <c r="C195" s="4"/>
       <c r="E195" s="4"/>
@@ -8368,7 +8379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="2:29" ht="13.2">
+    <row r="196" spans="2:29" ht="12.75">
       <c r="B196" s="2"/>
       <c r="C196" s="4"/>
       <c r="E196" s="4"/>
@@ -8379,7 +8390,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="2:29" ht="13.2">
+    <row r="197" spans="2:29" ht="12.75">
       <c r="B197" s="2"/>
       <c r="C197" s="4"/>
       <c r="E197" s="4"/>
@@ -8389,7 +8400,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" spans="2:29" ht="13.2">
+    <row r="198" spans="2:29" ht="12.75">
       <c r="B198" s="2"/>
       <c r="C198" s="4"/>
       <c r="E198" s="4"/>
@@ -8401,7 +8412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="2:29" ht="13.2">
+    <row r="199" spans="2:29" ht="12.75">
       <c r="B199" s="2"/>
       <c r="C199" s="4"/>
       <c r="E199" s="4"/>
@@ -8413,7 +8424,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="200" spans="2:29" ht="13.2">
+    <row r="200" spans="2:29" ht="12.75">
       <c r="B200" s="2"/>
       <c r="C200" s="4"/>
       <c r="E200" s="4"/>
@@ -8425,7 +8436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="201" spans="2:29" ht="13.2">
+    <row r="201" spans="2:29" ht="12.75">
       <c r="B201" s="2"/>
       <c r="C201" s="4"/>
       <c r="E201" s="4"/>
@@ -8436,7 +8447,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="202" spans="2:29" ht="13.2">
+    <row r="202" spans="2:29" ht="12.75">
       <c r="B202" s="2"/>
       <c r="C202" s="4"/>
       <c r="E202" s="4"/>
@@ -8447,7 +8458,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="2:29" ht="13.2">
+    <row r="203" spans="2:29" ht="12.75">
       <c r="B203" s="2"/>
       <c r="C203" s="4"/>
       <c r="E203" s="4"/>
@@ -8457,7 +8468,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="204" spans="2:29" ht="13.2">
+    <row r="204" spans="2:29" ht="12.75">
       <c r="B204" s="2"/>
       <c r="C204" s="4"/>
       <c r="E204" s="4"/>
@@ -8468,7 +8479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="2:29" ht="13.2">
+    <row r="205" spans="2:29" ht="12.75">
       <c r="B205" s="2"/>
       <c r="C205" s="4"/>
       <c r="E205" s="4"/>
@@ -8479,7 +8490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="206" spans="2:29" ht="13.2">
+    <row r="206" spans="2:29" ht="12.75">
       <c r="B206" s="2"/>
       <c r="C206" s="4"/>
       <c r="E206" s="4"/>
@@ -8490,7 +8501,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" spans="2:29" ht="13.2">
+    <row r="207" spans="2:29" ht="12.75">
       <c r="B207" s="2"/>
       <c r="C207" s="4"/>
       <c r="E207" s="4"/>
@@ -8501,7 +8512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="2:29" ht="13.2">
+    <row r="208" spans="2:29" ht="12.75">
       <c r="B208" s="2"/>
       <c r="C208" s="4"/>
       <c r="E208" s="4"/>
@@ -8512,7 +8523,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" spans="1:29" ht="13.2">
+    <row r="209" spans="1:29" ht="12.75">
       <c r="B209" s="2"/>
       <c r="C209" s="4"/>
       <c r="E209" s="4"/>
@@ -8523,7 +8534,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="210" spans="1:29" ht="13.2">
+    <row r="210" spans="1:29" ht="12.75">
       <c r="A210" s="4"/>
       <c r="B210" s="2"/>
       <c r="C210" s="4"/>
@@ -8541,7 +8552,7 @@
       <c r="O210" s="4"/>
       <c r="P210" s="4"/>
     </row>
-    <row r="211" spans="1:29" ht="13.2">
+    <row r="211" spans="1:29" ht="12.75">
       <c r="A211" s="4"/>
       <c r="B211" s="2"/>
       <c r="C211" s="4"/>
@@ -8559,7 +8570,7 @@
       <c r="O211" s="4"/>
       <c r="P211" s="4"/>
     </row>
-    <row r="212" spans="1:29" ht="13.2">
+    <row r="212" spans="1:29" ht="12.75">
       <c r="A212" s="4"/>
       <c r="B212" s="2"/>
       <c r="C212" s="4"/>
@@ -8577,7 +8588,7 @@
       <c r="O212" s="4"/>
       <c r="P212" s="4"/>
     </row>
-    <row r="213" spans="1:29" ht="13.2">
+    <row r="213" spans="1:29" ht="12.75">
       <c r="A213" s="4"/>
       <c r="B213" s="2"/>
       <c r="C213" s="4"/>
@@ -8595,7 +8606,7 @@
       <c r="O213" s="4"/>
       <c r="P213" s="4"/>
     </row>
-    <row r="214" spans="1:29" ht="13.2">
+    <row r="214" spans="1:29" ht="12.75">
       <c r="A214" s="4"/>
       <c r="B214" s="2"/>
       <c r="C214" s="4"/>
@@ -8613,7 +8624,7 @@
       <c r="O214" s="4"/>
       <c r="P214" s="4"/>
     </row>
-    <row r="215" spans="1:29" ht="13.2">
+    <row r="215" spans="1:29" ht="12.75">
       <c r="A215" s="4"/>
       <c r="B215" s="2"/>
       <c r="C215" s="4"/>
@@ -8631,7 +8642,7 @@
       <c r="O215" s="4"/>
       <c r="P215" s="4"/>
     </row>
-    <row r="216" spans="1:29" ht="13.2">
+    <row r="216" spans="1:29" ht="12.75">
       <c r="A216" s="4"/>
       <c r="B216" s="2"/>
       <c r="C216" s="4"/>
@@ -8649,7 +8660,7 @@
       <c r="O216" s="4"/>
       <c r="P216" s="4"/>
     </row>
-    <row r="217" spans="1:29" ht="13.2">
+    <row r="217" spans="1:29" ht="12.75">
       <c r="A217" s="4"/>
       <c r="B217" s="2"/>
       <c r="C217" s="4"/>
@@ -8700,7 +8711,7 @@
       <c r="AB218" s="21"/>
       <c r="AC218" s="21"/>
     </row>
-    <row r="219" spans="1:29" ht="13.2">
+    <row r="219" spans="1:29" ht="12.75">
       <c r="A219" s="4"/>
       <c r="B219" s="2"/>
       <c r="C219" s="4"/>
@@ -8717,7 +8728,7 @@
       <c r="O219" s="4"/>
       <c r="P219" s="4"/>
     </row>
-    <row r="233" spans="1:29" ht="13.2">
+    <row r="233" spans="1:29" ht="12.75">
       <c r="A233" s="4"/>
       <c r="B233" s="2"/>
       <c r="C233" s="4"/>
@@ -8750,7 +8761,7 @@
       <c r="AB233" s="4"/>
       <c r="AC233" s="4"/>
     </row>
-    <row r="234" spans="1:29" ht="13.2">
+    <row r="234" spans="1:29" ht="12.75">
       <c r="A234" s="4"/>
       <c r="B234" s="2"/>
       <c r="C234" s="4"/>
@@ -8783,7 +8794,7 @@
       <c r="AB234" s="4"/>
       <c r="AC234" s="4"/>
     </row>
-    <row r="235" spans="1:29" ht="13.2">
+    <row r="235" spans="1:29" ht="12.75">
       <c r="A235" s="4"/>
       <c r="B235" s="2"/>
       <c r="C235" s="4"/>
@@ -8801,7 +8812,7 @@
       <c r="O235" s="4"/>
       <c r="P235" s="4"/>
     </row>
-    <row r="236" spans="1:29" ht="13.2">
+    <row r="236" spans="1:29" ht="12.75">
       <c r="A236" s="4"/>
       <c r="B236" s="2"/>
       <c r="C236" s="4"/>
@@ -8819,7 +8830,7 @@
       <c r="O236" s="4"/>
       <c r="P236" s="4"/>
     </row>
-    <row r="237" spans="1:29" ht="13.2">
+    <row r="237" spans="1:29" ht="12.75">
       <c r="A237" s="4"/>
       <c r="B237" s="2"/>
       <c r="C237" s="4"/>
@@ -8837,7 +8848,7 @@
       <c r="O237" s="4"/>
       <c r="P237" s="4"/>
     </row>
-    <row r="238" spans="1:29" ht="13.2">
+    <row r="238" spans="1:29" ht="12.75">
       <c r="A238" s="4"/>
       <c r="B238" s="2"/>
       <c r="C238" s="4"/>
@@ -8855,7 +8866,7 @@
       <c r="O238" s="4"/>
       <c r="P238" s="4"/>
     </row>
-    <row r="239" spans="1:29" ht="13.2">
+    <row r="239" spans="1:29" ht="12.75">
       <c r="A239" s="4"/>
       <c r="B239" s="2"/>
       <c r="C239" s="4"/>
@@ -8873,7 +8884,7 @@
       <c r="O239" s="4"/>
       <c r="P239" s="4"/>
     </row>
-    <row r="240" spans="1:29" ht="13.2">
+    <row r="240" spans="1:29" ht="12.75">
       <c r="A240" s="4"/>
       <c r="B240" s="2"/>
       <c r="C240" s="4"/>
@@ -8891,7 +8902,7 @@
       <c r="O240" s="4"/>
       <c r="P240" s="4"/>
     </row>
-    <row r="241" spans="1:16" ht="13.2">
+    <row r="241" spans="1:16" ht="12.75">
       <c r="A241" s="4"/>
       <c r="B241" s="2"/>
       <c r="C241" s="4"/>
@@ -8909,7 +8920,7 @@
       <c r="O241" s="4"/>
       <c r="P241" s="4"/>
     </row>
-    <row r="242" spans="1:16" ht="13.2">
+    <row r="242" spans="1:16" ht="12.75">
       <c r="A242" s="4"/>
       <c r="B242" s="2"/>
       <c r="C242" s="4"/>
@@ -8927,7 +8938,7 @@
       <c r="O242" s="4"/>
       <c r="P242" s="4"/>
     </row>
-    <row r="243" spans="1:16" ht="13.2">
+    <row r="243" spans="1:16" ht="12.75">
       <c r="A243" s="4"/>
       <c r="B243" s="2"/>
       <c r="C243" s="4"/>
@@ -8945,7 +8956,7 @@
       <c r="O243" s="4"/>
       <c r="P243" s="4"/>
     </row>
-    <row r="244" spans="1:16" ht="13.2">
+    <row r="244" spans="1:16" ht="12.75">
       <c r="A244" s="4"/>
       <c r="B244" s="2"/>
       <c r="C244" s="4"/>
@@ -8963,7 +8974,7 @@
       <c r="O244" s="4"/>
       <c r="P244" s="4"/>
     </row>
-    <row r="245" spans="1:16" ht="13.2">
+    <row r="245" spans="1:16" ht="12.75">
       <c r="A245" s="4"/>
       <c r="B245" s="2"/>
       <c r="C245" s="4"/>
@@ -8981,7 +8992,7 @@
       <c r="O245" s="4"/>
       <c r="P245" s="4"/>
     </row>
-    <row r="246" spans="1:16" ht="13.2">
+    <row r="246" spans="1:16" ht="12.75">
       <c r="A246" s="4"/>
       <c r="B246" s="2"/>
       <c r="C246" s="4"/>
@@ -8999,7 +9010,7 @@
       <c r="O246" s="4"/>
       <c r="P246" s="4"/>
     </row>
-    <row r="247" spans="1:16" ht="13.2">
+    <row r="247" spans="1:16" ht="12.75">
       <c r="A247" s="4"/>
       <c r="B247" s="2"/>
       <c r="C247" s="4"/>
@@ -9017,7 +9028,7 @@
       <c r="O247" s="4"/>
       <c r="P247" s="4"/>
     </row>
-    <row r="248" spans="1:16" ht="13.2">
+    <row r="248" spans="1:16" ht="12.75">
       <c r="A248" s="4"/>
       <c r="B248" s="2"/>
       <c r="C248" s="4"/>
@@ -9035,7 +9046,7 @@
       <c r="O248" s="4"/>
       <c r="P248" s="4"/>
     </row>
-    <row r="249" spans="1:16" ht="13.2">
+    <row r="249" spans="1:16" ht="12.75">
       <c r="A249" s="4"/>
       <c r="B249" s="2"/>
       <c r="C249" s="4"/>
@@ -9053,7 +9064,7 @@
       <c r="O249" s="4"/>
       <c r="P249" s="4"/>
     </row>
-    <row r="250" spans="1:16" ht="13.2">
+    <row r="250" spans="1:16" ht="12.75">
       <c r="A250" s="4"/>
       <c r="B250" s="2"/>
       <c r="C250" s="4"/>
@@ -9071,7 +9082,7 @@
       <c r="O250" s="4"/>
       <c r="P250" s="4"/>
     </row>
-    <row r="251" spans="1:16" ht="13.2">
+    <row r="251" spans="1:16" ht="12.75">
       <c r="A251" s="4"/>
       <c r="B251" s="2"/>
       <c r="C251" s="4"/>
@@ -9089,7 +9100,7 @@
       <c r="O251" s="4"/>
       <c r="P251" s="4"/>
     </row>
-    <row r="252" spans="1:16" ht="13.2">
+    <row r="252" spans="1:16" ht="12.75">
       <c r="A252" s="4"/>
       <c r="B252" s="2"/>
       <c r="C252" s="4"/>
@@ -9107,7 +9118,7 @@
       <c r="O252" s="4"/>
       <c r="P252" s="4"/>
     </row>
-    <row r="253" spans="1:16" ht="13.2">
+    <row r="253" spans="1:16" ht="12.75">
       <c r="A253" s="4"/>
       <c r="B253" s="2"/>
       <c r="C253" s="4"/>
@@ -9125,7 +9136,7 @@
       <c r="O253" s="4"/>
       <c r="P253" s="4"/>
     </row>
-    <row r="254" spans="1:16" ht="13.2">
+    <row r="254" spans="1:16" ht="12.75">
       <c r="A254" s="4"/>
       <c r="B254" s="2"/>
       <c r="C254" s="4"/>
@@ -9143,7 +9154,7 @@
       <c r="O254" s="4"/>
       <c r="P254" s="4"/>
     </row>
-    <row r="255" spans="1:16" ht="13.2">
+    <row r="255" spans="1:16" ht="12.75">
       <c r="A255" s="4"/>
       <c r="B255" s="2"/>
       <c r="C255" s="4"/>
@@ -9161,7 +9172,7 @@
       <c r="O255" s="4"/>
       <c r="P255" s="4"/>
     </row>
-    <row r="256" spans="1:16" ht="13.2">
+    <row r="256" spans="1:16" ht="12.75">
       <c r="A256" s="4"/>
       <c r="B256" s="2"/>
       <c r="C256" s="4"/>
@@ -9179,7 +9190,7 @@
       <c r="O256" s="4"/>
       <c r="P256" s="4"/>
     </row>
-    <row r="257" spans="1:29" ht="13.2">
+    <row r="257" spans="1:29" ht="12.75">
       <c r="A257" s="4"/>
       <c r="B257" s="2"/>
       <c r="C257" s="4"/>
@@ -9197,7 +9208,7 @@
       <c r="O257" s="4"/>
       <c r="P257" s="4"/>
     </row>
-    <row r="258" spans="1:29" ht="13.2">
+    <row r="258" spans="1:29" ht="12.75">
       <c r="A258" s="4"/>
       <c r="B258" s="2"/>
       <c r="C258" s="4"/>
@@ -9215,7 +9226,7 @@
       <c r="O258" s="4"/>
       <c r="P258" s="4"/>
     </row>
-    <row r="259" spans="1:29" ht="13.2">
+    <row r="259" spans="1:29" ht="12.75">
       <c r="A259" s="4"/>
       <c r="B259" s="2"/>
       <c r="C259" s="4"/>
@@ -9266,7 +9277,7 @@
       <c r="AB260" s="22"/>
       <c r="AC260" s="22"/>
     </row>
-    <row r="261" spans="1:29" ht="13.2">
+    <row r="261" spans="1:29" ht="12.75">
       <c r="A261" s="4"/>
       <c r="B261" s="2"/>
       <c r="C261" s="4"/>
@@ -9282,7 +9293,7 @@
       <c r="O261" s="4"/>
       <c r="P261" s="4"/>
     </row>
-    <row r="262" spans="1:29" ht="13.2">
+    <row r="262" spans="1:29" ht="12.75">
       <c r="A262" s="4"/>
       <c r="B262" s="2"/>
       <c r="C262" s="4"/>
@@ -9298,7 +9309,7 @@
       <c r="O262" s="4"/>
       <c r="P262" s="4"/>
     </row>
-    <row r="263" spans="1:29" ht="13.2">
+    <row r="263" spans="1:29" ht="12.75">
       <c r="A263" s="4"/>
       <c r="B263" s="2"/>
       <c r="C263" s="4"/>
@@ -9314,7 +9325,7 @@
       <c r="O263" s="4"/>
       <c r="P263" s="4"/>
     </row>
-    <row r="264" spans="1:29" ht="13.2">
+    <row r="264" spans="1:29" ht="12.75">
       <c r="A264" s="4"/>
       <c r="B264" s="2"/>
       <c r="C264" s="4"/>
@@ -9328,7 +9339,7 @@
       <c r="O264" s="4"/>
       <c r="P264" s="4"/>
     </row>
-    <row r="265" spans="1:29" ht="13.2">
+    <row r="265" spans="1:29" ht="12.75">
       <c r="A265" s="4"/>
       <c r="B265" s="2"/>
       <c r="C265" s="4"/>
@@ -9342,7 +9353,7 @@
       <c r="O265" s="4"/>
       <c r="P265" s="4"/>
     </row>
-    <row r="266" spans="1:29" ht="13.2">
+    <row r="266" spans="1:29" ht="12.75">
       <c r="A266" s="4"/>
       <c r="B266" s="2"/>
       <c r="C266" s="4"/>
@@ -9356,7 +9367,7 @@
       <c r="O266" s="4"/>
       <c r="P266" s="4"/>
     </row>
-    <row r="267" spans="1:29" ht="13.2">
+    <row r="267" spans="1:29" ht="12.75">
       <c r="A267" s="4"/>
       <c r="B267" s="2"/>
       <c r="C267" s="4"/>
@@ -9370,7 +9381,7 @@
       <c r="O267" s="4"/>
       <c r="P267" s="4"/>
     </row>
-    <row r="268" spans="1:29" ht="13.2">
+    <row r="268" spans="1:29" ht="12.75">
       <c r="A268" s="4"/>
       <c r="B268" s="2"/>
       <c r="C268" s="4"/>
@@ -9384,7 +9395,7 @@
       <c r="O268" s="4"/>
       <c r="P268" s="4"/>
     </row>
-    <row r="269" spans="1:29" ht="13.2">
+    <row r="269" spans="1:29" ht="12.75">
       <c r="A269" s="4"/>
       <c r="B269" s="2"/>
       <c r="C269" s="4"/>
@@ -9398,7 +9409,7 @@
       <c r="O269" s="4"/>
       <c r="P269" s="4"/>
     </row>
-    <row r="270" spans="1:29" ht="13.2">
+    <row r="270" spans="1:29" ht="12.75">
       <c r="A270" s="4"/>
       <c r="B270" s="2"/>
       <c r="C270" s="4"/>
@@ -9412,7 +9423,7 @@
       <c r="O270" s="4"/>
       <c r="P270" s="4"/>
     </row>
-    <row r="271" spans="1:29" ht="13.2">
+    <row r="271" spans="1:29" ht="12.75">
       <c r="A271" s="4"/>
       <c r="B271" s="2"/>
       <c r="C271" s="4"/>
@@ -9426,7 +9437,7 @@
       <c r="O271" s="4"/>
       <c r="P271" s="4"/>
     </row>
-    <row r="272" spans="1:29" ht="13.2">
+    <row r="272" spans="1:29" ht="12.75">
       <c r="A272" s="4"/>
       <c r="B272" s="2"/>
       <c r="C272" s="4"/>
@@ -9440,7 +9451,7 @@
       <c r="O272" s="4"/>
       <c r="P272" s="4"/>
     </row>
-    <row r="273" spans="1:29" ht="13.2">
+    <row r="273" spans="1:29" ht="12.75">
       <c r="A273" s="4"/>
       <c r="B273" s="2"/>
       <c r="C273" s="4"/>
@@ -9454,7 +9465,7 @@
       <c r="O273" s="4"/>
       <c r="P273" s="4"/>
     </row>
-    <row r="274" spans="1:29" ht="13.2">
+    <row r="274" spans="1:29" ht="12.75">
       <c r="A274" s="4"/>
       <c r="B274" s="2"/>
       <c r="C274" s="4"/>
@@ -9468,7 +9479,7 @@
       <c r="O274" s="4"/>
       <c r="P274" s="4"/>
     </row>
-    <row r="275" spans="1:29" ht="13.2">
+    <row r="275" spans="1:29" ht="12.75">
       <c r="A275" s="4"/>
       <c r="B275" s="2"/>
       <c r="C275" s="4"/>
@@ -9484,7 +9495,7 @@
       <c r="O275" s="4"/>
       <c r="P275" s="4"/>
     </row>
-    <row r="276" spans="1:29" ht="13.2">
+    <row r="276" spans="1:29" ht="12.75">
       <c r="A276" s="4"/>
       <c r="B276" s="2"/>
       <c r="C276" s="4"/>
@@ -9533,7 +9544,7 @@
       <c r="AB277" s="23"/>
       <c r="AC277" s="23"/>
     </row>
-    <row r="278" spans="1:29" ht="13.2">
+    <row r="278" spans="1:29" ht="12.75">
       <c r="A278" s="4"/>
       <c r="B278" s="2"/>
       <c r="C278" s="4"/>
@@ -9549,7 +9560,7 @@
       <c r="O278" s="4"/>
       <c r="P278" s="4"/>
     </row>
-    <row r="279" spans="1:29" ht="13.2">
+    <row r="279" spans="1:29" ht="12.75">
       <c r="A279" s="4"/>
       <c r="B279" s="2"/>
       <c r="C279" s="4"/>
@@ -9565,7 +9576,7 @@
       <c r="O279" s="4"/>
       <c r="P279" s="4"/>
     </row>
-    <row r="280" spans="1:29" ht="13.2">
+    <row r="280" spans="1:29" ht="12.75">
       <c r="A280" s="4"/>
       <c r="B280" s="2"/>
       <c r="C280" s="4"/>
@@ -9581,7 +9592,7 @@
       <c r="O280" s="4"/>
       <c r="P280" s="4"/>
     </row>
-    <row r="281" spans="1:29" ht="13.2">
+    <row r="281" spans="1:29" ht="12.75">
       <c r="A281" s="4"/>
       <c r="B281" s="2"/>
       <c r="C281" s="4"/>
@@ -9597,7 +9608,7 @@
       <c r="O281" s="4"/>
       <c r="P281" s="4"/>
     </row>
-    <row r="282" spans="1:29" ht="13.2">
+    <row r="282" spans="1:29" ht="12.75">
       <c r="A282" s="4"/>
       <c r="B282" s="2"/>
       <c r="C282" s="4"/>
@@ -9613,7 +9624,7 @@
       <c r="O282" s="4"/>
       <c r="P282" s="4"/>
     </row>
-    <row r="283" spans="1:29" ht="13.2">
+    <row r="283" spans="1:29" ht="12.75">
       <c r="A283" s="4"/>
       <c r="B283" s="2"/>
       <c r="C283" s="4"/>
@@ -9629,7 +9640,7 @@
       <c r="O283" s="4"/>
       <c r="P283" s="4"/>
     </row>
-    <row r="284" spans="1:29" ht="13.2">
+    <row r="284" spans="1:29" ht="12.75">
       <c r="A284" s="4"/>
       <c r="B284" s="2"/>
       <c r="C284" s="4"/>
@@ -9645,7 +9656,7 @@
       <c r="O284" s="4"/>
       <c r="P284" s="4"/>
     </row>
-    <row r="285" spans="1:29" ht="13.2">
+    <row r="285" spans="1:29" ht="12.75">
       <c r="A285" s="4"/>
       <c r="B285" s="2"/>
       <c r="C285" s="4"/>
@@ -9661,7 +9672,7 @@
       <c r="O285" s="4"/>
       <c r="P285" s="4"/>
     </row>
-    <row r="286" spans="1:29" ht="13.2">
+    <row r="286" spans="1:29" ht="12.75">
       <c r="A286" s="4"/>
       <c r="B286" s="2"/>
       <c r="C286" s="4"/>
@@ -9677,7 +9688,7 @@
       <c r="O286" s="4"/>
       <c r="P286" s="4"/>
     </row>
-    <row r="287" spans="1:29" ht="13.2">
+    <row r="287" spans="1:29" ht="12.75">
       <c r="A287" s="4"/>
       <c r="B287" s="2"/>
       <c r="C287" s="4"/>
@@ -9693,7 +9704,7 @@
       <c r="O287" s="4"/>
       <c r="P287" s="4"/>
     </row>
-    <row r="288" spans="1:29" ht="13.2">
+    <row r="288" spans="1:29" ht="12.75">
       <c r="A288" s="4"/>
       <c r="B288" s="2"/>
       <c r="C288" s="4"/>
@@ -9709,7 +9720,7 @@
       <c r="O288" s="4"/>
       <c r="P288" s="4"/>
     </row>
-    <row r="289" spans="1:16" ht="13.2">
+    <row r="289" spans="1:16" ht="12.75">
       <c r="A289" s="4"/>
       <c r="B289" s="2"/>
       <c r="C289" s="4"/>
@@ -9725,7 +9736,7 @@
       <c r="O289" s="4"/>
       <c r="P289" s="4"/>
     </row>
-    <row r="290" spans="1:16" ht="13.2">
+    <row r="290" spans="1:16" ht="12.75">
       <c r="A290" s="4"/>
       <c r="B290" s="2"/>
       <c r="C290" s="4"/>
@@ -9741,7 +9752,7 @@
       <c r="O290" s="4"/>
       <c r="P290" s="4"/>
     </row>
-    <row r="291" spans="1:16" ht="13.2">
+    <row r="291" spans="1:16" ht="12.75">
       <c r="A291" s="4"/>
       <c r="B291" s="2"/>
       <c r="C291" s="4"/>
@@ -9757,7 +9768,7 @@
       <c r="O291" s="4"/>
       <c r="P291" s="4"/>
     </row>
-    <row r="292" spans="1:16" ht="13.2">
+    <row r="292" spans="1:16" ht="12.75">
       <c r="A292" s="4"/>
       <c r="B292" s="2"/>
       <c r="C292" s="4"/>
@@ -9773,7 +9784,7 @@
       <c r="O292" s="4"/>
       <c r="P292" s="4"/>
     </row>
-    <row r="293" spans="1:16" ht="13.2">
+    <row r="293" spans="1:16" ht="12.75">
       <c r="A293" s="4"/>
       <c r="B293" s="2"/>
       <c r="C293" s="4"/>
@@ -9789,7 +9800,7 @@
       <c r="O293" s="4"/>
       <c r="P293" s="4"/>
     </row>
-    <row r="294" spans="1:16" ht="13.2">
+    <row r="294" spans="1:16" ht="12.75">
       <c r="A294" s="4"/>
       <c r="B294" s="2"/>
       <c r="C294" s="4"/>
@@ -9805,7 +9816,7 @@
       <c r="O294" s="4"/>
       <c r="P294" s="4"/>
     </row>
-    <row r="295" spans="1:16" ht="13.2">
+    <row r="295" spans="1:16" ht="12.75">
       <c r="A295" s="4"/>
       <c r="B295" s="2"/>
       <c r="C295" s="4"/>
@@ -9821,7 +9832,7 @@
       <c r="O295" s="4"/>
       <c r="P295" s="4"/>
     </row>
-    <row r="296" spans="1:16" ht="13.2">
+    <row r="296" spans="1:16" ht="12.75">
       <c r="A296" s="4"/>
       <c r="B296" s="2"/>
       <c r="C296" s="4"/>
@@ -9837,7 +9848,7 @@
       <c r="O296" s="4"/>
       <c r="P296" s="4"/>
     </row>
-    <row r="297" spans="1:16" ht="13.2">
+    <row r="297" spans="1:16" ht="12.75">
       <c r="A297" s="4"/>
       <c r="B297" s="2"/>
       <c r="C297" s="4"/>
@@ -9853,7 +9864,7 @@
       <c r="O297" s="4"/>
       <c r="P297" s="4"/>
     </row>
-    <row r="298" spans="1:16" ht="13.2">
+    <row r="298" spans="1:16" ht="12.75">
       <c r="A298" s="4"/>
       <c r="B298" s="2"/>
       <c r="C298" s="4"/>
@@ -9869,7 +9880,7 @@
       <c r="O298" s="4"/>
       <c r="P298" s="4"/>
     </row>
-    <row r="299" spans="1:16" ht="13.2">
+    <row r="299" spans="1:16" ht="12.75">
       <c r="A299" s="4"/>
       <c r="B299" s="2"/>
       <c r="C299" s="4"/>
@@ -9885,7 +9896,7 @@
       <c r="O299" s="4"/>
       <c r="P299" s="4"/>
     </row>
-    <row r="300" spans="1:16" ht="13.2">
+    <row r="300" spans="1:16" ht="12.75">
       <c r="A300" s="4"/>
       <c r="B300" s="2"/>
       <c r="C300" s="4"/>
@@ -9901,12 +9912,12 @@
       <c r="O300" s="4"/>
       <c r="P300" s="4"/>
     </row>
-    <row r="301" spans="1:16" ht="13.2">
+    <row r="301" spans="1:16" ht="12.75">
       <c r="A301" s="4"/>
       <c r="B301" s="2"/>
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
-      <c r="E301" s="24"/>
+      <c r="E301" s="31"/>
       <c r="F301" s="4"/>
       <c r="G301" s="4"/>
       <c r="I301" s="4"/>
@@ -9917,12 +9928,12 @@
       <c r="O301" s="4"/>
       <c r="P301" s="4"/>
     </row>
-    <row r="302" spans="1:16" ht="13.2">
+    <row r="302" spans="1:16" ht="12.75">
       <c r="A302" s="4"/>
       <c r="B302" s="2"/>
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
-      <c r="E302" s="25"/>
+      <c r="E302" s="32"/>
       <c r="F302" s="4"/>
       <c r="G302" s="4"/>
       <c r="I302" s="4"/>
@@ -9938,7 +9949,7 @@
       <c r="B303" s="2"/>
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
-      <c r="E303" s="25"/>
+      <c r="E303" s="32"/>
       <c r="F303" s="4"/>
       <c r="G303" s="4"/>
       <c r="I303" s="4"/>
@@ -9954,7 +9965,7 @@
       <c r="B304" s="2"/>
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
-      <c r="E304" s="25"/>
+      <c r="E304" s="32"/>
       <c r="F304" s="4"/>
       <c r="G304" s="4"/>
       <c r="I304" s="4"/>
@@ -9970,7 +9981,7 @@
       <c r="B305" s="2"/>
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
-      <c r="E305" s="25"/>
+      <c r="E305" s="32"/>
       <c r="F305" s="4"/>
       <c r="G305" s="4"/>
       <c r="I305" s="4"/>
@@ -9986,7 +9997,7 @@
       <c r="B306" s="2"/>
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
-      <c r="E306" s="25"/>
+      <c r="E306" s="32"/>
       <c r="F306" s="4"/>
       <c r="G306" s="4"/>
       <c r="I306" s="4"/>
@@ -9997,7 +10008,7 @@
       <c r="O306" s="4"/>
       <c r="P306" s="4"/>
     </row>
-    <row r="307" spans="1:16" ht="13.2">
+    <row r="307" spans="1:16" ht="12.75">
       <c r="A307" s="4"/>
       <c r="B307" s="2"/>
       <c r="C307" s="4"/>
@@ -10013,7 +10024,7 @@
       <c r="O307" s="4"/>
       <c r="P307" s="4"/>
     </row>
-    <row r="308" spans="1:16" ht="13.2">
+    <row r="308" spans="1:16" ht="12.75">
       <c r="A308" s="4"/>
       <c r="B308" s="2"/>
       <c r="C308" s="4"/>
@@ -10029,7 +10040,7 @@
       <c r="O308" s="4"/>
       <c r="P308" s="4"/>
     </row>
-    <row r="309" spans="1:16" ht="13.2">
+    <row r="309" spans="1:16" ht="12.75">
       <c r="A309" s="4"/>
       <c r="B309" s="2"/>
       <c r="C309" s="4"/>
@@ -10045,7 +10056,7 @@
       <c r="O309" s="4"/>
       <c r="P309" s="4"/>
     </row>
-    <row r="310" spans="1:16" ht="13.2">
+    <row r="310" spans="1:16" ht="12.75">
       <c r="A310" s="4"/>
       <c r="B310" s="2"/>
       <c r="C310" s="4"/>
@@ -10061,7 +10072,7 @@
       <c r="O310" s="4"/>
       <c r="P310" s="4"/>
     </row>
-    <row r="311" spans="1:16" ht="13.2">
+    <row r="311" spans="1:16" ht="12.75">
       <c r="A311" s="4"/>
       <c r="B311" s="2"/>
       <c r="C311" s="4"/>
@@ -10077,7 +10088,7 @@
       <c r="O311" s="4"/>
       <c r="P311" s="4"/>
     </row>
-    <row r="312" spans="1:16" ht="13.2">
+    <row r="312" spans="1:16" ht="12.75">
       <c r="A312" s="4"/>
       <c r="B312" s="2"/>
       <c r="C312" s="4"/>
@@ -10093,7 +10104,7 @@
       <c r="O312" s="4"/>
       <c r="P312" s="4"/>
     </row>
-    <row r="313" spans="1:16" ht="13.2">
+    <row r="313" spans="1:16" ht="12.75">
       <c r="A313" s="4"/>
       <c r="B313" s="2"/>
       <c r="C313" s="4"/>
@@ -10109,7 +10120,7 @@
       <c r="O313" s="4"/>
       <c r="P313" s="4"/>
     </row>
-    <row r="314" spans="1:16" ht="13.2">
+    <row r="314" spans="1:16" ht="12.75">
       <c r="A314" s="4"/>
       <c r="B314" s="2"/>
       <c r="C314" s="4"/>
@@ -10125,7 +10136,7 @@
       <c r="O314" s="4"/>
       <c r="P314" s="4"/>
     </row>
-    <row r="315" spans="1:16" ht="13.2">
+    <row r="315" spans="1:16" ht="12.75">
       <c r="A315" s="4"/>
       <c r="B315" s="2"/>
       <c r="C315" s="4"/>
@@ -10141,7 +10152,7 @@
       <c r="O315" s="4"/>
       <c r="P315" s="4"/>
     </row>
-    <row r="316" spans="1:16" ht="13.2">
+    <row r="316" spans="1:16" ht="12.75">
       <c r="A316" s="4"/>
       <c r="B316" s="2"/>
       <c r="C316" s="4"/>
@@ -10157,7 +10168,7 @@
       <c r="O316" s="4"/>
       <c r="P316" s="4"/>
     </row>
-    <row r="317" spans="1:16" ht="13.2">
+    <row r="317" spans="1:16" ht="12.75">
       <c r="A317" s="4"/>
       <c r="B317" s="2"/>
       <c r="C317" s="4"/>
@@ -10173,7 +10184,7 @@
       <c r="O317" s="4"/>
       <c r="P317" s="4"/>
     </row>
-    <row r="318" spans="1:16" ht="13.2">
+    <row r="318" spans="1:16" ht="12.75">
       <c r="A318" s="4"/>
       <c r="B318" s="2"/>
       <c r="C318" s="4"/>
@@ -10189,7 +10200,7 @@
       <c r="O318" s="4"/>
       <c r="P318" s="4"/>
     </row>
-    <row r="319" spans="1:16" ht="13.2">
+    <row r="319" spans="1:16" ht="12.75">
       <c r="A319" s="4"/>
       <c r="B319" s="2"/>
       <c r="C319" s="4"/>
@@ -10205,7 +10216,7 @@
       <c r="O319" s="4"/>
       <c r="P319" s="4"/>
     </row>
-    <row r="320" spans="1:16" ht="13.2">
+    <row r="320" spans="1:16" ht="12.75">
       <c r="A320" s="4"/>
       <c r="B320" s="2"/>
       <c r="C320" s="4"/>
@@ -10221,7 +10232,7 @@
       <c r="O320" s="4"/>
       <c r="P320" s="4"/>
     </row>
-    <row r="321" spans="1:29" ht="13.2">
+    <row r="321" spans="1:29" ht="12.75">
       <c r="A321" s="4"/>
       <c r="B321" s="2"/>
       <c r="C321" s="4"/>
@@ -10237,7 +10248,7 @@
       <c r="O321" s="4"/>
       <c r="P321" s="4"/>
     </row>
-    <row r="322" spans="1:29" ht="13.2">
+    <row r="322" spans="1:29" ht="12.75">
       <c r="A322" s="4"/>
       <c r="B322" s="2"/>
       <c r="C322" s="4"/>
@@ -10253,7 +10264,7 @@
       <c r="O322" s="4"/>
       <c r="P322" s="4"/>
     </row>
-    <row r="323" spans="1:29" ht="13.2">
+    <row r="323" spans="1:29" ht="12.75">
       <c r="A323" s="4"/>
       <c r="B323" s="2"/>
       <c r="C323" s="4"/>
@@ -10269,7 +10280,7 @@
       <c r="O323" s="4"/>
       <c r="P323" s="4"/>
     </row>
-    <row r="324" spans="1:29" ht="13.2">
+    <row r="324" spans="1:29" ht="12.75">
       <c r="A324" s="4"/>
       <c r="B324" s="2"/>
       <c r="C324" s="4"/>
@@ -10285,7 +10296,7 @@
       <c r="O324" s="4"/>
       <c r="P324" s="4"/>
     </row>
-    <row r="325" spans="1:29" ht="13.2">
+    <row r="325" spans="1:29" ht="12.75">
       <c r="A325" s="4"/>
       <c r="B325" s="2"/>
       <c r="C325" s="4"/>
@@ -10301,7 +10312,7 @@
       <c r="O325" s="4"/>
       <c r="P325" s="4"/>
     </row>
-    <row r="326" spans="1:29" ht="13.2">
+    <row r="326" spans="1:29" ht="12.75">
       <c r="A326" s="4"/>
       <c r="B326" s="2"/>
       <c r="C326" s="4"/>
@@ -10317,7 +10328,7 @@
       <c r="O326" s="4"/>
       <c r="P326" s="4"/>
     </row>
-    <row r="327" spans="1:29" ht="13.2">
+    <row r="327" spans="1:29" ht="12.75">
       <c r="A327" s="4"/>
       <c r="B327" s="2"/>
       <c r="C327" s="4"/>
@@ -10333,7 +10344,7 @@
       <c r="O327" s="4"/>
       <c r="P327" s="4"/>
     </row>
-    <row r="328" spans="1:29" ht="13.2">
+    <row r="328" spans="1:29" ht="12.75">
       <c r="A328" s="4"/>
       <c r="B328" s="2"/>
       <c r="C328" s="4"/>
@@ -10349,7 +10360,7 @@
       <c r="O328" s="4"/>
       <c r="P328" s="4"/>
     </row>
-    <row r="329" spans="1:29" ht="13.2">
+    <row r="329" spans="1:29" ht="12.75">
       <c r="A329" s="4"/>
       <c r="B329" s="2"/>
       <c r="C329" s="4"/>
@@ -10370,35 +10381,35 @@
       <c r="B330" s="2"/>
       <c r="C330" s="4"/>
       <c r="D330" s="4"/>
-      <c r="E330" s="26"/>
+      <c r="E330" s="24"/>
       <c r="F330" s="4"/>
       <c r="G330" s="4"/>
-      <c r="H330" s="26"/>
+      <c r="H330" s="24"/>
       <c r="I330" s="4"/>
-      <c r="J330" s="26"/>
-      <c r="K330" s="26"/>
+      <c r="J330" s="24"/>
+      <c r="K330" s="24"/>
       <c r="L330" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M330" s="26"/>
+      <c r="M330" s="24"/>
       <c r="N330" s="4"/>
       <c r="O330" s="4"/>
       <c r="P330" s="4"/>
-      <c r="Q330" s="26"/>
-      <c r="R330" s="26"/>
-      <c r="S330" s="26"/>
-      <c r="T330" s="26"/>
-      <c r="U330" s="26"/>
-      <c r="V330" s="26"/>
-      <c r="W330" s="26"/>
-      <c r="X330" s="26"/>
-      <c r="Y330" s="26"/>
-      <c r="Z330" s="26"/>
-      <c r="AA330" s="26"/>
-      <c r="AB330" s="26"/>
-      <c r="AC330" s="26"/>
-    </row>
-    <row r="331" spans="1:29" ht="13.2">
+      <c r="Q330" s="24"/>
+      <c r="R330" s="24"/>
+      <c r="S330" s="24"/>
+      <c r="T330" s="24"/>
+      <c r="U330" s="24"/>
+      <c r="V330" s="24"/>
+      <c r="W330" s="24"/>
+      <c r="X330" s="24"/>
+      <c r="Y330" s="24"/>
+      <c r="Z330" s="24"/>
+      <c r="AA330" s="24"/>
+      <c r="AB330" s="24"/>
+      <c r="AC330" s="24"/>
+    </row>
+    <row r="331" spans="1:29" ht="12.75">
       <c r="A331" s="4"/>
       <c r="B331" s="2"/>
       <c r="C331" s="4"/>
@@ -10431,7 +10442,7 @@
       <c r="AB331" s="4"/>
       <c r="AC331" s="4"/>
     </row>
-    <row r="332" spans="1:29" ht="13.2">
+    <row r="332" spans="1:29" ht="12.75">
       <c r="A332" s="4"/>
       <c r="B332" s="2"/>
       <c r="C332" s="4"/>
@@ -10448,7 +10459,7 @@
       <c r="O332" s="4"/>
       <c r="P332" s="4"/>
     </row>
-    <row r="333" spans="1:29" ht="13.2">
+    <row r="333" spans="1:29" ht="12.75">
       <c r="A333" s="4"/>
       <c r="B333" s="2"/>
       <c r="C333" s="4"/>
@@ -10464,7 +10475,7 @@
       <c r="O333" s="4"/>
       <c r="P333" s="4"/>
     </row>
-    <row r="334" spans="1:29" ht="13.2">
+    <row r="334" spans="1:29" ht="12.75">
       <c r="A334" s="4"/>
       <c r="B334" s="2"/>
       <c r="C334" s="4"/>
@@ -10480,7 +10491,7 @@
       <c r="O334" s="4"/>
       <c r="P334" s="4"/>
     </row>
-    <row r="335" spans="1:29" ht="13.2">
+    <row r="335" spans="1:29" ht="12.75">
       <c r="A335" s="4"/>
       <c r="B335" s="2"/>
       <c r="C335" s="4"/>
@@ -10496,7 +10507,7 @@
       <c r="O335" s="4"/>
       <c r="P335" s="4"/>
     </row>
-    <row r="336" spans="1:29" ht="13.2">
+    <row r="336" spans="1:29" ht="12.75">
       <c r="A336" s="4"/>
       <c r="B336" s="2"/>
       <c r="C336" s="4"/>
@@ -10512,7 +10523,7 @@
       <c r="O336" s="4"/>
       <c r="P336" s="4"/>
     </row>
-    <row r="337" spans="1:16" ht="13.2">
+    <row r="337" spans="1:16" ht="12.75">
       <c r="A337" s="4"/>
       <c r="B337" s="2"/>
       <c r="C337" s="4"/>
@@ -10528,7 +10539,7 @@
       <c r="O337" s="4"/>
       <c r="P337" s="4"/>
     </row>
-    <row r="338" spans="1:16" ht="13.2">
+    <row r="338" spans="1:16" ht="12.75">
       <c r="A338" s="4"/>
       <c r="B338" s="2"/>
       <c r="C338" s="4"/>
@@ -10544,7 +10555,7 @@
       <c r="O338" s="4"/>
       <c r="P338" s="4"/>
     </row>
-    <row r="339" spans="1:16" ht="13.2">
+    <row r="339" spans="1:16" ht="12.75">
       <c r="A339" s="4"/>
       <c r="B339" s="2"/>
       <c r="C339" s="4"/>
@@ -10560,7 +10571,7 @@
       <c r="O339" s="4"/>
       <c r="P339" s="4"/>
     </row>
-    <row r="340" spans="1:16" ht="13.2">
+    <row r="340" spans="1:16" ht="12.75">
       <c r="A340" s="4"/>
       <c r="B340" s="2"/>
       <c r="C340" s="4"/>
@@ -10576,7 +10587,7 @@
       <c r="O340" s="4"/>
       <c r="P340" s="4"/>
     </row>
-    <row r="341" spans="1:16" ht="13.2">
+    <row r="341" spans="1:16" ht="12.75">
       <c r="A341" s="4"/>
       <c r="B341" s="2"/>
       <c r="C341" s="4"/>
@@ -10592,7 +10603,7 @@
       <c r="O341" s="4"/>
       <c r="P341" s="4"/>
     </row>
-    <row r="342" spans="1:16" ht="13.2">
+    <row r="342" spans="1:16" ht="12.75">
       <c r="A342" s="4"/>
       <c r="B342" s="2"/>
       <c r="C342" s="4"/>
@@ -10608,7 +10619,7 @@
       <c r="O342" s="4"/>
       <c r="P342" s="4"/>
     </row>
-    <row r="343" spans="1:16" ht="13.2">
+    <row r="343" spans="1:16" ht="12.75">
       <c r="A343" s="4"/>
       <c r="B343" s="2"/>
       <c r="C343" s="4"/>
@@ -10624,7 +10635,7 @@
       <c r="O343" s="4"/>
       <c r="P343" s="4"/>
     </row>
-    <row r="344" spans="1:16" ht="13.2">
+    <row r="344" spans="1:16" ht="12.75">
       <c r="A344" s="4"/>
       <c r="B344" s="2"/>
       <c r="C344" s="4"/>
@@ -10640,7 +10651,7 @@
       <c r="O344" s="4"/>
       <c r="P344" s="4"/>
     </row>
-    <row r="345" spans="1:16" ht="13.2">
+    <row r="345" spans="1:16" ht="12.75">
       <c r="A345" s="4"/>
       <c r="B345" s="2"/>
       <c r="C345" s="4"/>
@@ -10656,7 +10667,7 @@
       <c r="O345" s="4"/>
       <c r="P345" s="4"/>
     </row>
-    <row r="346" spans="1:16" ht="13.2">
+    <row r="346" spans="1:16" ht="12.75">
       <c r="A346" s="4"/>
       <c r="B346" s="2"/>
       <c r="C346" s="4"/>
@@ -10672,7 +10683,7 @@
       <c r="O346" s="4"/>
       <c r="P346" s="4"/>
     </row>
-    <row r="347" spans="1:16" ht="13.2">
+    <row r="347" spans="1:16" ht="12.75">
       <c r="A347" s="4"/>
       <c r="B347" s="2"/>
       <c r="C347" s="4"/>
@@ -10689,7 +10700,7 @@
       <c r="O347" s="4"/>
       <c r="P347" s="4"/>
     </row>
-    <row r="348" spans="1:16" ht="13.2">
+    <row r="348" spans="1:16" ht="12.75">
       <c r="A348" s="4"/>
       <c r="B348" s="2"/>
       <c r="C348" s="4"/>
@@ -10705,7 +10716,7 @@
       <c r="O348" s="4"/>
       <c r="P348" s="4"/>
     </row>
-    <row r="349" spans="1:16" ht="13.2">
+    <row r="349" spans="1:16" ht="12.75">
       <c r="A349" s="4"/>
       <c r="B349" s="2"/>
       <c r="C349" s="4"/>
@@ -10721,7 +10732,7 @@
       <c r="O349" s="4"/>
       <c r="P349" s="4"/>
     </row>
-    <row r="350" spans="1:16" ht="13.2">
+    <row r="350" spans="1:16" ht="12.75">
       <c r="A350" s="4"/>
       <c r="B350" s="2"/>
       <c r="C350" s="4"/>
@@ -10738,7 +10749,7 @@
       <c r="O350" s="4"/>
       <c r="P350" s="4"/>
     </row>
-    <row r="351" spans="1:16" ht="13.2">
+    <row r="351" spans="1:16" ht="12.75">
       <c r="A351" s="4"/>
       <c r="B351" s="2"/>
       <c r="C351" s="4"/>
@@ -10754,7 +10765,7 @@
       <c r="O351" s="4"/>
       <c r="P351" s="4"/>
     </row>
-    <row r="352" spans="1:16" ht="13.2">
+    <row r="352" spans="1:16" ht="12.75">
       <c r="A352" s="4"/>
       <c r="B352" s="2"/>
       <c r="C352" s="4"/>
@@ -10770,7 +10781,7 @@
       <c r="O352" s="4"/>
       <c r="P352" s="4"/>
     </row>
-    <row r="353" spans="1:29" ht="13.2">
+    <row r="353" spans="1:29" ht="12.75">
       <c r="A353" s="4"/>
       <c r="B353" s="2"/>
       <c r="C353" s="4"/>
@@ -10786,7 +10797,7 @@
       <c r="O353" s="4"/>
       <c r="P353" s="4"/>
     </row>
-    <row r="354" spans="1:29" ht="13.2">
+    <row r="354" spans="1:29" ht="12.75">
       <c r="A354" s="4"/>
       <c r="B354" s="2"/>
       <c r="C354" s="4"/>
@@ -10802,7 +10813,7 @@
       <c r="O354" s="4"/>
       <c r="P354" s="4"/>
     </row>
-    <row r="355" spans="1:29" ht="13.2">
+    <row r="355" spans="1:29" ht="12.75">
       <c r="A355" s="4"/>
       <c r="B355" s="2"/>
       <c r="C355" s="4"/>
@@ -10835,7 +10846,7 @@
       <c r="AB355" s="11"/>
       <c r="AC355" s="11"/>
     </row>
-    <row r="356" spans="1:29" ht="13.2">
+    <row r="356" spans="1:29" ht="12.75">
       <c r="A356" s="4"/>
       <c r="B356" s="2"/>
       <c r="C356" s="4"/>
@@ -10851,7 +10862,7 @@
       <c r="O356" s="4"/>
       <c r="P356" s="4"/>
     </row>
-    <row r="357" spans="1:29" ht="13.2">
+    <row r="357" spans="1:29" ht="12.75">
       <c r="A357" s="4"/>
       <c r="B357" s="2"/>
       <c r="C357" s="4"/>
@@ -10867,7 +10878,7 @@
       <c r="O357" s="4"/>
       <c r="P357" s="4"/>
     </row>
-    <row r="358" spans="1:29" ht="13.2">
+    <row r="358" spans="1:29" ht="12.75">
       <c r="A358" s="4"/>
       <c r="B358" s="2"/>
       <c r="C358" s="4"/>
@@ -10883,7 +10894,7 @@
       <c r="O358" s="4"/>
       <c r="P358" s="4"/>
     </row>
-    <row r="359" spans="1:29" ht="13.2">
+    <row r="359" spans="1:29" ht="12.75">
       <c r="A359" s="4"/>
       <c r="B359" s="2"/>
       <c r="C359" s="4"/>
@@ -10899,7 +10910,7 @@
       <c r="O359" s="4"/>
       <c r="P359" s="4"/>
     </row>
-    <row r="360" spans="1:29" ht="13.2">
+    <row r="360" spans="1:29" ht="12.75">
       <c r="A360" s="4"/>
       <c r="B360" s="2"/>
       <c r="C360" s="4"/>
@@ -10915,7 +10926,7 @@
       <c r="O360" s="4"/>
       <c r="P360" s="4"/>
     </row>
-    <row r="361" spans="1:29" ht="13.2">
+    <row r="361" spans="1:29" ht="12.75">
       <c r="A361" s="4"/>
       <c r="B361" s="2"/>
       <c r="C361" s="4"/>
@@ -10931,7 +10942,7 @@
       <c r="O361" s="4"/>
       <c r="P361" s="4"/>
     </row>
-    <row r="362" spans="1:29" ht="13.2">
+    <row r="362" spans="1:29" ht="12.75">
       <c r="A362" s="4"/>
       <c r="B362" s="2"/>
       <c r="C362" s="4"/>
@@ -10947,7 +10958,7 @@
       <c r="O362" s="4"/>
       <c r="P362" s="4"/>
     </row>
-    <row r="363" spans="1:29" ht="13.2">
+    <row r="363" spans="1:29" ht="12.75">
       <c r="A363" s="4"/>
       <c r="B363" s="2"/>
       <c r="C363" s="4"/>
@@ -10963,7 +10974,7 @@
       <c r="O363" s="4"/>
       <c r="P363" s="4"/>
     </row>
-    <row r="364" spans="1:29" ht="13.2">
+    <row r="364" spans="1:29" ht="12.75">
       <c r="A364" s="4"/>
       <c r="B364" s="2"/>
       <c r="C364" s="4"/>
@@ -10979,7 +10990,7 @@
       <c r="O364" s="4"/>
       <c r="P364" s="4"/>
     </row>
-    <row r="365" spans="1:29" ht="13.2">
+    <row r="365" spans="1:29" ht="12.75">
       <c r="A365" s="4"/>
       <c r="B365" s="2"/>
       <c r="C365" s="4"/>
@@ -10995,7 +11006,7 @@
       <c r="O365" s="4"/>
       <c r="P365" s="4"/>
     </row>
-    <row r="366" spans="1:29" ht="13.2">
+    <row r="366" spans="1:29" ht="12.75">
       <c r="A366" s="4"/>
       <c r="B366" s="2"/>
       <c r="C366" s="4"/>
@@ -11011,7 +11022,7 @@
       <c r="O366" s="4"/>
       <c r="P366" s="4"/>
     </row>
-    <row r="367" spans="1:29" ht="13.2">
+    <row r="367" spans="1:29" ht="12.75">
       <c r="A367" s="4"/>
       <c r="B367" s="2"/>
       <c r="C367" s="4"/>
@@ -11027,7 +11038,7 @@
       <c r="O367" s="4"/>
       <c r="P367" s="4"/>
     </row>
-    <row r="368" spans="1:29" ht="13.2">
+    <row r="368" spans="1:29" ht="12.75">
       <c r="A368" s="4"/>
       <c r="B368" s="2"/>
       <c r="C368" s="4"/>
@@ -11043,7 +11054,7 @@
       <c r="O368" s="4"/>
       <c r="P368" s="4"/>
     </row>
-    <row r="369" spans="1:16" ht="13.2">
+    <row r="369" spans="1:16" ht="12.75">
       <c r="A369" s="4"/>
       <c r="B369" s="2"/>
       <c r="C369" s="4"/>
@@ -11059,7 +11070,7 @@
       <c r="O369" s="4"/>
       <c r="P369" s="4"/>
     </row>
-    <row r="370" spans="1:16" ht="13.2">
+    <row r="370" spans="1:16" ht="12.75">
       <c r="A370" s="4"/>
       <c r="B370" s="2"/>
       <c r="C370" s="4"/>
@@ -11075,7 +11086,7 @@
       <c r="O370" s="4"/>
       <c r="P370" s="4"/>
     </row>
-    <row r="371" spans="1:16" ht="13.2">
+    <row r="371" spans="1:16" ht="12.75">
       <c r="A371" s="4"/>
       <c r="B371" s="2"/>
       <c r="C371" s="4"/>
@@ -11091,7 +11102,7 @@
       <c r="O371" s="4"/>
       <c r="P371" s="4"/>
     </row>
-    <row r="372" spans="1:16" ht="13.2">
+    <row r="372" spans="1:16" ht="12.75">
       <c r="A372" s="4"/>
       <c r="B372" s="2"/>
       <c r="C372" s="4"/>
@@ -11107,7 +11118,7 @@
       <c r="O372" s="4"/>
       <c r="P372" s="4"/>
     </row>
-    <row r="373" spans="1:16" ht="13.2">
+    <row r="373" spans="1:16" ht="12.75">
       <c r="A373" s="4"/>
       <c r="B373" s="2"/>
       <c r="C373" s="4"/>
@@ -11123,7 +11134,7 @@
       <c r="O373" s="4"/>
       <c r="P373" s="4"/>
     </row>
-    <row r="374" spans="1:16" ht="13.2">
+    <row r="374" spans="1:16" ht="12.75">
       <c r="A374" s="4"/>
       <c r="B374" s="2"/>
       <c r="C374" s="4"/>
@@ -11139,7 +11150,7 @@
       <c r="O374" s="4"/>
       <c r="P374" s="4"/>
     </row>
-    <row r="375" spans="1:16" ht="13.2">
+    <row r="375" spans="1:16" ht="12.75">
       <c r="A375" s="4"/>
       <c r="B375" s="2"/>
       <c r="C375" s="4"/>
@@ -11155,7 +11166,7 @@
       <c r="O375" s="4"/>
       <c r="P375" s="4"/>
     </row>
-    <row r="376" spans="1:16" ht="13.2">
+    <row r="376" spans="1:16" ht="12.75">
       <c r="A376" s="4"/>
       <c r="B376" s="2"/>
       <c r="C376" s="4"/>
@@ -11171,7 +11182,7 @@
       <c r="O376" s="4"/>
       <c r="P376" s="4"/>
     </row>
-    <row r="377" spans="1:16" ht="13.2">
+    <row r="377" spans="1:16" ht="12.75">
       <c r="A377" s="4"/>
       <c r="B377" s="2"/>
       <c r="C377" s="4"/>
@@ -11187,7 +11198,7 @@
       <c r="O377" s="4"/>
       <c r="P377" s="4"/>
     </row>
-    <row r="378" spans="1:16" ht="13.2">
+    <row r="378" spans="1:16" ht="12.75">
       <c r="A378" s="4"/>
       <c r="B378" s="2"/>
       <c r="C378" s="4"/>
@@ -11203,7 +11214,7 @@
       <c r="O378" s="4"/>
       <c r="P378" s="4"/>
     </row>
-    <row r="379" spans="1:16" ht="13.2">
+    <row r="379" spans="1:16" ht="12.75">
       <c r="A379" s="4"/>
       <c r="B379" s="2"/>
       <c r="C379" s="4"/>
@@ -11219,7 +11230,7 @@
       <c r="O379" s="4"/>
       <c r="P379" s="4"/>
     </row>
-    <row r="380" spans="1:16" ht="13.2">
+    <row r="380" spans="1:16" ht="12.75">
       <c r="A380" s="4"/>
       <c r="B380" s="2"/>
       <c r="C380" s="4"/>
@@ -11235,7 +11246,7 @@
       <c r="O380" s="4"/>
       <c r="P380" s="4"/>
     </row>
-    <row r="381" spans="1:16" ht="13.2">
+    <row r="381" spans="1:16" ht="12.75">
       <c r="A381" s="4"/>
       <c r="B381" s="2"/>
       <c r="C381" s="4"/>
@@ -11251,7 +11262,7 @@
       <c r="O381" s="4"/>
       <c r="P381" s="4"/>
     </row>
-    <row r="382" spans="1:16" ht="13.2">
+    <row r="382" spans="1:16" ht="12.75">
       <c r="A382" s="4"/>
       <c r="B382" s="2"/>
       <c r="C382" s="4"/>
@@ -11267,7 +11278,7 @@
       <c r="O382" s="4"/>
       <c r="P382" s="4"/>
     </row>
-    <row r="383" spans="1:16" ht="13.2">
+    <row r="383" spans="1:16" ht="12.75">
       <c r="A383" s="4"/>
       <c r="B383" s="2"/>
       <c r="C383" s="4"/>
@@ -11283,7 +11294,7 @@
       <c r="O383" s="4"/>
       <c r="P383" s="4"/>
     </row>
-    <row r="384" spans="1:16" ht="13.2">
+    <row r="384" spans="1:16" ht="12.75">
       <c r="A384" s="4"/>
       <c r="B384" s="2"/>
       <c r="C384" s="4"/>
@@ -11299,7 +11310,7 @@
       <c r="O384" s="4"/>
       <c r="P384" s="4"/>
     </row>
-    <row r="385" spans="1:16" ht="13.2">
+    <row r="385" spans="1:16" ht="12.75">
       <c r="A385" s="4"/>
       <c r="B385" s="2"/>
       <c r="C385" s="4"/>
@@ -11315,7 +11326,7 @@
       <c r="O385" s="4"/>
       <c r="P385" s="4"/>
     </row>
-    <row r="386" spans="1:16" ht="13.2">
+    <row r="386" spans="1:16" ht="12.75">
       <c r="A386" s="4"/>
       <c r="B386" s="2"/>
       <c r="C386" s="4"/>
@@ -11331,7 +11342,7 @@
       <c r="O386" s="4"/>
       <c r="P386" s="4"/>
     </row>
-    <row r="387" spans="1:16" ht="13.2">
+    <row r="387" spans="1:16" ht="12.75">
       <c r="A387" s="4"/>
       <c r="B387" s="2"/>
       <c r="C387" s="4"/>
@@ -11347,7 +11358,7 @@
       <c r="O387" s="4"/>
       <c r="P387" s="4"/>
     </row>
-    <row r="388" spans="1:16" ht="13.2">
+    <row r="388" spans="1:16" ht="12.75">
       <c r="A388" s="4"/>
       <c r="B388" s="2"/>
       <c r="C388" s="4"/>
@@ -11363,7 +11374,7 @@
       <c r="O388" s="4"/>
       <c r="P388" s="4"/>
     </row>
-    <row r="389" spans="1:16" ht="13.2">
+    <row r="389" spans="1:16" ht="12.75">
       <c r="A389" s="4"/>
       <c r="B389" s="2"/>
       <c r="C389" s="4"/>
@@ -11379,7 +11390,7 @@
       <c r="O389" s="4"/>
       <c r="P389" s="4"/>
     </row>
-    <row r="390" spans="1:16" ht="13.2">
+    <row r="390" spans="1:16" ht="12.75">
       <c r="A390" s="4"/>
       <c r="B390" s="2"/>
       <c r="C390" s="4"/>
@@ -11395,7 +11406,7 @@
       <c r="O390" s="4"/>
       <c r="P390" s="4"/>
     </row>
-    <row r="391" spans="1:16" ht="13.2">
+    <row r="391" spans="1:16" ht="12.75">
       <c r="A391" s="4"/>
       <c r="B391" s="2"/>
       <c r="C391" s="4"/>
@@ -11411,7 +11422,7 @@
       <c r="O391" s="4"/>
       <c r="P391" s="4"/>
     </row>
-    <row r="392" spans="1:16" ht="13.2">
+    <row r="392" spans="1:16" ht="12.75">
       <c r="A392" s="4"/>
       <c r="B392" s="2"/>
       <c r="C392" s="4"/>
@@ -11427,7 +11438,7 @@
       <c r="O392" s="4"/>
       <c r="P392" s="4"/>
     </row>
-    <row r="393" spans="1:16" ht="13.2">
+    <row r="393" spans="1:16" ht="12.75">
       <c r="A393" s="4"/>
       <c r="B393" s="2"/>
       <c r="C393" s="4"/>
@@ -11443,7 +11454,7 @@
       <c r="O393" s="4"/>
       <c r="P393" s="4"/>
     </row>
-    <row r="394" spans="1:16" ht="13.2">
+    <row r="394" spans="1:16" ht="12.75">
       <c r="A394" s="4"/>
       <c r="B394" s="2"/>
       <c r="C394" s="4"/>
@@ -11459,7 +11470,7 @@
       <c r="O394" s="4"/>
       <c r="P394" s="4"/>
     </row>
-    <row r="395" spans="1:16" ht="13.2">
+    <row r="395" spans="1:16" ht="12.75">
       <c r="A395" s="4"/>
       <c r="B395" s="2"/>
       <c r="C395" s="4"/>
@@ -11475,7 +11486,7 @@
       <c r="O395" s="4"/>
       <c r="P395" s="4"/>
     </row>
-    <row r="396" spans="1:16" ht="13.2">
+    <row r="396" spans="1:16" ht="12.75">
       <c r="A396" s="4"/>
       <c r="B396" s="2"/>
       <c r="C396" s="4"/>
@@ -11491,7 +11502,7 @@
       <c r="O396" s="4"/>
       <c r="P396" s="4"/>
     </row>
-    <row r="397" spans="1:16" ht="13.2">
+    <row r="397" spans="1:16" ht="12.75">
       <c r="A397" s="4"/>
       <c r="B397" s="2"/>
       <c r="C397" s="4"/>
@@ -11507,7 +11518,7 @@
       <c r="O397" s="4"/>
       <c r="P397" s="4"/>
     </row>
-    <row r="398" spans="1:16" ht="13.2">
+    <row r="398" spans="1:16" ht="12.75">
       <c r="A398" s="4"/>
       <c r="B398" s="2"/>
       <c r="C398" s="4"/>
@@ -11523,7 +11534,7 @@
       <c r="O398" s="4"/>
       <c r="P398" s="4"/>
     </row>
-    <row r="399" spans="1:16" ht="13.2">
+    <row r="399" spans="1:16" ht="12.75">
       <c r="A399" s="4"/>
       <c r="B399" s="2"/>
       <c r="C399" s="4"/>
@@ -11539,7 +11550,7 @@
       <c r="O399" s="4"/>
       <c r="P399" s="4"/>
     </row>
-    <row r="400" spans="1:16" ht="13.2">
+    <row r="400" spans="1:16" ht="12.75">
       <c r="A400" s="4"/>
       <c r="B400" s="2"/>
       <c r="C400" s="4"/>
@@ -11555,7 +11566,7 @@
       <c r="O400" s="4"/>
       <c r="P400" s="4"/>
     </row>
-    <row r="401" spans="1:16" ht="13.2">
+    <row r="401" spans="1:16" ht="12.75">
       <c r="A401" s="4"/>
       <c r="B401" s="2"/>
       <c r="C401" s="4"/>
@@ -11571,7 +11582,7 @@
       <c r="O401" s="4"/>
       <c r="P401" s="4"/>
     </row>
-    <row r="402" spans="1:16" ht="13.2">
+    <row r="402" spans="1:16" ht="12.75">
       <c r="A402" s="4"/>
       <c r="B402" s="2"/>
       <c r="C402" s="4"/>
@@ -11587,7 +11598,7 @@
       <c r="O402" s="4"/>
       <c r="P402" s="4"/>
     </row>
-    <row r="403" spans="1:16" ht="13.2">
+    <row r="403" spans="1:16" ht="12.75">
       <c r="A403" s="4"/>
       <c r="B403" s="2"/>
       <c r="C403" s="4"/>
@@ -11603,7 +11614,7 @@
       <c r="O403" s="4"/>
       <c r="P403" s="4"/>
     </row>
-    <row r="404" spans="1:16" ht="13.2">
+    <row r="404" spans="1:16" ht="12.75">
       <c r="A404" s="4"/>
       <c r="B404" s="2"/>
       <c r="C404" s="4"/>
@@ -11619,7 +11630,7 @@
       <c r="O404" s="4"/>
       <c r="P404" s="4"/>
     </row>
-    <row r="405" spans="1:16" ht="13.2">
+    <row r="405" spans="1:16" ht="12.75">
       <c r="A405" s="4"/>
       <c r="B405" s="2"/>
       <c r="C405" s="4"/>
@@ -11635,7 +11646,7 @@
       <c r="O405" s="4"/>
       <c r="P405" s="4"/>
     </row>
-    <row r="406" spans="1:16" ht="13.2">
+    <row r="406" spans="1:16" ht="12.75">
       <c r="A406" s="4"/>
       <c r="B406" s="2"/>
       <c r="C406" s="4"/>
@@ -11649,7 +11660,7 @@
       <c r="O406" s="4"/>
       <c r="P406" s="4"/>
     </row>
-    <row r="407" spans="1:16" ht="13.2">
+    <row r="407" spans="1:16" ht="12.75">
       <c r="A407" s="4"/>
       <c r="B407" s="2"/>
       <c r="C407" s="4"/>
@@ -11663,7 +11674,7 @@
       <c r="O407" s="4"/>
       <c r="P407" s="4"/>
     </row>
-    <row r="408" spans="1:16" ht="13.2">
+    <row r="408" spans="1:16" ht="12.75">
       <c r="A408" s="4"/>
       <c r="B408" s="2"/>
       <c r="C408" s="4"/>
@@ -11677,7 +11688,7 @@
       <c r="O408" s="4"/>
       <c r="P408" s="4"/>
     </row>
-    <row r="409" spans="1:16" ht="13.2">
+    <row r="409" spans="1:16" ht="12.75">
       <c r="A409" s="4"/>
       <c r="B409" s="2"/>
       <c r="C409" s="4"/>
@@ -11691,7 +11702,7 @@
       <c r="O409" s="4"/>
       <c r="P409" s="4"/>
     </row>
-    <row r="410" spans="1:16" ht="13.2">
+    <row r="410" spans="1:16" ht="12.75">
       <c r="A410" s="4"/>
       <c r="B410" s="2"/>
       <c r="C410" s="4"/>
@@ -11705,7 +11716,7 @@
       <c r="O410" s="4"/>
       <c r="P410" s="4"/>
     </row>
-    <row r="411" spans="1:16" ht="13.2">
+    <row r="411" spans="1:16" ht="12.75">
       <c r="A411" s="4"/>
       <c r="B411" s="2"/>
       <c r="C411" s="4"/>
@@ -11719,7 +11730,7 @@
       <c r="O411" s="4"/>
       <c r="P411" s="4"/>
     </row>
-    <row r="412" spans="1:16" ht="13.2">
+    <row r="412" spans="1:16" ht="12.75">
       <c r="A412" s="4"/>
       <c r="B412" s="2"/>
       <c r="C412" s="4"/>
@@ -11733,7 +11744,7 @@
       <c r="O412" s="4"/>
       <c r="P412" s="4"/>
     </row>
-    <row r="413" spans="1:16" ht="13.2">
+    <row r="413" spans="1:16" ht="12.75">
       <c r="A413" s="4"/>
       <c r="B413" s="2"/>
       <c r="C413" s="4"/>
@@ -11747,7 +11758,7 @@
       <c r="O413" s="4"/>
       <c r="P413" s="4"/>
     </row>
-    <row r="414" spans="1:16" ht="13.2">
+    <row r="414" spans="1:16" ht="12.75">
       <c r="A414" s="4"/>
       <c r="B414" s="2"/>
       <c r="C414" s="4"/>
@@ -11761,7 +11772,7 @@
       <c r="O414" s="4"/>
       <c r="P414" s="4"/>
     </row>
-    <row r="415" spans="1:16" ht="13.2">
+    <row r="415" spans="1:16" ht="12.75">
       <c r="A415" s="4"/>
       <c r="B415" s="2"/>
       <c r="C415" s="4"/>
@@ -11775,7 +11786,7 @@
       <c r="O415" s="4"/>
       <c r="P415" s="4"/>
     </row>
-    <row r="416" spans="1:16" ht="13.2">
+    <row r="416" spans="1:16" ht="12.75">
       <c r="A416" s="4"/>
       <c r="B416" s="2"/>
       <c r="C416" s="4"/>
@@ -11789,7 +11800,7 @@
       <c r="O416" s="4"/>
       <c r="P416" s="4"/>
     </row>
-    <row r="417" spans="1:16" ht="13.2">
+    <row r="417" spans="1:16" ht="12.75">
       <c r="A417" s="4"/>
       <c r="B417" s="2"/>
       <c r="C417" s="4"/>
@@ -11803,7 +11814,7 @@
       <c r="O417" s="4"/>
       <c r="P417" s="4"/>
     </row>
-    <row r="418" spans="1:16" ht="13.2">
+    <row r="418" spans="1:16" ht="12.75">
       <c r="A418" s="4"/>
       <c r="B418" s="2"/>
       <c r="C418" s="4"/>
@@ -11817,7 +11828,7 @@
       <c r="O418" s="4"/>
       <c r="P418" s="4"/>
     </row>
-    <row r="419" spans="1:16" ht="13.2">
+    <row r="419" spans="1:16" ht="12.75">
       <c r="A419" s="4"/>
       <c r="B419" s="2"/>
       <c r="C419" s="4"/>
@@ -11831,7 +11842,7 @@
       <c r="O419" s="4"/>
       <c r="P419" s="4"/>
     </row>
-    <row r="420" spans="1:16" ht="13.2">
+    <row r="420" spans="1:16" ht="12.75">
       <c r="A420" s="4"/>
       <c r="B420" s="2"/>
       <c r="C420" s="4"/>
@@ -11845,7 +11856,7 @@
       <c r="O420" s="4"/>
       <c r="P420" s="4"/>
     </row>
-    <row r="421" spans="1:16" ht="13.2">
+    <row r="421" spans="1:16" ht="12.75">
       <c r="A421" s="4"/>
       <c r="B421" s="2"/>
       <c r="C421" s="4"/>
@@ -11859,7 +11870,7 @@
       <c r="O421" s="4"/>
       <c r="P421" s="4"/>
     </row>
-    <row r="422" spans="1:16" ht="13.2">
+    <row r="422" spans="1:16" ht="12.75">
       <c r="A422" s="4"/>
       <c r="B422" s="2"/>
       <c r="C422" s="4"/>
@@ -11873,7 +11884,7 @@
       <c r="O422" s="4"/>
       <c r="P422" s="4"/>
     </row>
-    <row r="423" spans="1:16" ht="13.2">
+    <row r="423" spans="1:16" ht="12.75">
       <c r="A423" s="4"/>
       <c r="B423" s="2"/>
       <c r="C423" s="4"/>
@@ -11887,7 +11898,7 @@
       <c r="O423" s="4"/>
       <c r="P423" s="4"/>
     </row>
-    <row r="424" spans="1:16" ht="13.2">
+    <row r="424" spans="1:16" ht="12.75">
       <c r="A424" s="4"/>
       <c r="B424" s="2"/>
       <c r="C424" s="4"/>
@@ -11901,7 +11912,7 @@
       <c r="O424" s="4"/>
       <c r="P424" s="4"/>
     </row>
-    <row r="425" spans="1:16" ht="13.2">
+    <row r="425" spans="1:16" ht="12.75">
       <c r="A425" s="4"/>
       <c r="B425" s="2"/>
       <c r="C425" s="4"/>
@@ -11915,7 +11926,7 @@
       <c r="O425" s="4"/>
       <c r="P425" s="4"/>
     </row>
-    <row r="426" spans="1:16" ht="13.2">
+    <row r="426" spans="1:16" ht="12.75">
       <c r="A426" s="4"/>
       <c r="B426" s="2"/>
       <c r="C426" s="4"/>
@@ -11929,7 +11940,7 @@
       <c r="O426" s="4"/>
       <c r="P426" s="4"/>
     </row>
-    <row r="427" spans="1:16" ht="13.2">
+    <row r="427" spans="1:16" ht="12.75">
       <c r="A427" s="4"/>
       <c r="B427" s="2"/>
       <c r="C427" s="4"/>
@@ -11943,7 +11954,7 @@
       <c r="O427" s="4"/>
       <c r="P427" s="4"/>
     </row>
-    <row r="428" spans="1:16" ht="13.2">
+    <row r="428" spans="1:16" ht="12.75">
       <c r="A428" s="4"/>
       <c r="B428" s="2"/>
       <c r="C428" s="4"/>
@@ -11957,7 +11968,7 @@
       <c r="O428" s="4"/>
       <c r="P428" s="4"/>
     </row>
-    <row r="429" spans="1:16" ht="13.2">
+    <row r="429" spans="1:16" ht="12.75">
       <c r="A429" s="4"/>
       <c r="B429" s="2"/>
       <c r="C429" s="4"/>
@@ -11971,7 +11982,7 @@
       <c r="O429" s="4"/>
       <c r="P429" s="4"/>
     </row>
-    <row r="430" spans="1:16" ht="13.2">
+    <row r="430" spans="1:16" ht="12.75">
       <c r="A430" s="4"/>
       <c r="B430" s="2"/>
       <c r="C430" s="4"/>
@@ -11985,7 +11996,7 @@
       <c r="O430" s="4"/>
       <c r="P430" s="4"/>
     </row>
-    <row r="431" spans="1:16" ht="13.2">
+    <row r="431" spans="1:16" ht="12.75">
       <c r="A431" s="4"/>
       <c r="B431" s="2"/>
       <c r="C431" s="4"/>
@@ -11999,7 +12010,7 @@
       <c r="O431" s="4"/>
       <c r="P431" s="4"/>
     </row>
-    <row r="432" spans="1:16" ht="13.2">
+    <row r="432" spans="1:16" ht="12.75">
       <c r="A432" s="4"/>
       <c r="B432" s="2"/>
       <c r="C432" s="4"/>
@@ -12013,7 +12024,7 @@
       <c r="O432" s="4"/>
       <c r="P432" s="4"/>
     </row>
-    <row r="433" spans="1:16" ht="13.2">
+    <row r="433" spans="1:16" ht="12.75">
       <c r="A433" s="4"/>
       <c r="B433" s="2"/>
       <c r="C433" s="4"/>
@@ -12027,7 +12038,7 @@
       <c r="O433" s="4"/>
       <c r="P433" s="4"/>
     </row>
-    <row r="434" spans="1:16" ht="13.2">
+    <row r="434" spans="1:16" ht="12.75">
       <c r="A434" s="4"/>
       <c r="B434" s="2"/>
       <c r="C434" s="4"/>
@@ -12041,7 +12052,7 @@
       <c r="O434" s="4"/>
       <c r="P434" s="4"/>
     </row>
-    <row r="435" spans="1:16" ht="13.2">
+    <row r="435" spans="1:16" ht="12.75">
       <c r="A435" s="4"/>
       <c r="B435" s="2"/>
       <c r="C435" s="4"/>
@@ -12055,7 +12066,7 @@
       <c r="O435" s="4"/>
       <c r="P435" s="4"/>
     </row>
-    <row r="436" spans="1:16" ht="13.2">
+    <row r="436" spans="1:16" ht="12.75">
       <c r="A436" s="4"/>
       <c r="B436" s="2"/>
       <c r="C436" s="4"/>
@@ -12069,7 +12080,7 @@
       <c r="O436" s="4"/>
       <c r="P436" s="4"/>
     </row>
-    <row r="437" spans="1:16" ht="13.2">
+    <row r="437" spans="1:16" ht="12.75">
       <c r="A437" s="4"/>
       <c r="B437" s="2"/>
       <c r="C437" s="4"/>
@@ -12083,7 +12094,7 @@
       <c r="O437" s="4"/>
       <c r="P437" s="4"/>
     </row>
-    <row r="438" spans="1:16" ht="13.2">
+    <row r="438" spans="1:16" ht="12.75">
       <c r="A438" s="4"/>
       <c r="B438" s="2"/>
       <c r="C438" s="4"/>
@@ -12097,7 +12108,7 @@
       <c r="O438" s="4"/>
       <c r="P438" s="4"/>
     </row>
-    <row r="439" spans="1:16" ht="13.2">
+    <row r="439" spans="1:16" ht="12.75">
       <c r="A439" s="4"/>
       <c r="B439" s="2"/>
       <c r="C439" s="4"/>
@@ -12111,7 +12122,7 @@
       <c r="O439" s="4"/>
       <c r="P439" s="4"/>
     </row>
-    <row r="440" spans="1:16" ht="13.2">
+    <row r="440" spans="1:16" ht="12.75">
       <c r="A440" s="4"/>
       <c r="B440" s="2"/>
       <c r="C440" s="4"/>
@@ -12125,7 +12136,7 @@
       <c r="O440" s="4"/>
       <c r="P440" s="4"/>
     </row>
-    <row r="441" spans="1:16" ht="13.2">
+    <row r="441" spans="1:16" ht="12.75">
       <c r="A441" s="4"/>
       <c r="B441" s="2"/>
       <c r="C441" s="4"/>
@@ -12139,7 +12150,7 @@
       <c r="O441" s="4"/>
       <c r="P441" s="4"/>
     </row>
-    <row r="442" spans="1:16" ht="13.2">
+    <row r="442" spans="1:16" ht="12.75">
       <c r="A442" s="4"/>
       <c r="B442" s="2"/>
       <c r="C442" s="4"/>
@@ -12153,7 +12164,7 @@
       <c r="O442" s="4"/>
       <c r="P442" s="4"/>
     </row>
-    <row r="443" spans="1:16" ht="13.2">
+    <row r="443" spans="1:16" ht="12.75">
       <c r="A443" s="4"/>
       <c r="B443" s="2"/>
       <c r="C443" s="4"/>
@@ -12167,7 +12178,7 @@
       <c r="O443" s="4"/>
       <c r="P443" s="4"/>
     </row>
-    <row r="444" spans="1:16" ht="13.2">
+    <row r="444" spans="1:16" ht="12.75">
       <c r="A444" s="4"/>
       <c r="B444" s="2"/>
       <c r="C444" s="4"/>
@@ -12181,7 +12192,7 @@
       <c r="O444" s="4"/>
       <c r="P444" s="4"/>
     </row>
-    <row r="445" spans="1:16" ht="13.2">
+    <row r="445" spans="1:16" ht="12.75">
       <c r="A445" s="4"/>
       <c r="B445" s="2"/>
       <c r="C445" s="4"/>
@@ -12195,7 +12206,7 @@
       <c r="O445" s="4"/>
       <c r="P445" s="4"/>
     </row>
-    <row r="446" spans="1:16" ht="13.2">
+    <row r="446" spans="1:16" ht="12.75">
       <c r="A446" s="4"/>
       <c r="B446" s="2"/>
       <c r="C446" s="4"/>
@@ -12209,7 +12220,7 @@
       <c r="O446" s="4"/>
       <c r="P446" s="4"/>
     </row>
-    <row r="447" spans="1:16" ht="13.2">
+    <row r="447" spans="1:16" ht="12.75">
       <c r="A447" s="4"/>
       <c r="B447" s="2"/>
       <c r="C447" s="4"/>
@@ -12223,7 +12234,7 @@
       <c r="O447" s="4"/>
       <c r="P447" s="4"/>
     </row>
-    <row r="448" spans="1:16" ht="13.2">
+    <row r="448" spans="1:16" ht="12.75">
       <c r="A448" s="4"/>
       <c r="B448" s="2"/>
       <c r="C448" s="4"/>
@@ -12237,7 +12248,7 @@
       <c r="O448" s="4"/>
       <c r="P448" s="4"/>
     </row>
-    <row r="449" spans="1:16" ht="13.2">
+    <row r="449" spans="1:16" ht="12.75">
       <c r="A449" s="4"/>
       <c r="B449" s="2"/>
       <c r="C449" s="4"/>
@@ -12251,7 +12262,7 @@
       <c r="O449" s="4"/>
       <c r="P449" s="4"/>
     </row>
-    <row r="450" spans="1:16" ht="13.2">
+    <row r="450" spans="1:16" ht="12.75">
       <c r="A450" s="4"/>
       <c r="B450" s="2"/>
       <c r="C450" s="4"/>
@@ -12265,7 +12276,7 @@
       <c r="O450" s="4"/>
       <c r="P450" s="4"/>
     </row>
-    <row r="451" spans="1:16" ht="13.2">
+    <row r="451" spans="1:16" ht="12.75">
       <c r="A451" s="4"/>
       <c r="B451" s="2"/>
       <c r="C451" s="4"/>
@@ -12279,7 +12290,7 @@
       <c r="O451" s="4"/>
       <c r="P451" s="4"/>
     </row>
-    <row r="452" spans="1:16" ht="13.2">
+    <row r="452" spans="1:16" ht="12.75">
       <c r="A452" s="4"/>
       <c r="B452" s="2"/>
       <c r="C452" s="4"/>
@@ -12293,7 +12304,7 @@
       <c r="O452" s="4"/>
       <c r="P452" s="4"/>
     </row>
-    <row r="453" spans="1:16" ht="13.2">
+    <row r="453" spans="1:16" ht="12.75">
       <c r="A453" s="4"/>
       <c r="B453" s="2"/>
       <c r="C453" s="4"/>
@@ -12307,7 +12318,7 @@
       <c r="O453" s="4"/>
       <c r="P453" s="4"/>
     </row>
-    <row r="454" spans="1:16" ht="13.2">
+    <row r="454" spans="1:16" ht="12.75">
       <c r="A454" s="4"/>
       <c r="B454" s="2"/>
       <c r="C454" s="4"/>
@@ -12321,7 +12332,7 @@
       <c r="O454" s="4"/>
       <c r="P454" s="4"/>
     </row>
-    <row r="455" spans="1:16" ht="13.2">
+    <row r="455" spans="1:16" ht="12.75">
       <c r="A455" s="4"/>
       <c r="B455" s="2"/>
       <c r="C455" s="4"/>
@@ -12335,7 +12346,7 @@
       <c r="O455" s="4"/>
       <c r="P455" s="4"/>
     </row>
-    <row r="456" spans="1:16" ht="13.2">
+    <row r="456" spans="1:16" ht="12.75">
       <c r="A456" s="4"/>
       <c r="B456" s="2"/>
       <c r="C456" s="4"/>
@@ -12349,7 +12360,7 @@
       <c r="O456" s="4"/>
       <c r="P456" s="4"/>
     </row>
-    <row r="457" spans="1:16" ht="13.2">
+    <row r="457" spans="1:16" ht="12.75">
       <c r="A457" s="4"/>
       <c r="B457" s="2"/>
       <c r="C457" s="4"/>
@@ -12363,7 +12374,7 @@
       <c r="O457" s="4"/>
       <c r="P457" s="4"/>
     </row>
-    <row r="458" spans="1:16" ht="13.2">
+    <row r="458" spans="1:16" ht="12.75">
       <c r="A458" s="4"/>
       <c r="B458" s="2"/>
       <c r="C458" s="4"/>
@@ -12377,7 +12388,7 @@
       <c r="O458" s="4"/>
       <c r="P458" s="4"/>
     </row>
-    <row r="459" spans="1:16" ht="13.2">
+    <row r="459" spans="1:16" ht="12.75">
       <c r="A459" s="4"/>
       <c r="B459" s="2"/>
       <c r="C459" s="4"/>
@@ -12391,7 +12402,7 @@
       <c r="O459" s="4"/>
       <c r="P459" s="4"/>
     </row>
-    <row r="460" spans="1:16" ht="13.2">
+    <row r="460" spans="1:16" ht="12.75">
       <c r="A460" s="4"/>
       <c r="B460" s="2"/>
       <c r="C460" s="4"/>
@@ -12405,7 +12416,7 @@
       <c r="O460" s="4"/>
       <c r="P460" s="4"/>
     </row>
-    <row r="461" spans="1:16" ht="13.2">
+    <row r="461" spans="1:16" ht="12.75">
       <c r="A461" s="4"/>
       <c r="B461" s="2"/>
       <c r="C461" s="4"/>
@@ -12419,7 +12430,7 @@
       <c r="O461" s="4"/>
       <c r="P461" s="4"/>
     </row>
-    <row r="462" spans="1:16" ht="13.2">
+    <row r="462" spans="1:16" ht="12.75">
       <c r="A462" s="4"/>
       <c r="B462" s="2"/>
       <c r="C462" s="4"/>
@@ -12433,7 +12444,7 @@
       <c r="O462" s="4"/>
       <c r="P462" s="4"/>
     </row>
-    <row r="463" spans="1:16" ht="13.2">
+    <row r="463" spans="1:16" ht="12.75">
       <c r="A463" s="4"/>
       <c r="B463" s="2"/>
       <c r="C463" s="4"/>
@@ -12447,7 +12458,7 @@
       <c r="O463" s="4"/>
       <c r="P463" s="4"/>
     </row>
-    <row r="464" spans="1:16" ht="13.2">
+    <row r="464" spans="1:16" ht="12.75">
       <c r="A464" s="4"/>
       <c r="B464" s="2"/>
       <c r="C464" s="4"/>
@@ -12461,7 +12472,7 @@
       <c r="O464" s="4"/>
       <c r="P464" s="4"/>
     </row>
-    <row r="465" spans="1:16" ht="13.2">
+    <row r="465" spans="1:16" ht="12.75">
       <c r="A465" s="4"/>
       <c r="B465" s="2"/>
       <c r="C465" s="4"/>
@@ -12475,7 +12486,7 @@
       <c r="O465" s="4"/>
       <c r="P465" s="4"/>
     </row>
-    <row r="466" spans="1:16" ht="13.2">
+    <row r="466" spans="1:16" ht="12.75">
       <c r="A466" s="4"/>
       <c r="B466" s="2"/>
       <c r="C466" s="4"/>
@@ -12489,7 +12500,7 @@
       <c r="O466" s="4"/>
       <c r="P466" s="4"/>
     </row>
-    <row r="467" spans="1:16" ht="13.2">
+    <row r="467" spans="1:16" ht="12.75">
       <c r="A467" s="4"/>
       <c r="B467" s="2"/>
       <c r="C467" s="4"/>
@@ -12503,7 +12514,7 @@
       <c r="O467" s="4"/>
       <c r="P467" s="4"/>
     </row>
-    <row r="468" spans="1:16" ht="13.2">
+    <row r="468" spans="1:16" ht="12.75">
       <c r="A468" s="4"/>
       <c r="B468" s="2"/>
       <c r="C468" s="4"/>
@@ -12517,7 +12528,7 @@
       <c r="O468" s="4"/>
       <c r="P468" s="4"/>
     </row>
-    <row r="469" spans="1:16" ht="13.2">
+    <row r="469" spans="1:16" ht="12.75">
       <c r="A469" s="4"/>
       <c r="B469" s="2"/>
       <c r="C469" s="4"/>
@@ -12531,7 +12542,7 @@
       <c r="O469" s="4"/>
       <c r="P469" s="4"/>
     </row>
-    <row r="470" spans="1:16" ht="13.2">
+    <row r="470" spans="1:16" ht="12.75">
       <c r="A470" s="4"/>
       <c r="B470" s="2"/>
       <c r="C470" s="4"/>
@@ -12545,7 +12556,7 @@
       <c r="O470" s="4"/>
       <c r="P470" s="4"/>
     </row>
-    <row r="471" spans="1:16" ht="13.2">
+    <row r="471" spans="1:16" ht="12.75">
       <c r="A471" s="4"/>
       <c r="B471" s="2"/>
       <c r="C471" s="4"/>
@@ -12559,7 +12570,7 @@
       <c r="O471" s="4"/>
       <c r="P471" s="4"/>
     </row>
-    <row r="472" spans="1:16" ht="13.2">
+    <row r="472" spans="1:16" ht="12.75">
       <c r="A472" s="4"/>
       <c r="B472" s="2"/>
       <c r="C472" s="4"/>
@@ -12573,7 +12584,7 @@
       <c r="O472" s="4"/>
       <c r="P472" s="4"/>
     </row>
-    <row r="473" spans="1:16" ht="13.2">
+    <row r="473" spans="1:16" ht="12.75">
       <c r="A473" s="4"/>
       <c r="B473" s="2"/>
       <c r="C473" s="4"/>
@@ -12587,7 +12598,7 @@
       <c r="O473" s="4"/>
       <c r="P473" s="4"/>
     </row>
-    <row r="474" spans="1:16" ht="13.2">
+    <row r="474" spans="1:16" ht="12.75">
       <c r="A474" s="4"/>
       <c r="B474" s="2"/>
       <c r="C474" s="4"/>
@@ -12601,7 +12612,7 @@
       <c r="O474" s="4"/>
       <c r="P474" s="4"/>
     </row>
-    <row r="475" spans="1:16" ht="13.2">
+    <row r="475" spans="1:16" ht="12.75">
       <c r="A475" s="4"/>
       <c r="B475" s="2"/>
       <c r="C475" s="4"/>
@@ -12615,7 +12626,7 @@
       <c r="O475" s="4"/>
       <c r="P475" s="4"/>
     </row>
-    <row r="476" spans="1:16" ht="13.2">
+    <row r="476" spans="1:16" ht="12.75">
       <c r="A476" s="4"/>
       <c r="B476" s="2"/>
       <c r="C476" s="4"/>
@@ -12629,7 +12640,7 @@
       <c r="O476" s="4"/>
       <c r="P476" s="4"/>
     </row>
-    <row r="477" spans="1:16" ht="13.2">
+    <row r="477" spans="1:16" ht="12.75">
       <c r="A477" s="4"/>
       <c r="B477" s="2"/>
       <c r="C477" s="4"/>
@@ -12643,7 +12654,7 @@
       <c r="O477" s="4"/>
       <c r="P477" s="4"/>
     </row>
-    <row r="478" spans="1:16" ht="13.2">
+    <row r="478" spans="1:16" ht="12.75">
       <c r="A478" s="4"/>
       <c r="B478" s="2"/>
       <c r="C478" s="4"/>
@@ -12657,7 +12668,7 @@
       <c r="O478" s="4"/>
       <c r="P478" s="4"/>
     </row>
-    <row r="479" spans="1:16" ht="13.2">
+    <row r="479" spans="1:16" ht="12.75">
       <c r="A479" s="4"/>
       <c r="B479" s="2"/>
       <c r="C479" s="4"/>
@@ -12671,7 +12682,7 @@
       <c r="O479" s="4"/>
       <c r="P479" s="4"/>
     </row>
-    <row r="480" spans="1:16" ht="13.2">
+    <row r="480" spans="1:16" ht="12.75">
       <c r="A480" s="4"/>
       <c r="B480" s="2"/>
       <c r="C480" s="4"/>
@@ -12685,7 +12696,7 @@
       <c r="O480" s="4"/>
       <c r="P480" s="4"/>
     </row>
-    <row r="481" spans="1:16" ht="13.2">
+    <row r="481" spans="1:16" ht="12.75">
       <c r="A481" s="4"/>
       <c r="B481" s="2"/>
       <c r="C481" s="4"/>
@@ -12699,7 +12710,7 @@
       <c r="O481" s="4"/>
       <c r="P481" s="4"/>
     </row>
-    <row r="482" spans="1:16" ht="13.2">
+    <row r="482" spans="1:16" ht="12.75">
       <c r="A482" s="4"/>
       <c r="B482" s="2"/>
       <c r="C482" s="4"/>
@@ -12713,7 +12724,7 @@
       <c r="O482" s="4"/>
       <c r="P482" s="4"/>
     </row>
-    <row r="483" spans="1:16" ht="13.2">
+    <row r="483" spans="1:16" ht="12.75">
       <c r="A483" s="4"/>
       <c r="B483" s="2"/>
       <c r="C483" s="4"/>
@@ -12727,7 +12738,7 @@
       <c r="O483" s="4"/>
       <c r="P483" s="4"/>
     </row>
-    <row r="484" spans="1:16" ht="13.2">
+    <row r="484" spans="1:16" ht="12.75">
       <c r="A484" s="4"/>
       <c r="B484" s="2"/>
       <c r="C484" s="4"/>
@@ -12741,7 +12752,7 @@
       <c r="O484" s="4"/>
       <c r="P484" s="4"/>
     </row>
-    <row r="485" spans="1:16" ht="13.2">
+    <row r="485" spans="1:16" ht="12.75">
       <c r="A485" s="4"/>
       <c r="B485" s="2"/>
       <c r="C485" s="4"/>
@@ -12755,7 +12766,7 @@
       <c r="O485" s="4"/>
       <c r="P485" s="4"/>
     </row>
-    <row r="486" spans="1:16" ht="13.2">
+    <row r="486" spans="1:16" ht="12.75">
       <c r="A486" s="4"/>
       <c r="B486" s="2"/>
       <c r="C486" s="4"/>
@@ -12769,7 +12780,7 @@
       <c r="O486" s="4"/>
       <c r="P486" s="4"/>
     </row>
-    <row r="487" spans="1:16" ht="13.2">
+    <row r="487" spans="1:16" ht="12.75">
       <c r="A487" s="4"/>
       <c r="B487" s="2"/>
       <c r="C487" s="4"/>
@@ -12783,7 +12794,7 @@
       <c r="O487" s="4"/>
       <c r="P487" s="4"/>
     </row>
-    <row r="488" spans="1:16" ht="13.2">
+    <row r="488" spans="1:16" ht="12.75">
       <c r="A488" s="4"/>
       <c r="B488" s="2"/>
       <c r="C488" s="4"/>
@@ -12797,7 +12808,7 @@
       <c r="O488" s="4"/>
       <c r="P488" s="4"/>
     </row>
-    <row r="489" spans="1:16" ht="13.2">
+    <row r="489" spans="1:16" ht="12.75">
       <c r="A489" s="4"/>
       <c r="B489" s="2"/>
       <c r="C489" s="4"/>
@@ -12811,7 +12822,7 @@
       <c r="O489" s="4"/>
       <c r="P489" s="4"/>
     </row>
-    <row r="490" spans="1:16" ht="13.2">
+    <row r="490" spans="1:16" ht="12.75">
       <c r="A490" s="4"/>
       <c r="B490" s="2"/>
       <c r="C490" s="4"/>
@@ -12825,7 +12836,7 @@
       <c r="O490" s="4"/>
       <c r="P490" s="4"/>
     </row>
-    <row r="491" spans="1:16" ht="13.2">
+    <row r="491" spans="1:16" ht="12.75">
       <c r="A491" s="4"/>
       <c r="B491" s="2"/>
       <c r="C491" s="4"/>
@@ -12839,7 +12850,7 @@
       <c r="O491" s="4"/>
       <c r="P491" s="4"/>
     </row>
-    <row r="492" spans="1:16" ht="13.2">
+    <row r="492" spans="1:16" ht="12.75">
       <c r="A492" s="4"/>
       <c r="B492" s="2"/>
       <c r="C492" s="4"/>
@@ -12853,7 +12864,7 @@
       <c r="O492" s="4"/>
       <c r="P492" s="4"/>
     </row>
-    <row r="493" spans="1:16" ht="13.2">
+    <row r="493" spans="1:16" ht="12.75">
       <c r="A493" s="4"/>
       <c r="B493" s="2"/>
       <c r="C493" s="4"/>
@@ -12867,7 +12878,7 @@
       <c r="O493" s="4"/>
       <c r="P493" s="4"/>
     </row>
-    <row r="494" spans="1:16" ht="13.2">
+    <row r="494" spans="1:16" ht="12.75">
       <c r="A494" s="4"/>
       <c r="B494" s="2"/>
       <c r="C494" s="4"/>
@@ -12881,7 +12892,7 @@
       <c r="O494" s="4"/>
       <c r="P494" s="4"/>
     </row>
-    <row r="495" spans="1:16" ht="13.2">
+    <row r="495" spans="1:16" ht="12.75">
       <c r="A495" s="4"/>
       <c r="B495" s="2"/>
       <c r="C495" s="4"/>
@@ -12895,7 +12906,7 @@
       <c r="O495" s="4"/>
       <c r="P495" s="4"/>
     </row>
-    <row r="496" spans="1:16" ht="13.2">
+    <row r="496" spans="1:16" ht="12.75">
       <c r="A496" s="4"/>
       <c r="B496" s="2"/>
       <c r="C496" s="4"/>
@@ -12909,7 +12920,7 @@
       <c r="O496" s="4"/>
       <c r="P496" s="4"/>
     </row>
-    <row r="497" spans="1:16" ht="13.2">
+    <row r="497" spans="1:16" ht="12.75">
       <c r="A497" s="4"/>
       <c r="B497" s="2"/>
       <c r="C497" s="4"/>
@@ -12923,7 +12934,7 @@
       <c r="O497" s="4"/>
       <c r="P497" s="4"/>
     </row>
-    <row r="498" spans="1:16" ht="13.2">
+    <row r="498" spans="1:16" ht="12.75">
       <c r="A498" s="4"/>
       <c r="B498" s="2"/>
       <c r="C498" s="4"/>
@@ -12937,7 +12948,7 @@
       <c r="O498" s="4"/>
       <c r="P498" s="4"/>
     </row>
-    <row r="499" spans="1:16" ht="13.2">
+    <row r="499" spans="1:16" ht="12.75">
       <c r="A499" s="4"/>
       <c r="B499" s="2"/>
       <c r="C499" s="4"/>
@@ -12951,7 +12962,7 @@
       <c r="O499" s="4"/>
       <c r="P499" s="4"/>
     </row>
-    <row r="500" spans="1:16" ht="13.2">
+    <row r="500" spans="1:16" ht="12.75">
       <c r="A500" s="4"/>
       <c r="B500" s="2"/>
       <c r="C500" s="4"/>
@@ -12965,7 +12976,7 @@
       <c r="O500" s="4"/>
       <c r="P500" s="4"/>
     </row>
-    <row r="501" spans="1:16" ht="13.2">
+    <row r="501" spans="1:16" ht="12.75">
       <c r="A501" s="4"/>
       <c r="B501" s="2"/>
       <c r="C501" s="4"/>
@@ -12979,7 +12990,7 @@
       <c r="O501" s="4"/>
       <c r="P501" s="4"/>
     </row>
-    <row r="502" spans="1:16" ht="13.2">
+    <row r="502" spans="1:16" ht="12.75">
       <c r="A502" s="4"/>
       <c r="B502" s="2"/>
       <c r="C502" s="4"/>
@@ -12993,7 +13004,7 @@
       <c r="O502" s="4"/>
       <c r="P502" s="4"/>
     </row>
-    <row r="503" spans="1:16" ht="13.2">
+    <row r="503" spans="1:16" ht="12.75">
       <c r="A503" s="4"/>
       <c r="B503" s="2"/>
       <c r="C503" s="4"/>
@@ -13007,7 +13018,7 @@
       <c r="O503" s="4"/>
       <c r="P503" s="4"/>
     </row>
-    <row r="504" spans="1:16" ht="13.2">
+    <row r="504" spans="1:16" ht="12.75">
       <c r="A504" s="4"/>
       <c r="B504" s="2"/>
       <c r="C504" s="4"/>
@@ -13021,7 +13032,7 @@
       <c r="O504" s="4"/>
       <c r="P504" s="4"/>
     </row>
-    <row r="505" spans="1:16" ht="13.2">
+    <row r="505" spans="1:16" ht="12.75">
       <c r="A505" s="4"/>
       <c r="B505" s="2"/>
       <c r="C505" s="4"/>
@@ -13035,7 +13046,7 @@
       <c r="O505" s="4"/>
       <c r="P505" s="4"/>
     </row>
-    <row r="506" spans="1:16" ht="13.2">
+    <row r="506" spans="1:16" ht="12.75">
       <c r="A506" s="4"/>
       <c r="B506" s="2"/>
       <c r="C506" s="4"/>
@@ -13049,7 +13060,7 @@
       <c r="O506" s="4"/>
       <c r="P506" s="4"/>
     </row>
-    <row r="507" spans="1:16" ht="13.2">
+    <row r="507" spans="1:16" ht="12.75">
       <c r="A507" s="4"/>
       <c r="B507" s="2"/>
       <c r="C507" s="4"/>
@@ -13063,7 +13074,7 @@
       <c r="O507" s="4"/>
       <c r="P507" s="4"/>
     </row>
-    <row r="508" spans="1:16" ht="13.2">
+    <row r="508" spans="1:16" ht="12.75">
       <c r="A508" s="4"/>
       <c r="B508" s="2"/>
       <c r="C508" s="4"/>
@@ -13077,7 +13088,7 @@
       <c r="O508" s="4"/>
       <c r="P508" s="4"/>
     </row>
-    <row r="509" spans="1:16" ht="13.2">
+    <row r="509" spans="1:16" ht="12.75">
       <c r="A509" s="4"/>
       <c r="B509" s="2"/>
       <c r="C509" s="4"/>
@@ -13091,7 +13102,7 @@
       <c r="O509" s="4"/>
       <c r="P509" s="4"/>
     </row>
-    <row r="510" spans="1:16" ht="13.2">
+    <row r="510" spans="1:16" ht="12.75">
       <c r="A510" s="4"/>
       <c r="B510" s="2"/>
       <c r="C510" s="4"/>
@@ -13105,7 +13116,7 @@
       <c r="O510" s="4"/>
       <c r="P510" s="4"/>
     </row>
-    <row r="511" spans="1:16" ht="13.2">
+    <row r="511" spans="1:16" ht="12.75">
       <c r="A511" s="4"/>
       <c r="B511" s="2"/>
       <c r="C511" s="4"/>
@@ -13119,7 +13130,7 @@
       <c r="O511" s="4"/>
       <c r="P511" s="4"/>
     </row>
-    <row r="512" spans="1:16" ht="13.2">
+    <row r="512" spans="1:16" ht="12.75">
       <c r="A512" s="4"/>
       <c r="B512" s="2"/>
       <c r="C512" s="4"/>
@@ -13133,7 +13144,7 @@
       <c r="O512" s="4"/>
       <c r="P512" s="4"/>
     </row>
-    <row r="513" spans="1:16" ht="13.2">
+    <row r="513" spans="1:16" ht="12.75">
       <c r="A513" s="4"/>
       <c r="B513" s="2"/>
       <c r="C513" s="4"/>
@@ -13147,7 +13158,7 @@
       <c r="O513" s="4"/>
       <c r="P513" s="4"/>
     </row>
-    <row r="514" spans="1:16" ht="13.2">
+    <row r="514" spans="1:16" ht="12.75">
       <c r="A514" s="4"/>
       <c r="B514" s="2"/>
       <c r="C514" s="4"/>
@@ -13161,7 +13172,7 @@
       <c r="O514" s="4"/>
       <c r="P514" s="4"/>
     </row>
-    <row r="515" spans="1:16" ht="13.2">
+    <row r="515" spans="1:16" ht="12.75">
       <c r="A515" s="4"/>
       <c r="B515" s="2"/>
       <c r="C515" s="4"/>
@@ -13175,7 +13186,7 @@
       <c r="O515" s="4"/>
       <c r="P515" s="4"/>
     </row>
-    <row r="516" spans="1:16" ht="13.2">
+    <row r="516" spans="1:16" ht="12.75">
       <c r="A516" s="4"/>
       <c r="B516" s="2"/>
       <c r="C516" s="4"/>
@@ -13189,7 +13200,7 @@
       <c r="O516" s="4"/>
       <c r="P516" s="4"/>
     </row>
-    <row r="517" spans="1:16" ht="13.2">
+    <row r="517" spans="1:16" ht="12.75">
       <c r="A517" s="4"/>
       <c r="B517" s="2"/>
       <c r="C517" s="4"/>
@@ -13203,7 +13214,7 @@
       <c r="O517" s="4"/>
       <c r="P517" s="4"/>
     </row>
-    <row r="518" spans="1:16" ht="13.2">
+    <row r="518" spans="1:16" ht="12.75">
       <c r="A518" s="4"/>
       <c r="B518" s="2"/>
       <c r="C518" s="4"/>
@@ -13217,7 +13228,7 @@
       <c r="O518" s="4"/>
       <c r="P518" s="4"/>
     </row>
-    <row r="519" spans="1:16" ht="13.2">
+    <row r="519" spans="1:16" ht="12.75">
       <c r="A519" s="4"/>
       <c r="B519" s="2"/>
       <c r="C519" s="4"/>
@@ -13231,7 +13242,7 @@
       <c r="O519" s="4"/>
       <c r="P519" s="4"/>
     </row>
-    <row r="520" spans="1:16" ht="13.2">
+    <row r="520" spans="1:16" ht="12.75">
       <c r="A520" s="4"/>
       <c r="B520" s="2"/>
       <c r="C520" s="4"/>
@@ -13245,7 +13256,7 @@
       <c r="O520" s="4"/>
       <c r="P520" s="4"/>
     </row>
-    <row r="521" spans="1:16" ht="13.2">
+    <row r="521" spans="1:16" ht="12.75">
       <c r="A521" s="4"/>
       <c r="B521" s="2"/>
       <c r="C521" s="4"/>
@@ -13259,7 +13270,7 @@
       <c r="O521" s="4"/>
       <c r="P521" s="4"/>
     </row>
-    <row r="522" spans="1:16" ht="13.2">
+    <row r="522" spans="1:16" ht="12.75">
       <c r="A522" s="4"/>
       <c r="B522" s="2"/>
       <c r="C522" s="4"/>
@@ -13273,7 +13284,7 @@
       <c r="O522" s="4"/>
       <c r="P522" s="4"/>
     </row>
-    <row r="523" spans="1:16" ht="13.2">
+    <row r="523" spans="1:16" ht="12.75">
       <c r="A523" s="4"/>
       <c r="B523" s="2"/>
       <c r="C523" s="4"/>
@@ -13287,7 +13298,7 @@
       <c r="O523" s="4"/>
       <c r="P523" s="4"/>
     </row>
-    <row r="524" spans="1:16" ht="13.2">
+    <row r="524" spans="1:16" ht="12.75">
       <c r="A524" s="4"/>
       <c r="B524" s="2"/>
       <c r="C524" s="4"/>
@@ -13301,7 +13312,7 @@
       <c r="O524" s="4"/>
       <c r="P524" s="4"/>
     </row>
-    <row r="525" spans="1:16" ht="13.2">
+    <row r="525" spans="1:16" ht="12.75">
       <c r="A525" s="4"/>
       <c r="B525" s="2"/>
       <c r="C525" s="4"/>
@@ -13315,7 +13326,7 @@
       <c r="O525" s="4"/>
       <c r="P525" s="4"/>
     </row>
-    <row r="526" spans="1:16" ht="13.2">
+    <row r="526" spans="1:16" ht="12.75">
       <c r="A526" s="4"/>
       <c r="B526" s="2"/>
       <c r="C526" s="4"/>
@@ -13329,7 +13340,7 @@
       <c r="O526" s="4"/>
       <c r="P526" s="4"/>
     </row>
-    <row r="527" spans="1:16" ht="13.2">
+    <row r="527" spans="1:16" ht="12.75">
       <c r="A527" s="4"/>
       <c r="B527" s="2"/>
       <c r="C527" s="4"/>
@@ -13343,7 +13354,7 @@
       <c r="O527" s="4"/>
       <c r="P527" s="4"/>
     </row>
-    <row r="528" spans="1:16" ht="13.2">
+    <row r="528" spans="1:16" ht="12.75">
       <c r="A528" s="4"/>
       <c r="B528" s="2"/>
       <c r="C528" s="4"/>
@@ -13357,7 +13368,7 @@
       <c r="O528" s="4"/>
       <c r="P528" s="4"/>
     </row>
-    <row r="529" spans="1:16" ht="13.2">
+    <row r="529" spans="1:16" ht="12.75">
       <c r="A529" s="4"/>
       <c r="B529" s="2"/>
       <c r="C529" s="4"/>
@@ -13371,7 +13382,7 @@
       <c r="O529" s="4"/>
       <c r="P529" s="4"/>
     </row>
-    <row r="530" spans="1:16" ht="13.2">
+    <row r="530" spans="1:16" ht="12.75">
       <c r="A530" s="4"/>
       <c r="B530" s="2"/>
       <c r="C530" s="4"/>
@@ -13385,7 +13396,7 @@
       <c r="O530" s="4"/>
       <c r="P530" s="4"/>
     </row>
-    <row r="531" spans="1:16" ht="13.2">
+    <row r="531" spans="1:16" ht="12.75">
       <c r="A531" s="4"/>
       <c r="B531" s="2"/>
       <c r="C531" s="4"/>
@@ -13399,7 +13410,7 @@
       <c r="O531" s="4"/>
       <c r="P531" s="4"/>
     </row>
-    <row r="532" spans="1:16" ht="13.2">
+    <row r="532" spans="1:16" ht="12.75">
       <c r="A532" s="4"/>
       <c r="B532" s="2"/>
       <c r="C532" s="4"/>
@@ -13413,7 +13424,7 @@
       <c r="O532" s="4"/>
       <c r="P532" s="4"/>
     </row>
-    <row r="533" spans="1:16" ht="13.2">
+    <row r="533" spans="1:16" ht="12.75">
       <c r="A533" s="4"/>
       <c r="B533" s="2"/>
       <c r="C533" s="4"/>
@@ -13427,7 +13438,7 @@
       <c r="O533" s="4"/>
       <c r="P533" s="4"/>
     </row>
-    <row r="534" spans="1:16" ht="13.2">
+    <row r="534" spans="1:16" ht="12.75">
       <c r="A534" s="4"/>
       <c r="B534" s="2"/>
       <c r="C534" s="4"/>
@@ -13441,7 +13452,7 @@
       <c r="O534" s="4"/>
       <c r="P534" s="4"/>
     </row>
-    <row r="535" spans="1:16" ht="13.2">
+    <row r="535" spans="1:16" ht="12.75">
       <c r="A535" s="4"/>
       <c r="B535" s="2"/>
       <c r="C535" s="4"/>
@@ -13455,7 +13466,7 @@
       <c r="O535" s="4"/>
       <c r="P535" s="4"/>
     </row>
-    <row r="536" spans="1:16" ht="13.2">
+    <row r="536" spans="1:16" ht="12.75">
       <c r="A536" s="4"/>
       <c r="B536" s="2"/>
       <c r="C536" s="4"/>
@@ -13469,7 +13480,7 @@
       <c r="O536" s="4"/>
       <c r="P536" s="4"/>
     </row>
-    <row r="537" spans="1:16" ht="13.2">
+    <row r="537" spans="1:16" ht="12.75">
       <c r="A537" s="4"/>
       <c r="B537" s="2"/>
       <c r="C537" s="4"/>
@@ -13483,7 +13494,7 @@
       <c r="O537" s="4"/>
       <c r="P537" s="4"/>
     </row>
-    <row r="538" spans="1:16" ht="13.2">
+    <row r="538" spans="1:16" ht="12.75">
       <c r="A538" s="4"/>
       <c r="B538" s="2"/>
       <c r="C538" s="4"/>
@@ -13497,7 +13508,7 @@
       <c r="O538" s="4"/>
       <c r="P538" s="4"/>
     </row>
-    <row r="539" spans="1:16" ht="13.2">
+    <row r="539" spans="1:16" ht="12.75">
       <c r="A539" s="4"/>
       <c r="B539" s="2"/>
       <c r="C539" s="4"/>
@@ -13511,7 +13522,7 @@
       <c r="O539" s="4"/>
       <c r="P539" s="4"/>
     </row>
-    <row r="540" spans="1:16" ht="13.2">
+    <row r="540" spans="1:16" ht="12.75">
       <c r="A540" s="4"/>
       <c r="B540" s="2"/>
       <c r="C540" s="4"/>
@@ -13525,7 +13536,7 @@
       <c r="O540" s="4"/>
       <c r="P540" s="4"/>
     </row>
-    <row r="541" spans="1:16" ht="13.2">
+    <row r="541" spans="1:16" ht="12.75">
       <c r="A541" s="4"/>
       <c r="B541" s="2"/>
       <c r="C541" s="4"/>
@@ -13539,7 +13550,7 @@
       <c r="O541" s="4"/>
       <c r="P541" s="4"/>
     </row>
-    <row r="542" spans="1:16" ht="13.2">
+    <row r="542" spans="1:16" ht="12.75">
       <c r="A542" s="4"/>
       <c r="B542" s="2"/>
       <c r="C542" s="4"/>
@@ -13553,7 +13564,7 @@
       <c r="O542" s="4"/>
       <c r="P542" s="4"/>
     </row>
-    <row r="543" spans="1:16" ht="13.2">
+    <row r="543" spans="1:16" ht="12.75">
       <c r="A543" s="4"/>
       <c r="B543" s="2"/>
       <c r="C543" s="4"/>
@@ -13567,7 +13578,7 @@
       <c r="O543" s="4"/>
       <c r="P543" s="4"/>
     </row>
-    <row r="544" spans="1:16" ht="13.2">
+    <row r="544" spans="1:16" ht="12.75">
       <c r="A544" s="4"/>
       <c r="B544" s="2"/>
       <c r="C544" s="4"/>
@@ -13581,7 +13592,7 @@
       <c r="O544" s="4"/>
       <c r="P544" s="4"/>
     </row>
-    <row r="545" spans="1:16" ht="13.2">
+    <row r="545" spans="1:16" ht="12.75">
       <c r="A545" s="4"/>
       <c r="B545" s="2"/>
       <c r="C545" s="4"/>
@@ -13595,7 +13606,7 @@
       <c r="O545" s="4"/>
       <c r="P545" s="4"/>
     </row>
-    <row r="546" spans="1:16" ht="13.2">
+    <row r="546" spans="1:16" ht="12.75">
       <c r="A546" s="4"/>
       <c r="B546" s="2"/>
       <c r="C546" s="4"/>
@@ -13609,7 +13620,7 @@
       <c r="O546" s="4"/>
       <c r="P546" s="4"/>
     </row>
-    <row r="547" spans="1:16" ht="13.2">
+    <row r="547" spans="1:16" ht="12.75">
       <c r="A547" s="4"/>
       <c r="B547" s="2"/>
       <c r="C547" s="4"/>
@@ -13623,7 +13634,7 @@
       <c r="O547" s="4"/>
       <c r="P547" s="4"/>
     </row>
-    <row r="548" spans="1:16" ht="13.2">
+    <row r="548" spans="1:16" ht="12.75">
       <c r="A548" s="4"/>
       <c r="B548" s="2"/>
       <c r="C548" s="4"/>
@@ -13637,7 +13648,7 @@
       <c r="O548" s="4"/>
       <c r="P548" s="4"/>
     </row>
-    <row r="549" spans="1:16" ht="13.2">
+    <row r="549" spans="1:16" ht="12.75">
       <c r="A549" s="4"/>
       <c r="B549" s="2"/>
       <c r="C549" s="4"/>
@@ -13651,7 +13662,7 @@
       <c r="O549" s="4"/>
       <c r="P549" s="4"/>
     </row>
-    <row r="550" spans="1:16" ht="13.2">
+    <row r="550" spans="1:16" ht="12.75">
       <c r="A550" s="4"/>
       <c r="B550" s="2"/>
       <c r="C550" s="4"/>
@@ -13665,7 +13676,7 @@
       <c r="O550" s="4"/>
       <c r="P550" s="4"/>
     </row>
-    <row r="551" spans="1:16" ht="13.2">
+    <row r="551" spans="1:16" ht="12.75">
       <c r="A551" s="4"/>
       <c r="B551" s="2"/>
       <c r="C551" s="4"/>
@@ -13679,7 +13690,7 @@
       <c r="O551" s="4"/>
       <c r="P551" s="4"/>
     </row>
-    <row r="552" spans="1:16" ht="13.2">
+    <row r="552" spans="1:16" ht="12.75">
       <c r="A552" s="4"/>
       <c r="B552" s="2"/>
       <c r="C552" s="4"/>
@@ -13693,7 +13704,7 @@
       <c r="O552" s="4"/>
       <c r="P552" s="4"/>
     </row>
-    <row r="553" spans="1:16" ht="13.2">
+    <row r="553" spans="1:16" ht="12.75">
       <c r="A553" s="4"/>
       <c r="B553" s="2"/>
       <c r="C553" s="4"/>
@@ -13707,7 +13718,7 @@
       <c r="O553" s="4"/>
       <c r="P553" s="4"/>
     </row>
-    <row r="554" spans="1:16" ht="13.2">
+    <row r="554" spans="1:16" ht="12.75">
       <c r="A554" s="4"/>
       <c r="B554" s="2"/>
       <c r="C554" s="4"/>
@@ -13721,7 +13732,7 @@
       <c r="O554" s="4"/>
       <c r="P554" s="4"/>
     </row>
-    <row r="555" spans="1:16" ht="13.2">
+    <row r="555" spans="1:16" ht="12.75">
       <c r="A555" s="4"/>
       <c r="B555" s="2"/>
       <c r="C555" s="4"/>
@@ -13735,7 +13746,7 @@
       <c r="O555" s="4"/>
       <c r="P555" s="4"/>
     </row>
-    <row r="556" spans="1:16" ht="13.2">
+    <row r="556" spans="1:16" ht="12.75">
       <c r="A556" s="4"/>
       <c r="B556" s="2"/>
       <c r="C556" s="4"/>
@@ -13749,7 +13760,7 @@
       <c r="O556" s="4"/>
       <c r="P556" s="4"/>
     </row>
-    <row r="557" spans="1:16" ht="13.2">
+    <row r="557" spans="1:16" ht="12.75">
       <c r="A557" s="4"/>
       <c r="B557" s="2"/>
       <c r="C557" s="4"/>
@@ -13763,7 +13774,7 @@
       <c r="O557" s="4"/>
       <c r="P557" s="4"/>
     </row>
-    <row r="558" spans="1:16" ht="13.2">
+    <row r="558" spans="1:16" ht="12.75">
       <c r="A558" s="4"/>
       <c r="B558" s="2"/>
       <c r="C558" s="4"/>
@@ -13777,7 +13788,7 @@
       <c r="O558" s="4"/>
       <c r="P558" s="4"/>
     </row>
-    <row r="559" spans="1:16" ht="13.2">
+    <row r="559" spans="1:16" ht="12.75">
       <c r="A559" s="4"/>
       <c r="B559" s="2"/>
       <c r="C559" s="4"/>
@@ -13791,7 +13802,7 @@
       <c r="O559" s="4"/>
       <c r="P559" s="4"/>
     </row>
-    <row r="560" spans="1:16" ht="13.2">
+    <row r="560" spans="1:16" ht="12.75">
       <c r="A560" s="4"/>
       <c r="B560" s="2"/>
       <c r="C560" s="4"/>
@@ -13805,7 +13816,7 @@
       <c r="O560" s="4"/>
       <c r="P560" s="4"/>
     </row>
-    <row r="561" spans="1:16" ht="13.2">
+    <row r="561" spans="1:16" ht="12.75">
       <c r="A561" s="4"/>
       <c r="B561" s="2"/>
       <c r="C561" s="4"/>
@@ -13819,7 +13830,7 @@
       <c r="O561" s="4"/>
       <c r="P561" s="4"/>
     </row>
-    <row r="562" spans="1:16" ht="13.2">
+    <row r="562" spans="1:16" ht="12.75">
       <c r="A562" s="4"/>
       <c r="B562" s="2"/>
       <c r="C562" s="4"/>
@@ -13833,7 +13844,7 @@
       <c r="O562" s="4"/>
       <c r="P562" s="4"/>
     </row>
-    <row r="563" spans="1:16" ht="13.2">
+    <row r="563" spans="1:16" ht="12.75">
       <c r="A563" s="4"/>
       <c r="B563" s="2"/>
       <c r="C563" s="4"/>
@@ -13847,7 +13858,7 @@
       <c r="O563" s="4"/>
       <c r="P563" s="4"/>
     </row>
-    <row r="564" spans="1:16" ht="13.2">
+    <row r="564" spans="1:16" ht="12.75">
       <c r="A564" s="4"/>
       <c r="B564" s="2"/>
       <c r="C564" s="4"/>
@@ -13861,7 +13872,7 @@
       <c r="O564" s="4"/>
       <c r="P564" s="4"/>
     </row>
-    <row r="565" spans="1:16" ht="13.2">
+    <row r="565" spans="1:16" ht="12.75">
       <c r="A565" s="4"/>
       <c r="B565" s="2"/>
       <c r="C565" s="4"/>
@@ -13875,7 +13886,7 @@
       <c r="O565" s="4"/>
       <c r="P565" s="4"/>
     </row>
-    <row r="566" spans="1:16" ht="13.2">
+    <row r="566" spans="1:16" ht="12.75">
       <c r="A566" s="4"/>
       <c r="B566" s="2"/>
       <c r="C566" s="4"/>
@@ -13889,7 +13900,7 @@
       <c r="O566" s="4"/>
       <c r="P566" s="4"/>
     </row>
-    <row r="567" spans="1:16" ht="13.2">
+    <row r="567" spans="1:16" ht="12.75">
       <c r="A567" s="4"/>
       <c r="B567" s="2"/>
       <c r="C567" s="4"/>
@@ -13903,7 +13914,7 @@
       <c r="O567" s="4"/>
       <c r="P567" s="4"/>
     </row>
-    <row r="568" spans="1:16" ht="13.2">
+    <row r="568" spans="1:16" ht="12.75">
       <c r="A568" s="4"/>
       <c r="B568" s="2"/>
       <c r="C568" s="4"/>
@@ -13917,7 +13928,7 @@
       <c r="O568" s="4"/>
       <c r="P568" s="4"/>
     </row>
-    <row r="569" spans="1:16" ht="13.2">
+    <row r="569" spans="1:16" ht="12.75">
       <c r="A569" s="4"/>
       <c r="B569" s="2"/>
       <c r="C569" s="4"/>
@@ -13931,7 +13942,7 @@
       <c r="O569" s="4"/>
       <c r="P569" s="4"/>
     </row>
-    <row r="570" spans="1:16" ht="13.2">
+    <row r="570" spans="1:16" ht="12.75">
       <c r="A570" s="4"/>
       <c r="B570" s="2"/>
       <c r="C570" s="4"/>
@@ -13945,7 +13956,7 @@
       <c r="O570" s="4"/>
       <c r="P570" s="4"/>
     </row>
-    <row r="571" spans="1:16" ht="13.2">
+    <row r="571" spans="1:16" ht="12.75">
       <c r="A571" s="4"/>
       <c r="B571" s="2"/>
       <c r="C571" s="4"/>
@@ -13959,7 +13970,7 @@
       <c r="O571" s="4"/>
       <c r="P571" s="4"/>
     </row>
-    <row r="572" spans="1:16" ht="13.2">
+    <row r="572" spans="1:16" ht="12.75">
       <c r="A572" s="4"/>
       <c r="B572" s="2"/>
       <c r="C572" s="4"/>
@@ -13973,7 +13984,7 @@
       <c r="O572" s="4"/>
       <c r="P572" s="4"/>
     </row>
-    <row r="573" spans="1:16" ht="13.2">
+    <row r="573" spans="1:16" ht="12.75">
       <c r="A573" s="4"/>
       <c r="B573" s="2"/>
       <c r="C573" s="4"/>
@@ -13987,7 +13998,7 @@
       <c r="O573" s="4"/>
       <c r="P573" s="4"/>
     </row>
-    <row r="574" spans="1:16" ht="13.2">
+    <row r="574" spans="1:16" ht="12.75">
       <c r="A574" s="4"/>
       <c r="B574" s="2"/>
       <c r="C574" s="4"/>
@@ -14001,7 +14012,7 @@
       <c r="O574" s="4"/>
       <c r="P574" s="4"/>
     </row>
-    <row r="575" spans="1:16" ht="13.2">
+    <row r="575" spans="1:16" ht="12.75">
       <c r="A575" s="4"/>
       <c r="B575" s="2"/>
       <c r="C575" s="4"/>
@@ -14015,7 +14026,7 @@
       <c r="O575" s="4"/>
       <c r="P575" s="4"/>
     </row>
-    <row r="576" spans="1:16" ht="13.2">
+    <row r="576" spans="1:16" ht="12.75">
       <c r="A576" s="4"/>
       <c r="B576" s="2"/>
       <c r="C576" s="4"/>
@@ -14029,7 +14040,7 @@
       <c r="O576" s="4"/>
       <c r="P576" s="4"/>
     </row>
-    <row r="577" spans="1:16" ht="13.2">
+    <row r="577" spans="1:16" ht="12.75">
       <c r="A577" s="4"/>
       <c r="B577" s="2"/>
       <c r="C577" s="4"/>
@@ -14043,7 +14054,7 @@
       <c r="O577" s="4"/>
       <c r="P577" s="4"/>
     </row>
-    <row r="578" spans="1:16" ht="13.2">
+    <row r="578" spans="1:16" ht="12.75">
       <c r="A578" s="4"/>
       <c r="B578" s="2"/>
       <c r="C578" s="4"/>
@@ -14057,7 +14068,7 @@
       <c r="O578" s="4"/>
       <c r="P578" s="4"/>
     </row>
-    <row r="579" spans="1:16" ht="13.2">
+    <row r="579" spans="1:16" ht="12.75">
       <c r="A579" s="4"/>
       <c r="B579" s="2"/>
       <c r="C579" s="4"/>
@@ -14071,7 +14082,7 @@
       <c r="O579" s="4"/>
       <c r="P579" s="4"/>
     </row>
-    <row r="580" spans="1:16" ht="13.2">
+    <row r="580" spans="1:16" ht="12.75">
       <c r="A580" s="4"/>
       <c r="B580" s="2"/>
       <c r="C580" s="4"/>
@@ -14085,7 +14096,7 @@
       <c r="O580" s="4"/>
       <c r="P580" s="4"/>
     </row>
-    <row r="581" spans="1:16" ht="13.2">
+    <row r="581" spans="1:16" ht="12.75">
       <c r="A581" s="4"/>
       <c r="B581" s="2"/>
       <c r="C581" s="4"/>
@@ -14099,7 +14110,7 @@
       <c r="O581" s="4"/>
       <c r="P581" s="4"/>
     </row>
-    <row r="582" spans="1:16" ht="13.2">
+    <row r="582" spans="1:16" ht="12.75">
       <c r="A582" s="4"/>
       <c r="B582" s="2"/>
       <c r="C582" s="4"/>
@@ -14113,7 +14124,7 @@
       <c r="O582" s="4"/>
       <c r="P582" s="4"/>
     </row>
-    <row r="583" spans="1:16" ht="13.2">
+    <row r="583" spans="1:16" ht="12.75">
       <c r="A583" s="4"/>
       <c r="B583" s="2"/>
       <c r="C583" s="4"/>
@@ -14127,7 +14138,7 @@
       <c r="O583" s="4"/>
       <c r="P583" s="4"/>
     </row>
-    <row r="584" spans="1:16" ht="13.2">
+    <row r="584" spans="1:16" ht="12.75">
       <c r="A584" s="4"/>
       <c r="B584" s="2"/>
       <c r="C584" s="4"/>
@@ -14141,7 +14152,7 @@
       <c r="O584" s="4"/>
       <c r="P584" s="4"/>
     </row>
-    <row r="585" spans="1:16" ht="13.2">
+    <row r="585" spans="1:16" ht="12.75">
       <c r="A585" s="4"/>
       <c r="B585" s="2"/>
       <c r="C585" s="4"/>
@@ -14155,7 +14166,7 @@
       <c r="O585" s="4"/>
       <c r="P585" s="4"/>
     </row>
-    <row r="586" spans="1:16" ht="13.2">
+    <row r="586" spans="1:16" ht="12.75">
       <c r="A586" s="4"/>
       <c r="B586" s="2"/>
       <c r="C586" s="4"/>
@@ -14169,7 +14180,7 @@
       <c r="O586" s="4"/>
       <c r="P586" s="4"/>
     </row>
-    <row r="587" spans="1:16" ht="13.2">
+    <row r="587" spans="1:16" ht="12.75">
       <c r="A587" s="4"/>
       <c r="B587" s="2"/>
       <c r="C587" s="4"/>
@@ -14183,7 +14194,7 @@
       <c r="O587" s="4"/>
       <c r="P587" s="4"/>
     </row>
-    <row r="588" spans="1:16" ht="13.2">
+    <row r="588" spans="1:16" ht="12.75">
       <c r="A588" s="4"/>
       <c r="B588" s="2"/>
       <c r="C588" s="4"/>
@@ -14197,7 +14208,7 @@
       <c r="O588" s="4"/>
       <c r="P588" s="4"/>
     </row>
-    <row r="589" spans="1:16" ht="13.2">
+    <row r="589" spans="1:16" ht="12.75">
       <c r="A589" s="4"/>
       <c r="B589" s="2"/>
       <c r="C589" s="4"/>
@@ -14211,7 +14222,7 @@
       <c r="O589" s="4"/>
       <c r="P589" s="4"/>
     </row>
-    <row r="590" spans="1:16" ht="13.2">
+    <row r="590" spans="1:16" ht="12.75">
       <c r="A590" s="4"/>
       <c r="B590" s="2"/>
       <c r="C590" s="4"/>
@@ -14225,7 +14236,7 @@
       <c r="O590" s="4"/>
       <c r="P590" s="4"/>
     </row>
-    <row r="591" spans="1:16" ht="13.2">
+    <row r="591" spans="1:16" ht="12.75">
       <c r="A591" s="4"/>
       <c r="B591" s="2"/>
       <c r="C591" s="4"/>
@@ -14239,7 +14250,7 @@
       <c r="O591" s="4"/>
       <c r="P591" s="4"/>
     </row>
-    <row r="592" spans="1:16" ht="13.2">
+    <row r="592" spans="1:16" ht="12.75">
       <c r="A592" s="4"/>
       <c r="B592" s="2"/>
       <c r="C592" s="4"/>
@@ -14253,7 +14264,7 @@
       <c r="O592" s="4"/>
       <c r="P592" s="4"/>
     </row>
-    <row r="593" spans="1:16" ht="13.2">
+    <row r="593" spans="1:16" ht="12.75">
       <c r="A593" s="4"/>
       <c r="B593" s="2"/>
       <c r="C593" s="4"/>
@@ -14267,7 +14278,7 @@
       <c r="O593" s="4"/>
       <c r="P593" s="4"/>
     </row>
-    <row r="594" spans="1:16" ht="13.2">
+    <row r="594" spans="1:16" ht="12.75">
       <c r="A594" s="4"/>
       <c r="B594" s="2"/>
       <c r="C594" s="4"/>
@@ -14281,7 +14292,7 @@
       <c r="O594" s="4"/>
       <c r="P594" s="4"/>
     </row>
-    <row r="595" spans="1:16" ht="13.2">
+    <row r="595" spans="1:16" ht="12.75">
       <c r="A595" s="4"/>
       <c r="B595" s="2"/>
       <c r="C595" s="4"/>
@@ -14295,7 +14306,7 @@
       <c r="O595" s="4"/>
       <c r="P595" s="4"/>
     </row>
-    <row r="596" spans="1:16" ht="13.2">
+    <row r="596" spans="1:16" ht="12.75">
       <c r="A596" s="4"/>
       <c r="B596" s="2"/>
       <c r="C596" s="4"/>
@@ -14309,7 +14320,7 @@
       <c r="O596" s="4"/>
       <c r="P596" s="4"/>
     </row>
-    <row r="597" spans="1:16" ht="13.2">
+    <row r="597" spans="1:16" ht="12.75">
       <c r="A597" s="4"/>
       <c r="B597" s="2"/>
       <c r="C597" s="4"/>
@@ -14323,7 +14334,7 @@
       <c r="O597" s="4"/>
       <c r="P597" s="4"/>
     </row>
-    <row r="598" spans="1:16" ht="13.2">
+    <row r="598" spans="1:16" ht="12.75">
       <c r="A598" s="4"/>
       <c r="B598" s="2"/>
       <c r="C598" s="4"/>
@@ -14337,7 +14348,7 @@
       <c r="O598" s="4"/>
       <c r="P598" s="4"/>
     </row>
-    <row r="599" spans="1:16" ht="13.2">
+    <row r="599" spans="1:16" ht="12.75">
       <c r="A599" s="4"/>
       <c r="B599" s="2"/>
       <c r="C599" s="4"/>
@@ -14351,7 +14362,7 @@
       <c r="O599" s="4"/>
       <c r="P599" s="4"/>
     </row>
-    <row r="600" spans="1:16" ht="13.2">
+    <row r="600" spans="1:16" ht="12.75">
       <c r="A600" s="4"/>
       <c r="B600" s="2"/>
       <c r="C600" s="4"/>
@@ -14365,7 +14376,7 @@
       <c r="O600" s="4"/>
       <c r="P600" s="4"/>
     </row>
-    <row r="601" spans="1:16" ht="13.2">
+    <row r="601" spans="1:16" ht="12.75">
       <c r="A601" s="4"/>
       <c r="B601" s="2"/>
       <c r="C601" s="4"/>
@@ -14379,7 +14390,7 @@
       <c r="O601" s="4"/>
       <c r="P601" s="4"/>
     </row>
-    <row r="602" spans="1:16" ht="13.2">
+    <row r="602" spans="1:16" ht="12.75">
       <c r="A602" s="4"/>
       <c r="B602" s="2"/>
       <c r="C602" s="4"/>
@@ -14393,7 +14404,7 @@
       <c r="O602" s="4"/>
       <c r="P602" s="4"/>
     </row>
-    <row r="603" spans="1:16" ht="13.2">
+    <row r="603" spans="1:16" ht="12.75">
       <c r="A603" s="4"/>
       <c r="B603" s="2"/>
       <c r="C603" s="4"/>
@@ -14407,7 +14418,7 @@
       <c r="O603" s="4"/>
       <c r="P603" s="4"/>
     </row>
-    <row r="604" spans="1:16" ht="13.2">
+    <row r="604" spans="1:16" ht="12.75">
       <c r="A604" s="4"/>
       <c r="B604" s="2"/>
       <c r="C604" s="4"/>
@@ -14421,7 +14432,7 @@
       <c r="O604" s="4"/>
       <c r="P604" s="4"/>
     </row>
-    <row r="605" spans="1:16" ht="13.2">
+    <row r="605" spans="1:16" ht="12.75">
       <c r="A605" s="4"/>
       <c r="B605" s="2"/>
       <c r="C605" s="4"/>
@@ -14435,7 +14446,7 @@
       <c r="O605" s="4"/>
       <c r="P605" s="4"/>
     </row>
-    <row r="606" spans="1:16" ht="13.2">
+    <row r="606" spans="1:16" ht="12.75">
       <c r="A606" s="4"/>
       <c r="B606" s="2"/>
       <c r="C606" s="4"/>
@@ -14449,7 +14460,7 @@
       <c r="O606" s="4"/>
       <c r="P606" s="4"/>
     </row>
-    <row r="607" spans="1:16" ht="13.2">
+    <row r="607" spans="1:16" ht="12.75">
       <c r="A607" s="4"/>
       <c r="B607" s="2"/>
       <c r="C607" s="4"/>
@@ -14463,7 +14474,7 @@
       <c r="O607" s="4"/>
       <c r="P607" s="4"/>
     </row>
-    <row r="608" spans="1:16" ht="13.2">
+    <row r="608" spans="1:16" ht="12.75">
       <c r="A608" s="4"/>
       <c r="B608" s="2"/>
       <c r="C608" s="4"/>
@@ -14477,7 +14488,7 @@
       <c r="O608" s="4"/>
       <c r="P608" s="4"/>
     </row>
-    <row r="609" spans="1:16" ht="13.2">
+    <row r="609" spans="1:16" ht="12.75">
       <c r="A609" s="4"/>
       <c r="B609" s="2"/>
       <c r="C609" s="4"/>
@@ -14491,7 +14502,7 @@
       <c r="O609" s="4"/>
       <c r="P609" s="4"/>
     </row>
-    <row r="610" spans="1:16" ht="13.2">
+    <row r="610" spans="1:16" ht="12.75">
       <c r="A610" s="4"/>
       <c r="B610" s="2"/>
       <c r="C610" s="4"/>
@@ -14505,7 +14516,7 @@
       <c r="O610" s="4"/>
       <c r="P610" s="4"/>
     </row>
-    <row r="611" spans="1:16" ht="13.2">
+    <row r="611" spans="1:16" ht="12.75">
       <c r="A611" s="4"/>
       <c r="B611" s="2"/>
       <c r="C611" s="4"/>
@@ -14519,7 +14530,7 @@
       <c r="O611" s="4"/>
       <c r="P611" s="4"/>
     </row>
-    <row r="612" spans="1:16" ht="13.2">
+    <row r="612" spans="1:16" ht="12.75">
       <c r="A612" s="4"/>
       <c r="B612" s="2"/>
       <c r="C612" s="4"/>
@@ -14533,7 +14544,7 @@
       <c r="O612" s="4"/>
       <c r="P612" s="4"/>
     </row>
-    <row r="613" spans="1:16" ht="13.2">
+    <row r="613" spans="1:16" ht="12.75">
       <c r="A613" s="4"/>
       <c r="B613" s="2"/>
       <c r="C613" s="4"/>
@@ -14547,7 +14558,7 @@
       <c r="O613" s="4"/>
       <c r="P613" s="4"/>
     </row>
-    <row r="614" spans="1:16" ht="13.2">
+    <row r="614" spans="1:16" ht="12.75">
       <c r="A614" s="4"/>
       <c r="B614" s="2"/>
       <c r="C614" s="4"/>
@@ -14561,7 +14572,7 @@
       <c r="O614" s="4"/>
       <c r="P614" s="4"/>
     </row>
-    <row r="615" spans="1:16" ht="13.2">
+    <row r="615" spans="1:16" ht="12.75">
       <c r="A615" s="4"/>
       <c r="B615" s="2"/>
       <c r="C615" s="4"/>
@@ -14575,7 +14586,7 @@
       <c r="O615" s="4"/>
       <c r="P615" s="4"/>
     </row>
-    <row r="616" spans="1:16" ht="13.2">
+    <row r="616" spans="1:16" ht="12.75">
       <c r="A616" s="4"/>
       <c r="B616" s="2"/>
       <c r="C616" s="4"/>
@@ -14589,7 +14600,7 @@
       <c r="O616" s="4"/>
       <c r="P616" s="4"/>
     </row>
-    <row r="617" spans="1:16" ht="13.2">
+    <row r="617" spans="1:16" ht="12.75">
       <c r="A617" s="4"/>
       <c r="B617" s="2"/>
       <c r="C617" s="4"/>
@@ -14603,7 +14614,7 @@
       <c r="O617" s="4"/>
       <c r="P617" s="4"/>
     </row>
-    <row r="618" spans="1:16" ht="13.2">
+    <row r="618" spans="1:16" ht="12.75">
       <c r="A618" s="4"/>
       <c r="B618" s="2"/>
       <c r="C618" s="4"/>
@@ -14617,7 +14628,7 @@
       <c r="O618" s="4"/>
       <c r="P618" s="4"/>
     </row>
-    <row r="619" spans="1:16" ht="13.2">
+    <row r="619" spans="1:16" ht="12.75">
       <c r="A619" s="4"/>
       <c r="B619" s="2"/>
       <c r="C619" s="4"/>
@@ -14631,7 +14642,7 @@
       <c r="O619" s="4"/>
       <c r="P619" s="4"/>
     </row>
-    <row r="620" spans="1:16" ht="13.2">
+    <row r="620" spans="1:16" ht="12.75">
       <c r="A620" s="4"/>
       <c r="B620" s="2"/>
       <c r="C620" s="4"/>
@@ -14645,7 +14656,7 @@
       <c r="O620" s="4"/>
       <c r="P620" s="4"/>
     </row>
-    <row r="621" spans="1:16" ht="13.2">
+    <row r="621" spans="1:16" ht="12.75">
       <c r="A621" s="4"/>
       <c r="B621" s="2"/>
       <c r="C621" s="4"/>
@@ -14659,7 +14670,7 @@
       <c r="O621" s="4"/>
       <c r="P621" s="4"/>
     </row>
-    <row r="622" spans="1:16" ht="13.2">
+    <row r="622" spans="1:16" ht="12.75">
       <c r="A622" s="4"/>
       <c r="B622" s="2"/>
       <c r="C622" s="4"/>
@@ -14673,7 +14684,7 @@
       <c r="O622" s="4"/>
       <c r="P622" s="4"/>
     </row>
-    <row r="623" spans="1:16" ht="13.2">
+    <row r="623" spans="1:16" ht="12.75">
       <c r="A623" s="4"/>
       <c r="B623" s="2"/>
       <c r="C623" s="4"/>
@@ -14687,7 +14698,7 @@
       <c r="O623" s="4"/>
       <c r="P623" s="4"/>
     </row>
-    <row r="624" spans="1:16" ht="13.2">
+    <row r="624" spans="1:16" ht="12.75">
       <c r="A624" s="4"/>
       <c r="B624" s="2"/>
       <c r="C624" s="4"/>
@@ -14701,7 +14712,7 @@
       <c r="O624" s="4"/>
       <c r="P624" s="4"/>
     </row>
-    <row r="625" spans="1:16" ht="13.2">
+    <row r="625" spans="1:16" ht="12.75">
       <c r="A625" s="4"/>
       <c r="B625" s="2"/>
       <c r="C625" s="4"/>
@@ -14715,7 +14726,7 @@
       <c r="O625" s="4"/>
       <c r="P625" s="4"/>
     </row>
-    <row r="626" spans="1:16" ht="13.2">
+    <row r="626" spans="1:16" ht="12.75">
       <c r="A626" s="4"/>
       <c r="B626" s="2"/>
       <c r="C626" s="4"/>
@@ -14729,7 +14740,7 @@
       <c r="O626" s="4"/>
       <c r="P626" s="4"/>
     </row>
-    <row r="627" spans="1:16" ht="13.2">
+    <row r="627" spans="1:16" ht="12.75">
       <c r="A627" s="4"/>
       <c r="B627" s="2"/>
       <c r="C627" s="4"/>
@@ -14743,7 +14754,7 @@
       <c r="O627" s="4"/>
       <c r="P627" s="4"/>
     </row>
-    <row r="628" spans="1:16" ht="13.2">
+    <row r="628" spans="1:16" ht="12.75">
       <c r="A628" s="4"/>
       <c r="B628" s="2"/>
       <c r="C628" s="4"/>
@@ -14757,7 +14768,7 @@
       <c r="O628" s="4"/>
       <c r="P628" s="4"/>
     </row>
-    <row r="629" spans="1:16" ht="13.2">
+    <row r="629" spans="1:16" ht="12.75">
       <c r="A629" s="4"/>
       <c r="B629" s="2"/>
       <c r="C629" s="4"/>
@@ -14771,7 +14782,7 @@
       <c r="O629" s="4"/>
       <c r="P629" s="4"/>
     </row>
-    <row r="630" spans="1:16" ht="13.2">
+    <row r="630" spans="1:16" ht="12.75">
       <c r="A630" s="4"/>
       <c r="B630" s="2"/>
       <c r="C630" s="4"/>
@@ -14785,7 +14796,7 @@
       <c r="O630" s="4"/>
       <c r="P630" s="4"/>
     </row>
-    <row r="631" spans="1:16" ht="13.2">
+    <row r="631" spans="1:16" ht="12.75">
       <c r="A631" s="4"/>
       <c r="B631" s="2"/>
       <c r="C631" s="4"/>
@@ -14799,7 +14810,7 @@
       <c r="O631" s="4"/>
       <c r="P631" s="4"/>
     </row>
-    <row r="632" spans="1:16" ht="13.2">
+    <row r="632" spans="1:16" ht="12.75">
       <c r="A632" s="4"/>
       <c r="B632" s="2"/>
       <c r="C632" s="4"/>
@@ -14813,7 +14824,7 @@
       <c r="O632" s="4"/>
       <c r="P632" s="4"/>
     </row>
-    <row r="633" spans="1:16" ht="13.2">
+    <row r="633" spans="1:16" ht="12.75">
       <c r="A633" s="4"/>
       <c r="B633" s="2"/>
       <c r="C633" s="4"/>
@@ -14827,7 +14838,7 @@
       <c r="O633" s="4"/>
       <c r="P633" s="4"/>
     </row>
-    <row r="634" spans="1:16" ht="13.2">
+    <row r="634" spans="1:16" ht="12.75">
       <c r="A634" s="4"/>
       <c r="B634" s="2"/>
       <c r="C634" s="4"/>
@@ -14841,7 +14852,7 @@
       <c r="O634" s="4"/>
       <c r="P634" s="4"/>
     </row>
-    <row r="635" spans="1:16" ht="13.2">
+    <row r="635" spans="1:16" ht="12.75">
       <c r="A635" s="4"/>
       <c r="B635" s="2"/>
       <c r="C635" s="4"/>
@@ -14855,7 +14866,7 @@
       <c r="O635" s="4"/>
       <c r="P635" s="4"/>
     </row>
-    <row r="636" spans="1:16" ht="13.2">
+    <row r="636" spans="1:16" ht="12.75">
       <c r="A636" s="4"/>
       <c r="B636" s="2"/>
       <c r="C636" s="4"/>
@@ -14869,7 +14880,7 @@
       <c r="O636" s="4"/>
       <c r="P636" s="4"/>
     </row>
-    <row r="637" spans="1:16" ht="13.2">
+    <row r="637" spans="1:16" ht="12.75">
       <c r="A637" s="4"/>
       <c r="B637" s="2"/>
       <c r="C637" s="4"/>
@@ -14883,7 +14894,7 @@
       <c r="O637" s="4"/>
       <c r="P637" s="4"/>
     </row>
-    <row r="638" spans="1:16" ht="13.2">
+    <row r="638" spans="1:16" ht="12.75">
       <c r="A638" s="4"/>
       <c r="B638" s="2"/>
       <c r="C638" s="4"/>
@@ -14897,7 +14908,7 @@
       <c r="O638" s="4"/>
       <c r="P638" s="4"/>
     </row>
-    <row r="639" spans="1:16" ht="13.2">
+    <row r="639" spans="1:16" ht="12.75">
       <c r="A639" s="4"/>
       <c r="B639" s="2"/>
       <c r="C639" s="4"/>
@@ -14911,7 +14922,7 @@
       <c r="O639" s="4"/>
       <c r="P639" s="4"/>
     </row>
-    <row r="640" spans="1:16" ht="13.2">
+    <row r="640" spans="1:16" ht="12.75">
       <c r="A640" s="4"/>
       <c r="B640" s="2"/>
       <c r="C640" s="4"/>
@@ -14925,7 +14936,7 @@
       <c r="O640" s="4"/>
       <c r="P640" s="4"/>
     </row>
-    <row r="641" spans="1:16" ht="13.2">
+    <row r="641" spans="1:16" ht="12.75">
       <c r="A641" s="4"/>
       <c r="B641" s="2"/>
       <c r="C641" s="4"/>
@@ -14939,7 +14950,7 @@
       <c r="O641" s="4"/>
       <c r="P641" s="4"/>
     </row>
-    <row r="642" spans="1:16" ht="13.2">
+    <row r="642" spans="1:16" ht="12.75">
       <c r="A642" s="4"/>
       <c r="B642" s="2"/>
       <c r="C642" s="4"/>
@@ -14953,7 +14964,7 @@
       <c r="O642" s="4"/>
       <c r="P642" s="4"/>
     </row>
-    <row r="643" spans="1:16" ht="13.2">
+    <row r="643" spans="1:16" ht="12.75">
       <c r="A643" s="4"/>
       <c r="B643" s="2"/>
       <c r="C643" s="4"/>
@@ -14967,7 +14978,7 @@
       <c r="O643" s="4"/>
       <c r="P643" s="4"/>
     </row>
-    <row r="644" spans="1:16" ht="13.2">
+    <row r="644" spans="1:16" ht="12.75">
       <c r="A644" s="4"/>
       <c r="B644" s="2"/>
       <c r="C644" s="4"/>
@@ -14981,7 +14992,7 @@
       <c r="O644" s="4"/>
       <c r="P644" s="4"/>
     </row>
-    <row r="645" spans="1:16" ht="13.2">
+    <row r="645" spans="1:16" ht="12.75">
       <c r="A645" s="4"/>
       <c r="B645" s="2"/>
       <c r="C645" s="4"/>
@@ -14995,7 +15006,7 @@
       <c r="O645" s="4"/>
       <c r="P645" s="4"/>
     </row>
-    <row r="646" spans="1:16" ht="13.2">
+    <row r="646" spans="1:16" ht="12.75">
       <c r="A646" s="4"/>
       <c r="B646" s="2"/>
       <c r="C646" s="4"/>
@@ -15009,7 +15020,7 @@
       <c r="O646" s="4"/>
       <c r="P646" s="4"/>
     </row>
-    <row r="647" spans="1:16" ht="13.2">
+    <row r="647" spans="1:16" ht="12.75">
       <c r="A647" s="4"/>
       <c r="B647" s="2"/>
       <c r="C647" s="4"/>
@@ -15023,7 +15034,7 @@
       <c r="O647" s="4"/>
       <c r="P647" s="4"/>
     </row>
-    <row r="648" spans="1:16" ht="13.2">
+    <row r="648" spans="1:16" ht="12.75">
       <c r="A648" s="4"/>
       <c r="B648" s="2"/>
       <c r="C648" s="4"/>
@@ -15037,7 +15048,7 @@
       <c r="O648" s="4"/>
       <c r="P648" s="4"/>
     </row>
-    <row r="649" spans="1:16" ht="13.2">
+    <row r="649" spans="1:16" ht="12.75">
       <c r="A649" s="4"/>
       <c r="B649" s="2"/>
       <c r="C649" s="4"/>
@@ -15051,7 +15062,7 @@
       <c r="O649" s="4"/>
       <c r="P649" s="4"/>
     </row>
-    <row r="650" spans="1:16" ht="13.2">
+    <row r="650" spans="1:16" ht="12.75">
       <c r="A650" s="4"/>
       <c r="B650" s="2"/>
       <c r="C650" s="4"/>
@@ -15065,7 +15076,7 @@
       <c r="O650" s="4"/>
       <c r="P650" s="4"/>
     </row>
-    <row r="651" spans="1:16" ht="13.2">
+    <row r="651" spans="1:16" ht="12.75">
       <c r="A651" s="4"/>
       <c r="B651" s="2"/>
       <c r="C651" s="4"/>
@@ -15079,7 +15090,7 @@
       <c r="O651" s="4"/>
       <c r="P651" s="4"/>
     </row>
-    <row r="652" spans="1:16" ht="13.2">
+    <row r="652" spans="1:16" ht="12.75">
       <c r="A652" s="4"/>
       <c r="B652" s="2"/>
       <c r="C652" s="4"/>
@@ -15093,7 +15104,7 @@
       <c r="O652" s="4"/>
       <c r="P652" s="4"/>
     </row>
-    <row r="653" spans="1:16" ht="13.2">
+    <row r="653" spans="1:16" ht="12.75">
       <c r="A653" s="4"/>
       <c r="B653" s="2"/>
       <c r="C653" s="4"/>
@@ -15107,7 +15118,7 @@
       <c r="O653" s="4"/>
       <c r="P653" s="4"/>
     </row>
-    <row r="654" spans="1:16" ht="13.2">
+    <row r="654" spans="1:16" ht="12.75">
       <c r="A654" s="4"/>
       <c r="B654" s="2"/>
       <c r="C654" s="4"/>
@@ -15121,7 +15132,7 @@
       <c r="O654" s="4"/>
       <c r="P654" s="4"/>
     </row>
-    <row r="655" spans="1:16" ht="13.2">
+    <row r="655" spans="1:16" ht="12.75">
       <c r="A655" s="4"/>
       <c r="B655" s="2"/>
       <c r="C655" s="4"/>
@@ -15135,7 +15146,7 @@
       <c r="O655" s="4"/>
       <c r="P655" s="4"/>
     </row>
-    <row r="656" spans="1:16" ht="13.2">
+    <row r="656" spans="1:16" ht="12.75">
       <c r="A656" s="4"/>
       <c r="B656" s="2"/>
       <c r="C656" s="4"/>
@@ -15149,7 +15160,7 @@
       <c r="O656" s="4"/>
       <c r="P656" s="4"/>
     </row>
-    <row r="657" spans="1:16" ht="13.2">
+    <row r="657" spans="1:16" ht="12.75">
       <c r="A657" s="4"/>
       <c r="B657" s="2"/>
       <c r="C657" s="4"/>
@@ -15163,7 +15174,7 @@
       <c r="O657" s="4"/>
       <c r="P657" s="4"/>
     </row>
-    <row r="658" spans="1:16" ht="13.2">
+    <row r="658" spans="1:16" ht="12.75">
       <c r="A658" s="4"/>
       <c r="B658" s="2"/>
       <c r="C658" s="4"/>
@@ -15177,7 +15188,7 @@
       <c r="O658" s="4"/>
       <c r="P658" s="4"/>
     </row>
-    <row r="659" spans="1:16" ht="13.2">
+    <row r="659" spans="1:16" ht="12.75">
       <c r="A659" s="4"/>
       <c r="B659" s="2"/>
       <c r="C659" s="4"/>
@@ -15191,7 +15202,7 @@
       <c r="O659" s="4"/>
       <c r="P659" s="4"/>
     </row>
-    <row r="660" spans="1:16" ht="13.2">
+    <row r="660" spans="1:16" ht="12.75">
       <c r="A660" s="4"/>
       <c r="B660" s="2"/>
       <c r="C660" s="4"/>
@@ -15205,7 +15216,7 @@
       <c r="O660" s="4"/>
       <c r="P660" s="4"/>
     </row>
-    <row r="661" spans="1:16" ht="13.2">
+    <row r="661" spans="1:16" ht="12.75">
       <c r="A661" s="4"/>
       <c r="B661" s="2"/>
       <c r="C661" s="4"/>
@@ -15219,7 +15230,7 @@
       <c r="O661" s="4"/>
       <c r="P661" s="4"/>
     </row>
-    <row r="662" spans="1:16" ht="13.2">
+    <row r="662" spans="1:16" ht="12.75">
       <c r="A662" s="4"/>
       <c r="B662" s="2"/>
       <c r="C662" s="4"/>
@@ -15233,7 +15244,7 @@
       <c r="O662" s="4"/>
       <c r="P662" s="4"/>
     </row>
-    <row r="663" spans="1:16" ht="13.2">
+    <row r="663" spans="1:16" ht="12.75">
       <c r="A663" s="4"/>
       <c r="B663" s="2"/>
       <c r="C663" s="4"/>
@@ -15247,7 +15258,7 @@
       <c r="O663" s="4"/>
       <c r="P663" s="4"/>
     </row>
-    <row r="664" spans="1:16" ht="13.2">
+    <row r="664" spans="1:16" ht="12.75">
       <c r="A664" s="4"/>
       <c r="B664" s="2"/>
       <c r="C664" s="4"/>
@@ -15261,7 +15272,7 @@
       <c r="O664" s="4"/>
       <c r="P664" s="4"/>
     </row>
-    <row r="665" spans="1:16" ht="13.2">
+    <row r="665" spans="1:16" ht="12.75">
       <c r="A665" s="4"/>
       <c r="B665" s="2"/>
       <c r="C665" s="4"/>
@@ -15275,7 +15286,7 @@
       <c r="O665" s="4"/>
       <c r="P665" s="4"/>
     </row>
-    <row r="666" spans="1:16" ht="13.2">
+    <row r="666" spans="1:16" ht="12.75">
       <c r="A666" s="4"/>
       <c r="B666" s="2"/>
       <c r="C666" s="4"/>
@@ -15289,7 +15300,7 @@
       <c r="O666" s="4"/>
       <c r="P666" s="4"/>
     </row>
-    <row r="667" spans="1:16" ht="13.2">
+    <row r="667" spans="1:16" ht="12.75">
       <c r="A667" s="4"/>
       <c r="B667" s="2"/>
       <c r="C667" s="4"/>
@@ -15303,7 +15314,7 @@
       <c r="O667" s="4"/>
       <c r="P667" s="4"/>
     </row>
-    <row r="668" spans="1:16" ht="13.2">
+    <row r="668" spans="1:16" ht="12.75">
       <c r="A668" s="4"/>
       <c r="B668" s="2"/>
       <c r="C668" s="4"/>
@@ -15317,7 +15328,7 @@
       <c r="O668" s="4"/>
       <c r="P668" s="4"/>
     </row>
-    <row r="669" spans="1:16" ht="13.2">
+    <row r="669" spans="1:16" ht="12.75">
       <c r="A669" s="4"/>
       <c r="B669" s="2"/>
       <c r="C669" s="4"/>
@@ -15331,7 +15342,7 @@
       <c r="O669" s="4"/>
       <c r="P669" s="4"/>
     </row>
-    <row r="670" spans="1:16" ht="13.2">
+    <row r="670" spans="1:16" ht="12.75">
       <c r="A670" s="4"/>
       <c r="B670" s="2"/>
       <c r="C670" s="4"/>
@@ -15345,7 +15356,7 @@
       <c r="O670" s="4"/>
       <c r="P670" s="4"/>
     </row>
-    <row r="671" spans="1:16" ht="13.2">
+    <row r="671" spans="1:16" ht="12.75">
       <c r="A671" s="4"/>
       <c r="B671" s="2"/>
       <c r="C671" s="4"/>
@@ -15359,7 +15370,7 @@
       <c r="O671" s="4"/>
       <c r="P671" s="4"/>
     </row>
-    <row r="672" spans="1:16" ht="13.2">
+    <row r="672" spans="1:16" ht="12.75">
       <c r="A672" s="4"/>
       <c r="B672" s="2"/>
       <c r="C672" s="4"/>
@@ -15373,7 +15384,7 @@
       <c r="O672" s="4"/>
       <c r="P672" s="4"/>
     </row>
-    <row r="673" spans="1:16" ht="13.2">
+    <row r="673" spans="1:16" ht="12.75">
       <c r="A673" s="4"/>
       <c r="B673" s="2"/>
       <c r="C673" s="4"/>
@@ -15387,7 +15398,7 @@
       <c r="O673" s="4"/>
       <c r="P673" s="4"/>
     </row>
-    <row r="674" spans="1:16" ht="13.2">
+    <row r="674" spans="1:16" ht="12.75">
       <c r="A674" s="4"/>
       <c r="B674" s="2"/>
       <c r="C674" s="4"/>
@@ -15401,7 +15412,7 @@
       <c r="O674" s="4"/>
       <c r="P674" s="4"/>
     </row>
-    <row r="675" spans="1:16" ht="13.2">
+    <row r="675" spans="1:16" ht="12.75">
       <c r="A675" s="4"/>
       <c r="B675" s="2"/>
       <c r="C675" s="4"/>
@@ -15415,7 +15426,7 @@
       <c r="O675" s="4"/>
       <c r="P675" s="4"/>
     </row>
-    <row r="676" spans="1:16" ht="13.2">
+    <row r="676" spans="1:16" ht="12.75">
       <c r="A676" s="4"/>
       <c r="B676" s="2"/>
       <c r="C676" s="4"/>
@@ -15429,7 +15440,7 @@
       <c r="O676" s="4"/>
       <c r="P676" s="4"/>
     </row>
-    <row r="677" spans="1:16" ht="13.2">
+    <row r="677" spans="1:16" ht="12.75">
       <c r="A677" s="4"/>
       <c r="B677" s="2"/>
       <c r="C677" s="4"/>
@@ -15443,7 +15454,7 @@
       <c r="O677" s="4"/>
       <c r="P677" s="4"/>
     </row>
-    <row r="678" spans="1:16" ht="13.2">
+    <row r="678" spans="1:16" ht="12.75">
       <c r="A678" s="4"/>
       <c r="B678" s="2"/>
       <c r="C678" s="4"/>
@@ -15457,7 +15468,7 @@
       <c r="O678" s="4"/>
       <c r="P678" s="4"/>
     </row>
-    <row r="679" spans="1:16" ht="13.2">
+    <row r="679" spans="1:16" ht="12.75">
       <c r="A679" s="4"/>
       <c r="B679" s="2"/>
       <c r="C679" s="4"/>
@@ -15471,7 +15482,7 @@
       <c r="O679" s="4"/>
       <c r="P679" s="4"/>
     </row>
-    <row r="680" spans="1:16" ht="13.2">
+    <row r="680" spans="1:16" ht="12.75">
       <c r="A680" s="4"/>
       <c r="B680" s="2"/>
       <c r="C680" s="4"/>
@@ -15485,7 +15496,7 @@
       <c r="O680" s="4"/>
       <c r="P680" s="4"/>
     </row>
-    <row r="681" spans="1:16" ht="13.2">
+    <row r="681" spans="1:16" ht="12.75">
       <c r="A681" s="4"/>
       <c r="B681" s="2"/>
       <c r="C681" s="4"/>
@@ -15499,7 +15510,7 @@
       <c r="O681" s="4"/>
       <c r="P681" s="4"/>
     </row>
-    <row r="682" spans="1:16" ht="13.2">
+    <row r="682" spans="1:16" ht="12.75">
       <c r="A682" s="4"/>
       <c r="B682" s="2"/>
       <c r="C682" s="4"/>
@@ -15513,7 +15524,7 @@
       <c r="O682" s="4"/>
       <c r="P682" s="4"/>
     </row>
-    <row r="683" spans="1:16" ht="13.2">
+    <row r="683" spans="1:16" ht="12.75">
       <c r="A683" s="4"/>
       <c r="B683" s="2"/>
       <c r="C683" s="4"/>
@@ -15527,7 +15538,7 @@
       <c r="O683" s="4"/>
       <c r="P683" s="4"/>
     </row>
-    <row r="684" spans="1:16" ht="13.2">
+    <row r="684" spans="1:16" ht="12.75">
       <c r="A684" s="4"/>
       <c r="B684" s="2"/>
       <c r="C684" s="4"/>
@@ -15541,7 +15552,7 @@
       <c r="O684" s="4"/>
       <c r="P684" s="4"/>
     </row>
-    <row r="685" spans="1:16" ht="13.2">
+    <row r="685" spans="1:16" ht="12.75">
       <c r="A685" s="4"/>
       <c r="B685" s="2"/>
       <c r="C685" s="4"/>
@@ -15555,7 +15566,7 @@
       <c r="O685" s="4"/>
       <c r="P685" s="4"/>
     </row>
-    <row r="686" spans="1:16" ht="13.2">
+    <row r="686" spans="1:16" ht="12.75">
       <c r="A686" s="4"/>
       <c r="B686" s="2"/>
       <c r="C686" s="4"/>
@@ -15569,7 +15580,7 @@
       <c r="O686" s="4"/>
       <c r="P686" s="4"/>
     </row>
-    <row r="687" spans="1:16" ht="13.2">
+    <row r="687" spans="1:16" ht="12.75">
       <c r="A687" s="4"/>
       <c r="B687" s="2"/>
       <c r="C687" s="4"/>
@@ -15583,7 +15594,7 @@
       <c r="O687" s="4"/>
       <c r="P687" s="4"/>
     </row>
-    <row r="688" spans="1:16" ht="13.2">
+    <row r="688" spans="1:16" ht="12.75">
       <c r="A688" s="4"/>
       <c r="B688" s="2"/>
       <c r="C688" s="4"/>
@@ -15597,7 +15608,7 @@
       <c r="O688" s="4"/>
       <c r="P688" s="4"/>
     </row>
-    <row r="689" spans="1:16" ht="13.2">
+    <row r="689" spans="1:16" ht="12.75">
       <c r="A689" s="4"/>
       <c r="B689" s="2"/>
       <c r="C689" s="4"/>
@@ -15611,7 +15622,7 @@
       <c r="O689" s="4"/>
       <c r="P689" s="4"/>
     </row>
-    <row r="690" spans="1:16" ht="13.2">
+    <row r="690" spans="1:16" ht="12.75">
       <c r="A690" s="4"/>
       <c r="B690" s="2"/>
       <c r="C690" s="4"/>
@@ -15625,7 +15636,7 @@
       <c r="O690" s="4"/>
       <c r="P690" s="4"/>
     </row>
-    <row r="691" spans="1:16" ht="13.2">
+    <row r="691" spans="1:16" ht="12.75">
       <c r="A691" s="4"/>
       <c r="B691" s="2"/>
       <c r="C691" s="4"/>
@@ -15639,7 +15650,7 @@
       <c r="O691" s="4"/>
       <c r="P691" s="4"/>
     </row>
-    <row r="692" spans="1:16" ht="13.2">
+    <row r="692" spans="1:16" ht="12.75">
       <c r="A692" s="4"/>
       <c r="B692" s="2"/>
       <c r="C692" s="4"/>
@@ -15653,7 +15664,7 @@
       <c r="O692" s="4"/>
       <c r="P692" s="4"/>
     </row>
-    <row r="693" spans="1:16" ht="13.2">
+    <row r="693" spans="1:16" ht="12.75">
       <c r="A693" s="4"/>
       <c r="B693" s="2"/>
       <c r="C693" s="4"/>
@@ -15667,7 +15678,7 @@
       <c r="O693" s="4"/>
       <c r="P693" s="4"/>
     </row>
-    <row r="694" spans="1:16" ht="13.2">
+    <row r="694" spans="1:16" ht="12.75">
       <c r="A694" s="4"/>
       <c r="B694" s="2"/>
       <c r="C694" s="4"/>
@@ -15681,7 +15692,7 @@
       <c r="O694" s="4"/>
       <c r="P694" s="4"/>
     </row>
-    <row r="695" spans="1:16" ht="13.2">
+    <row r="695" spans="1:16" ht="12.75">
       <c r="A695" s="4"/>
       <c r="B695" s="2"/>
       <c r="C695" s="4"/>
@@ -15695,7 +15706,7 @@
       <c r="O695" s="4"/>
       <c r="P695" s="4"/>
     </row>
-    <row r="696" spans="1:16" ht="13.2">
+    <row r="696" spans="1:16" ht="12.75">
       <c r="A696" s="4"/>
       <c r="B696" s="2"/>
       <c r="C696" s="4"/>
@@ -15709,7 +15720,7 @@
       <c r="O696" s="4"/>
       <c r="P696" s="4"/>
     </row>
-    <row r="697" spans="1:16" ht="13.2">
+    <row r="697" spans="1:16" ht="12.75">
       <c r="A697" s="4"/>
       <c r="B697" s="2"/>
       <c r="C697" s="4"/>
@@ -15723,7 +15734,7 @@
       <c r="O697" s="4"/>
       <c r="P697" s="4"/>
     </row>
-    <row r="698" spans="1:16" ht="13.2">
+    <row r="698" spans="1:16" ht="12.75">
       <c r="A698" s="4"/>
       <c r="B698" s="2"/>
       <c r="C698" s="4"/>
@@ -15737,7 +15748,7 @@
       <c r="O698" s="4"/>
       <c r="P698" s="4"/>
     </row>
-    <row r="699" spans="1:16" ht="13.2">
+    <row r="699" spans="1:16" ht="12.75">
       <c r="A699" s="4"/>
       <c r="B699" s="2"/>
       <c r="C699" s="4"/>
@@ -15751,7 +15762,7 @@
       <c r="O699" s="4"/>
       <c r="P699" s="4"/>
     </row>
-    <row r="700" spans="1:16" ht="13.2">
+    <row r="700" spans="1:16" ht="12.75">
       <c r="A700" s="4"/>
       <c r="B700" s="2"/>
       <c r="C700" s="4"/>
@@ -15765,7 +15776,7 @@
       <c r="O700" s="4"/>
       <c r="P700" s="4"/>
     </row>
-    <row r="701" spans="1:16" ht="13.2">
+    <row r="701" spans="1:16" ht="12.75">
       <c r="A701" s="4"/>
       <c r="B701" s="2"/>
       <c r="C701" s="4"/>
@@ -15779,7 +15790,7 @@
       <c r="O701" s="4"/>
       <c r="P701" s="4"/>
     </row>
-    <row r="702" spans="1:16" ht="13.2">
+    <row r="702" spans="1:16" ht="12.75">
       <c r="A702" s="4"/>
       <c r="B702" s="2"/>
       <c r="C702" s="4"/>
@@ -15793,7 +15804,7 @@
       <c r="O702" s="4"/>
       <c r="P702" s="4"/>
     </row>
-    <row r="703" spans="1:16" ht="13.2">
+    <row r="703" spans="1:16" ht="12.75">
       <c r="A703" s="4"/>
       <c r="B703" s="2"/>
       <c r="C703" s="4"/>
@@ -15807,7 +15818,7 @@
       <c r="O703" s="4"/>
       <c r="P703" s="4"/>
     </row>
-    <row r="704" spans="1:16" ht="13.2">
+    <row r="704" spans="1:16" ht="12.75">
       <c r="A704" s="4"/>
       <c r="B704" s="2"/>
       <c r="C704" s="4"/>
@@ -15821,7 +15832,7 @@
       <c r="O704" s="4"/>
       <c r="P704" s="4"/>
     </row>
-    <row r="705" spans="1:16" ht="13.2">
+    <row r="705" spans="1:16" ht="12.75">
       <c r="A705" s="4"/>
       <c r="B705" s="2"/>
       <c r="C705" s="4"/>
@@ -15835,7 +15846,7 @@
       <c r="O705" s="4"/>
       <c r="P705" s="4"/>
     </row>
-    <row r="706" spans="1:16" ht="13.2">
+    <row r="706" spans="1:16" ht="12.75">
       <c r="A706" s="4"/>
       <c r="B706" s="2"/>
       <c r="C706" s="4"/>
@@ -15849,7 +15860,7 @@
       <c r="O706" s="4"/>
       <c r="P706" s="4"/>
     </row>
-    <row r="707" spans="1:16" ht="13.2">
+    <row r="707" spans="1:16" ht="12.75">
       <c r="A707" s="4"/>
       <c r="B707" s="2"/>
       <c r="C707" s="4"/>
@@ -15863,7 +15874,7 @@
       <c r="O707" s="4"/>
       <c r="P707" s="4"/>
     </row>
-    <row r="708" spans="1:16" ht="13.2">
+    <row r="708" spans="1:16" ht="12.75">
       <c r="A708" s="4"/>
       <c r="B708" s="2"/>
       <c r="C708" s="4"/>
@@ -15877,7 +15888,7 @@
       <c r="O708" s="4"/>
       <c r="P708" s="4"/>
     </row>
-    <row r="709" spans="1:16" ht="13.2">
+    <row r="709" spans="1:16" ht="12.75">
       <c r="A709" s="4"/>
       <c r="B709" s="2"/>
       <c r="C709" s="4"/>
@@ -15891,7 +15902,7 @@
       <c r="O709" s="4"/>
       <c r="P709" s="4"/>
     </row>
-    <row r="710" spans="1:16" ht="13.2">
+    <row r="710" spans="1:16" ht="12.75">
       <c r="A710" s="4"/>
       <c r="B710" s="2"/>
       <c r="C710" s="4"/>
@@ -15905,7 +15916,7 @@
       <c r="O710" s="4"/>
       <c r="P710" s="4"/>
     </row>
-    <row r="711" spans="1:16" ht="13.2">
+    <row r="711" spans="1:16" ht="12.75">
       <c r="A711" s="4"/>
       <c r="B711" s="2"/>
       <c r="C711" s="4"/>
@@ -15919,7 +15930,7 @@
       <c r="O711" s="4"/>
       <c r="P711" s="4"/>
     </row>
-    <row r="712" spans="1:16" ht="13.2">
+    <row r="712" spans="1:16" ht="12.75">
       <c r="A712" s="4"/>
       <c r="B712" s="2"/>
       <c r="C712" s="4"/>
@@ -15933,7 +15944,7 @@
       <c r="O712" s="4"/>
       <c r="P712" s="4"/>
     </row>
-    <row r="713" spans="1:16" ht="13.2">
+    <row r="713" spans="1:16" ht="12.75">
       <c r="A713" s="4"/>
       <c r="B713" s="2"/>
       <c r="C713" s="4"/>
@@ -15947,7 +15958,7 @@
       <c r="O713" s="4"/>
       <c r="P713" s="4"/>
     </row>
-    <row r="714" spans="1:16" ht="13.2">
+    <row r="714" spans="1:16" ht="12.75">
       <c r="A714" s="4"/>
       <c r="B714" s="2"/>
       <c r="C714" s="4"/>
@@ -15961,7 +15972,7 @@
       <c r="O714" s="4"/>
       <c r="P714" s="4"/>
     </row>
-    <row r="715" spans="1:16" ht="13.2">
+    <row r="715" spans="1:16" ht="12.75">
       <c r="A715" s="4"/>
       <c r="B715" s="2"/>
       <c r="C715" s="4"/>
@@ -15975,7 +15986,7 @@
       <c r="O715" s="4"/>
       <c r="P715" s="4"/>
     </row>
-    <row r="716" spans="1:16" ht="13.2">
+    <row r="716" spans="1:16" ht="12.75">
       <c r="A716" s="4"/>
       <c r="B716" s="2"/>
       <c r="C716" s="4"/>
@@ -15989,7 +16000,7 @@
       <c r="O716" s="4"/>
       <c r="P716" s="4"/>
     </row>
-    <row r="717" spans="1:16" ht="13.2">
+    <row r="717" spans="1:16" ht="12.75">
       <c r="A717" s="4"/>
       <c r="B717" s="2"/>
       <c r="C717" s="4"/>
@@ -16003,7 +16014,7 @@
       <c r="O717" s="4"/>
       <c r="P717" s="4"/>
     </row>
-    <row r="718" spans="1:16" ht="13.2">
+    <row r="718" spans="1:16" ht="12.75">
       <c r="A718" s="4"/>
       <c r="B718" s="2"/>
       <c r="C718" s="4"/>
@@ -16017,7 +16028,7 @@
       <c r="O718" s="4"/>
       <c r="P718" s="4"/>
     </row>
-    <row r="719" spans="1:16" ht="13.2">
+    <row r="719" spans="1:16" ht="12.75">
       <c r="A719" s="4"/>
       <c r="B719" s="2"/>
       <c r="C719" s="4"/>
@@ -16031,7 +16042,7 @@
       <c r="O719" s="4"/>
       <c r="P719" s="4"/>
     </row>
-    <row r="720" spans="1:16" ht="13.2">
+    <row r="720" spans="1:16" ht="12.75">
       <c r="A720" s="4"/>
       <c r="B720" s="2"/>
       <c r="C720" s="4"/>
@@ -16045,7 +16056,7 @@
       <c r="O720" s="4"/>
       <c r="P720" s="4"/>
     </row>
-    <row r="721" spans="1:16" ht="13.2">
+    <row r="721" spans="1:16" ht="12.75">
       <c r="A721" s="4"/>
       <c r="B721" s="2"/>
       <c r="C721" s="4"/>
@@ -16059,7 +16070,7 @@
       <c r="O721" s="4"/>
       <c r="P721" s="4"/>
     </row>
-    <row r="722" spans="1:16" ht="13.2">
+    <row r="722" spans="1:16" ht="12.75">
       <c r="A722" s="4"/>
       <c r="B722" s="2"/>
       <c r="C722" s="4"/>
@@ -16073,7 +16084,7 @@
       <c r="O722" s="4"/>
       <c r="P722" s="4"/>
     </row>
-    <row r="723" spans="1:16" ht="13.2">
+    <row r="723" spans="1:16" ht="12.75">
       <c r="A723" s="4"/>
       <c r="B723" s="2"/>
       <c r="C723" s="4"/>
@@ -16087,7 +16098,7 @@
       <c r="O723" s="4"/>
       <c r="P723" s="4"/>
     </row>
-    <row r="724" spans="1:16" ht="13.2">
+    <row r="724" spans="1:16" ht="12.75">
       <c r="A724" s="4"/>
       <c r="B724" s="2"/>
       <c r="C724" s="4"/>
@@ -16101,7 +16112,7 @@
       <c r="O724" s="4"/>
       <c r="P724" s="4"/>
     </row>
-    <row r="725" spans="1:16" ht="13.2">
+    <row r="725" spans="1:16" ht="12.75">
       <c r="A725" s="4"/>
       <c r="B725" s="2"/>
       <c r="C725" s="4"/>
@@ -16115,7 +16126,7 @@
       <c r="O725" s="4"/>
       <c r="P725" s="4"/>
     </row>
-    <row r="726" spans="1:16" ht="13.2">
+    <row r="726" spans="1:16" ht="12.75">
       <c r="A726" s="4"/>
       <c r="B726" s="2"/>
       <c r="C726" s="4"/>
@@ -16129,7 +16140,7 @@
       <c r="O726" s="4"/>
       <c r="P726" s="4"/>
     </row>
-    <row r="727" spans="1:16" ht="13.2">
+    <row r="727" spans="1:16" ht="12.75">
       <c r="A727" s="4"/>
       <c r="B727" s="2"/>
       <c r="C727" s="4"/>
@@ -16143,7 +16154,7 @@
       <c r="O727" s="4"/>
       <c r="P727" s="4"/>
     </row>
-    <row r="728" spans="1:16" ht="13.2">
+    <row r="728" spans="1:16" ht="12.75">
       <c r="A728" s="4"/>
       <c r="B728" s="2"/>
       <c r="C728" s="4"/>
@@ -16157,7 +16168,7 @@
       <c r="O728" s="4"/>
       <c r="P728" s="4"/>
     </row>
-    <row r="729" spans="1:16" ht="13.2">
+    <row r="729" spans="1:16" ht="12.75">
       <c r="A729" s="4"/>
       <c r="B729" s="2"/>
       <c r="C729" s="4"/>
@@ -16171,7 +16182,7 @@
       <c r="O729" s="4"/>
       <c r="P729" s="4"/>
     </row>
-    <row r="730" spans="1:16" ht="13.2">
+    <row r="730" spans="1:16" ht="12.75">
       <c r="A730" s="4"/>
       <c r="B730" s="2"/>
       <c r="C730" s="4"/>
@@ -16185,7 +16196,7 @@
       <c r="O730" s="4"/>
       <c r="P730" s="4"/>
     </row>
-    <row r="731" spans="1:16" ht="13.2">
+    <row r="731" spans="1:16" ht="12.75">
       <c r="A731" s="4"/>
       <c r="B731" s="2"/>
       <c r="C731" s="4"/>
@@ -16199,7 +16210,7 @@
       <c r="O731" s="4"/>
       <c r="P731" s="4"/>
     </row>
-    <row r="732" spans="1:16" ht="13.2">
+    <row r="732" spans="1:16" ht="12.75">
       <c r="A732" s="4"/>
       <c r="B732" s="2"/>
       <c r="C732" s="4"/>
@@ -16213,7 +16224,7 @@
       <c r="O732" s="4"/>
       <c r="P732" s="4"/>
     </row>
-    <row r="733" spans="1:16" ht="13.2">
+    <row r="733" spans="1:16" ht="12.75">
       <c r="A733" s="4"/>
       <c r="B733" s="2"/>
       <c r="C733" s="4"/>
@@ -16227,7 +16238,7 @@
       <c r="O733" s="4"/>
       <c r="P733" s="4"/>
     </row>
-    <row r="734" spans="1:16" ht="13.2">
+    <row r="734" spans="1:16" ht="12.75">
       <c r="A734" s="4"/>
       <c r="B734" s="2"/>
       <c r="C734" s="4"/>
@@ -16241,7 +16252,7 @@
       <c r="O734" s="4"/>
       <c r="P734" s="4"/>
     </row>
-    <row r="735" spans="1:16" ht="13.2">
+    <row r="735" spans="1:16" ht="12.75">
       <c r="A735" s="4"/>
       <c r="B735" s="2"/>
       <c r="C735" s="4"/>
@@ -16255,7 +16266,7 @@
       <c r="O735" s="4"/>
       <c r="P735" s="4"/>
     </row>
-    <row r="736" spans="1:16" ht="13.2">
+    <row r="736" spans="1:16" ht="12.75">
       <c r="A736" s="4"/>
       <c r="B736" s="2"/>
       <c r="C736" s="4"/>
@@ -16269,7 +16280,7 @@
       <c r="O736" s="4"/>
       <c r="P736" s="4"/>
     </row>
-    <row r="737" spans="1:16" ht="13.2">
+    <row r="737" spans="1:16" ht="12.75">
       <c r="A737" s="4"/>
       <c r="B737" s="2"/>
       <c r="C737" s="4"/>
@@ -16283,7 +16294,7 @@
       <c r="O737" s="4"/>
       <c r="P737" s="4"/>
     </row>
-    <row r="738" spans="1:16" ht="13.2">
+    <row r="738" spans="1:16" ht="12.75">
       <c r="A738" s="4"/>
       <c r="B738" s="2"/>
       <c r="C738" s="4"/>
@@ -16297,7 +16308,7 @@
       <c r="O738" s="4"/>
       <c r="P738" s="4"/>
     </row>
-    <row r="739" spans="1:16" ht="13.2">
+    <row r="739" spans="1:16" ht="12.75">
       <c r="A739" s="4"/>
       <c r="B739" s="2"/>
       <c r="C739" s="4"/>
@@ -16311,7 +16322,7 @@
       <c r="O739" s="4"/>
       <c r="P739" s="4"/>
     </row>
-    <row r="740" spans="1:16" ht="13.2">
+    <row r="740" spans="1:16" ht="12.75">
       <c r="A740" s="4"/>
       <c r="B740" s="2"/>
       <c r="C740" s="4"/>
@@ -16325,7 +16336,7 @@
       <c r="O740" s="4"/>
       <c r="P740" s="4"/>
     </row>
-    <row r="741" spans="1:16" ht="13.2">
+    <row r="741" spans="1:16" ht="12.75">
       <c r="A741" s="4"/>
       <c r="B741" s="2"/>
       <c r="C741" s="4"/>
@@ -16339,7 +16350,7 @@
       <c r="O741" s="4"/>
       <c r="P741" s="4"/>
     </row>
-    <row r="742" spans="1:16" ht="13.2">
+    <row r="742" spans="1:16" ht="12.75">
       <c r="A742" s="4"/>
       <c r="B742" s="2"/>
       <c r="C742" s="4"/>
@@ -16353,7 +16364,7 @@
       <c r="O742" s="4"/>
       <c r="P742" s="4"/>
     </row>
-    <row r="743" spans="1:16" ht="13.2">
+    <row r="743" spans="1:16" ht="12.75">
       <c r="A743" s="4"/>
       <c r="B743" s="2"/>
       <c r="C743" s="4"/>
@@ -16367,7 +16378,7 @@
       <c r="O743" s="4"/>
       <c r="P743" s="4"/>
     </row>
-    <row r="744" spans="1:16" ht="13.2">
+    <row r="744" spans="1:16" ht="12.75">
       <c r="A744" s="4"/>
       <c r="B744" s="2"/>
       <c r="C744" s="4"/>
@@ -16381,7 +16392,7 @@
       <c r="O744" s="4"/>
       <c r="P744" s="4"/>
     </row>
-    <row r="745" spans="1:16" ht="13.2">
+    <row r="745" spans="1:16" ht="12.75">
       <c r="A745" s="4"/>
       <c r="B745" s="2"/>
       <c r="C745" s="4"/>
@@ -16395,7 +16406,7 @@
       <c r="O745" s="4"/>
       <c r="P745" s="4"/>
     </row>
-    <row r="746" spans="1:16" ht="13.2">
+    <row r="746" spans="1:16" ht="12.75">
       <c r="A746" s="4"/>
       <c r="B746" s="2"/>
       <c r="C746" s="4"/>
@@ -16409,7 +16420,7 @@
       <c r="O746" s="4"/>
       <c r="P746" s="4"/>
     </row>
-    <row r="747" spans="1:16" ht="13.2">
+    <row r="747" spans="1:16" ht="12.75">
       <c r="A747" s="4"/>
       <c r="B747" s="2"/>
       <c r="C747" s="4"/>
@@ -16423,7 +16434,7 @@
       <c r="O747" s="4"/>
       <c r="P747" s="4"/>
     </row>
-    <row r="748" spans="1:16" ht="13.2">
+    <row r="748" spans="1:16" ht="12.75">
       <c r="A748" s="4"/>
       <c r="B748" s="2"/>
       <c r="C748" s="4"/>
@@ -16437,7 +16448,7 @@
       <c r="O748" s="4"/>
       <c r="P748" s="4"/>
     </row>
-    <row r="749" spans="1:16" ht="13.2">
+    <row r="749" spans="1:16" ht="12.75">
       <c r="A749" s="4"/>
       <c r="B749" s="2"/>
       <c r="C749" s="4"/>
@@ -16451,7 +16462,7 @@
       <c r="O749" s="4"/>
       <c r="P749" s="4"/>
     </row>
-    <row r="750" spans="1:16" ht="13.2">
+    <row r="750" spans="1:16" ht="12.75">
       <c r="A750" s="4"/>
       <c r="B750" s="2"/>
       <c r="C750" s="4"/>
@@ -16465,7 +16476,7 @@
       <c r="O750" s="4"/>
       <c r="P750" s="4"/>
     </row>
-    <row r="751" spans="1:16" ht="13.2">
+    <row r="751" spans="1:16" ht="12.75">
       <c r="A751" s="4"/>
       <c r="B751" s="2"/>
       <c r="C751" s="4"/>
@@ -16479,7 +16490,7 @@
       <c r="O751" s="4"/>
       <c r="P751" s="4"/>
     </row>
-    <row r="752" spans="1:16" ht="13.2">
+    <row r="752" spans="1:16" ht="12.75">
       <c r="A752" s="4"/>
       <c r="B752" s="2"/>
       <c r="C752" s="4"/>
@@ -16493,7 +16504,7 @@
       <c r="O752" s="4"/>
       <c r="P752" s="4"/>
     </row>
-    <row r="753" spans="1:16" ht="13.2">
+    <row r="753" spans="1:16" ht="12.75">
       <c r="A753" s="4"/>
       <c r="B753" s="2"/>
       <c r="C753" s="4"/>
@@ -16507,7 +16518,7 @@
       <c r="O753" s="4"/>
       <c r="P753" s="4"/>
     </row>
-    <row r="754" spans="1:16" ht="13.2">
+    <row r="754" spans="1:16" ht="12.75">
       <c r="A754" s="4"/>
       <c r="B754" s="2"/>
       <c r="C754" s="4"/>
@@ -16521,7 +16532,7 @@
       <c r="O754" s="4"/>
       <c r="P754" s="4"/>
     </row>
-    <row r="755" spans="1:16" ht="13.2">
+    <row r="755" spans="1:16" ht="12.75">
       <c r="A755" s="4"/>
       <c r="B755" s="2"/>
       <c r="C755" s="4"/>
@@ -16535,7 +16546,7 @@
       <c r="O755" s="4"/>
       <c r="P755" s="4"/>
     </row>
-    <row r="756" spans="1:16" ht="13.2">
+    <row r="756" spans="1:16" ht="12.75">
       <c r="A756" s="4"/>
       <c r="B756" s="2"/>
       <c r="C756" s="4"/>
@@ -16549,7 +16560,7 @@
       <c r="O756" s="4"/>
       <c r="P756" s="4"/>
     </row>
-    <row r="757" spans="1:16" ht="13.2">
+    <row r="757" spans="1:16" ht="12.75">
       <c r="A757" s="4"/>
       <c r="B757" s="2"/>
       <c r="C757" s="4"/>
@@ -16563,7 +16574,7 @@
       <c r="O757" s="4"/>
       <c r="P757" s="4"/>
     </row>
-    <row r="758" spans="1:16" ht="13.2">
+    <row r="758" spans="1:16" ht="12.75">
       <c r="A758" s="4"/>
       <c r="B758" s="2"/>
       <c r="C758" s="4"/>
@@ -16577,7 +16588,7 @@
       <c r="O758" s="4"/>
       <c r="P758" s="4"/>
     </row>
-    <row r="759" spans="1:16" ht="13.2">
+    <row r="759" spans="1:16" ht="12.75">
       <c r="A759" s="4"/>
       <c r="B759" s="2"/>
       <c r="C759" s="4"/>
@@ -16591,7 +16602,7 @@
       <c r="O759" s="4"/>
       <c r="P759" s="4"/>
     </row>
-    <row r="760" spans="1:16" ht="13.2">
+    <row r="760" spans="1:16" ht="12.75">
       <c r="A760" s="4"/>
       <c r="B760" s="2"/>
       <c r="C760" s="4"/>
@@ -16605,7 +16616,7 @@
       <c r="O760" s="4"/>
       <c r="P760" s="4"/>
     </row>
-    <row r="761" spans="1:16" ht="13.2">
+    <row r="761" spans="1:16" ht="12.75">
       <c r="A761" s="4"/>
       <c r="B761" s="2"/>
       <c r="C761" s="4"/>
@@ -16619,7 +16630,7 @@
       <c r="O761" s="4"/>
       <c r="P761" s="4"/>
     </row>
-    <row r="762" spans="1:16" ht="13.2">
+    <row r="762" spans="1:16" ht="12.75">
       <c r="A762" s="4"/>
       <c r="B762" s="2"/>
       <c r="C762" s="4"/>
@@ -16633,7 +16644,7 @@
       <c r="O762" s="4"/>
       <c r="P762" s="4"/>
     </row>
-    <row r="763" spans="1:16" ht="13.2">
+    <row r="763" spans="1:16" ht="12.75">
       <c r="A763" s="4"/>
       <c r="B763" s="2"/>
       <c r="C763" s="4"/>
@@ -16647,7 +16658,7 @@
       <c r="O763" s="4"/>
       <c r="P763" s="4"/>
     </row>
-    <row r="764" spans="1:16" ht="13.2">
+    <row r="764" spans="1:16" ht="12.75">
       <c r="A764" s="4"/>
       <c r="B764" s="2"/>
       <c r="C764" s="4"/>
@@ -16661,7 +16672,7 @@
       <c r="O764" s="4"/>
       <c r="P764" s="4"/>
     </row>
-    <row r="765" spans="1:16" ht="13.2">
+    <row r="765" spans="1:16" ht="12.75">
       <c r="A765" s="4"/>
       <c r="B765" s="2"/>
       <c r="C765" s="4"/>
@@ -16675,7 +16686,7 @@
       <c r="O765" s="4"/>
       <c r="P765" s="4"/>
     </row>
-    <row r="766" spans="1:16" ht="13.2">
+    <row r="766" spans="1:16" ht="12.75">
       <c r="A766" s="4"/>
       <c r="B766" s="2"/>
       <c r="C766" s="4"/>
@@ -16689,7 +16700,7 @@
       <c r="O766" s="4"/>
       <c r="P766" s="4"/>
     </row>
-    <row r="767" spans="1:16" ht="13.2">
+    <row r="767" spans="1:16" ht="12.75">
       <c r="A767" s="4"/>
       <c r="B767" s="2"/>
       <c r="C767" s="4"/>
@@ -16703,7 +16714,7 @@
       <c r="O767" s="4"/>
       <c r="P767" s="4"/>
     </row>
-    <row r="768" spans="1:16" ht="13.2">
+    <row r="768" spans="1:16" ht="12.75">
       <c r="A768" s="4"/>
       <c r="B768" s="2"/>
       <c r="C768" s="4"/>
@@ -16717,7 +16728,7 @@
       <c r="O768" s="4"/>
       <c r="P768" s="4"/>
     </row>
-    <row r="769" spans="1:16" ht="13.2">
+    <row r="769" spans="1:16" ht="12.75">
       <c r="A769" s="4"/>
       <c r="B769" s="2"/>
       <c r="C769" s="4"/>
@@ -16731,7 +16742,7 @@
       <c r="O769" s="4"/>
       <c r="P769" s="4"/>
     </row>
-    <row r="770" spans="1:16" ht="13.2">
+    <row r="770" spans="1:16" ht="12.75">
       <c r="A770" s="4"/>
       <c r="B770" s="2"/>
       <c r="C770" s="4"/>
@@ -16745,7 +16756,7 @@
       <c r="O770" s="4"/>
       <c r="P770" s="4"/>
     </row>
-    <row r="771" spans="1:16" ht="13.2">
+    <row r="771" spans="1:16" ht="12.75">
       <c r="A771" s="4"/>
       <c r="B771" s="2"/>
       <c r="C771" s="4"/>
@@ -16759,7 +16770,7 @@
       <c r="O771" s="4"/>
       <c r="P771" s="4"/>
     </row>
-    <row r="772" spans="1:16" ht="13.2">
+    <row r="772" spans="1:16" ht="12.75">
       <c r="A772" s="4"/>
       <c r="B772" s="2"/>
       <c r="C772" s="4"/>
@@ -16773,7 +16784,7 @@
       <c r="O772" s="4"/>
       <c r="P772" s="4"/>
     </row>
-    <row r="773" spans="1:16" ht="13.2">
+    <row r="773" spans="1:16" ht="12.75">
       <c r="A773" s="4"/>
       <c r="B773" s="2"/>
       <c r="C773" s="4"/>
@@ -16787,7 +16798,7 @@
       <c r="O773" s="4"/>
       <c r="P773" s="4"/>
     </row>
-    <row r="774" spans="1:16" ht="13.2">
+    <row r="774" spans="1:16" ht="12.75">
       <c r="A774" s="4"/>
       <c r="B774" s="2"/>
       <c r="C774" s="4"/>
@@ -16801,7 +16812,7 @@
       <c r="O774" s="4"/>
       <c r="P774" s="4"/>
     </row>
-    <row r="775" spans="1:16" ht="13.2">
+    <row r="775" spans="1:16" ht="12.75">
       <c r="A775" s="4"/>
       <c r="B775" s="2"/>
       <c r="C775" s="4"/>
@@ -16815,7 +16826,7 @@
       <c r="O775" s="4"/>
       <c r="P775" s="4"/>
     </row>
-    <row r="776" spans="1:16" ht="13.2">
+    <row r="776" spans="1:16" ht="12.75">
       <c r="A776" s="4"/>
       <c r="B776" s="2"/>
       <c r="C776" s="4"/>
@@ -16829,7 +16840,7 @@
       <c r="O776" s="4"/>
       <c r="P776" s="4"/>
     </row>
-    <row r="777" spans="1:16" ht="13.2">
+    <row r="777" spans="1:16" ht="12.75">
       <c r="A777" s="4"/>
       <c r="B777" s="2"/>
       <c r="C777" s="4"/>
@@ -16843,7 +16854,7 @@
       <c r="O777" s="4"/>
       <c r="P777" s="4"/>
     </row>
-    <row r="778" spans="1:16" ht="13.2">
+    <row r="778" spans="1:16" ht="12.75">
       <c r="A778" s="4"/>
       <c r="B778" s="2"/>
       <c r="C778" s="4"/>
@@ -16857,7 +16868,7 @@
       <c r="O778" s="4"/>
       <c r="P778" s="4"/>
     </row>
-    <row r="779" spans="1:16" ht="13.2">
+    <row r="779" spans="1:16" ht="12.75">
       <c r="A779" s="4"/>
       <c r="B779" s="2"/>
       <c r="C779" s="4"/>
@@ -16871,7 +16882,7 @@
       <c r="O779" s="4"/>
       <c r="P779" s="4"/>
     </row>
-    <row r="780" spans="1:16" ht="13.2">
+    <row r="780" spans="1:16" ht="12.75">
       <c r="A780" s="4"/>
       <c r="B780" s="2"/>
       <c r="C780" s="4"/>
@@ -16885,7 +16896,7 @@
       <c r="O780" s="4"/>
       <c r="P780" s="4"/>
     </row>
-    <row r="781" spans="1:16" ht="13.2">
+    <row r="781" spans="1:16" ht="12.75">
       <c r="A781" s="4"/>
       <c r="B781" s="2"/>
       <c r="C781" s="4"/>
@@ -16899,7 +16910,7 @@
       <c r="O781" s="4"/>
       <c r="P781" s="4"/>
     </row>
-    <row r="782" spans="1:16" ht="13.2">
+    <row r="782" spans="1:16" ht="12.75">
       <c r="A782" s="4"/>
       <c r="B782" s="2"/>
       <c r="C782" s="4"/>
@@ -16913,7 +16924,7 @@
       <c r="O782" s="4"/>
       <c r="P782" s="4"/>
     </row>
-    <row r="783" spans="1:16" ht="13.2">
+    <row r="783" spans="1:16" ht="12.75">
       <c r="A783" s="4"/>
       <c r="B783" s="2"/>
       <c r="C783" s="4"/>
@@ -16927,7 +16938,7 @@
       <c r="O783" s="4"/>
       <c r="P783" s="4"/>
     </row>
-    <row r="784" spans="1:16" ht="13.2">
+    <row r="784" spans="1:16" ht="12.75">
       <c r="A784" s="4"/>
       <c r="B784" s="2"/>
       <c r="C784" s="4"/>
@@ -16941,7 +16952,7 @@
       <c r="O784" s="4"/>
       <c r="P784" s="4"/>
     </row>
-    <row r="785" spans="1:16" ht="13.2">
+    <row r="785" spans="1:16" ht="12.75">
       <c r="A785" s="4"/>
       <c r="B785" s="2"/>
       <c r="C785" s="4"/>
@@ -16955,7 +16966,7 @@
       <c r="O785" s="4"/>
       <c r="P785" s="4"/>
     </row>
-    <row r="786" spans="1:16" ht="13.2">
+    <row r="786" spans="1:16" ht="12.75">
       <c r="A786" s="4"/>
       <c r="B786" s="2"/>
       <c r="C786" s="4"/>
@@ -16969,7 +16980,7 @@
       <c r="O786" s="4"/>
       <c r="P786" s="4"/>
     </row>
-    <row r="787" spans="1:16" ht="13.2">
+    <row r="787" spans="1:16" ht="12.75">
       <c r="A787" s="4"/>
       <c r="B787" s="2"/>
       <c r="C787" s="4"/>
@@ -16983,7 +16994,7 @@
       <c r="O787" s="4"/>
       <c r="P787" s="4"/>
     </row>
-    <row r="788" spans="1:16" ht="13.2">
+    <row r="788" spans="1:16" ht="12.75">
       <c r="A788" s="4"/>
       <c r="B788" s="2"/>
       <c r="C788" s="4"/>
@@ -16997,7 +17008,7 @@
       <c r="O788" s="4"/>
       <c r="P788" s="4"/>
     </row>
-    <row r="789" spans="1:16" ht="13.2">
+    <row r="789" spans="1:16" ht="12.75">
       <c r="A789" s="4"/>
       <c r="B789" s="2"/>
       <c r="C789" s="4"/>
@@ -17011,7 +17022,7 @@
       <c r="O789" s="4"/>
       <c r="P789" s="4"/>
     </row>
-    <row r="790" spans="1:16" ht="13.2">
+    <row r="790" spans="1:16" ht="12.75">
       <c r="A790" s="4"/>
       <c r="B790" s="2"/>
       <c r="C790" s="4"/>
@@ -17025,7 +17036,7 @@
       <c r="O790" s="4"/>
       <c r="P790" s="4"/>
     </row>
-    <row r="791" spans="1:16" ht="13.2">
+    <row r="791" spans="1:16" ht="12.75">
       <c r="A791" s="4"/>
       <c r="B791" s="2"/>
       <c r="C791" s="4"/>
@@ -17039,7 +17050,7 @@
       <c r="O791" s="4"/>
       <c r="P791" s="4"/>
     </row>
-    <row r="792" spans="1:16" ht="13.2">
+    <row r="792" spans="1:16" ht="12.75">
       <c r="A792" s="4"/>
       <c r="B792" s="2"/>
       <c r="C792" s="4"/>
@@ -17053,7 +17064,7 @@
       <c r="O792" s="4"/>
       <c r="P792" s="4"/>
     </row>
-    <row r="793" spans="1:16" ht="13.2">
+    <row r="793" spans="1:16" ht="12.75">
       <c r="A793" s="4"/>
       <c r="B793" s="2"/>
       <c r="C793" s="4"/>
@@ -17067,7 +17078,7 @@
       <c r="O793" s="4"/>
       <c r="P793" s="4"/>
     </row>
-    <row r="794" spans="1:16" ht="13.2">
+    <row r="794" spans="1:16" ht="12.75">
       <c r="A794" s="4"/>
       <c r="B794" s="2"/>
       <c r="C794" s="4"/>
@@ -17081,7 +17092,7 @@
       <c r="O794" s="4"/>
       <c r="P794" s="4"/>
     </row>
-    <row r="795" spans="1:16" ht="13.2">
+    <row r="795" spans="1:16" ht="12.75">
       <c r="A795" s="4"/>
       <c r="B795" s="2"/>
       <c r="C795" s="4"/>
@@ -17095,7 +17106,7 @@
       <c r="O795" s="4"/>
       <c r="P795" s="4"/>
     </row>
-    <row r="796" spans="1:16" ht="13.2">
+    <row r="796" spans="1:16" ht="12.75">
       <c r="A796" s="4"/>
       <c r="B796" s="2"/>
       <c r="C796" s="4"/>
@@ -17109,7 +17120,7 @@
       <c r="O796" s="4"/>
       <c r="P796" s="4"/>
     </row>
-    <row r="797" spans="1:16" ht="13.2">
+    <row r="797" spans="1:16" ht="12.75">
       <c r="A797" s="4"/>
       <c r="B797" s="2"/>
       <c r="C797" s="4"/>
@@ -17123,7 +17134,7 @@
       <c r="O797" s="4"/>
       <c r="P797" s="4"/>
     </row>
-    <row r="798" spans="1:16" ht="13.2">
+    <row r="798" spans="1:16" ht="12.75">
       <c r="A798" s="4"/>
       <c r="B798" s="2"/>
       <c r="C798" s="4"/>
@@ -17137,7 +17148,7 @@
       <c r="O798" s="4"/>
       <c r="P798" s="4"/>
     </row>
-    <row r="799" spans="1:16" ht="13.2">
+    <row r="799" spans="1:16" ht="12.75">
       <c r="A799" s="4"/>
       <c r="B799" s="2"/>
       <c r="C799" s="4"/>
@@ -17151,7 +17162,7 @@
       <c r="O799" s="4"/>
       <c r="P799" s="4"/>
     </row>
-    <row r="800" spans="1:16" ht="13.2">
+    <row r="800" spans="1:16" ht="12.75">
       <c r="A800" s="4"/>
       <c r="B800" s="2"/>
       <c r="C800" s="4"/>
@@ -17165,7 +17176,7 @@
       <c r="O800" s="4"/>
       <c r="P800" s="4"/>
     </row>
-    <row r="801" spans="1:16" ht="13.2">
+    <row r="801" spans="1:16" ht="12.75">
       <c r="A801" s="4"/>
       <c r="B801" s="2"/>
       <c r="C801" s="4"/>
@@ -17179,7 +17190,7 @@
       <c r="O801" s="4"/>
       <c r="P801" s="4"/>
     </row>
-    <row r="802" spans="1:16" ht="13.2">
+    <row r="802" spans="1:16" ht="12.75">
       <c r="A802" s="4"/>
       <c r="B802" s="2"/>
       <c r="C802" s="4"/>
@@ -17193,7 +17204,7 @@
       <c r="O802" s="4"/>
       <c r="P802" s="4"/>
     </row>
-    <row r="803" spans="1:16" ht="13.2">
+    <row r="803" spans="1:16" ht="12.75">
       <c r="A803" s="4"/>
       <c r="B803" s="2"/>
       <c r="C803" s="4"/>
@@ -17207,7 +17218,7 @@
       <c r="O803" s="4"/>
       <c r="P803" s="4"/>
     </row>
-    <row r="804" spans="1:16" ht="13.2">
+    <row r="804" spans="1:16" ht="12.75">
       <c r="A804" s="4"/>
       <c r="B804" s="2"/>
       <c r="C804" s="4"/>
@@ -17221,7 +17232,7 @@
       <c r="O804" s="4"/>
       <c r="P804" s="4"/>
     </row>
-    <row r="805" spans="1:16" ht="13.2">
+    <row r="805" spans="1:16" ht="12.75">
       <c r="A805" s="4"/>
       <c r="B805" s="2"/>
       <c r="C805" s="4"/>
@@ -17235,7 +17246,7 @@
       <c r="O805" s="4"/>
       <c r="P805" s="4"/>
     </row>
-    <row r="806" spans="1:16" ht="13.2">
+    <row r="806" spans="1:16" ht="12.75">
       <c r="A806" s="4"/>
       <c r="B806" s="2"/>
       <c r="C806" s="4"/>
@@ -17249,7 +17260,7 @@
       <c r="O806" s="4"/>
       <c r="P806" s="4"/>
     </row>
-    <row r="807" spans="1:16" ht="13.2">
+    <row r="807" spans="1:16" ht="12.75">
       <c r="A807" s="4"/>
       <c r="B807" s="2"/>
       <c r="C807" s="4"/>
@@ -17263,7 +17274,7 @@
       <c r="O807" s="4"/>
       <c r="P807" s="4"/>
     </row>
-    <row r="808" spans="1:16" ht="13.2">
+    <row r="808" spans="1:16" ht="12.75">
       <c r="A808" s="4"/>
       <c r="B808" s="2"/>
       <c r="C808" s="4"/>
@@ -17277,7 +17288,7 @@
       <c r="O808" s="4"/>
       <c r="P808" s="4"/>
     </row>
-    <row r="809" spans="1:16" ht="13.2">
+    <row r="809" spans="1:16" ht="12.75">
       <c r="A809" s="4"/>
       <c r="B809" s="2"/>
       <c r="C809" s="4"/>
@@ -17291,7 +17302,7 @@
       <c r="O809" s="4"/>
       <c r="P809" s="4"/>
     </row>
-    <row r="810" spans="1:16" ht="13.2">
+    <row r="810" spans="1:16" ht="12.75">
       <c r="A810" s="4"/>
       <c r="B810" s="2"/>
       <c r="C810" s="4"/>
@@ -17305,7 +17316,7 @@
       <c r="O810" s="4"/>
       <c r="P810" s="4"/>
     </row>
-    <row r="811" spans="1:16" ht="13.2">
+    <row r="811" spans="1:16" ht="12.75">
       <c r="A811" s="4"/>
       <c r="B811" s="2"/>
       <c r="C811" s="4"/>
@@ -17319,7 +17330,7 @@
       <c r="O811" s="4"/>
       <c r="P811" s="4"/>
     </row>
-    <row r="812" spans="1:16" ht="13.2">
+    <row r="812" spans="1:16" ht="12.75">
       <c r="A812" s="4"/>
       <c r="B812" s="2"/>
       <c r="C812" s="4"/>
@@ -17333,7 +17344,7 @@
       <c r="O812" s="4"/>
       <c r="P812" s="4"/>
     </row>
-    <row r="813" spans="1:16" ht="13.2">
+    <row r="813" spans="1:16" ht="12.75">
       <c r="A813" s="4"/>
       <c r="B813" s="2"/>
       <c r="C813" s="4"/>
@@ -17347,7 +17358,7 @@
       <c r="O813" s="4"/>
       <c r="P813" s="4"/>
     </row>
-    <row r="814" spans="1:16" ht="13.2">
+    <row r="814" spans="1:16" ht="12.75">
       <c r="A814" s="4"/>
       <c r="B814" s="2"/>
       <c r="C814" s="4"/>
@@ -17361,7 +17372,7 @@
       <c r="O814" s="4"/>
       <c r="P814" s="4"/>
     </row>
-    <row r="815" spans="1:16" ht="13.2">
+    <row r="815" spans="1:16" ht="12.75">
       <c r="A815" s="4"/>
       <c r="B815" s="2"/>
       <c r="C815" s="4"/>
@@ -17375,7 +17386,7 @@
       <c r="O815" s="4"/>
       <c r="P815" s="4"/>
     </row>
-    <row r="816" spans="1:16" ht="13.2">
+    <row r="816" spans="1:16" ht="12.75">
       <c r="A816" s="4"/>
       <c r="B816" s="2"/>
       <c r="C816" s="4"/>
@@ -17389,7 +17400,7 @@
       <c r="O816" s="4"/>
       <c r="P816" s="4"/>
     </row>
-    <row r="817" spans="1:16" ht="13.2">
+    <row r="817" spans="1:16" ht="12.75">
       <c r="A817" s="4"/>
       <c r="B817" s="2"/>
       <c r="C817" s="4"/>
@@ -17403,7 +17414,7 @@
       <c r="O817" s="4"/>
       <c r="P817" s="4"/>
     </row>
-    <row r="818" spans="1:16" ht="13.2">
+    <row r="818" spans="1:16" ht="12.75">
       <c r="A818" s="4"/>
       <c r="B818" s="2"/>
       <c r="C818" s="4"/>
@@ -17417,7 +17428,7 @@
       <c r="O818" s="4"/>
       <c r="P818" s="4"/>
     </row>
-    <row r="819" spans="1:16" ht="13.2">
+    <row r="819" spans="1:16" ht="12.75">
       <c r="A819" s="4"/>
       <c r="B819" s="2"/>
       <c r="C819" s="4"/>
@@ -17431,7 +17442,7 @@
       <c r="O819" s="4"/>
       <c r="P819" s="4"/>
     </row>
-    <row r="820" spans="1:16" ht="13.2">
+    <row r="820" spans="1:16" ht="12.75">
       <c r="A820" s="4"/>
       <c r="B820" s="2"/>
       <c r="C820" s="4"/>
@@ -17445,7 +17456,7 @@
       <c r="O820" s="4"/>
       <c r="P820" s="4"/>
     </row>
-    <row r="821" spans="1:16" ht="13.2">
+    <row r="821" spans="1:16" ht="12.75">
       <c r="A821" s="4"/>
       <c r="B821" s="2"/>
       <c r="C821" s="4"/>
@@ -17459,7 +17470,7 @@
       <c r="O821" s="4"/>
       <c r="P821" s="4"/>
     </row>
-    <row r="822" spans="1:16" ht="13.2">
+    <row r="822" spans="1:16" ht="12.75">
       <c r="A822" s="4"/>
       <c r="B822" s="2"/>
       <c r="C822" s="4"/>
@@ -17473,7 +17484,7 @@
       <c r="O822" s="4"/>
       <c r="P822" s="4"/>
     </row>
-    <row r="823" spans="1:16" ht="13.2">
+    <row r="823" spans="1:16" ht="12.75">
       <c r="A823" s="4"/>
       <c r="B823" s="2"/>
       <c r="C823" s="4"/>
@@ -17487,7 +17498,7 @@
       <c r="O823" s="4"/>
       <c r="P823" s="4"/>
     </row>
-    <row r="824" spans="1:16" ht="13.2">
+    <row r="824" spans="1:16" ht="12.75">
       <c r="A824" s="4"/>
       <c r="B824" s="2"/>
       <c r="C824" s="4"/>
@@ -17501,7 +17512,7 @@
       <c r="O824" s="4"/>
       <c r="P824" s="4"/>
     </row>
-    <row r="825" spans="1:16" ht="13.2">
+    <row r="825" spans="1:16" ht="12.75">
       <c r="A825" s="4"/>
       <c r="B825" s="2"/>
       <c r="C825" s="4"/>
@@ -17515,7 +17526,7 @@
       <c r="O825" s="4"/>
       <c r="P825" s="4"/>
     </row>
-    <row r="826" spans="1:16" ht="13.2">
+    <row r="826" spans="1:16" ht="12.75">
       <c r="A826" s="4"/>
       <c r="B826" s="2"/>
       <c r="C826" s="4"/>
@@ -17529,7 +17540,7 @@
       <c r="O826" s="4"/>
       <c r="P826" s="4"/>
     </row>
-    <row r="827" spans="1:16" ht="13.2">
+    <row r="827" spans="1:16" ht="12.75">
       <c r="A827" s="4"/>
       <c r="B827" s="2"/>
       <c r="C827" s="4"/>
@@ -17543,7 +17554,7 @@
       <c r="O827" s="4"/>
       <c r="P827" s="4"/>
     </row>
-    <row r="828" spans="1:16" ht="13.2">
+    <row r="828" spans="1:16" ht="12.75">
       <c r="A828" s="4"/>
       <c r="B828" s="2"/>
       <c r="C828" s="4"/>
@@ -17557,7 +17568,7 @@
       <c r="O828" s="4"/>
       <c r="P828" s="4"/>
     </row>
-    <row r="829" spans="1:16" ht="13.2">
+    <row r="829" spans="1:16" ht="12.75">
       <c r="A829" s="4"/>
       <c r="B829" s="2"/>
       <c r="C829" s="4"/>
@@ -17571,7 +17582,7 @@
       <c r="O829" s="4"/>
       <c r="P829" s="4"/>
     </row>
-    <row r="830" spans="1:16" ht="13.2">
+    <row r="830" spans="1:16" ht="12.75">
       <c r="A830" s="4"/>
       <c r="B830" s="2"/>
       <c r="C830" s="4"/>
@@ -17585,7 +17596,7 @@
       <c r="O830" s="4"/>
       <c r="P830" s="4"/>
     </row>
-    <row r="831" spans="1:16" ht="13.2">
+    <row r="831" spans="1:16" ht="12.75">
       <c r="A831" s="4"/>
       <c r="B831" s="2"/>
       <c r="C831" s="4"/>
@@ -17599,7 +17610,7 @@
       <c r="O831" s="4"/>
       <c r="P831" s="4"/>
     </row>
-    <row r="832" spans="1:16" ht="13.2">
+    <row r="832" spans="1:16" ht="12.75">
       <c r="A832" s="4"/>
       <c r="B832" s="2"/>
       <c r="C832" s="4"/>
@@ -17613,7 +17624,7 @@
       <c r="O832" s="4"/>
       <c r="P832" s="4"/>
     </row>
-    <row r="833" spans="1:16" ht="13.2">
+    <row r="833" spans="1:16" ht="12.75">
       <c r="A833" s="4"/>
       <c r="B833" s="2"/>
       <c r="C833" s="4"/>
@@ -17627,7 +17638,7 @@
       <c r="O833" s="4"/>
       <c r="P833" s="4"/>
     </row>
-    <row r="834" spans="1:16" ht="13.2">
+    <row r="834" spans="1:16" ht="12.75">
       <c r="A834" s="4"/>
       <c r="B834" s="2"/>
       <c r="C834" s="4"/>
@@ -17641,7 +17652,7 @@
       <c r="O834" s="4"/>
       <c r="P834" s="4"/>
     </row>
-    <row r="835" spans="1:16" ht="13.2">
+    <row r="835" spans="1:16" ht="12.75">
       <c r="A835" s="4"/>
       <c r="B835" s="2"/>
       <c r="C835" s="4"/>
@@ -17655,7 +17666,7 @@
       <c r="O835" s="4"/>
       <c r="P835" s="4"/>
     </row>
-    <row r="836" spans="1:16" ht="13.2">
+    <row r="836" spans="1:16" ht="12.75">
       <c r="A836" s="4"/>
       <c r="B836" s="2"/>
       <c r="C836" s="4"/>
@@ -17669,7 +17680,7 @@
       <c r="O836" s="4"/>
       <c r="P836" s="4"/>
     </row>
-    <row r="837" spans="1:16" ht="13.2">
+    <row r="837" spans="1:16" ht="12.75">
       <c r="A837" s="4"/>
       <c r="B837" s="2"/>
       <c r="C837" s="4"/>
@@ -17683,7 +17694,7 @@
       <c r="O837" s="4"/>
       <c r="P837" s="4"/>
     </row>
-    <row r="838" spans="1:16" ht="13.2">
+    <row r="838" spans="1:16" ht="12.75">
       <c r="A838" s="4"/>
       <c r="B838" s="2"/>
       <c r="C838" s="4"/>
@@ -17697,7 +17708,7 @@
       <c r="O838" s="4"/>
       <c r="P838" s="4"/>
     </row>
-    <row r="839" spans="1:16" ht="13.2">
+    <row r="839" spans="1:16" ht="12.75">
       <c r="A839" s="4"/>
       <c r="B839" s="2"/>
       <c r="C839" s="4"/>
@@ -17711,7 +17722,7 @@
       <c r="O839" s="4"/>
       <c r="P839" s="4"/>
     </row>
-    <row r="840" spans="1:16" ht="13.2">
+    <row r="840" spans="1:16" ht="12.75">
       <c r="A840" s="4"/>
       <c r="B840" s="2"/>
       <c r="C840" s="4"/>
@@ -17725,7 +17736,7 @@
       <c r="O840" s="4"/>
       <c r="P840" s="4"/>
     </row>
-    <row r="841" spans="1:16" ht="13.2">
+    <row r="841" spans="1:16" ht="12.75">
       <c r="A841" s="4"/>
       <c r="B841" s="2"/>
       <c r="C841" s="4"/>
@@ -17739,7 +17750,7 @@
       <c r="O841" s="4"/>
       <c r="P841" s="4"/>
     </row>
-    <row r="842" spans="1:16" ht="13.2">
+    <row r="842" spans="1:16" ht="12.75">
       <c r="A842" s="4"/>
       <c r="B842" s="2"/>
       <c r="C842" s="4"/>
@@ -17753,7 +17764,7 @@
       <c r="O842" s="4"/>
       <c r="P842" s="4"/>
     </row>
-    <row r="843" spans="1:16" ht="13.2">
+    <row r="843" spans="1:16" ht="12.75">
       <c r="A843" s="4"/>
       <c r="B843" s="2"/>
       <c r="C843" s="4"/>
@@ -17767,7 +17778,7 @@
       <c r="O843" s="4"/>
       <c r="P843" s="4"/>
     </row>
-    <row r="844" spans="1:16" ht="13.2">
+    <row r="844" spans="1:16" ht="12.75">
       <c r="A844" s="4"/>
       <c r="B844" s="2"/>
       <c r="C844" s="4"/>
@@ -17781,7 +17792,7 @@
       <c r="O844" s="4"/>
       <c r="P844" s="4"/>
     </row>
-    <row r="845" spans="1:16" ht="13.2">
+    <row r="845" spans="1:16" ht="12.75">
       <c r="A845" s="4"/>
       <c r="B845" s="2"/>
       <c r="C845" s="4"/>
@@ -17795,7 +17806,7 @@
       <c r="O845" s="4"/>
       <c r="P845" s="4"/>
     </row>
-    <row r="846" spans="1:16" ht="13.2">
+    <row r="846" spans="1:16" ht="12.75">
       <c r="A846" s="4"/>
       <c r="B846" s="2"/>
       <c r="C846" s="4"/>
@@ -17809,7 +17820,7 @@
       <c r="O846" s="4"/>
       <c r="P846" s="4"/>
     </row>
-    <row r="847" spans="1:16" ht="13.2">
+    <row r="847" spans="1:16" ht="12.75">
       <c r="A847" s="4"/>
       <c r="B847" s="2"/>
       <c r="C847" s="4"/>
@@ -17823,7 +17834,7 @@
       <c r="O847" s="4"/>
       <c r="P847" s="4"/>
     </row>
-    <row r="848" spans="1:16" ht="13.2">
+    <row r="848" spans="1:16" ht="12.75">
       <c r="A848" s="4"/>
       <c r="B848" s="2"/>
       <c r="C848" s="4"/>
@@ -17837,7 +17848,7 @@
       <c r="O848" s="4"/>
       <c r="P848" s="4"/>
     </row>
-    <row r="849" spans="1:16" ht="13.2">
+    <row r="849" spans="1:16" ht="12.75">
       <c r="A849" s="4"/>
       <c r="B849" s="2"/>
       <c r="C849" s="4"/>
@@ -17851,7 +17862,7 @@
       <c r="O849" s="4"/>
       <c r="P849" s="4"/>
     </row>
-    <row r="850" spans="1:16" ht="13.2">
+    <row r="850" spans="1:16" ht="12.75">
       <c r="A850" s="4"/>
       <c r="B850" s="2"/>
       <c r="C850" s="4"/>
@@ -17865,7 +17876,7 @@
       <c r="O850" s="4"/>
       <c r="P850" s="4"/>
     </row>
-    <row r="851" spans="1:16" ht="13.2">
+    <row r="851" spans="1:16" ht="12.75">
       <c r="A851" s="4"/>
       <c r="B851" s="2"/>
       <c r="C851" s="4"/>
@@ -17879,7 +17890,7 @@
       <c r="O851" s="4"/>
       <c r="P851" s="4"/>
     </row>
-    <row r="852" spans="1:16" ht="13.2">
+    <row r="852" spans="1:16" ht="12.75">
       <c r="A852" s="4"/>
       <c r="B852" s="2"/>
       <c r="C852" s="4"/>
@@ -17893,7 +17904,7 @@
       <c r="O852" s="4"/>
       <c r="P852" s="4"/>
     </row>
-    <row r="853" spans="1:16" ht="13.2">
+    <row r="853" spans="1:16" ht="12.75">
       <c r="A853" s="4"/>
       <c r="B853" s="2"/>
       <c r="C853" s="4"/>
@@ -17907,7 +17918,7 @@
       <c r="O853" s="4"/>
       <c r="P853" s="4"/>
     </row>
-    <row r="854" spans="1:16" ht="13.2">
+    <row r="854" spans="1:16" ht="12.75">
       <c r="A854" s="4"/>
       <c r="B854" s="2"/>
       <c r="C854" s="4"/>
@@ -17921,7 +17932,7 @@
       <c r="O854" s="4"/>
       <c r="P854" s="4"/>
     </row>
-    <row r="855" spans="1:16" ht="13.2">
+    <row r="855" spans="1:16" ht="12.75">
       <c r="A855" s="4"/>
       <c r="B855" s="2"/>
       <c r="C855" s="4"/>
@@ -17935,7 +17946,7 @@
       <c r="O855" s="4"/>
       <c r="P855" s="4"/>
     </row>
-    <row r="856" spans="1:16" ht="13.2">
+    <row r="856" spans="1:16" ht="12.75">
       <c r="A856" s="4"/>
       <c r="B856" s="2"/>
       <c r="C856" s="4"/>
@@ -17949,7 +17960,7 @@
       <c r="O856" s="4"/>
       <c r="P856" s="4"/>
     </row>
-    <row r="857" spans="1:16" ht="13.2">
+    <row r="857" spans="1:16" ht="12.75">
       <c r="A857" s="4"/>
       <c r="B857" s="2"/>
       <c r="C857" s="4"/>
@@ -17963,7 +17974,7 @@
       <c r="O857" s="4"/>
       <c r="P857" s="4"/>
     </row>
-    <row r="858" spans="1:16" ht="13.2">
+    <row r="858" spans="1:16" ht="12.75">
       <c r="A858" s="4"/>
       <c r="B858" s="2"/>
       <c r="C858" s="4"/>
@@ -17977,7 +17988,7 @@
       <c r="O858" s="4"/>
       <c r="P858" s="4"/>
     </row>
-    <row r="859" spans="1:16" ht="13.2">
+    <row r="859" spans="1:16" ht="12.75">
       <c r="A859" s="4"/>
       <c r="B859" s="2"/>
       <c r="C859" s="4"/>
@@ -17991,7 +18002,7 @@
       <c r="O859" s="4"/>
       <c r="P859" s="4"/>
     </row>
-    <row r="860" spans="1:16" ht="13.2">
+    <row r="860" spans="1:16" ht="12.75">
       <c r="A860" s="4"/>
       <c r="B860" s="2"/>
       <c r="C860" s="4"/>
@@ -18005,7 +18016,7 @@
       <c r="O860" s="4"/>
       <c r="P860" s="4"/>
     </row>
-    <row r="861" spans="1:16" ht="13.2">
+    <row r="861" spans="1:16" ht="12.75">
       <c r="A861" s="4"/>
       <c r="B861" s="2"/>
       <c r="C861" s="4"/>
@@ -18019,7 +18030,7 @@
       <c r="O861" s="4"/>
       <c r="P861" s="4"/>
     </row>
-    <row r="862" spans="1:16" ht="13.2">
+    <row r="862" spans="1:16" ht="12.75">
       <c r="A862" s="4"/>
       <c r="B862" s="2"/>
       <c r="C862" s="4"/>
@@ -18033,7 +18044,7 @@
       <c r="O862" s="4"/>
       <c r="P862" s="4"/>
     </row>
-    <row r="863" spans="1:16" ht="13.2">
+    <row r="863" spans="1:16" ht="12.75">
       <c r="A863" s="4"/>
       <c r="B863" s="2"/>
       <c r="C863" s="4"/>
@@ -18047,7 +18058,7 @@
       <c r="O863" s="4"/>
       <c r="P863" s="4"/>
     </row>
-    <row r="864" spans="1:16" ht="13.2">
+    <row r="864" spans="1:16" ht="12.75">
       <c r="A864" s="4"/>
       <c r="B864" s="2"/>
       <c r="C864" s="4"/>
@@ -18061,7 +18072,7 @@
       <c r="O864" s="4"/>
       <c r="P864" s="4"/>
     </row>
-    <row r="865" spans="1:16" ht="13.2">
+    <row r="865" spans="1:16" ht="12.75">
       <c r="A865" s="4"/>
       <c r="B865" s="2"/>
       <c r="C865" s="4"/>
@@ -18075,7 +18086,7 @@
       <c r="O865" s="4"/>
       <c r="P865" s="4"/>
     </row>
-    <row r="866" spans="1:16" ht="13.2">
+    <row r="866" spans="1:16" ht="12.75">
       <c r="A866" s="4"/>
       <c r="B866" s="2"/>
       <c r="C866" s="4"/>
@@ -18089,7 +18100,7 @@
       <c r="O866" s="4"/>
       <c r="P866" s="4"/>
     </row>
-    <row r="867" spans="1:16" ht="13.2">
+    <row r="867" spans="1:16" ht="12.75">
       <c r="A867" s="4"/>
       <c r="B867" s="2"/>
       <c r="C867" s="4"/>
@@ -18103,7 +18114,7 @@
       <c r="O867" s="4"/>
       <c r="P867" s="4"/>
     </row>
-    <row r="868" spans="1:16" ht="13.2">
+    <row r="868" spans="1:16" ht="12.75">
       <c r="A868" s="4"/>
       <c r="B868" s="2"/>
       <c r="C868" s="4"/>
@@ -18117,7 +18128,7 @@
       <c r="O868" s="4"/>
       <c r="P868" s="4"/>
     </row>
-    <row r="869" spans="1:16" ht="13.2">
+    <row r="869" spans="1:16" ht="12.75">
       <c r="A869" s="4"/>
       <c r="B869" s="2"/>
       <c r="C869" s="4"/>
@@ -18131,7 +18142,7 @@
       <c r="O869" s="4"/>
       <c r="P869" s="4"/>
     </row>
-    <row r="870" spans="1:16" ht="13.2">
+    <row r="870" spans="1:16" ht="12.75">
       <c r="A870" s="4"/>
       <c r="B870" s="2"/>
       <c r="C870" s="4"/>
@@ -18145,7 +18156,7 @@
       <c r="O870" s="4"/>
       <c r="P870" s="4"/>
     </row>
-    <row r="871" spans="1:16" ht="13.2">
+    <row r="871" spans="1:16" ht="12.75">
       <c r="A871" s="4"/>
       <c r="B871" s="2"/>
       <c r="C871" s="4"/>
@@ -18159,7 +18170,7 @@
       <c r="O871" s="4"/>
       <c r="P871" s="4"/>
     </row>
-    <row r="872" spans="1:16" ht="13.2">
+    <row r="872" spans="1:16" ht="12.75">
       <c r="A872" s="4"/>
       <c r="B872" s="2"/>
       <c r="C872" s="4"/>
@@ -18173,7 +18184,7 @@
       <c r="O872" s="4"/>
       <c r="P872" s="4"/>
     </row>
-    <row r="873" spans="1:16" ht="13.2">
+    <row r="873" spans="1:16" ht="12.75">
       <c r="A873" s="4"/>
       <c r="B873" s="2"/>
       <c r="C873" s="4"/>
@@ -18187,7 +18198,7 @@
       <c r="O873" s="4"/>
       <c r="P873" s="4"/>
     </row>
-    <row r="874" spans="1:16" ht="13.2">
+    <row r="874" spans="1:16" ht="12.75">
       <c r="A874" s="4"/>
       <c r="B874" s="2"/>
       <c r="C874" s="4"/>
@@ -18201,7 +18212,7 @@
       <c r="O874" s="4"/>
       <c r="P874" s="4"/>
     </row>
-    <row r="875" spans="1:16" ht="13.2">
+    <row r="875" spans="1:16" ht="12.75">
       <c r="A875" s="4"/>
       <c r="B875" s="2"/>
       <c r="C875" s="4"/>
@@ -18215,7 +18226,7 @@
       <c r="O875" s="4"/>
       <c r="P875" s="4"/>
     </row>
-    <row r="876" spans="1:16" ht="13.2">
+    <row r="876" spans="1:16" ht="12.75">
       <c r="A876" s="4"/>
       <c r="B876" s="2"/>
       <c r="C876" s="4"/>
@@ -18229,7 +18240,7 @@
       <c r="O876" s="4"/>
       <c r="P876" s="4"/>
     </row>
-    <row r="877" spans="1:16" ht="13.2">
+    <row r="877" spans="1:16" ht="12.75">
       <c r="A877" s="4"/>
       <c r="B877" s="2"/>
       <c r="C877" s="4"/>
@@ -18243,7 +18254,7 @@
       <c r="O877" s="4"/>
       <c r="P877" s="4"/>
     </row>
-    <row r="878" spans="1:16" ht="13.2">
+    <row r="878" spans="1:16" ht="12.75">
       <c r="A878" s="4"/>
       <c r="B878" s="2"/>
       <c r="C878" s="4"/>
@@ -18257,7 +18268,7 @@
       <c r="O878" s="4"/>
       <c r="P878" s="4"/>
     </row>
-    <row r="879" spans="1:16" ht="13.2">
+    <row r="879" spans="1:16" ht="12.75">
       <c r="A879" s="4"/>
       <c r="B879" s="2"/>
       <c r="C879" s="4"/>
@@ -18271,7 +18282,7 @@
       <c r="O879" s="4"/>
       <c r="P879" s="4"/>
     </row>
-    <row r="880" spans="1:16" ht="13.2">
+    <row r="880" spans="1:16" ht="12.75">
       <c r="A880" s="4"/>
       <c r="B880" s="2"/>
       <c r="C880" s="4"/>
@@ -18285,7 +18296,7 @@
       <c r="O880" s="4"/>
       <c r="P880" s="4"/>
     </row>
-    <row r="881" spans="1:16" ht="13.2">
+    <row r="881" spans="1:16" ht="12.75">
       <c r="A881" s="4"/>
       <c r="B881" s="2"/>
       <c r="C881" s="4"/>
@@ -18299,7 +18310,7 @@
       <c r="O881" s="4"/>
       <c r="P881" s="4"/>
     </row>
-    <row r="882" spans="1:16" ht="13.2">
+    <row r="882" spans="1:16" ht="12.75">
       <c r="A882" s="4"/>
       <c r="B882" s="2"/>
       <c r="C882" s="4"/>
@@ -18313,7 +18324,7 @@
       <c r="O882" s="4"/>
       <c r="P882" s="4"/>
     </row>
-    <row r="883" spans="1:16" ht="13.2">
+    <row r="883" spans="1:16" ht="12.75">
       <c r="A883" s="4"/>
       <c r="B883" s="2"/>
       <c r="C883" s="4"/>
@@ -18327,7 +18338,7 @@
       <c r="O883" s="4"/>
       <c r="P883" s="4"/>
     </row>
-    <row r="884" spans="1:16" ht="13.2">
+    <row r="884" spans="1:16" ht="12.75">
       <c r="A884" s="4"/>
       <c r="B884" s="2"/>
       <c r="C884" s="4"/>
@@ -18341,7 +18352,7 @@
       <c r="O884" s="4"/>
       <c r="P884" s="4"/>
     </row>
-    <row r="885" spans="1:16" ht="13.2">
+    <row r="885" spans="1:16" ht="12.75">
       <c r="A885" s="4"/>
       <c r="B885" s="2"/>
       <c r="C885" s="4"/>
@@ -18355,7 +18366,7 @@
       <c r="O885" s="4"/>
       <c r="P885" s="4"/>
     </row>
-    <row r="886" spans="1:16" ht="13.2">
+    <row r="886" spans="1:16" ht="12.75">
       <c r="A886" s="4"/>
       <c r="B886" s="2"/>
       <c r="C886" s="4"/>
@@ -18369,7 +18380,7 @@
       <c r="O886" s="4"/>
       <c r="P886" s="4"/>
     </row>
-    <row r="887" spans="1:16" ht="13.2">
+    <row r="887" spans="1:16" ht="12.75">
       <c r="A887" s="4"/>
       <c r="B887" s="2"/>
       <c r="C887" s="4"/>
@@ -18383,7 +18394,7 @@
       <c r="O887" s="4"/>
       <c r="P887" s="4"/>
     </row>
-    <row r="888" spans="1:16" ht="13.2">
+    <row r="888" spans="1:16" ht="12.75">
       <c r="A888" s="4"/>
       <c r="B888" s="2"/>
       <c r="C888" s="4"/>
@@ -18397,7 +18408,7 @@
       <c r="O888" s="4"/>
       <c r="P888" s="4"/>
     </row>
-    <row r="889" spans="1:16" ht="13.2">
+    <row r="889" spans="1:16" ht="12.75">
       <c r="A889" s="4"/>
       <c r="B889" s="2"/>
       <c r="C889" s="4"/>
@@ -18411,7 +18422,7 @@
       <c r="O889" s="4"/>
       <c r="P889" s="4"/>
     </row>
-    <row r="890" spans="1:16" ht="13.2">
+    <row r="890" spans="1:16" ht="12.75">
       <c r="A890" s="4"/>
       <c r="B890" s="2"/>
       <c r="C890" s="4"/>
@@ -18425,7 +18436,7 @@
       <c r="O890" s="4"/>
       <c r="P890" s="4"/>
     </row>
-    <row r="891" spans="1:16" ht="13.2">
+    <row r="891" spans="1:16" ht="12.75">
       <c r="A891" s="4"/>
       <c r="B891" s="2"/>
       <c r="C891" s="4"/>
@@ -18439,7 +18450,7 @@
       <c r="O891" s="4"/>
       <c r="P891" s="4"/>
     </row>
-    <row r="892" spans="1:16" ht="13.2">
+    <row r="892" spans="1:16" ht="12.75">
       <c r="A892" s="4"/>
       <c r="B892" s="2"/>
       <c r="C892" s="4"/>
@@ -18453,7 +18464,7 @@
       <c r="O892" s="4"/>
       <c r="P892" s="4"/>
     </row>
-    <row r="893" spans="1:16" ht="13.2">
+    <row r="893" spans="1:16" ht="12.75">
       <c r="A893" s="4"/>
       <c r="B893" s="2"/>
       <c r="C893" s="4"/>
@@ -18467,7 +18478,7 @@
       <c r="O893" s="4"/>
       <c r="P893" s="4"/>
     </row>
-    <row r="894" spans="1:16" ht="13.2">
+    <row r="894" spans="1:16" ht="12.75">
       <c r="A894" s="4"/>
       <c r="B894" s="2"/>
       <c r="C894" s="4"/>
@@ -18481,7 +18492,7 @@
       <c r="O894" s="4"/>
       <c r="P894" s="4"/>
     </row>
-    <row r="895" spans="1:16" ht="13.2">
+    <row r="895" spans="1:16" ht="12.75">
       <c r="A895" s="4"/>
       <c r="B895" s="2"/>
       <c r="C895" s="4"/>
@@ -18495,7 +18506,7 @@
       <c r="O895" s="4"/>
       <c r="P895" s="4"/>
     </row>
-    <row r="896" spans="1:16" ht="13.2">
+    <row r="896" spans="1:16" ht="12.75">
       <c r="A896" s="4"/>
       <c r="B896" s="2"/>
       <c r="C896" s="4"/>
@@ -18509,7 +18520,7 @@
       <c r="O896" s="4"/>
       <c r="P896" s="4"/>
     </row>
-    <row r="897" spans="1:16" ht="13.2">
+    <row r="897" spans="1:16" ht="12.75">
       <c r="A897" s="4"/>
       <c r="B897" s="2"/>
       <c r="C897" s="4"/>
@@ -18523,7 +18534,7 @@
       <c r="O897" s="4"/>
       <c r="P897" s="4"/>
     </row>
-    <row r="898" spans="1:16" ht="13.2">
+    <row r="898" spans="1:16" ht="12.75">
       <c r="A898" s="4"/>
       <c r="B898" s="2"/>
       <c r="C898" s="4"/>
@@ -18537,7 +18548,7 @@
       <c r="O898" s="4"/>
       <c r="P898" s="4"/>
     </row>
-    <row r="899" spans="1:16" ht="13.2">
+    <row r="899" spans="1:16" ht="12.75">
       <c r="A899" s="4"/>
       <c r="B899" s="2"/>
       <c r="C899" s="4"/>
@@ -18551,7 +18562,7 @@
       <c r="O899" s="4"/>
       <c r="P899" s="4"/>
     </row>
-    <row r="900" spans="1:16" ht="13.2">
+    <row r="900" spans="1:16" ht="12.75">
       <c r="A900" s="4"/>
       <c r="B900" s="2"/>
       <c r="C900" s="4"/>
@@ -18565,7 +18576,7 @@
       <c r="O900" s="4"/>
       <c r="P900" s="4"/>
     </row>
-    <row r="901" spans="1:16" ht="13.2">
+    <row r="901" spans="1:16" ht="12.75">
       <c r="A901" s="4"/>
       <c r="B901" s="2"/>
       <c r="C901" s="4"/>
@@ -18579,7 +18590,7 @@
       <c r="O901" s="4"/>
       <c r="P901" s="4"/>
     </row>
-    <row r="902" spans="1:16" ht="13.2">
+    <row r="902" spans="1:16" ht="12.75">
       <c r="A902" s="4"/>
       <c r="B902" s="2"/>
       <c r="C902" s="4"/>
@@ -18593,7 +18604,7 @@
       <c r="O902" s="4"/>
       <c r="P902" s="4"/>
     </row>
-    <row r="903" spans="1:16" ht="13.2">
+    <row r="903" spans="1:16" ht="12.75">
       <c r="A903" s="4"/>
       <c r="B903" s="2"/>
       <c r="C903" s="4"/>
@@ -18607,7 +18618,7 @@
       <c r="O903" s="4"/>
       <c r="P903" s="4"/>
     </row>
-    <row r="904" spans="1:16" ht="13.2">
+    <row r="904" spans="1:16" ht="12.75">
       <c r="A904" s="4"/>
       <c r="B904" s="2"/>
       <c r="C904" s="4"/>
@@ -18621,7 +18632,7 @@
       <c r="O904" s="4"/>
       <c r="P904" s="4"/>
     </row>
-    <row r="905" spans="1:16" ht="13.2">
+    <row r="905" spans="1:16" ht="12.75">
       <c r="A905" s="4"/>
       <c r="B905" s="2"/>
       <c r="C905" s="4"/>
@@ -18635,7 +18646,7 @@
       <c r="O905" s="4"/>
       <c r="P905" s="4"/>
     </row>
-    <row r="906" spans="1:16" ht="13.2">
+    <row r="906" spans="1:16" ht="12.75">
       <c r="A906" s="4"/>
       <c r="B906" s="2"/>
       <c r="C906" s="4"/>
@@ -18649,7 +18660,7 @@
       <c r="O906" s="4"/>
       <c r="P906" s="4"/>
     </row>
-    <row r="907" spans="1:16" ht="13.2">
+    <row r="907" spans="1:16" ht="12.75">
       <c r="A907" s="4"/>
       <c r="B907" s="2"/>
       <c r="C907" s="4"/>
@@ -18663,7 +18674,7 @@
       <c r="O907" s="4"/>
       <c r="P907" s="4"/>
     </row>
-    <row r="908" spans="1:16" ht="13.2">
+    <row r="908" spans="1:16" ht="12.75">
       <c r="A908" s="4"/>
       <c r="B908" s="2"/>
       <c r="C908" s="4"/>
@@ -18677,7 +18688,7 @@
       <c r="O908" s="4"/>
       <c r="P908" s="4"/>
     </row>
-    <row r="909" spans="1:16" ht="13.2">
+    <row r="909" spans="1:16" ht="12.75">
       <c r="A909" s="4"/>
       <c r="B909" s="2"/>
       <c r="C909" s="4"/>
@@ -18691,7 +18702,7 @@
       <c r="O909" s="4"/>
       <c r="P909" s="4"/>
     </row>
-    <row r="910" spans="1:16" ht="13.2">
+    <row r="910" spans="1:16" ht="12.75">
       <c r="A910" s="4"/>
       <c r="B910" s="2"/>
       <c r="C910" s="4"/>
@@ -18705,7 +18716,7 @@
       <c r="O910" s="4"/>
       <c r="P910" s="4"/>
     </row>
-    <row r="911" spans="1:16" ht="13.2">
+    <row r="911" spans="1:16" ht="12.75">
       <c r="A911" s="4"/>
       <c r="B911" s="2"/>
       <c r="C911" s="4"/>
@@ -18719,7 +18730,7 @@
       <c r="O911" s="4"/>
       <c r="P911" s="4"/>
     </row>
-    <row r="912" spans="1:16" ht="13.2">
+    <row r="912" spans="1:16" ht="12.75">
       <c r="A912" s="4"/>
       <c r="B912" s="2"/>
       <c r="C912" s="4"/>
@@ -18733,7 +18744,7 @@
       <c r="O912" s="4"/>
       <c r="P912" s="4"/>
     </row>
-    <row r="913" spans="1:16" ht="13.2">
+    <row r="913" spans="1:16" ht="12.75">
       <c r="A913" s="4"/>
       <c r="B913" s="2"/>
       <c r="C913" s="4"/>
@@ -18747,7 +18758,7 @@
       <c r="O913" s="4"/>
       <c r="P913" s="4"/>
     </row>
-    <row r="914" spans="1:16" ht="13.2">
+    <row r="914" spans="1:16" ht="12.75">
       <c r="A914" s="4"/>
       <c r="B914" s="2"/>
       <c r="C914" s="4"/>
@@ -18761,7 +18772,7 @@
       <c r="O914" s="4"/>
       <c r="P914" s="4"/>
     </row>
-    <row r="915" spans="1:16" ht="13.2">
+    <row r="915" spans="1:16" ht="12.75">
       <c r="A915" s="4"/>
       <c r="B915" s="2"/>
       <c r="C915" s="4"/>
@@ -18775,7 +18786,7 @@
       <c r="O915" s="4"/>
       <c r="P915" s="4"/>
     </row>
-    <row r="916" spans="1:16" ht="13.2">
+    <row r="916" spans="1:16" ht="12.75">
       <c r="A916" s="4"/>
       <c r="B916" s="2"/>
       <c r="C916" s="4"/>
@@ -18789,7 +18800,7 @@
       <c r="O916" s="4"/>
       <c r="P916" s="4"/>
     </row>
-    <row r="917" spans="1:16" ht="13.2">
+    <row r="917" spans="1:16" ht="12.75">
       <c r="A917" s="4"/>
       <c r="B917" s="2"/>
       <c r="C917" s="4"/>
@@ -18803,7 +18814,7 @@
       <c r="O917" s="4"/>
       <c r="P917" s="4"/>
     </row>
-    <row r="918" spans="1:16" ht="13.2">
+    <row r="918" spans="1:16" ht="12.75">
       <c r="A918" s="4"/>
       <c r="B918" s="2"/>
       <c r="C918" s="4"/>
@@ -18817,7 +18828,7 @@
       <c r="O918" s="4"/>
       <c r="P918" s="4"/>
     </row>
-    <row r="919" spans="1:16" ht="13.2">
+    <row r="919" spans="1:16" ht="12.75">
       <c r="A919" s="4"/>
       <c r="B919" s="2"/>
       <c r="C919" s="4"/>
@@ -18831,7 +18842,7 @@
       <c r="O919" s="4"/>
       <c r="P919" s="4"/>
     </row>
-    <row r="920" spans="1:16" ht="13.2">
+    <row r="920" spans="1:16" ht="12.75">
       <c r="A920" s="4"/>
       <c r="B920" s="2"/>
       <c r="C920" s="4"/>
@@ -18845,7 +18856,7 @@
       <c r="O920" s="4"/>
       <c r="P920" s="4"/>
     </row>
-    <row r="921" spans="1:16" ht="13.2">
+    <row r="921" spans="1:16" ht="12.75">
       <c r="A921" s="4"/>
       <c r="B921" s="2"/>
       <c r="C921" s="4"/>
@@ -18859,7 +18870,7 @@
       <c r="O921" s="4"/>
       <c r="P921" s="4"/>
     </row>
-    <row r="922" spans="1:16" ht="13.2">
+    <row r="922" spans="1:16" ht="12.75">
       <c r="A922" s="4"/>
       <c r="B922" s="2"/>
       <c r="C922" s="4"/>
@@ -18873,7 +18884,7 @@
       <c r="O922" s="4"/>
       <c r="P922" s="4"/>
     </row>
-    <row r="923" spans="1:16" ht="13.2">
+    <row r="923" spans="1:16" ht="12.75">
       <c r="A923" s="4"/>
       <c r="B923" s="2"/>
       <c r="C923" s="4"/>
@@ -18887,7 +18898,7 @@
       <c r="O923" s="4"/>
       <c r="P923" s="4"/>
     </row>
-    <row r="924" spans="1:16" ht="13.2">
+    <row r="924" spans="1:16" ht="12.75">
       <c r="A924" s="4"/>
       <c r="B924" s="2"/>
       <c r="C924" s="4"/>
@@ -18901,7 +18912,7 @@
       <c r="O924" s="4"/>
       <c r="P924" s="4"/>
     </row>
-    <row r="925" spans="1:16" ht="13.2">
+    <row r="925" spans="1:16" ht="12.75">
       <c r="A925" s="4"/>
       <c r="B925" s="2"/>
       <c r="C925" s="4"/>
@@ -18915,7 +18926,7 @@
       <c r="O925" s="4"/>
       <c r="P925" s="4"/>
     </row>
-    <row r="926" spans="1:16" ht="13.2">
+    <row r="926" spans="1:16" ht="12.75">
       <c r="A926" s="4"/>
       <c r="B926" s="2"/>
       <c r="C926" s="4"/>
@@ -18929,7 +18940,7 @@
       <c r="O926" s="4"/>
       <c r="P926" s="4"/>
     </row>
-    <row r="927" spans="1:16" ht="13.2">
+    <row r="927" spans="1:16" ht="12.75">
       <c r="A927" s="4"/>
       <c r="B927" s="2"/>
       <c r="C927" s="4"/>
@@ -18943,7 +18954,7 @@
       <c r="O927" s="4"/>
       <c r="P927" s="4"/>
     </row>
-    <row r="928" spans="1:16" ht="13.2">
+    <row r="928" spans="1:16" ht="12.75">
       <c r="A928" s="4"/>
       <c r="B928" s="2"/>
       <c r="C928" s="4"/>
@@ -18957,7 +18968,7 @@
       <c r="O928" s="4"/>
       <c r="P928" s="4"/>
     </row>
-    <row r="929" spans="1:16" ht="13.2">
+    <row r="929" spans="1:16" ht="12.75">
       <c r="A929" s="4"/>
       <c r="B929" s="2"/>
       <c r="C929" s="4"/>
@@ -18971,7 +18982,7 @@
       <c r="O929" s="4"/>
       <c r="P929" s="4"/>
     </row>
-    <row r="930" spans="1:16" ht="13.2">
+    <row r="930" spans="1:16" ht="12.75">
       <c r="A930" s="4"/>
       <c r="B930" s="2"/>
       <c r="C930" s="4"/>
@@ -18985,7 +18996,7 @@
       <c r="O930" s="4"/>
       <c r="P930" s="4"/>
     </row>
-    <row r="931" spans="1:16" ht="13.2">
+    <row r="931" spans="1:16" ht="12.75">
       <c r="A931" s="4"/>
       <c r="B931" s="2"/>
       <c r="C931" s="4"/>
@@ -18999,7 +19010,7 @@
       <c r="O931" s="4"/>
       <c r="P931" s="4"/>
     </row>
-    <row r="932" spans="1:16" ht="13.2">
+    <row r="932" spans="1:16" ht="12.75">
       <c r="A932" s="4"/>
       <c r="B932" s="2"/>
       <c r="C932" s="4"/>
@@ -19013,7 +19024,7 @@
       <c r="O932" s="4"/>
       <c r="P932" s="4"/>
     </row>
-    <row r="933" spans="1:16" ht="13.2">
+    <row r="933" spans="1:16" ht="12.75">
       <c r="A933" s="4"/>
       <c r="B933" s="2"/>
       <c r="C933" s="4"/>
@@ -19027,7 +19038,7 @@
       <c r="O933" s="4"/>
       <c r="P933" s="4"/>
     </row>
-    <row r="934" spans="1:16" ht="13.2">
+    <row r="934" spans="1:16" ht="12.75">
       <c r="A934" s="4"/>
       <c r="B934" s="2"/>
       <c r="C934" s="4"/>
@@ -19041,7 +19052,7 @@
       <c r="O934" s="4"/>
       <c r="P934" s="4"/>
     </row>
-    <row r="935" spans="1:16" ht="13.2">
+    <row r="935" spans="1:16" ht="12.75">
       <c r="A935" s="4"/>
       <c r="B935" s="2"/>
       <c r="C935" s="4"/>
@@ -19055,7 +19066,7 @@
       <c r="O935" s="4"/>
       <c r="P935" s="4"/>
     </row>
-    <row r="936" spans="1:16" ht="13.2">
+    <row r="936" spans="1:16" ht="12.75">
       <c r="A936" s="4"/>
       <c r="B936" s="2"/>
       <c r="C936" s="4"/>
@@ -19069,7 +19080,7 @@
       <c r="O936" s="4"/>
       <c r="P936" s="4"/>
     </row>
-    <row r="937" spans="1:16" ht="13.2">
+    <row r="937" spans="1:16" ht="12.75">
       <c r="A937" s="4"/>
       <c r="B937" s="2"/>
       <c r="C937" s="4"/>
@@ -19083,7 +19094,7 @@
       <c r="O937" s="4"/>
       <c r="P937" s="4"/>
     </row>
-    <row r="938" spans="1:16" ht="13.2">
+    <row r="938" spans="1:16" ht="12.75">
       <c r="A938" s="4"/>
       <c r="B938" s="2"/>
       <c r="C938" s="4"/>
@@ -19097,7 +19108,7 @@
       <c r="O938" s="4"/>
       <c r="P938" s="4"/>
     </row>
-    <row r="939" spans="1:16" ht="13.2">
+    <row r="939" spans="1:16" ht="12.75">
       <c r="A939" s="4"/>
       <c r="B939" s="2"/>
       <c r="C939" s="4"/>
@@ -19111,7 +19122,7 @@
       <c r="O939" s="4"/>
       <c r="P939" s="4"/>
     </row>
-    <row r="940" spans="1:16" ht="13.2">
+    <row r="940" spans="1:16" ht="12.75">
       <c r="A940" s="4"/>
       <c r="B940" s="2"/>
       <c r="C940" s="4"/>
@@ -19125,7 +19136,7 @@
       <c r="O940" s="4"/>
       <c r="P940" s="4"/>
     </row>
-    <row r="941" spans="1:16" ht="13.2">
+    <row r="941" spans="1:16" ht="12.75">
       <c r="A941" s="4"/>
       <c r="B941" s="2"/>
       <c r="C941" s="4"/>
@@ -19139,7 +19150,7 @@
       <c r="O941" s="4"/>
       <c r="P941" s="4"/>
     </row>
-    <row r="942" spans="1:16" ht="13.2">
+    <row r="942" spans="1:16" ht="12.75">
       <c r="A942" s="4"/>
       <c r="B942" s="2"/>
       <c r="C942" s="4"/>
@@ -19153,7 +19164,7 @@
       <c r="O942" s="4"/>
       <c r="P942" s="4"/>
     </row>
-    <row r="943" spans="1:16" ht="13.2">
+    <row r="943" spans="1:16" ht="12.75">
       <c r="A943" s="4"/>
       <c r="B943" s="2"/>
       <c r="C943" s="4"/>
@@ -19167,7 +19178,7 @@
       <c r="O943" s="4"/>
       <c r="P943" s="4"/>
     </row>
-    <row r="944" spans="1:16" ht="13.2">
+    <row r="944" spans="1:16" ht="12.75">
       <c r="A944" s="4"/>
       <c r="B944" s="2"/>
       <c r="C944" s="4"/>
@@ -19181,7 +19192,7 @@
       <c r="O944" s="4"/>
       <c r="P944" s="4"/>
     </row>
-    <row r="945" spans="1:16" ht="13.2">
+    <row r="945" spans="1:16" ht="12.75">
       <c r="A945" s="4"/>
       <c r="B945" s="2"/>
       <c r="C945" s="4"/>
@@ -19195,7 +19206,7 @@
       <c r="O945" s="4"/>
       <c r="P945" s="4"/>
     </row>
-    <row r="946" spans="1:16" ht="13.2">
+    <row r="946" spans="1:16" ht="12.75">
       <c r="A946" s="4"/>
       <c r="B946" s="2"/>
       <c r="C946" s="4"/>
@@ -19209,7 +19220,7 @@
       <c r="O946" s="4"/>
       <c r="P946" s="4"/>
     </row>
-    <row r="947" spans="1:16" ht="13.2">
+    <row r="947" spans="1:16" ht="12.75">
       <c r="A947" s="4"/>
       <c r="B947" s="2"/>
       <c r="C947" s="4"/>
@@ -19223,7 +19234,7 @@
       <c r="O947" s="4"/>
       <c r="P947" s="4"/>
     </row>
-    <row r="948" spans="1:16" ht="13.2">
+    <row r="948" spans="1:16" ht="12.75">
       <c r="A948" s="4"/>
       <c r="B948" s="2"/>
       <c r="C948" s="4"/>
@@ -19237,7 +19248,7 @@
       <c r="O948" s="4"/>
       <c r="P948" s="4"/>
     </row>
-    <row r="949" spans="1:16" ht="13.2">
+    <row r="949" spans="1:16" ht="12.75">
       <c r="A949" s="4"/>
       <c r="B949" s="2"/>
       <c r="C949" s="4"/>
@@ -19251,7 +19262,7 @@
       <c r="O949" s="4"/>
       <c r="P949" s="4"/>
     </row>
-    <row r="950" spans="1:16" ht="13.2">
+    <row r="950" spans="1:16" ht="12.75">
       <c r="A950" s="4"/>
       <c r="B950" s="2"/>
       <c r="C950" s="4"/>
@@ -19265,7 +19276,7 @@
       <c r="O950" s="4"/>
       <c r="P950" s="4"/>
     </row>
-    <row r="951" spans="1:16" ht="13.2">
+    <row r="951" spans="1:16" ht="12.75">
       <c r="A951" s="4"/>
       <c r="B951" s="2"/>
       <c r="C951" s="4"/>
@@ -19279,7 +19290,7 @@
       <c r="O951" s="4"/>
       <c r="P951" s="4"/>
     </row>
-    <row r="952" spans="1:16" ht="13.2">
+    <row r="952" spans="1:16" ht="12.75">
       <c r="B952" s="2"/>
       <c r="C952" s="4"/>
       <c r="D952" s="4"/>
@@ -19289,7 +19300,7 @@
       <c r="L952" s="4"/>
       <c r="O952" s="4"/>
     </row>
-    <row r="953" spans="1:16" ht="13.2">
+    <row r="953" spans="1:16" ht="12.75">
       <c r="B953" s="2"/>
       <c r="C953" s="4"/>
       <c r="D953" s="4"/>
@@ -19299,7 +19310,7 @@
       <c r="L953" s="4"/>
       <c r="O953" s="4"/>
     </row>
-    <row r="954" spans="1:16" ht="13.2">
+    <row r="954" spans="1:16" ht="12.75">
       <c r="B954" s="2"/>
       <c r="C954" s="4"/>
       <c r="D954" s="4"/>
@@ -19309,7 +19320,7 @@
       <c r="L954" s="4"/>
       <c r="O954" s="4"/>
     </row>
-    <row r="955" spans="1:16" ht="13.2">
+    <row r="955" spans="1:16" ht="12.75">
       <c r="B955" s="2"/>
       <c r="C955" s="4"/>
       <c r="D955" s="4"/>
@@ -19319,7 +19330,7 @@
       <c r="L955" s="4"/>
       <c r="O955" s="4"/>
     </row>
-    <row r="956" spans="1:16" ht="13.2">
+    <row r="956" spans="1:16" ht="12.75">
       <c r="B956" s="2"/>
       <c r="C956" s="4"/>
       <c r="D956" s="4"/>
@@ -19329,7 +19340,7 @@
       <c r="L956" s="4"/>
       <c r="O956" s="4"/>
     </row>
-    <row r="957" spans="1:16" ht="13.2">
+    <row r="957" spans="1:16" ht="12.75">
       <c r="B957" s="2"/>
       <c r="C957" s="4"/>
       <c r="D957" s="4"/>
@@ -19339,7 +19350,7 @@
       <c r="L957" s="4"/>
       <c r="O957" s="4"/>
     </row>
-    <row r="958" spans="1:16" ht="13.2">
+    <row r="958" spans="1:16" ht="12.75">
       <c r="B958" s="2"/>
       <c r="C958" s="4"/>
       <c r="D958" s="4"/>
@@ -19349,7 +19360,7 @@
       <c r="L958" s="4"/>
       <c r="O958" s="4"/>
     </row>
-    <row r="959" spans="1:16" ht="13.2">
+    <row r="959" spans="1:16" ht="12.75">
       <c r="B959" s="2"/>
       <c r="C959" s="4"/>
       <c r="D959" s="4"/>
@@ -19359,7 +19370,7 @@
       <c r="L959" s="4"/>
       <c r="O959" s="4"/>
     </row>
-    <row r="960" spans="1:16" ht="13.2">
+    <row r="960" spans="1:16" ht="12.75">
       <c r="B960" s="2"/>
       <c r="C960" s="4"/>
       <c r="D960" s="4"/>
@@ -19369,7 +19380,7 @@
       <c r="L960" s="4"/>
       <c r="O960" s="4"/>
     </row>
-    <row r="961" spans="2:15" ht="13.2">
+    <row r="961" spans="2:15" ht="12.75">
       <c r="B961" s="2"/>
       <c r="C961" s="4"/>
       <c r="D961" s="4"/>
@@ -19379,7 +19390,7 @@
       <c r="L961" s="4"/>
       <c r="O961" s="4"/>
     </row>
-    <row r="962" spans="2:15" ht="13.2">
+    <row r="962" spans="2:15" ht="12.75">
       <c r="B962" s="2"/>
       <c r="C962" s="4"/>
       <c r="D962" s="4"/>
@@ -19389,7 +19400,7 @@
       <c r="L962" s="4"/>
       <c r="O962" s="4"/>
     </row>
-    <row r="963" spans="2:15" ht="13.2">
+    <row r="963" spans="2:15" ht="12.75">
       <c r="B963" s="2"/>
       <c r="C963" s="4"/>
       <c r="D963" s="4"/>
@@ -19399,7 +19410,7 @@
       <c r="L963" s="4"/>
       <c r="O963" s="4"/>
     </row>
-    <row r="964" spans="2:15" ht="13.2">
+    <row r="964" spans="2:15" ht="12.75">
       <c r="B964" s="2"/>
       <c r="C964" s="4"/>
       <c r="D964" s="4"/>
@@ -19409,7 +19420,7 @@
       <c r="L964" s="4"/>
       <c r="O964" s="4"/>
     </row>
-    <row r="965" spans="2:15" ht="13.2">
+    <row r="965" spans="2:15" ht="12.75">
       <c r="B965" s="4"/>
       <c r="C965" s="4"/>
       <c r="D965" s="4"/>
@@ -19419,7 +19430,7 @@
       <c r="L965" s="4"/>
       <c r="O965" s="4"/>
     </row>
-    <row r="966" spans="2:15" ht="13.2">
+    <row r="966" spans="2:15" ht="12.75">
       <c r="B966" s="4"/>
       <c r="C966" s="4"/>
       <c r="D966" s="4"/>
@@ -19429,7 +19440,7 @@
       <c r="L966" s="4"/>
       <c r="O966" s="4"/>
     </row>
-    <row r="967" spans="2:15" ht="13.2">
+    <row r="967" spans="2:15" ht="12.75">
       <c r="B967" s="4"/>
       <c r="C967" s="4"/>
       <c r="D967" s="4"/>
@@ -19439,7 +19450,7 @@
       <c r="L967" s="4"/>
       <c r="O967" s="4"/>
     </row>
-    <row r="968" spans="2:15" ht="13.2">
+    <row r="968" spans="2:15" ht="12.75">
       <c r="B968" s="4"/>
       <c r="C968" s="4"/>
       <c r="D968" s="4"/>
@@ -19449,7 +19460,7 @@
       <c r="L968" s="4"/>
       <c r="O968" s="4"/>
     </row>
-    <row r="969" spans="2:15" ht="13.2">
+    <row r="969" spans="2:15" ht="12.75">
       <c r="B969" s="4"/>
       <c r="C969" s="4"/>
       <c r="D969" s="4"/>
@@ -19459,7 +19470,7 @@
       <c r="L969" s="4"/>
       <c r="O969" s="4"/>
     </row>
-    <row r="970" spans="2:15" ht="13.2">
+    <row r="970" spans="2:15" ht="12.75">
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
       <c r="D970" s="4"/>
@@ -19469,7 +19480,7 @@
       <c r="L970" s="4"/>
       <c r="O970" s="4"/>
     </row>
-    <row r="971" spans="2:15" ht="13.2">
+    <row r="971" spans="2:15" ht="12.75">
       <c r="B971" s="4"/>
       <c r="C971" s="4"/>
       <c r="D971" s="4"/>
@@ -19479,7 +19490,7 @@
       <c r="L971" s="4"/>
       <c r="O971" s="4"/>
     </row>
-    <row r="972" spans="2:15" ht="13.2">
+    <row r="972" spans="2:15" ht="12.75">
       <c r="B972" s="4"/>
       <c r="C972" s="4"/>
       <c r="D972" s="4"/>
@@ -19489,7 +19500,7 @@
       <c r="L972" s="4"/>
       <c r="O972" s="4"/>
     </row>
-    <row r="973" spans="2:15" ht="13.2">
+    <row r="973" spans="2:15" ht="12.75">
       <c r="B973" s="4"/>
       <c r="C973" s="4"/>
       <c r="D973" s="4"/>
@@ -19499,7 +19510,7 @@
       <c r="L973" s="4"/>
       <c r="O973" s="4"/>
     </row>
-    <row r="974" spans="2:15" ht="13.2">
+    <row r="974" spans="2:15" ht="12.75">
       <c r="B974" s="4"/>
       <c r="C974" s="4"/>
       <c r="D974" s="4"/>
@@ -19509,7 +19520,7 @@
       <c r="L974" s="4"/>
       <c r="O974" s="4"/>
     </row>
-    <row r="975" spans="2:15" ht="13.2">
+    <row r="975" spans="2:15" ht="12.75">
       <c r="B975" s="4"/>
       <c r="C975" s="4"/>
       <c r="D975" s="4"/>
@@ -19519,7 +19530,7 @@
       <c r="L975" s="4"/>
       <c r="O975" s="4"/>
     </row>
-    <row r="976" spans="2:15" ht="13.2">
+    <row r="976" spans="2:15" ht="12.75">
       <c r="B976" s="4"/>
       <c r="C976" s="4"/>
       <c r="D976" s="4"/>
@@ -19529,7 +19540,7 @@
       <c r="L976" s="4"/>
       <c r="O976" s="4"/>
     </row>
-    <row r="977" spans="2:15" ht="13.2">
+    <row r="977" spans="2:15" ht="12.75">
       <c r="B977" s="4"/>
       <c r="C977" s="4"/>
       <c r="D977" s="4"/>
@@ -19539,7 +19550,7 @@
       <c r="L977" s="4"/>
       <c r="O977" s="4"/>
     </row>
-    <row r="978" spans="2:15" ht="13.2">
+    <row r="978" spans="2:15" ht="12.75">
       <c r="B978" s="4"/>
       <c r="C978" s="4"/>
       <c r="D978" s="4"/>
@@ -19549,7 +19560,7 @@
       <c r="L978" s="4"/>
       <c r="O978" s="4"/>
     </row>
-    <row r="979" spans="2:15" ht="13.2">
+    <row r="979" spans="2:15" ht="12.75">
       <c r="B979" s="4"/>
       <c r="C979" s="4"/>
       <c r="D979" s="4"/>
@@ -19559,7 +19570,7 @@
       <c r="L979" s="4"/>
       <c r="O979" s="4"/>
     </row>
-    <row r="980" spans="2:15" ht="13.2">
+    <row r="980" spans="2:15" ht="12.75">
       <c r="B980" s="4"/>
       <c r="C980" s="4"/>
       <c r="D980" s="4"/>
@@ -19569,7 +19580,7 @@
       <c r="L980" s="4"/>
       <c r="O980" s="4"/>
     </row>
-    <row r="981" spans="2:15" ht="13.2">
+    <row r="981" spans="2:15" ht="12.75">
       <c r="B981" s="4"/>
       <c r="C981" s="4"/>
       <c r="D981" s="4"/>
@@ -19579,7 +19590,7 @@
       <c r="L981" s="4"/>
       <c r="O981" s="4"/>
     </row>
-    <row r="982" spans="2:15" ht="13.2">
+    <row r="982" spans="2:15" ht="12.75">
       <c r="B982" s="4"/>
       <c r="C982" s="4"/>
       <c r="D982" s="4"/>
@@ -19589,7 +19600,7 @@
       <c r="L982" s="4"/>
       <c r="O982" s="4"/>
     </row>
-    <row r="983" spans="2:15" ht="13.2">
+    <row r="983" spans="2:15" ht="12.75">
       <c r="B983" s="4"/>
       <c r="C983" s="4"/>
       <c r="D983" s="4"/>
@@ -19599,7 +19610,7 @@
       <c r="L983" s="4"/>
       <c r="O983" s="4"/>
     </row>
-    <row r="984" spans="2:15" ht="13.2">
+    <row r="984" spans="2:15" ht="12.75">
       <c r="B984" s="4"/>
       <c r="C984" s="4"/>
       <c r="D984" s="4"/>
@@ -19609,7 +19620,7 @@
       <c r="L984" s="4"/>
       <c r="O984" s="4"/>
     </row>
-    <row r="985" spans="2:15" ht="13.2">
+    <row r="985" spans="2:15" ht="12.75">
       <c r="B985" s="4"/>
       <c r="C985" s="4"/>
       <c r="D985" s="4"/>
@@ -19619,7 +19630,7 @@
       <c r="L985" s="4"/>
       <c r="O985" s="4"/>
     </row>
-    <row r="986" spans="2:15" ht="13.2">
+    <row r="986" spans="2:15" ht="12.75">
       <c r="B986" s="4"/>
       <c r="C986" s="4"/>
       <c r="D986" s="4"/>
@@ -19629,7 +19640,7 @@
       <c r="L986" s="4"/>
       <c r="O986" s="4"/>
     </row>
-    <row r="987" spans="2:15" ht="13.2">
+    <row r="987" spans="2:15" ht="12.75">
       <c r="B987" s="4"/>
       <c r="C987" s="4"/>
       <c r="D987" s="4"/>
@@ -19639,7 +19650,7 @@
       <c r="L987" s="4"/>
       <c r="O987" s="4"/>
     </row>
-    <row r="988" spans="2:15" ht="13.2">
+    <row r="988" spans="2:15" ht="12.75">
       <c r="B988" s="4"/>
       <c r="C988" s="4"/>
       <c r="D988" s="4"/>
@@ -19649,7 +19660,7 @@
       <c r="L988" s="4"/>
       <c r="O988" s="4"/>
     </row>
-    <row r="989" spans="2:15" ht="13.2">
+    <row r="989" spans="2:15" ht="12.75">
       <c r="B989" s="4"/>
       <c r="C989" s="4"/>
       <c r="D989" s="4"/>
@@ -19659,7 +19670,7 @@
       <c r="L989" s="4"/>
       <c r="O989" s="4"/>
     </row>
-    <row r="990" spans="2:15" ht="13.2">
+    <row r="990" spans="2:15" ht="12.75">
       <c r="B990" s="4"/>
       <c r="C990" s="4"/>
       <c r="D990" s="4"/>
@@ -19669,7 +19680,7 @@
       <c r="L990" s="4"/>
       <c r="O990" s="4"/>
     </row>
-    <row r="991" spans="2:15" ht="13.2">
+    <row r="991" spans="2:15" ht="12.75">
       <c r="B991" s="4"/>
       <c r="C991" s="4"/>
       <c r="D991" s="4"/>
@@ -19679,7 +19690,7 @@
       <c r="L991" s="4"/>
       <c r="O991" s="4"/>
     </row>
-    <row r="992" spans="2:15" ht="13.2">
+    <row r="992" spans="2:15" ht="12.75">
       <c r="B992" s="4"/>
       <c r="C992" s="4"/>
       <c r="D992" s="4"/>
@@ -19689,7 +19700,7 @@
       <c r="L992" s="4"/>
       <c r="O992" s="4"/>
     </row>
-    <row r="993" spans="2:15" ht="13.2">
+    <row r="993" spans="2:15" ht="12.75">
       <c r="B993" s="4"/>
       <c r="C993" s="4"/>
       <c r="D993" s="4"/>
@@ -19699,7 +19710,7 @@
       <c r="L993" s="4"/>
       <c r="O993" s="4"/>
     </row>
-    <row r="994" spans="2:15" ht="13.2">
+    <row r="994" spans="2:15" ht="12.75">
       <c r="B994" s="4"/>
       <c r="C994" s="4"/>
       <c r="D994" s="4"/>
@@ -19709,7 +19720,7 @@
       <c r="L994" s="4"/>
       <c r="O994" s="4"/>
     </row>
-    <row r="995" spans="2:15" ht="13.2">
+    <row r="995" spans="2:15" ht="12.75">
       <c r="B995" s="4"/>
       <c r="C995" s="4"/>
       <c r="D995" s="4"/>
@@ -19719,7 +19730,7 @@
       <c r="L995" s="4"/>
       <c r="O995" s="4"/>
     </row>
-    <row r="996" spans="2:15" ht="13.2">
+    <row r="996" spans="2:15" ht="12.75">
       <c r="B996" s="4"/>
       <c r="C996" s="4"/>
       <c r="D996" s="4"/>
@@ -19729,7 +19740,7 @@
       <c r="L996" s="4"/>
       <c r="O996" s="4"/>
     </row>
-    <row r="997" spans="2:15" ht="13.2">
+    <row r="997" spans="2:15" ht="12.75">
       <c r="B997" s="4"/>
       <c r="C997" s="4"/>
       <c r="D997" s="4"/>
@@ -19739,7 +19750,7 @@
       <c r="L997" s="4"/>
       <c r="O997" s="4"/>
     </row>
-    <row r="998" spans="2:15" ht="13.2">
+    <row r="998" spans="2:15" ht="12.75">
       <c r="B998" s="4"/>
       <c r="C998" s="4"/>
       <c r="D998" s="4"/>
@@ -19749,7 +19760,7 @@
       <c r="L998" s="4"/>
       <c r="O998" s="4"/>
     </row>
-    <row r="999" spans="2:15" ht="13.2">
+    <row r="999" spans="2:15" ht="12.75">
       <c r="B999" s="4"/>
       <c r="C999" s="4"/>
       <c r="D999" s="4"/>
@@ -19759,7 +19770,7 @@
       <c r="L999" s="4"/>
       <c r="O999" s="4"/>
     </row>
-    <row r="1000" spans="2:15" ht="13.2">
+    <row r="1000" spans="2:15" ht="12.75">
       <c r="B1000" s="4"/>
       <c r="C1000" s="4"/>
       <c r="D1000" s="4"/>
@@ -19769,7 +19780,7 @@
       <c r="L1000" s="4"/>
       <c r="O1000" s="4"/>
     </row>
-    <row r="1001" spans="2:15" ht="13.2">
+    <row r="1001" spans="2:15" ht="12.75">
       <c r="B1001" s="4"/>
       <c r="C1001" s="4"/>
       <c r="D1001" s="4"/>
@@ -19779,7 +19790,7 @@
       <c r="L1001" s="4"/>
       <c r="O1001" s="4"/>
     </row>
-    <row r="1002" spans="2:15" ht="13.2">
+    <row r="1002" spans="2:15" ht="12.75">
       <c r="B1002" s="4"/>
       <c r="C1002" s="4"/>
       <c r="D1002" s="4"/>
@@ -19789,7 +19800,7 @@
       <c r="L1002" s="4"/>
       <c r="O1002" s="4"/>
     </row>
-    <row r="1003" spans="2:15" ht="13.2">
+    <row r="1003" spans="2:15" ht="12.75">
       <c r="B1003" s="4"/>
       <c r="C1003" s="4"/>
       <c r="D1003" s="4"/>
@@ -19799,7 +19810,7 @@
       <c r="L1003" s="4"/>
       <c r="O1003" s="4"/>
     </row>
-    <row r="1004" spans="2:15" ht="13.2">
+    <row r="1004" spans="2:15" ht="12.75">
       <c r="B1004" s="4"/>
       <c r="C1004" s="4"/>
       <c r="D1004" s="4"/>
@@ -19809,7 +19820,7 @@
       <c r="L1004" s="4"/>
       <c r="O1004" s="4"/>
     </row>
-    <row r="1005" spans="2:15" ht="13.2">
+    <row r="1005" spans="2:15" ht="12.75">
       <c r="B1005" s="4"/>
       <c r="C1005" s="4"/>
       <c r="D1005" s="4"/>
@@ -19819,7 +19830,7 @@
       <c r="L1005" s="4"/>
       <c r="O1005" s="4"/>
     </row>
-    <row r="1006" spans="2:15" ht="13.2">
+    <row r="1006" spans="2:15" ht="12.75">
       <c r="B1006" s="4"/>
       <c r="C1006" s="4"/>
       <c r="D1006" s="4"/>
@@ -19829,7 +19840,7 @@
       <c r="L1006" s="4"/>
       <c r="O1006" s="4"/>
     </row>
-    <row r="1007" spans="2:15" ht="13.2">
+    <row r="1007" spans="2:15" ht="12.75">
       <c r="B1007" s="4"/>
       <c r="C1007" s="4"/>
       <c r="D1007" s="4"/>
@@ -19839,7 +19850,7 @@
       <c r="L1007" s="4"/>
       <c r="O1007" s="4"/>
     </row>
-    <row r="1008" spans="2:15" ht="13.2">
+    <row r="1008" spans="2:15" ht="12.75">
       <c r="B1008" s="4"/>
       <c r="C1008" s="4"/>
       <c r="D1008" s="4"/>
@@ -19849,7 +19860,7 @@
       <c r="L1008" s="4"/>
       <c r="O1008" s="4"/>
     </row>
-    <row r="1009" spans="2:15" ht="13.2">
+    <row r="1009" spans="2:15" ht="12.75">
       <c r="B1009" s="4"/>
       <c r="C1009" s="4"/>
       <c r="D1009" s="4"/>
@@ -19859,7 +19870,7 @@
       <c r="L1009" s="4"/>
       <c r="O1009" s="4"/>
     </row>
-    <row r="1010" spans="2:15" ht="13.2">
+    <row r="1010" spans="2:15" ht="12.75">
       <c r="B1010" s="4"/>
       <c r="C1010" s="4"/>
       <c r="D1010" s="4"/>
@@ -19869,7 +19880,7 @@
       <c r="L1010" s="4"/>
       <c r="O1010" s="4"/>
     </row>
-    <row r="1011" spans="2:15" ht="13.2">
+    <row r="1011" spans="2:15" ht="12.75">
       <c r="B1011" s="4"/>
       <c r="C1011" s="4"/>
       <c r="D1011" s="4"/>
@@ -19879,7 +19890,7 @@
       <c r="L1011" s="4"/>
       <c r="O1011" s="4"/>
     </row>
-    <row r="1012" spans="2:15" ht="13.2">
+    <row r="1012" spans="2:15" ht="12.75">
       <c r="B1012" s="4"/>
       <c r="C1012" s="4"/>
       <c r="D1012" s="4"/>
@@ -19889,7 +19900,7 @@
       <c r="L1012" s="4"/>
       <c r="O1012" s="4"/>
     </row>
-    <row r="1013" spans="2:15" ht="13.2">
+    <row r="1013" spans="2:15" ht="12.75">
       <c r="B1013" s="4"/>
       <c r="C1013" s="4"/>
       <c r="D1013" s="4"/>
@@ -19899,7 +19910,7 @@
       <c r="L1013" s="4"/>
       <c r="O1013" s="4"/>
     </row>
-    <row r="1014" spans="2:15" ht="13.2">
+    <row r="1014" spans="2:15" ht="12.75">
       <c r="B1014" s="4"/>
       <c r="C1014" s="4"/>
       <c r="D1014" s="4"/>
@@ -19909,7 +19920,7 @@
       <c r="L1014" s="4"/>
       <c r="O1014" s="4"/>
     </row>
-    <row r="1015" spans="2:15" ht="13.2">
+    <row r="1015" spans="2:15" ht="12.75">
       <c r="B1015" s="4"/>
       <c r="C1015" s="4"/>
       <c r="D1015" s="4"/>
@@ -19919,7 +19930,7 @@
       <c r="L1015" s="4"/>
       <c r="O1015" s="4"/>
     </row>
-    <row r="1016" spans="2:15" ht="13.2">
+    <row r="1016" spans="2:15" ht="12.75">
       <c r="B1016" s="4"/>
       <c r="C1016" s="4"/>
       <c r="D1016" s="4"/>
@@ -19929,7 +19940,7 @@
       <c r="L1016" s="4"/>
       <c r="O1016" s="4"/>
     </row>
-    <row r="1017" spans="2:15" ht="13.2">
+    <row r="1017" spans="2:15" ht="12.75">
       <c r="B1017" s="4"/>
       <c r="C1017" s="4"/>
       <c r="D1017" s="4"/>
@@ -19939,7 +19950,7 @@
       <c r="L1017" s="4"/>
       <c r="O1017" s="4"/>
     </row>
-    <row r="1018" spans="2:15" ht="13.2">
+    <row r="1018" spans="2:15" ht="12.75">
       <c r="B1018" s="4"/>
       <c r="C1018" s="4"/>
       <c r="D1018" s="4"/>
@@ -19949,7 +19960,7 @@
       <c r="L1018" s="4"/>
       <c r="O1018" s="4"/>
     </row>
-    <row r="1019" spans="2:15" ht="13.2">
+    <row r="1019" spans="2:15" ht="12.75">
       <c r="B1019" s="4"/>
       <c r="C1019" s="4"/>
       <c r="D1019" s="4"/>
@@ -19959,7 +19970,7 @@
       <c r="L1019" s="4"/>
       <c r="O1019" s="4"/>
     </row>
-    <row r="1020" spans="2:15" ht="13.2">
+    <row r="1020" spans="2:15" ht="12.75">
       <c r="B1020" s="4"/>
       <c r="C1020" s="4"/>
       <c r="D1020" s="4"/>
@@ -19969,7 +19980,7 @@
       <c r="L1020" s="4"/>
       <c r="O1020" s="4"/>
     </row>
-    <row r="1021" spans="2:15" ht="13.2">
+    <row r="1021" spans="2:15" ht="12.75">
       <c r="B1021" s="4"/>
       <c r="C1021" s="4"/>
       <c r="D1021" s="4"/>
@@ -19979,7 +19990,7 @@
       <c r="L1021" s="4"/>
       <c r="O1021" s="4"/>
     </row>
-    <row r="1022" spans="2:15" ht="13.2">
+    <row r="1022" spans="2:15" ht="12.75">
       <c r="B1022" s="4"/>
       <c r="C1022" s="4"/>
       <c r="D1022" s="4"/>
@@ -19989,7 +20000,7 @@
       <c r="L1022" s="4"/>
       <c r="O1022" s="4"/>
     </row>
-    <row r="1023" spans="2:15" ht="13.2">
+    <row r="1023" spans="2:15" ht="12.75">
       <c r="B1023" s="4"/>
       <c r="C1023" s="4"/>
       <c r="D1023" s="4"/>
@@ -19999,7 +20010,7 @@
       <c r="L1023" s="4"/>
       <c r="O1023" s="4"/>
     </row>
-    <row r="1024" spans="2:15" ht="13.2">
+    <row r="1024" spans="2:15" ht="12.75">
       <c r="B1024" s="4"/>
       <c r="C1024" s="4"/>
       <c r="D1024" s="4"/>
@@ -20009,7 +20020,7 @@
       <c r="L1024" s="4"/>
       <c r="O1024" s="4"/>
     </row>
-    <row r="1025" spans="2:15" ht="13.2">
+    <row r="1025" spans="2:15" ht="12.75">
       <c r="B1025" s="4"/>
       <c r="C1025" s="4"/>
       <c r="D1025" s="4"/>
@@ -20019,7 +20030,7 @@
       <c r="L1025" s="4"/>
       <c r="O1025" s="4"/>
     </row>
-    <row r="1026" spans="2:15" ht="13.2">
+    <row r="1026" spans="2:15" ht="12.75">
       <c r="B1026" s="4"/>
       <c r="C1026" s="4"/>
       <c r="D1026" s="4"/>
@@ -20029,7 +20040,7 @@
       <c r="L1026" s="4"/>
       <c r="O1026" s="4"/>
     </row>
-    <row r="1027" spans="2:15" ht="13.2">
+    <row r="1027" spans="2:15" ht="12.75">
       <c r="B1027" s="4"/>
       <c r="C1027" s="4"/>
       <c r="D1027" s="4"/>
@@ -20039,7 +20050,7 @@
       <c r="L1027" s="4"/>
       <c r="O1027" s="4"/>
     </row>
-    <row r="1028" spans="2:15" ht="13.2">
+    <row r="1028" spans="2:15" ht="12.75">
       <c r="B1028" s="4"/>
       <c r="C1028" s="4"/>
       <c r="D1028" s="4"/>
@@ -20049,7 +20060,7 @@
       <c r="L1028" s="4"/>
       <c r="O1028" s="4"/>
     </row>
-    <row r="1029" spans="2:15" ht="13.2">
+    <row r="1029" spans="2:15" ht="12.75">
       <c r="B1029" s="4"/>
       <c r="C1029" s="4"/>
       <c r="D1029" s="4"/>
@@ -20059,7 +20070,7 @@
       <c r="L1029" s="4"/>
       <c r="O1029" s="4"/>
     </row>
-    <row r="1030" spans="2:15" ht="13.2">
+    <row r="1030" spans="2:15" ht="12.75">
       <c r="B1030" s="4"/>
       <c r="C1030" s="4"/>
       <c r="D1030" s="4"/>
@@ -20069,7 +20080,7 @@
       <c r="L1030" s="4"/>
       <c r="O1030" s="4"/>
     </row>
-    <row r="1031" spans="2:15" ht="13.2">
+    <row r="1031" spans="2:15" ht="12.75">
       <c r="B1031" s="4"/>
       <c r="C1031" s="4"/>
       <c r="D1031" s="4"/>
@@ -20079,7 +20090,7 @@
       <c r="L1031" s="4"/>
       <c r="O1031" s="4"/>
     </row>
-    <row r="1032" spans="2:15" ht="13.2">
+    <row r="1032" spans="2:15" ht="12.75">
       <c r="B1032" s="4"/>
       <c r="C1032" s="4"/>
       <c r="D1032" s="4"/>
@@ -20089,7 +20100,7 @@
       <c r="L1032" s="4"/>
       <c r="O1032" s="4"/>
     </row>
-    <row r="1033" spans="2:15" ht="13.2">
+    <row r="1033" spans="2:15" ht="12.75">
       <c r="B1033" s="4"/>
       <c r="C1033" s="4"/>
       <c r="D1033" s="4"/>
@@ -20099,7 +20110,7 @@
       <c r="L1033" s="4"/>
       <c r="O1033" s="4"/>
     </row>
-    <row r="1034" spans="2:15" ht="13.2">
+    <row r="1034" spans="2:15" ht="12.75">
       <c r="B1034" s="4"/>
       <c r="C1034" s="4"/>
       <c r="D1034" s="4"/>
@@ -20109,7 +20120,7 @@
       <c r="L1034" s="4"/>
       <c r="O1034" s="4"/>
     </row>
-    <row r="1035" spans="2:15" ht="13.2">
+    <row r="1035" spans="2:15" ht="12.75">
       <c r="B1035" s="4"/>
       <c r="C1035" s="4"/>
       <c r="D1035" s="4"/>
@@ -20119,7 +20130,7 @@
       <c r="L1035" s="4"/>
       <c r="O1035" s="4"/>
     </row>
-    <row r="1036" spans="2:15" ht="13.2">
+    <row r="1036" spans="2:15" ht="12.75">
       <c r="B1036" s="4"/>
       <c r="C1036" s="4"/>
       <c r="D1036" s="4"/>
@@ -20129,7 +20140,7 @@
       <c r="L1036" s="4"/>
       <c r="O1036" s="4"/>
     </row>
-    <row r="1037" spans="2:15" ht="13.2">
+    <row r="1037" spans="2:15" ht="12.75">
       <c r="B1037" s="4"/>
       <c r="C1037" s="4"/>
       <c r="D1037" s="4"/>
@@ -20139,7 +20150,7 @@
       <c r="L1037" s="4"/>
       <c r="O1037" s="4"/>
     </row>
-    <row r="1038" spans="2:15" ht="13.2">
+    <row r="1038" spans="2:15" ht="12.75">
       <c r="B1038" s="4"/>
       <c r="C1038" s="4"/>
       <c r="D1038" s="4"/>
@@ -20149,7 +20160,7 @@
       <c r="L1038" s="4"/>
       <c r="O1038" s="4"/>
     </row>
-    <row r="1039" spans="2:15" ht="13.2">
+    <row r="1039" spans="2:15" ht="12.75">
       <c r="B1039" s="4"/>
       <c r="C1039" s="4"/>
       <c r="D1039" s="4"/>
@@ -20159,7 +20170,7 @@
       <c r="L1039" s="4"/>
       <c r="O1039" s="4"/>
     </row>
-    <row r="1040" spans="2:15" ht="13.2">
+    <row r="1040" spans="2:15" ht="12.75">
       <c r="B1040" s="4"/>
       <c r="C1040" s="4"/>
       <c r="D1040" s="4"/>
@@ -20169,7 +20180,7 @@
       <c r="L1040" s="4"/>
       <c r="O1040" s="4"/>
     </row>
-    <row r="1041" spans="2:15" ht="13.2">
+    <row r="1041" spans="2:15" ht="12.75">
       <c r="B1041" s="4"/>
       <c r="C1041" s="4"/>
       <c r="D1041" s="4"/>
@@ -20179,7 +20190,7 @@
       <c r="L1041" s="4"/>
       <c r="O1041" s="4"/>
     </row>
-    <row r="1042" spans="2:15" ht="13.2">
+    <row r="1042" spans="2:15" ht="12.75">
       <c r="B1042" s="4"/>
       <c r="C1042" s="4"/>
       <c r="D1042" s="4"/>
@@ -20189,7 +20200,7 @@
       <c r="L1042" s="4"/>
       <c r="O1042" s="4"/>
     </row>
-    <row r="1043" spans="2:15" ht="13.2">
+    <row r="1043" spans="2:15" ht="12.75">
       <c r="B1043" s="4"/>
       <c r="C1043" s="4"/>
       <c r="D1043" s="4"/>
@@ -20199,7 +20210,7 @@
       <c r="L1043" s="4"/>
       <c r="O1043" s="4"/>
     </row>
-    <row r="1044" spans="2:15" ht="13.2">
+    <row r="1044" spans="2:15" ht="12.75">
       <c r="B1044" s="4"/>
       <c r="C1044" s="4"/>
       <c r="D1044" s="4"/>
@@ -20209,7 +20220,7 @@
       <c r="L1044" s="4"/>
       <c r="O1044" s="4"/>
     </row>
-    <row r="1045" spans="2:15" ht="13.2">
+    <row r="1045" spans="2:15" ht="12.75">
       <c r="B1045" s="4"/>
       <c r="C1045" s="4"/>
       <c r="D1045" s="4"/>
@@ -20219,7 +20230,7 @@
       <c r="L1045" s="4"/>
       <c r="O1045" s="4"/>
     </row>
-    <row r="1046" spans="2:15" ht="13.2">
+    <row r="1046" spans="2:15" ht="12.75">
       <c r="B1046" s="4"/>
       <c r="C1046" s="4"/>
       <c r="D1046" s="4"/>
@@ -20229,7 +20240,7 @@
       <c r="L1046" s="4"/>
       <c r="O1046" s="4"/>
     </row>
-    <row r="1047" spans="2:15" ht="13.2">
+    <row r="1047" spans="2:15" ht="12.75">
       <c r="B1047" s="4"/>
       <c r="C1047" s="4"/>
       <c r="D1047" s="4"/>
@@ -20239,7 +20250,7 @@
       <c r="L1047" s="4"/>
       <c r="O1047" s="4"/>
     </row>
-    <row r="1048" spans="2:15" ht="13.2">
+    <row r="1048" spans="2:15" ht="12.75">
       <c r="B1048" s="4"/>
       <c r="C1048" s="4"/>
       <c r="D1048" s="4"/>
@@ -20249,7 +20260,7 @@
       <c r="L1048" s="4"/>
       <c r="O1048" s="4"/>
     </row>
-    <row r="1049" spans="2:15" ht="13.2">
+    <row r="1049" spans="2:15" ht="12.75">
       <c r="B1049" s="4"/>
       <c r="C1049" s="4"/>
       <c r="D1049" s="4"/>
@@ -20259,7 +20270,7 @@
       <c r="L1049" s="4"/>
       <c r="O1049" s="4"/>
     </row>
-    <row r="1050" spans="2:15" ht="13.2">
+    <row r="1050" spans="2:15" ht="12.75">
       <c r="B1050" s="4"/>
       <c r="C1050" s="4"/>
       <c r="D1050" s="4"/>
@@ -20269,7 +20280,7 @@
       <c r="L1050" s="4"/>
       <c r="O1050" s="4"/>
     </row>
-    <row r="1051" spans="2:15" ht="13.2">
+    <row r="1051" spans="2:15" ht="12.75">
       <c r="B1051" s="4"/>
       <c r="C1051" s="4"/>
       <c r="D1051" s="4"/>
@@ -20279,7 +20290,7 @@
       <c r="L1051" s="4"/>
       <c r="O1051" s="4"/>
     </row>
-    <row r="1052" spans="2:15" ht="13.2">
+    <row r="1052" spans="2:15" ht="12.75">
       <c r="B1052" s="4"/>
       <c r="C1052" s="4"/>
       <c r="D1052" s="4"/>
@@ -20289,7 +20300,7 @@
       <c r="L1052" s="4"/>
       <c r="O1052" s="4"/>
     </row>
-    <row r="1053" spans="2:15" ht="13.2">
+    <row r="1053" spans="2:15" ht="12.75">
       <c r="B1053" s="4"/>
       <c r="C1053" s="4"/>
       <c r="D1053" s="4"/>
@@ -20299,7 +20310,7 @@
       <c r="L1053" s="4"/>
       <c r="O1053" s="4"/>
     </row>
-    <row r="1054" spans="2:15" ht="13.2">
+    <row r="1054" spans="2:15" ht="12.75">
       <c r="B1054" s="4"/>
       <c r="C1054" s="4"/>
       <c r="D1054" s="4"/>
@@ -20309,7 +20320,7 @@
       <c r="L1054" s="4"/>
       <c r="O1054" s="4"/>
     </row>
-    <row r="1055" spans="2:15" ht="13.2">
+    <row r="1055" spans="2:15" ht="12.75">
       <c r="B1055" s="4"/>
       <c r="C1055" s="4"/>
       <c r="D1055" s="4"/>
@@ -20319,7 +20330,7 @@
       <c r="L1055" s="4"/>
       <c r="O1055" s="4"/>
     </row>
-    <row r="1056" spans="2:15" ht="13.2">
+    <row r="1056" spans="2:15" ht="12.75">
       <c r="B1056" s="4"/>
       <c r="C1056" s="4"/>
       <c r="D1056" s="4"/>
@@ -20329,7 +20340,7 @@
       <c r="L1056" s="4"/>
       <c r="O1056" s="4"/>
     </row>
-    <row r="1057" spans="2:15" ht="13.2">
+    <row r="1057" spans="2:15" ht="12.75">
       <c r="B1057" s="4"/>
       <c r="C1057" s="4"/>
       <c r="D1057" s="4"/>
@@ -20339,7 +20350,7 @@
       <c r="L1057" s="4"/>
       <c r="O1057" s="4"/>
     </row>
-    <row r="1058" spans="2:15" ht="13.2">
+    <row r="1058" spans="2:15" ht="12.75">
       <c r="B1058" s="4"/>
       <c r="C1058" s="4"/>
       <c r="D1058" s="4"/>
@@ -20349,7 +20360,7 @@
       <c r="L1058" s="4"/>
       <c r="O1058" s="4"/>
     </row>
-    <row r="1059" spans="2:15" ht="13.2">
+    <row r="1059" spans="2:15" ht="12.75">
       <c r="B1059" s="4"/>
       <c r="C1059" s="4"/>
       <c r="D1059" s="4"/>
@@ -20359,7 +20370,7 @@
       <c r="L1059" s="4"/>
       <c r="O1059" s="4"/>
     </row>
-    <row r="1060" spans="2:15" ht="13.2">
+    <row r="1060" spans="2:15" ht="12.75">
       <c r="B1060" s="4"/>
       <c r="C1060" s="4"/>
       <c r="D1060" s="4"/>
@@ -20369,7 +20380,7 @@
       <c r="L1060" s="4"/>
       <c r="O1060" s="4"/>
     </row>
-    <row r="1061" spans="2:15" ht="13.2">
+    <row r="1061" spans="2:15" ht="12.75">
       <c r="B1061" s="4"/>
       <c r="C1061" s="4"/>
       <c r="D1061" s="4"/>
@@ -20379,7 +20390,7 @@
       <c r="L1061" s="4"/>
       <c r="O1061" s="4"/>
     </row>
-    <row r="1062" spans="2:15" ht="13.2">
+    <row r="1062" spans="2:15" ht="12.75">
       <c r="B1062" s="4"/>
       <c r="C1062" s="4"/>
       <c r="D1062" s="4"/>
@@ -20389,7 +20400,7 @@
       <c r="L1062" s="4"/>
       <c r="O1062" s="4"/>
     </row>
-    <row r="1063" spans="2:15" ht="13.2">
+    <row r="1063" spans="2:15" ht="12.75">
       <c r="B1063" s="4"/>
       <c r="C1063" s="4"/>
       <c r="D1063" s="4"/>
@@ -20399,7 +20410,7 @@
       <c r="L1063" s="4"/>
       <c r="O1063" s="4"/>
     </row>
-    <row r="1064" spans="2:15" ht="13.2">
+    <row r="1064" spans="2:15" ht="12.75">
       <c r="B1064" s="4"/>
       <c r="C1064" s="4"/>
       <c r="D1064" s="4"/>
@@ -20409,7 +20420,7 @@
       <c r="L1064" s="4"/>
       <c r="O1064" s="4"/>
     </row>
-    <row r="1065" spans="2:15" ht="13.2">
+    <row r="1065" spans="2:15" ht="12.75">
       <c r="B1065" s="4"/>
       <c r="C1065" s="4"/>
       <c r="D1065" s="4"/>
@@ -20419,7 +20430,7 @@
       <c r="L1065" s="4"/>
       <c r="O1065" s="4"/>
     </row>
-    <row r="1066" spans="2:15" ht="13.2">
+    <row r="1066" spans="2:15" ht="12.75">
       <c r="B1066" s="4"/>
       <c r="C1066" s="4"/>
       <c r="D1066" s="4"/>
@@ -20429,7 +20440,7 @@
       <c r="L1066" s="4"/>
       <c r="O1066" s="4"/>
     </row>
-    <row r="1067" spans="2:15" ht="13.2">
+    <row r="1067" spans="2:15" ht="12.75">
       <c r="B1067" s="4"/>
       <c r="C1067" s="4"/>
       <c r="D1067" s="4"/>
@@ -20439,7 +20450,7 @@
       <c r="L1067" s="4"/>
       <c r="O1067" s="4"/>
     </row>
-    <row r="1068" spans="2:15" ht="13.2">
+    <row r="1068" spans="2:15" ht="12.75">
       <c r="B1068" s="4"/>
       <c r="C1068" s="4"/>
       <c r="D1068" s="4"/>
@@ -20449,7 +20460,7 @@
       <c r="L1068" s="4"/>
       <c r="O1068" s="4"/>
     </row>
-    <row r="1069" spans="2:15" ht="13.2">
+    <row r="1069" spans="2:15" ht="12.75">
       <c r="B1069" s="4"/>
       <c r="C1069" s="4"/>
       <c r="D1069" s="4"/>
@@ -20459,7 +20470,7 @@
       <c r="L1069" s="4"/>
       <c r="O1069" s="4"/>
     </row>
-    <row r="1070" spans="2:15" ht="13.2">
+    <row r="1070" spans="2:15" ht="12.75">
       <c r="B1070" s="4"/>
       <c r="C1070" s="4"/>
       <c r="D1070" s="4"/>
@@ -20469,7 +20480,7 @@
       <c r="L1070" s="4"/>
       <c r="O1070" s="4"/>
     </row>
-    <row r="1071" spans="2:15" ht="13.2">
+    <row r="1071" spans="2:15" ht="12.75">
       <c r="B1071" s="4"/>
       <c r="C1071" s="4"/>
       <c r="D1071" s="4"/>
@@ -20479,7 +20490,7 @@
       <c r="L1071" s="4"/>
       <c r="O1071" s="4"/>
     </row>
-    <row r="1072" spans="2:15" ht="13.2">
+    <row r="1072" spans="2:15" ht="12.75">
       <c r="B1072" s="4"/>
       <c r="C1072" s="4"/>
       <c r="D1072" s="4"/>
@@ -20489,7 +20500,7 @@
       <c r="L1072" s="4"/>
       <c r="O1072" s="4"/>
     </row>
-    <row r="1073" spans="2:15" ht="13.2">
+    <row r="1073" spans="2:15" ht="12.75">
       <c r="B1073" s="4"/>
       <c r="C1073" s="4"/>
       <c r="D1073" s="4"/>
@@ -20499,7 +20510,7 @@
       <c r="L1073" s="4"/>
       <c r="O1073" s="4"/>
     </row>
-    <row r="1074" spans="2:15" ht="13.2">
+    <row r="1074" spans="2:15" ht="12.75">
       <c r="B1074" s="4"/>
       <c r="C1074" s="4"/>
       <c r="D1074" s="4"/>
@@ -20509,7 +20520,7 @@
       <c r="L1074" s="4"/>
       <c r="O1074" s="4"/>
     </row>
-    <row r="1075" spans="2:15" ht="13.2">
+    <row r="1075" spans="2:15" ht="12.75">
       <c r="B1075" s="4"/>
       <c r="C1075" s="4"/>
       <c r="D1075" s="4"/>
@@ -20519,7 +20530,7 @@
       <c r="L1075" s="4"/>
       <c r="O1075" s="4"/>
     </row>
-    <row r="1076" spans="2:15" ht="13.2">
+    <row r="1076" spans="2:15" ht="12.75">
       <c r="B1076" s="4"/>
       <c r="C1076" s="4"/>
       <c r="D1076" s="4"/>
@@ -20529,7 +20540,7 @@
       <c r="L1076" s="4"/>
       <c r="O1076" s="4"/>
     </row>
-    <row r="1077" spans="2:15" ht="13.2">
+    <row r="1077" spans="2:15" ht="12.75">
       <c r="B1077" s="4"/>
       <c r="C1077" s="4"/>
       <c r="D1077" s="4"/>
@@ -20539,7 +20550,7 @@
       <c r="L1077" s="4"/>
       <c r="O1077" s="4"/>
     </row>
-    <row r="1078" spans="2:15" ht="13.2">
+    <row r="1078" spans="2:15" ht="12.75">
       <c r="B1078" s="4"/>
       <c r="C1078" s="4"/>
       <c r="D1078" s="4"/>
@@ -20549,7 +20560,7 @@
       <c r="L1078" s="4"/>
       <c r="O1078" s="4"/>
     </row>
-    <row r="1079" spans="2:15" ht="13.2">
+    <row r="1079" spans="2:15" ht="12.75">
       <c r="B1079" s="4"/>
       <c r="C1079" s="4"/>
       <c r="D1079" s="4"/>
@@ -20559,7 +20570,7 @@
       <c r="L1079" s="4"/>
       <c r="O1079" s="4"/>
     </row>
-    <row r="1080" spans="2:15" ht="13.2">
+    <row r="1080" spans="2:15" ht="12.75">
       <c r="B1080" s="4"/>
       <c r="C1080" s="4"/>
       <c r="D1080" s="4"/>
@@ -20569,7 +20580,7 @@
       <c r="L1080" s="4"/>
       <c r="O1080" s="4"/>
     </row>
-    <row r="1081" spans="2:15" ht="13.2">
+    <row r="1081" spans="2:15" ht="12.75">
       <c r="B1081" s="4"/>
       <c r="C1081" s="4"/>
       <c r="D1081" s="4"/>
@@ -20579,7 +20590,7 @@
       <c r="L1081" s="4"/>
       <c r="O1081" s="4"/>
     </row>
-    <row r="1082" spans="2:15" ht="13.2">
+    <row r="1082" spans="2:15" ht="12.75">
       <c r="B1082" s="4"/>
       <c r="C1082" s="4"/>
       <c r="D1082" s="4"/>
@@ -20589,7 +20600,7 @@
       <c r="L1082" s="4"/>
       <c r="O1082" s="4"/>
     </row>
-    <row r="1083" spans="2:15" ht="13.2">
+    <row r="1083" spans="2:15" ht="12.75">
       <c r="B1083" s="4"/>
       <c r="C1083" s="4"/>
       <c r="D1083" s="4"/>
@@ -20631,7 +20642,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L219 L233:L951" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"In Progress,In Review,Approved,Cancelled,Draft"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B308:B1083 B2:B31 B42 B33:B40 B44:B54 B56:B64 B66:B70 B72:B76 B78:B79 B91:B219 B233:B303 B81:B89" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B308:B1083 B2:B31 B42 B33:B40 B56:B64 B81:B89 B233:B303 B44:B54 B78:B79 B91:B219 B66:B70 B72:B76" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"not executed,passed,failed,blocked"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L952:L1083" xr:uid="{00000000-0002-0000-0000-000003000000}">

--- a/test/TestExecutionReport.xlsx
+++ b/test/TestExecutionReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITI_Courses\QA\QA-project-tool\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A73AA9-2204-4F3A-98B1-7FF4807F63C8}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C6F90A-7CC3-4503-9094-D1A7524F355F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/test/TestExecutionReport.xlsx
+++ b/test/TestExecutionReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITI_Courses\QA\QA-project-tool\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C6F90A-7CC3-4503-9094-D1A7524F355F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58794C8-BEB0-4F0A-8B2F-F2AA87CA03DC}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="405">
   <si>
     <t>TesTCASE ID</t>
   </si>
@@ -1405,6 +1405,18 @@
   <si>
     <t>email:ali@gmail.com
 password:  ali123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is correctly redirected to Find Flights page but Destination field is not prefilled with selected destination from My Bookings page </t>
+  </si>
+  <si>
+    <t>User is redirected to login page</t>
+  </si>
+  <si>
+    <t>User is redirected to login page and input is correctly accepted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same as expected </t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1670,12 +1682,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1697,91 +1703,20 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1826,6 +1761,86 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1862,10 +1877,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="C86:D90" headerRowCount="0" headerRowDxfId="7" dataDxfId="10" totalsRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="C86:D90" headerRowCount="0" headerRowDxfId="4" dataDxfId="3" totalsRowDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Test Execution -style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2181,7 +2196,7 @@
       <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="25" t="s">
         <v>360</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -2231,7 +2246,7 @@
       <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -2244,7 +2259,9 @@
       <c r="I3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="6" t="s">
+        <v>402</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
         <v>23</v>
@@ -2286,7 +2303,7 @@
       <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -2301,7 +2318,9 @@
       <c r="I4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="4"/>
+      <c r="J4" s="6" t="s">
+        <v>402</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
         <v>23</v>
@@ -2343,7 +2362,7 @@
       <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2358,7 +2377,9 @@
       <c r="I5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="4"/>
+      <c r="J5" s="6" t="s">
+        <v>403</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
         <v>23</v>
@@ -2400,7 +2421,7 @@
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2415,7 +2436,9 @@
       <c r="I6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="4"/>
+      <c r="J6" s="6" t="s">
+        <v>402</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
         <v>23</v>
@@ -2457,7 +2480,7 @@
       <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -2466,13 +2489,15 @@
       <c r="G7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="26" t="s">
         <v>368</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="6" t="s">
+        <v>402</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
         <v>23</v>
@@ -2514,7 +2539,7 @@
       <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -2529,7 +2554,9 @@
       <c r="I8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="4"/>
+      <c r="J8" s="6" t="s">
+        <v>402</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
         <v>23</v>
@@ -2571,7 +2598,7 @@
       <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -2586,7 +2613,9 @@
       <c r="I9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="4"/>
+      <c r="J9" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
         <v>23</v>
@@ -2628,7 +2657,7 @@
       <c r="D10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -2643,7 +2672,9 @@
       <c r="I10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="4"/>
+      <c r="J10" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4" t="s">
         <v>23</v>
@@ -2685,7 +2716,7 @@
       <c r="D11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -2700,7 +2731,9 @@
       <c r="I11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="4"/>
+      <c r="J11" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
         <v>23</v>
@@ -2742,7 +2775,7 @@
       <c r="D12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F12" s="4" t="s">
@@ -2757,7 +2790,9 @@
       <c r="I12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="4"/>
+      <c r="J12" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4" t="s">
         <v>23</v>
@@ -2799,7 +2834,7 @@
       <c r="D13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F13" s="4" t="s">
@@ -2814,7 +2849,9 @@
       <c r="I13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J13" s="4"/>
+      <c r="J13" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="s">
         <v>23</v>
@@ -2856,7 +2893,7 @@
       <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -2871,7 +2908,9 @@
       <c r="I14" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J14" s="4"/>
+      <c r="J14" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4" t="s">
         <v>23</v>
@@ -2913,7 +2952,7 @@
       <c r="D15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -2928,7 +2967,9 @@
       <c r="I15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J15" s="4"/>
+      <c r="J15" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
         <v>23</v>
@@ -2961,7 +3002,7 @@
       <c r="A16" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="26" t="s">
         <v>364</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2970,7 +3011,7 @@
       <c r="D16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -2985,7 +3026,9 @@
       <c r="I16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J16" s="4"/>
+      <c r="J16" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4" t="s">
         <v>23</v>
@@ -3027,7 +3070,7 @@
       <c r="D17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -3042,7 +3085,9 @@
       <c r="I17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J17" s="4"/>
+      <c r="J17" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="s">
         <v>23</v>
@@ -3084,7 +3129,7 @@
       <c r="D18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -3099,7 +3144,9 @@
       <c r="I18" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="4"/>
+      <c r="J18" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4" t="s">
         <v>23</v>
@@ -3141,7 +3188,7 @@
       <c r="D19" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -3156,7 +3203,9 @@
       <c r="I19" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J19" s="4"/>
+      <c r="J19" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4" t="s">
         <v>23</v>
@@ -3198,7 +3247,7 @@
       <c r="D20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -3213,7 +3262,9 @@
       <c r="I20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="4"/>
+      <c r="J20" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4" t="s">
         <v>23</v>
@@ -3255,7 +3306,7 @@
       <c r="D21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F21" s="4" t="s">
@@ -3270,7 +3321,9 @@
       <c r="I21" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J21" s="4"/>
+      <c r="J21" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4" t="s">
         <v>23</v>
@@ -3312,7 +3365,7 @@
       <c r="D22" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F22" s="4" t="s">
@@ -3327,7 +3380,9 @@
       <c r="I22" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="4"/>
+      <c r="J22" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4" t="s">
         <v>23</v>
@@ -3369,7 +3424,7 @@
       <c r="D23" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F23" s="4" t="s">
@@ -3384,7 +3439,9 @@
       <c r="I23" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J23" s="4"/>
+      <c r="J23" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4" t="s">
         <v>23</v>
@@ -3426,7 +3483,7 @@
       <c r="D24" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F24" s="4" t="s">
@@ -3441,7 +3498,9 @@
       <c r="I24" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J24" s="4"/>
+      <c r="J24" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4" t="s">
         <v>23</v>
@@ -3483,7 +3542,7 @@
       <c r="D25" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F25" s="4" t="s">
@@ -3498,7 +3557,9 @@
       <c r="I25" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J25" s="4"/>
+      <c r="J25" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4" t="s">
         <v>23</v>
@@ -3540,7 +3601,7 @@
       <c r="D26" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -3555,7 +3616,9 @@
       <c r="I26" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="J26" s="4"/>
+      <c r="J26" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4" t="s">
         <v>23</v>
@@ -3597,7 +3660,7 @@
       <c r="D27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -3612,7 +3675,9 @@
       <c r="I27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J27" s="4"/>
+      <c r="J27" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4" t="s">
         <v>23</v>
@@ -3654,7 +3719,7 @@
       <c r="D28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="27" t="s">
+      <c r="E28" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -3669,7 +3734,9 @@
       <c r="I28" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="J28" s="4"/>
+      <c r="J28" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4" t="s">
         <v>23</v>
@@ -3711,7 +3778,7 @@
       <c r="D29" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="27" t="s">
+      <c r="E29" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -3726,7 +3793,9 @@
       <c r="I29" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="J29" s="4"/>
+      <c r="J29" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4" t="s">
         <v>23</v>
@@ -3768,7 +3837,7 @@
       <c r="D30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -3783,7 +3852,9 @@
       <c r="I30" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J30" s="4"/>
+      <c r="J30" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4" t="s">
         <v>23</v>
@@ -3825,7 +3896,7 @@
       <c r="D31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -3840,7 +3911,9 @@
       <c r="I31" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="J31" s="4"/>
+      <c r="J31" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4" t="s">
         <v>23</v>
@@ -5680,7 +5753,7 @@
       <c r="G68" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="H68" s="29"/>
+      <c r="H68" s="27"/>
       <c r="I68" s="4" t="s">
         <v>267</v>
       </c>
@@ -6157,7 +6230,7 @@
       <c r="G81" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="H81" s="32" t="s">
+      <c r="H81" s="30" t="s">
         <v>393</v>
       </c>
       <c r="I81" s="4" t="s">
@@ -6539,7 +6612,7 @@
       <c r="AB90" s="8"/>
       <c r="AC90" s="8"/>
     </row>
-    <row r="91" spans="1:29" ht="36.75" customHeight="1">
+    <row r="91" spans="1:29" ht="52.8">
       <c r="A91" s="4" t="s">
         <v>352</v>
       </c>
@@ -6559,16 +6632,18 @@
       <c r="G91" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H91" s="31"/>
+      <c r="H91" s="29"/>
       <c r="I91" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="J91" s="14"/>
-      <c r="K91" s="14"/>
+      <c r="J91" s="33" t="s">
+        <v>401</v>
+      </c>
+      <c r="K91" s="29"/>
       <c r="L91" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M91" s="14"/>
+      <c r="M91" s="29"/>
       <c r="N91" s="4" t="s">
         <v>357</v>
       </c>
@@ -6680,7 +6755,7 @@
       <c r="E97" s="16"/>
       <c r="F97" s="15"/>
       <c r="G97" s="15"/>
-      <c r="H97" s="30"/>
+      <c r="H97" s="28"/>
       <c r="I97" s="15"/>
       <c r="J97" s="17"/>
       <c r="K97" s="17"/>
@@ -9906,7 +9981,7 @@
       <c r="B301" s="2"/>
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
-      <c r="E301" s="24"/>
+      <c r="E301" s="31"/>
       <c r="F301" s="4"/>
       <c r="G301" s="4"/>
       <c r="I301" s="4"/>
@@ -9922,7 +9997,7 @@
       <c r="B302" s="2"/>
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
-      <c r="E302" s="25"/>
+      <c r="E302" s="32"/>
       <c r="F302" s="4"/>
       <c r="G302" s="4"/>
       <c r="I302" s="4"/>
@@ -9938,7 +10013,7 @@
       <c r="B303" s="2"/>
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
-      <c r="E303" s="25"/>
+      <c r="E303" s="32"/>
       <c r="F303" s="4"/>
       <c r="G303" s="4"/>
       <c r="I303" s="4"/>
@@ -9954,7 +10029,7 @@
       <c r="B304" s="2"/>
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
-      <c r="E304" s="25"/>
+      <c r="E304" s="32"/>
       <c r="F304" s="4"/>
       <c r="G304" s="4"/>
       <c r="I304" s="4"/>
@@ -9970,7 +10045,7 @@
       <c r="B305" s="2"/>
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
-      <c r="E305" s="25"/>
+      <c r="E305" s="32"/>
       <c r="F305" s="4"/>
       <c r="G305" s="4"/>
       <c r="I305" s="4"/>
@@ -9986,7 +10061,7 @@
       <c r="B306" s="2"/>
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
-      <c r="E306" s="25"/>
+      <c r="E306" s="32"/>
       <c r="F306" s="4"/>
       <c r="G306" s="4"/>
       <c r="I306" s="4"/>
@@ -10370,33 +10445,33 @@
       <c r="B330" s="2"/>
       <c r="C330" s="4"/>
       <c r="D330" s="4"/>
-      <c r="E330" s="26"/>
+      <c r="E330" s="24"/>
       <c r="F330" s="4"/>
       <c r="G330" s="4"/>
-      <c r="H330" s="26"/>
+      <c r="H330" s="24"/>
       <c r="I330" s="4"/>
-      <c r="J330" s="26"/>
-      <c r="K330" s="26"/>
+      <c r="J330" s="24"/>
+      <c r="K330" s="24"/>
       <c r="L330" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M330" s="26"/>
+      <c r="M330" s="24"/>
       <c r="N330" s="4"/>
       <c r="O330" s="4"/>
       <c r="P330" s="4"/>
-      <c r="Q330" s="26"/>
-      <c r="R330" s="26"/>
-      <c r="S330" s="26"/>
-      <c r="T330" s="26"/>
-      <c r="U330" s="26"/>
-      <c r="V330" s="26"/>
-      <c r="W330" s="26"/>
-      <c r="X330" s="26"/>
-      <c r="Y330" s="26"/>
-      <c r="Z330" s="26"/>
-      <c r="AA330" s="26"/>
-      <c r="AB330" s="26"/>
-      <c r="AC330" s="26"/>
+      <c r="Q330" s="24"/>
+      <c r="R330" s="24"/>
+      <c r="S330" s="24"/>
+      <c r="T330" s="24"/>
+      <c r="U330" s="24"/>
+      <c r="V330" s="24"/>
+      <c r="W330" s="24"/>
+      <c r="X330" s="24"/>
+      <c r="Y330" s="24"/>
+      <c r="Z330" s="24"/>
+      <c r="AA330" s="24"/>
+      <c r="AB330" s="24"/>
+      <c r="AC330" s="24"/>
     </row>
     <row r="331" spans="1:29" ht="13.2">
       <c r="A331" s="4"/>
@@ -20605,22 +20680,22 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"valid"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"invalid"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"not executed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"passed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"failed"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/test/TestExecutionReport.xlsx
+++ b/test/TestExecutionReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITI_Courses\QA\QA-project-tool\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58794C8-BEB0-4F0A-8B2F-F2AA87CA03DC}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AC4362-7800-43B4-BB79-EF6A7E6AB8A0}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="404">
   <si>
     <t>TesTCASE ID</t>
   </si>
@@ -99,9 +99,6 @@
 4-Enter password in password field
 5-Enter confirm password in Confirm password field
 6-Click on Create account button</t>
-  </si>
-  <si>
-    <t>User should successfully be redirected to Explore/home page</t>
   </si>
   <si>
     <t>Draft</t>
@@ -1703,13 +1700,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2175,11 +2172,11 @@
       <c r="AC1" s="2"/>
     </row>
     <row r="2" spans="1:29" ht="92.4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>18</v>
@@ -2188,36 +2185,36 @@
         <v>19</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>359</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="25" t="s">
+      <c r="I2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="25" t="s">
         <v>360</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>361</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M2" s="7"/>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -2235,46 +2232,46 @@
     </row>
     <row r="3" spans="1:29" ht="26.4">
       <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -2292,19 +2289,19 @@
     </row>
     <row r="4" spans="1:29" ht="92.4">
       <c r="A4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>20</v>
@@ -2313,27 +2310,27 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
@@ -2351,19 +2348,19 @@
     </row>
     <row r="5" spans="1:29" ht="105.6">
       <c r="A5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>20</v>
@@ -2372,27 +2369,27 @@
         <v>21</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
@@ -2410,19 +2407,19 @@
     </row>
     <row r="6" spans="1:29" ht="92.4">
       <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>20</v>
@@ -2431,27 +2428,27 @@
         <v>21</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
@@ -2469,48 +2466,48 @@
     </row>
     <row r="7" spans="1:29" ht="92.4">
       <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -2528,19 +2525,19 @@
     </row>
     <row r="8" spans="1:29" ht="92.4">
       <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>20</v>
@@ -2549,27 +2546,27 @@
         <v>21</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M8" s="4"/>
       <c r="N8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
@@ -2587,48 +2584,48 @@
     </row>
     <row r="9" spans="1:29" ht="66">
       <c r="A9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="E9" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="J9" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
@@ -2646,48 +2643,48 @@
     </row>
     <row r="10" spans="1:29" ht="92.4">
       <c r="A10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="J10" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -2705,48 +2702,48 @@
     </row>
     <row r="11" spans="1:29" ht="66">
       <c r="A11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -2764,48 +2761,48 @@
     </row>
     <row r="12" spans="1:29" ht="92.4">
       <c r="A12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
@@ -2823,48 +2820,48 @@
     </row>
     <row r="13" spans="1:29" ht="66">
       <c r="A13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="J13" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
@@ -2882,48 +2879,48 @@
     </row>
     <row r="14" spans="1:29" ht="66">
       <c r="A14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -2941,48 +2938,48 @@
     </row>
     <row r="15" spans="1:29" ht="66">
       <c r="A15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="D15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
@@ -3000,48 +2997,48 @@
     </row>
     <row r="16" spans="1:29" ht="66">
       <c r="A16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
@@ -3059,48 +3056,48 @@
     </row>
     <row r="17" spans="1:29" ht="66">
       <c r="A17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="D17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
@@ -3118,48 +3115,48 @@
     </row>
     <row r="18" spans="1:29" ht="66">
       <c r="A18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>72</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="J18" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P18" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
@@ -3177,48 +3174,48 @@
     </row>
     <row r="19" spans="1:29" ht="66">
       <c r="A19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="J19" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
@@ -3236,48 +3233,48 @@
     </row>
     <row r="20" spans="1:29" ht="66">
       <c r="A20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="D20" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="J20" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
@@ -3295,48 +3292,48 @@
     </row>
     <row r="21" spans="1:29" ht="66">
       <c r="A21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="J21" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M21" s="4"/>
       <c r="N21" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
@@ -3354,48 +3351,48 @@
     </row>
     <row r="22" spans="1:29" ht="66">
       <c r="A22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="J22" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P22" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
@@ -3413,48 +3410,48 @@
     </row>
     <row r="23" spans="1:29" ht="66">
       <c r="A23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="J23" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
@@ -3472,48 +3469,48 @@
     </row>
     <row r="24" spans="1:29" ht="66">
       <c r="A24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="D24" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P24" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
@@ -3531,48 +3528,48 @@
     </row>
     <row r="25" spans="1:29" ht="66">
       <c r="A25" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="D25" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
@@ -3590,48 +3587,48 @@
     </row>
     <row r="26" spans="1:29" ht="92.4">
       <c r="A26" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="D26" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>359</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
@@ -3649,48 +3646,48 @@
     </row>
     <row r="27" spans="1:29" ht="79.2">
       <c r="A27" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="D27" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="J27" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P27" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
@@ -3708,48 +3705,48 @@
     </row>
     <row r="28" spans="1:29" ht="79.2">
       <c r="A28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="D28" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="J28" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P28" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
@@ -3767,48 +3764,48 @@
     </row>
     <row r="29" spans="1:29" ht="79.2">
       <c r="A29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="D29" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="I29" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="J29" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
@@ -3826,48 +3823,48 @@
     </row>
     <row r="30" spans="1:29" ht="79.2">
       <c r="A30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="D30" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="I30" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="J30" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P30" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P30" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
@@ -3885,48 +3882,48 @@
     </row>
     <row r="31" spans="1:29" ht="66">
       <c r="A31" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="D31" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="J31" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P31" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q31" s="4"/>
       <c r="R31" s="4"/>
@@ -3955,7 +3952,7 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
@@ -3977,20 +3974,20 @@
     </row>
     <row r="33" spans="1:29" ht="39.6">
       <c r="A33" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G33" s="4" t="str">
         <f t="shared" ref="G33:G36" si="0">CONCATENATE("1- ",LEFT(F33,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),2))),"Clicks",MID(F33,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),7)) - 1 + 1,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),9)) - (FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),7)) - 1)),CHAR(34),MID(C33,FIND(" “",C33) + 1 + 1,FIND("” ",C33) - 1 - (FIND(" “",C33) + 1)),CHAR(34)&amp;" Butt",MID(F33,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),7)) + 1,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),8)) - (FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),7)))),MID(F33,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),4)) + 1,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),5)) - (FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),4)))),MID(F33,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),8)) + 1,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),9)) - (FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),8)))),"navigati",MID(F33,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),7)) + 1,FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),8)) - (FIND(CHAR(160),SUBSTITUTE(F33," ",CHAR(160),7)))),"bar")</f>
@@ -3998,20 +3995,20 @@
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
@@ -4029,20 +4026,20 @@
     </row>
     <row r="34" spans="1:29" ht="39.6">
       <c r="A34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G34" s="4" t="str">
         <f t="shared" si="0"/>
@@ -4050,20 +4047,20 @@
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="4"/>
       <c r="R34" s="4"/>
@@ -4081,20 +4078,20 @@
     </row>
     <row r="35" spans="1:29" ht="28.8">
       <c r="A35" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G35" s="4" t="str">
         <f t="shared" si="0"/>
@@ -4102,20 +4099,20 @@
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q35" s="4"/>
       <c r="R35" s="4"/>
@@ -4133,20 +4130,20 @@
     </row>
     <row r="36" spans="1:29" ht="39.6">
       <c r="A36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G36" s="4" t="str">
         <f t="shared" si="0"/>
@@ -4154,20 +4151,20 @@
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
@@ -4185,40 +4182,40 @@
     </row>
     <row r="37" spans="1:29" ht="28.8">
       <c r="A37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
@@ -4236,40 +4233,40 @@
     </row>
     <row r="38" spans="1:29" ht="28.8">
       <c r="A38" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
@@ -4287,40 +4284,40 @@
     </row>
     <row r="39" spans="1:29" ht="28.8">
       <c r="A39" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
@@ -4338,39 +4335,39 @@
     </row>
     <row r="40" spans="1:29" ht="39.6">
       <c r="A40" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M40" s="4"/>
       <c r="O40" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
@@ -4399,7 +4396,7 @@
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M41" s="8"/>
       <c r="N41" s="8"/>
@@ -4421,38 +4418,38 @@
     </row>
     <row r="42" spans="1:29" ht="52.8">
       <c r="A42" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F42" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M42" s="4"/>
       <c r="O42" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
@@ -4481,7 +4478,7 @@
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
       <c r="L43" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M43" s="9"/>
       <c r="N43" s="8"/>
@@ -4503,42 +4500,42 @@
     </row>
     <row r="44" spans="1:29" ht="26.4">
       <c r="A44" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P44" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
@@ -4556,42 +4553,42 @@
     </row>
     <row r="45" spans="1:29" ht="26.4">
       <c r="A45" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="D45" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
@@ -4609,42 +4606,42 @@
     </row>
     <row r="46" spans="1:29" ht="26.4">
       <c r="A46" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="D46" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
@@ -4662,42 +4659,42 @@
     </row>
     <row r="47" spans="1:29" ht="26.4">
       <c r="A47" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>176</v>
-      </c>
       <c r="D47" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
@@ -4715,42 +4712,42 @@
     </row>
     <row r="48" spans="1:29" ht="13.2">
       <c r="A48" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="D48" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
@@ -4768,42 +4765,42 @@
     </row>
     <row r="49" spans="1:29" ht="13.2">
       <c r="A49" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="D49" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
@@ -4821,42 +4818,42 @@
     </row>
     <row r="50" spans="1:29" ht="13.2">
       <c r="A50" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>188</v>
-      </c>
       <c r="D50" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
@@ -4874,42 +4871,42 @@
     </row>
     <row r="51" spans="1:29" ht="13.2">
       <c r="A51" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="D51" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
@@ -4927,42 +4924,42 @@
     </row>
     <row r="52" spans="1:29" ht="13.2">
       <c r="A52" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="D52" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
@@ -4980,42 +4977,42 @@
     </row>
     <row r="53" spans="1:29" ht="13.2">
       <c r="A53" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>199</v>
-      </c>
       <c r="D53" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
@@ -5033,42 +5030,42 @@
     </row>
     <row r="54" spans="1:29" ht="13.2">
       <c r="A54" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>203</v>
-      </c>
       <c r="D54" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
@@ -5097,7 +5094,7 @@
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
       <c r="L55" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M55" s="9"/>
       <c r="N55" s="8"/>
@@ -5119,42 +5116,42 @@
     </row>
     <row r="56" spans="1:29" ht="26.4">
       <c r="A56" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
@@ -5172,42 +5169,42 @@
     </row>
     <row r="57" spans="1:29" ht="26.4">
       <c r="A57" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>213</v>
-      </c>
       <c r="D57" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
@@ -5225,42 +5222,42 @@
     </row>
     <row r="58" spans="1:29" ht="26.4">
       <c r="A58" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="D58" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
@@ -5278,42 +5275,42 @@
     </row>
     <row r="59" spans="1:29" ht="26.4">
       <c r="A59" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="D59" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
@@ -5331,42 +5328,42 @@
     </row>
     <row r="60" spans="1:29" ht="26.4">
       <c r="A60" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="D60" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
@@ -5384,42 +5381,42 @@
     </row>
     <row r="61" spans="1:29" ht="13.2">
       <c r="A61" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
@@ -5437,42 +5434,42 @@
     </row>
     <row r="62" spans="1:29" ht="26.4">
       <c r="A62" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
       <c r="L62" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
@@ -5490,42 +5487,42 @@
     </row>
     <row r="63" spans="1:29" ht="26.4">
       <c r="A63" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
       <c r="L63" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
@@ -5543,42 +5540,42 @@
     </row>
     <row r="64" spans="1:29" ht="26.4">
       <c r="A64" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
       <c r="L64" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
@@ -5607,7 +5604,7 @@
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
       <c r="L65" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M65" s="9"/>
       <c r="N65" s="8"/>
@@ -5629,42 +5626,42 @@
     </row>
     <row r="66" spans="1:29" ht="13.2">
       <c r="A66" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
       <c r="L66" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
@@ -5682,42 +5679,42 @@
     </row>
     <row r="67" spans="1:29" ht="13.2">
       <c r="A67" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
       <c r="L67" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
@@ -5735,42 +5732,42 @@
     </row>
     <row r="68" spans="1:29" ht="36.75" customHeight="1">
       <c r="A68" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="H68" s="27"/>
       <c r="I68" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J68" s="11"/>
       <c r="K68" s="11"/>
       <c r="L68" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M68" s="11"/>
       <c r="N68" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q68" s="11"/>
       <c r="R68" s="11"/>
@@ -5788,76 +5785,76 @@
     </row>
     <row r="69" spans="1:29" ht="13.2">
       <c r="A69" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="I69" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="J69" s="4"/>
       <c r="L69" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="13.2">
       <c r="A70" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J70" s="4"/>
       <c r="L70" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="13.2">
@@ -5873,7 +5870,7 @@
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
       <c r="L71" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M71" s="8"/>
       <c r="N71" s="8"/>
@@ -5895,187 +5892,187 @@
     </row>
     <row r="72" spans="1:29" ht="13.2">
       <c r="A72" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G72" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I72" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="J72" s="4"/>
       <c r="L72" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="13.2">
       <c r="A73" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="I73" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="J73" s="4"/>
       <c r="L73" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="13.2">
       <c r="A74" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="I74" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J74" s="4"/>
       <c r="L74" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:29" ht="13.2">
       <c r="A75" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>296</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I75" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="J75" s="4"/>
       <c r="L75" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:29" ht="13.2">
       <c r="A76" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>301</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J76" s="4"/>
       <c r="L76" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="1:29" ht="13.2">
@@ -6091,7 +6088,7 @@
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
       <c r="L77" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M77" s="8"/>
       <c r="N77" s="8"/>
@@ -6113,13 +6110,13 @@
     </row>
     <row r="78" spans="1:29" ht="72">
       <c r="A78" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>19</v>
@@ -6128,53 +6125,53 @@
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
       <c r="I78" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J78" s="4"/>
       <c r="L78" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N78" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P78" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="O78" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P78" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="79" spans="1:29" ht="14.4">
       <c r="A79" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>310</v>
-      </c>
       <c r="D79" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
       <c r="I79" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J79" s="4"/>
       <c r="L79" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N79" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P79" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="O79" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P79" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="80" spans="1:29" ht="24.75" customHeight="1">
@@ -6190,7 +6187,7 @@
       <c r="J80" s="8"/>
       <c r="K80" s="8"/>
       <c r="L80" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M80" s="8"/>
       <c r="N80" s="8"/>
@@ -6212,198 +6209,198 @@
     </row>
     <row r="81" spans="1:29" ht="39.6">
       <c r="A81" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="H81" s="30" t="s">
-        <v>393</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="K81" s="4"/>
       <c r="L81" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O81" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P81" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P81" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:29" ht="39.6">
       <c r="A82" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="I82" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="K82" s="4"/>
       <c r="L82" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P82" s="4"/>
     </row>
     <row r="83" spans="1:29" ht="26.4">
       <c r="A83" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="G83" s="4" t="s">
+      <c r="I83" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="K83" s="4"/>
       <c r="L83" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N83" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O83" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P83" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P83" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:29" ht="52.8">
       <c r="A84" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G84" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="I84" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="K84" s="4"/>
       <c r="L84" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N84" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O84" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P84" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P84" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:29" ht="52.8">
       <c r="A85" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>335</v>
-      </c>
       <c r="D85" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="H85" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="K85" s="4"/>
       <c r="L85" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M85" s="12"/>
       <c r="N85" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O85" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P85" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P85" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q85" s="12"/>
       <c r="R85" s="12"/>
@@ -6421,162 +6418,162 @@
     </row>
     <row r="86" spans="1:29" ht="39.6">
       <c r="A86" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>340</v>
-      </c>
       <c r="D86" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="G86" s="4" t="s">
-        <v>342</v>
-      </c>
       <c r="H86" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K86" s="4"/>
       <c r="L86" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N86" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O86" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P86" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P86" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:29" ht="39.6">
       <c r="A87" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>345</v>
-      </c>
       <c r="D87" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="G87" s="4" t="s">
-        <v>342</v>
-      </c>
       <c r="H87" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K87" s="4"/>
       <c r="L87" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N87" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O87" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P87" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P87" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="39.6">
       <c r="A88" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>347</v>
-      </c>
       <c r="D88" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="G88" s="4" t="s">
-        <v>342</v>
-      </c>
       <c r="H88" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K88" s="4"/>
       <c r="L88" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N88" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O88" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P88" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P88" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:29" ht="39.6">
       <c r="A89" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>349</v>
-      </c>
       <c r="D89" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K89" s="4"/>
       <c r="L89" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N89" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O89" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P89" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P89" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:29" ht="24.75" customHeight="1">
@@ -6592,7 +6589,7 @@
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
       <c r="L90" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M90" s="8"/>
       <c r="N90" s="8"/>
@@ -6613,45 +6610,45 @@
       <c r="AC90" s="8"/>
     </row>
     <row r="91" spans="1:29" ht="52.8">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E91" s="13"/>
-      <c r="F91" s="4" t="s">
+      <c r="F91" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="G91" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="H91" s="29"/>
+      <c r="I91" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="H91" s="29"/>
-      <c r="I91" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="J91" s="33" t="s">
-        <v>401</v>
+      <c r="J91" s="31" t="s">
+        <v>400</v>
       </c>
       <c r="K91" s="29"/>
       <c r="L91" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M91" s="29"/>
-      <c r="N91" s="4" t="s">
-        <v>357</v>
+      <c r="N91" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="O91" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P91" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="P91" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="Q91" s="14"/>
       <c r="R91" s="14"/>
@@ -6677,7 +6674,7 @@
       <c r="G92" s="15"/>
       <c r="I92" s="15"/>
       <c r="L92" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N92" s="15"/>
       <c r="O92" s="15"/>
@@ -6693,7 +6690,7 @@
       <c r="G93" s="15"/>
       <c r="I93" s="15"/>
       <c r="L93" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N93" s="15"/>
       <c r="O93" s="15"/>
@@ -6709,7 +6706,7 @@
       <c r="G94" s="15"/>
       <c r="I94" s="15"/>
       <c r="L94" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N94" s="15"/>
       <c r="O94" s="15"/>
@@ -6725,7 +6722,7 @@
       <c r="G95" s="15"/>
       <c r="I95" s="15"/>
       <c r="L95" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N95" s="15"/>
       <c r="O95" s="15"/>
@@ -6741,7 +6738,7 @@
       <c r="G96" s="15"/>
       <c r="I96" s="15"/>
       <c r="L96" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N96" s="15"/>
       <c r="O96" s="15"/>
@@ -6760,7 +6757,7 @@
       <c r="J97" s="17"/>
       <c r="K97" s="17"/>
       <c r="L97" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M97" s="17"/>
       <c r="N97" s="15"/>
@@ -6791,7 +6788,7 @@
       <c r="I98" s="15"/>
       <c r="J98" s="4"/>
       <c r="L98" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N98" s="15"/>
       <c r="O98" s="15"/>
@@ -6808,7 +6805,7 @@
       <c r="I99" s="15"/>
       <c r="J99" s="4"/>
       <c r="L99" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N99" s="15"/>
       <c r="O99" s="15"/>
@@ -6825,7 +6822,7 @@
       <c r="I100" s="15"/>
       <c r="J100" s="4"/>
       <c r="L100" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N100" s="15"/>
       <c r="O100" s="15"/>
@@ -6842,7 +6839,7 @@
       <c r="I101" s="15"/>
       <c r="J101" s="4"/>
       <c r="L101" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N101" s="15"/>
       <c r="O101" s="15"/>
@@ -6858,7 +6855,7 @@
       <c r="G102" s="15"/>
       <c r="I102" s="15"/>
       <c r="L102" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N102" s="15"/>
       <c r="O102" s="15"/>
@@ -6875,7 +6872,7 @@
       <c r="I103" s="15"/>
       <c r="J103" s="4"/>
       <c r="L103" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N103" s="15"/>
       <c r="O103" s="15"/>
@@ -6891,7 +6888,7 @@
       <c r="G104" s="15"/>
       <c r="I104" s="15"/>
       <c r="L104" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N104" s="15"/>
       <c r="O104" s="15"/>
@@ -6908,7 +6905,7 @@
       <c r="I105" s="15"/>
       <c r="J105" s="4"/>
       <c r="L105" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N105" s="15"/>
       <c r="O105" s="15"/>
@@ -6925,7 +6922,7 @@
       <c r="I106" s="15"/>
       <c r="J106" s="4"/>
       <c r="L106" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N106" s="15"/>
       <c r="O106" s="15"/>
@@ -6942,7 +6939,7 @@
       <c r="I107" s="15"/>
       <c r="J107" s="4"/>
       <c r="L107" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N107" s="15"/>
       <c r="O107" s="15"/>
@@ -6958,7 +6955,7 @@
       <c r="G108" s="15"/>
       <c r="I108" s="15"/>
       <c r="L108" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N108" s="15"/>
       <c r="O108" s="15"/>
@@ -6977,7 +6974,7 @@
       <c r="J109" s="17"/>
       <c r="K109" s="17"/>
       <c r="L109" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M109" s="17"/>
       <c r="N109" s="15"/>
@@ -7009,7 +7006,7 @@
       <c r="I110" s="15"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N110" s="15"/>
       <c r="O110" s="15"/>
@@ -7027,7 +7024,7 @@
       <c r="I111" s="15"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N111" s="15"/>
       <c r="O111" s="15"/>
@@ -7045,7 +7042,7 @@
       <c r="I112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
@@ -7063,7 +7060,7 @@
       <c r="I113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
@@ -7081,7 +7078,7 @@
       <c r="I114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
@@ -7099,7 +7096,7 @@
       <c r="I115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
@@ -7117,7 +7114,7 @@
       <c r="I116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
@@ -7135,7 +7132,7 @@
       <c r="I117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
@@ -7153,7 +7150,7 @@
       <c r="I118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
@@ -7171,7 +7168,7 @@
       <c r="I119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
@@ -7377,7 +7374,7 @@
       <c r="I137" s="4"/>
       <c r="K137" s="4"/>
       <c r="L137" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N137" s="4"/>
       <c r="O137" s="4"/>
@@ -7394,7 +7391,7 @@
       <c r="I138" s="4"/>
       <c r="K138" s="4"/>
       <c r="L138" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N138" s="4"/>
       <c r="O138" s="4"/>
@@ -7412,7 +7409,7 @@
       <c r="I139" s="4"/>
       <c r="K139" s="4"/>
       <c r="L139" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N139" s="4"/>
       <c r="O139" s="4"/>
@@ -7437,7 +7434,7 @@
       <c r="H141" s="4"/>
       <c r="K141" s="4"/>
       <c r="L141" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="13.2">
@@ -7448,7 +7445,7 @@
       <c r="H142" s="4"/>
       <c r="K142" s="4"/>
       <c r="L142" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143" spans="1:16" ht="54.75" customHeight="1">
@@ -7459,7 +7456,7 @@
       <c r="H143" s="4"/>
       <c r="K143" s="4"/>
       <c r="L143" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144" spans="1:16" ht="60.75" customHeight="1">
@@ -7470,7 +7467,7 @@
       <c r="H144" s="4"/>
       <c r="K144" s="4"/>
       <c r="L144" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145" spans="1:16" ht="66" customHeight="1">
@@ -7706,7 +7703,7 @@
       <c r="H161" s="4"/>
       <c r="K161" s="4"/>
       <c r="L161" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="162" spans="2:29" ht="71.25" customHeight="1">
@@ -7717,7 +7714,7 @@
       <c r="H162" s="4"/>
       <c r="K162" s="4"/>
       <c r="L162" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="163" spans="2:29" ht="71.25" customHeight="1">
@@ -7728,7 +7725,7 @@
       <c r="H163" s="4"/>
       <c r="K163" s="4"/>
       <c r="L163" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="2:29" ht="71.25" customHeight="1">
@@ -7739,7 +7736,7 @@
       <c r="H164" s="4"/>
       <c r="K164" s="4"/>
       <c r="L164" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165" spans="2:29" ht="77.25" customHeight="1">
@@ -7750,7 +7747,7 @@
       <c r="H165" s="4"/>
       <c r="K165" s="4"/>
       <c r="L165" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="166" spans="2:29" ht="77.25" customHeight="1">
@@ -7761,7 +7758,7 @@
       <c r="H166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="167" spans="2:29" ht="77.25" customHeight="1">
@@ -7772,7 +7769,7 @@
       <c r="H167" s="4"/>
       <c r="K167" s="4"/>
       <c r="L167" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168" spans="2:29" ht="77.25" customHeight="1">
@@ -7783,7 +7780,7 @@
       <c r="H168" s="4"/>
       <c r="K168" s="4"/>
       <c r="L168" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="169" spans="2:29" ht="77.25" customHeight="1">
@@ -7794,7 +7791,7 @@
       <c r="H169" s="4"/>
       <c r="K169" s="4"/>
       <c r="L169" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="170" spans="2:29" ht="38.25" customHeight="1">
@@ -7806,7 +7803,7 @@
       <c r="J170" s="11"/>
       <c r="K170" s="11"/>
       <c r="L170" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M170" s="11"/>
       <c r="Q170" s="11"/>
@@ -7832,7 +7829,7 @@
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
       <c r="L171" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M171" s="2"/>
       <c r="Q171" s="2"/>
@@ -7858,7 +7855,7 @@
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
       <c r="L172" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M172" s="2"/>
       <c r="Q172" s="2"/>
@@ -7884,7 +7881,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
       <c r="L173" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M173" s="2"/>
       <c r="Q173" s="2"/>
@@ -7910,7 +7907,7 @@
       <c r="J174" s="2"/>
       <c r="K174" s="2"/>
       <c r="L174" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M174" s="2"/>
       <c r="Q174" s="2"/>
@@ -7936,7 +7933,7 @@
       <c r="J175" s="2"/>
       <c r="K175" s="2"/>
       <c r="L175" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M175" s="2"/>
       <c r="Q175" s="2"/>
@@ -7962,7 +7959,7 @@
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
       <c r="L176" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M176" s="2"/>
       <c r="Q176" s="2"/>
@@ -7988,7 +7985,7 @@
       <c r="J177" s="2"/>
       <c r="K177" s="2"/>
       <c r="L177" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M177" s="2"/>
       <c r="Q177" s="2"/>
@@ -8014,7 +8011,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
       <c r="L178" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M178" s="2"/>
       <c r="Q178" s="2"/>
@@ -8040,7 +8037,7 @@
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
       <c r="L179" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M179" s="2"/>
       <c r="Q179" s="2"/>
@@ -8066,7 +8063,7 @@
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
       <c r="L180" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M180" s="2"/>
       <c r="Q180" s="2"/>
@@ -8092,7 +8089,7 @@
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
       <c r="L181" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M181" s="2"/>
       <c r="Q181" s="2"/>
@@ -8118,7 +8115,7 @@
       <c r="J182" s="2"/>
       <c r="K182" s="2"/>
       <c r="L182" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M182" s="2"/>
       <c r="Q182" s="2"/>
@@ -8144,7 +8141,7 @@
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
       <c r="L183" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M183" s="2"/>
       <c r="Q183" s="2"/>
@@ -8170,7 +8167,7 @@
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
       <c r="L184" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M184" s="2"/>
       <c r="Q184" s="2"/>
@@ -8196,7 +8193,7 @@
       <c r="J185" s="2"/>
       <c r="K185" s="2"/>
       <c r="L185" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M185" s="2"/>
       <c r="Q185" s="2"/>
@@ -8222,7 +8219,7 @@
       <c r="J186" s="2"/>
       <c r="K186" s="2"/>
       <c r="L186" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M186" s="2"/>
       <c r="Q186" s="2"/>
@@ -8248,7 +8245,7 @@
       <c r="J187" s="2"/>
       <c r="K187" s="2"/>
       <c r="L187" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M187" s="2"/>
       <c r="Q187" s="2"/>
@@ -8274,7 +8271,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="2"/>
       <c r="L188" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M188" s="2"/>
       <c r="Q188" s="2"/>
@@ -8300,7 +8297,7 @@
       <c r="J189" s="2"/>
       <c r="K189" s="2"/>
       <c r="L189" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M189" s="2"/>
       <c r="Q189" s="2"/>
@@ -8326,7 +8323,7 @@
       <c r="J190" s="2"/>
       <c r="K190" s="2"/>
       <c r="L190" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M190" s="2"/>
       <c r="Q190" s="2"/>
@@ -8352,7 +8349,7 @@
       <c r="J191" s="2"/>
       <c r="K191" s="2"/>
       <c r="L191" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M191" s="2"/>
       <c r="Q191" s="2"/>
@@ -8378,7 +8375,7 @@
       <c r="J192" s="2"/>
       <c r="K192" s="2"/>
       <c r="L192" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M192" s="2"/>
       <c r="Q192" s="2"/>
@@ -8404,7 +8401,7 @@
       <c r="J193" s="21"/>
       <c r="K193" s="21"/>
       <c r="L193" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M193" s="21"/>
       <c r="Q193" s="21"/>
@@ -8429,7 +8426,7 @@
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195" spans="2:29" ht="13.2">
@@ -8440,7 +8437,7 @@
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
       <c r="L195" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="196" spans="2:29" ht="13.2">
@@ -8451,7 +8448,7 @@
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
       <c r="L196" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="197" spans="2:29" ht="13.2">
@@ -8461,7 +8458,7 @@
       <c r="F197" s="4"/>
       <c r="K197" s="4"/>
       <c r="L197" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198" spans="2:29" ht="13.2">
@@ -8473,7 +8470,7 @@
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
       <c r="L198" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="2:29" ht="13.2">
@@ -8485,7 +8482,7 @@
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
       <c r="L199" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="200" spans="2:29" ht="13.2">
@@ -8497,7 +8494,7 @@
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
       <c r="L200" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="201" spans="2:29" ht="13.2">
@@ -8508,7 +8505,7 @@
       <c r="H201" s="4"/>
       <c r="K201" s="4"/>
       <c r="L201" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="202" spans="2:29" ht="13.2">
@@ -8519,7 +8516,7 @@
       <c r="J202" s="4"/>
       <c r="K202" s="4"/>
       <c r="L202" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="203" spans="2:29" ht="13.2">
@@ -8529,7 +8526,7 @@
       <c r="F203" s="4"/>
       <c r="K203" s="4"/>
       <c r="L203" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="204" spans="2:29" ht="13.2">
@@ -8540,7 +8537,7 @@
       <c r="H204" s="4"/>
       <c r="K204" s="4"/>
       <c r="L204" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="205" spans="2:29" ht="13.2">
@@ -8551,7 +8548,7 @@
       <c r="H205" s="4"/>
       <c r="K205" s="4"/>
       <c r="L205" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="206" spans="2:29" ht="13.2">
@@ -8562,7 +8559,7 @@
       <c r="H206" s="4"/>
       <c r="K206" s="4"/>
       <c r="L206" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="207" spans="2:29" ht="13.2">
@@ -8573,7 +8570,7 @@
       <c r="H207" s="4"/>
       <c r="K207" s="4"/>
       <c r="L207" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="208" spans="2:29" ht="13.2">
@@ -8584,7 +8581,7 @@
       <c r="H208" s="4"/>
       <c r="K208" s="4"/>
       <c r="L208" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="209" spans="1:29" ht="13.2">
@@ -8595,7 +8592,7 @@
       <c r="H209" s="4"/>
       <c r="K209" s="4"/>
       <c r="L209" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="210" spans="1:29" ht="13.2">
@@ -8610,7 +8607,7 @@
       <c r="I210" s="4"/>
       <c r="K210" s="4"/>
       <c r="L210" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N210" s="4"/>
       <c r="O210" s="4"/>
@@ -8628,7 +8625,7 @@
       <c r="I211" s="4"/>
       <c r="K211" s="4"/>
       <c r="L211" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N211" s="4"/>
       <c r="O211" s="4"/>
@@ -8646,7 +8643,7 @@
       <c r="I212" s="4"/>
       <c r="K212" s="4"/>
       <c r="L212" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N212" s="4"/>
       <c r="O212" s="4"/>
@@ -8664,7 +8661,7 @@
       <c r="I213" s="4"/>
       <c r="K213" s="4"/>
       <c r="L213" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N213" s="4"/>
       <c r="O213" s="4"/>
@@ -8682,7 +8679,7 @@
       <c r="I214" s="4"/>
       <c r="K214" s="4"/>
       <c r="L214" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N214" s="4"/>
       <c r="O214" s="4"/>
@@ -8700,7 +8697,7 @@
       <c r="I215" s="4"/>
       <c r="K215" s="4"/>
       <c r="L215" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N215" s="4"/>
       <c r="O215" s="4"/>
@@ -8718,7 +8715,7 @@
       <c r="I216" s="4"/>
       <c r="K216" s="4"/>
       <c r="L216" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N216" s="4"/>
       <c r="O216" s="4"/>
@@ -8736,7 +8733,7 @@
       <c r="I217" s="4"/>
       <c r="K217" s="4"/>
       <c r="L217" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N217" s="4"/>
       <c r="O217" s="4"/>
@@ -8755,7 +8752,7 @@
       <c r="J218" s="21"/>
       <c r="K218" s="21"/>
       <c r="L218" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M218" s="21"/>
       <c r="N218" s="4"/>
@@ -8786,7 +8783,7 @@
       <c r="I219" s="4"/>
       <c r="K219" s="4"/>
       <c r="L219" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N219" s="4"/>
       <c r="O219" s="4"/>
@@ -8805,7 +8802,7 @@
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
       <c r="L233" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M233" s="4"/>
       <c r="N233" s="4"/>
@@ -8838,7 +8835,7 @@
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
       <c r="L234" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M234" s="4"/>
       <c r="N234" s="4"/>
@@ -8870,7 +8867,7 @@
       <c r="I235" s="4"/>
       <c r="J235" s="4"/>
       <c r="L235" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N235" s="4"/>
       <c r="O235" s="4"/>
@@ -8888,7 +8885,7 @@
       <c r="I236" s="4"/>
       <c r="J236" s="4"/>
       <c r="L236" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N236" s="4"/>
       <c r="O236" s="4"/>
@@ -8906,7 +8903,7 @@
       <c r="I237" s="4"/>
       <c r="J237" s="4"/>
       <c r="L237" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N237" s="4"/>
       <c r="O237" s="4"/>
@@ -8924,7 +8921,7 @@
       <c r="I238" s="4"/>
       <c r="J238" s="4"/>
       <c r="L238" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N238" s="4"/>
       <c r="O238" s="4"/>
@@ -8942,7 +8939,7 @@
       <c r="I239" s="4"/>
       <c r="J239" s="4"/>
       <c r="L239" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N239" s="4"/>
       <c r="O239" s="4"/>
@@ -8960,7 +8957,7 @@
       <c r="I240" s="4"/>
       <c r="J240" s="4"/>
       <c r="L240" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N240" s="4"/>
       <c r="O240" s="4"/>
@@ -8978,7 +8975,7 @@
       <c r="I241" s="4"/>
       <c r="J241" s="4"/>
       <c r="L241" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N241" s="4"/>
       <c r="O241" s="4"/>
@@ -8996,7 +8993,7 @@
       <c r="I242" s="4"/>
       <c r="J242" s="4"/>
       <c r="L242" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N242" s="4"/>
       <c r="O242" s="4"/>
@@ -9014,7 +9011,7 @@
       <c r="I243" s="4"/>
       <c r="J243" s="4"/>
       <c r="L243" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N243" s="4"/>
       <c r="O243" s="4"/>
@@ -9032,7 +9029,7 @@
       <c r="I244" s="4"/>
       <c r="J244" s="4"/>
       <c r="L244" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N244" s="4"/>
       <c r="O244" s="4"/>
@@ -9050,7 +9047,7 @@
       <c r="I245" s="4"/>
       <c r="J245" s="4"/>
       <c r="L245" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N245" s="4"/>
       <c r="O245" s="4"/>
@@ -9068,7 +9065,7 @@
       <c r="I246" s="4"/>
       <c r="J246" s="4"/>
       <c r="L246" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N246" s="4"/>
       <c r="O246" s="4"/>
@@ -9086,7 +9083,7 @@
       <c r="I247" s="4"/>
       <c r="J247" s="4"/>
       <c r="L247" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N247" s="4"/>
       <c r="O247" s="4"/>
@@ -9104,7 +9101,7 @@
       <c r="I248" s="4"/>
       <c r="J248" s="4"/>
       <c r="L248" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N248" s="4"/>
       <c r="O248" s="4"/>
@@ -9122,7 +9119,7 @@
       <c r="I249" s="4"/>
       <c r="J249" s="4"/>
       <c r="L249" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N249" s="4"/>
       <c r="O249" s="4"/>
@@ -9140,7 +9137,7 @@
       <c r="I250" s="4"/>
       <c r="J250" s="4"/>
       <c r="L250" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N250" s="4"/>
       <c r="O250" s="4"/>
@@ -9158,7 +9155,7 @@
       <c r="I251" s="4"/>
       <c r="J251" s="4"/>
       <c r="L251" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N251" s="4"/>
       <c r="O251" s="4"/>
@@ -9176,7 +9173,7 @@
       <c r="I252" s="4"/>
       <c r="J252" s="4"/>
       <c r="L252" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N252" s="4"/>
       <c r="O252" s="4"/>
@@ -9194,7 +9191,7 @@
       <c r="I253" s="4"/>
       <c r="J253" s="4"/>
       <c r="L253" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N253" s="4"/>
       <c r="O253" s="4"/>
@@ -9212,7 +9209,7 @@
       <c r="I254" s="4"/>
       <c r="J254" s="4"/>
       <c r="L254" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N254" s="4"/>
       <c r="O254" s="4"/>
@@ -9230,7 +9227,7 @@
       <c r="I255" s="4"/>
       <c r="J255" s="4"/>
       <c r="L255" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N255" s="4"/>
       <c r="O255" s="4"/>
@@ -9248,7 +9245,7 @@
       <c r="I256" s="4"/>
       <c r="J256" s="4"/>
       <c r="L256" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N256" s="4"/>
       <c r="O256" s="4"/>
@@ -9266,7 +9263,7 @@
       <c r="I257" s="4"/>
       <c r="J257" s="4"/>
       <c r="L257" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N257" s="4"/>
       <c r="O257" s="4"/>
@@ -9284,7 +9281,7 @@
       <c r="I258" s="4"/>
       <c r="J258" s="4"/>
       <c r="L258" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N258" s="4"/>
       <c r="O258" s="4"/>
@@ -9302,7 +9299,7 @@
       <c r="I259" s="4"/>
       <c r="J259" s="4"/>
       <c r="L259" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N259" s="4"/>
       <c r="O259" s="4"/>
@@ -9321,7 +9318,7 @@
       <c r="J260" s="22"/>
       <c r="K260" s="22"/>
       <c r="L260" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M260" s="22"/>
       <c r="N260" s="4"/>
@@ -9351,7 +9348,7 @@
       <c r="G261" s="4"/>
       <c r="I261" s="4"/>
       <c r="L261" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N261" s="4"/>
       <c r="O261" s="4"/>
@@ -9367,7 +9364,7 @@
       <c r="G262" s="4"/>
       <c r="I262" s="4"/>
       <c r="L262" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N262" s="4"/>
       <c r="O262" s="4"/>
@@ -9383,7 +9380,7 @@
       <c r="G263" s="4"/>
       <c r="I263" s="4"/>
       <c r="L263" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N263" s="4"/>
       <c r="O263" s="4"/>
@@ -9553,7 +9550,7 @@
       <c r="G275" s="4"/>
       <c r="I275" s="4"/>
       <c r="L275" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N275" s="4"/>
       <c r="O275" s="4"/>
@@ -9569,7 +9566,7 @@
       <c r="G276" s="4"/>
       <c r="I276" s="4"/>
       <c r="L276" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N276" s="4"/>
       <c r="O276" s="4"/>
@@ -9588,7 +9585,7 @@
       <c r="J277" s="23"/>
       <c r="K277" s="23"/>
       <c r="L277" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M277" s="23"/>
       <c r="N277" s="4"/>
@@ -9618,7 +9615,7 @@
       <c r="G278" s="4"/>
       <c r="I278" s="4"/>
       <c r="L278" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N278" s="4"/>
       <c r="O278" s="4"/>
@@ -9634,7 +9631,7 @@
       <c r="G279" s="4"/>
       <c r="I279" s="4"/>
       <c r="L279" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N279" s="4"/>
       <c r="O279" s="4"/>
@@ -9650,7 +9647,7 @@
       <c r="G280" s="4"/>
       <c r="I280" s="4"/>
       <c r="L280" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N280" s="4"/>
       <c r="O280" s="4"/>
@@ -9666,7 +9663,7 @@
       <c r="G281" s="4"/>
       <c r="I281" s="4"/>
       <c r="L281" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N281" s="4"/>
       <c r="O281" s="4"/>
@@ -9682,7 +9679,7 @@
       <c r="G282" s="4"/>
       <c r="I282" s="4"/>
       <c r="L282" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N282" s="4"/>
       <c r="O282" s="4"/>
@@ -9698,7 +9695,7 @@
       <c r="G283" s="4"/>
       <c r="I283" s="4"/>
       <c r="L283" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N283" s="4"/>
       <c r="O283" s="4"/>
@@ -9714,7 +9711,7 @@
       <c r="G284" s="4"/>
       <c r="I284" s="4"/>
       <c r="L284" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N284" s="4"/>
       <c r="O284" s="4"/>
@@ -9730,7 +9727,7 @@
       <c r="G285" s="4"/>
       <c r="I285" s="4"/>
       <c r="L285" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N285" s="4"/>
       <c r="O285" s="4"/>
@@ -9746,7 +9743,7 @@
       <c r="G286" s="4"/>
       <c r="I286" s="4"/>
       <c r="L286" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N286" s="4"/>
       <c r="O286" s="4"/>
@@ -9762,7 +9759,7 @@
       <c r="G287" s="4"/>
       <c r="I287" s="4"/>
       <c r="L287" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N287" s="4"/>
       <c r="O287" s="4"/>
@@ -9778,7 +9775,7 @@
       <c r="G288" s="4"/>
       <c r="I288" s="4"/>
       <c r="L288" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N288" s="4"/>
       <c r="O288" s="4"/>
@@ -9794,7 +9791,7 @@
       <c r="G289" s="4"/>
       <c r="I289" s="4"/>
       <c r="L289" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N289" s="4"/>
       <c r="O289" s="4"/>
@@ -9810,7 +9807,7 @@
       <c r="G290" s="4"/>
       <c r="I290" s="4"/>
       <c r="L290" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N290" s="4"/>
       <c r="O290" s="4"/>
@@ -9826,7 +9823,7 @@
       <c r="G291" s="4"/>
       <c r="I291" s="4"/>
       <c r="L291" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N291" s="4"/>
       <c r="O291" s="4"/>
@@ -9842,7 +9839,7 @@
       <c r="G292" s="4"/>
       <c r="I292" s="4"/>
       <c r="L292" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N292" s="4"/>
       <c r="O292" s="4"/>
@@ -9858,7 +9855,7 @@
       <c r="G293" s="4"/>
       <c r="I293" s="4"/>
       <c r="L293" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N293" s="4"/>
       <c r="O293" s="4"/>
@@ -9874,7 +9871,7 @@
       <c r="G294" s="4"/>
       <c r="I294" s="4"/>
       <c r="L294" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N294" s="4"/>
       <c r="O294" s="4"/>
@@ -9890,7 +9887,7 @@
       <c r="G295" s="4"/>
       <c r="I295" s="4"/>
       <c r="L295" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N295" s="4"/>
       <c r="O295" s="4"/>
@@ -9906,7 +9903,7 @@
       <c r="G296" s="4"/>
       <c r="I296" s="4"/>
       <c r="L296" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N296" s="4"/>
       <c r="O296" s="4"/>
@@ -9922,7 +9919,7 @@
       <c r="G297" s="4"/>
       <c r="I297" s="4"/>
       <c r="L297" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N297" s="4"/>
       <c r="O297" s="4"/>
@@ -9938,7 +9935,7 @@
       <c r="G298" s="4"/>
       <c r="I298" s="4"/>
       <c r="L298" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N298" s="4"/>
       <c r="O298" s="4"/>
@@ -9954,7 +9951,7 @@
       <c r="G299" s="4"/>
       <c r="I299" s="4"/>
       <c r="L299" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N299" s="4"/>
       <c r="O299" s="4"/>
@@ -9970,7 +9967,7 @@
       <c r="G300" s="4"/>
       <c r="I300" s="4"/>
       <c r="L300" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N300" s="4"/>
       <c r="O300" s="4"/>
@@ -9981,12 +9978,12 @@
       <c r="B301" s="2"/>
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
-      <c r="E301" s="31"/>
+      <c r="E301" s="32"/>
       <c r="F301" s="4"/>
       <c r="G301" s="4"/>
       <c r="I301" s="4"/>
       <c r="L301" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N301" s="4"/>
       <c r="O301" s="4"/>
@@ -9997,12 +9994,12 @@
       <c r="B302" s="2"/>
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
-      <c r="E302" s="32"/>
+      <c r="E302" s="33"/>
       <c r="F302" s="4"/>
       <c r="G302" s="4"/>
       <c r="I302" s="4"/>
       <c r="L302" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N302" s="4"/>
       <c r="O302" s="4"/>
@@ -10013,12 +10010,12 @@
       <c r="B303" s="2"/>
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
-      <c r="E303" s="32"/>
+      <c r="E303" s="33"/>
       <c r="F303" s="4"/>
       <c r="G303" s="4"/>
       <c r="I303" s="4"/>
       <c r="L303" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N303" s="4"/>
       <c r="O303" s="4"/>
@@ -10029,12 +10026,12 @@
       <c r="B304" s="2"/>
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
-      <c r="E304" s="32"/>
+      <c r="E304" s="33"/>
       <c r="F304" s="4"/>
       <c r="G304" s="4"/>
       <c r="I304" s="4"/>
       <c r="L304" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N304" s="4"/>
       <c r="O304" s="4"/>
@@ -10045,12 +10042,12 @@
       <c r="B305" s="2"/>
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
-      <c r="E305" s="32"/>
+      <c r="E305" s="33"/>
       <c r="F305" s="4"/>
       <c r="G305" s="4"/>
       <c r="I305" s="4"/>
       <c r="L305" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N305" s="4"/>
       <c r="O305" s="4"/>
@@ -10061,12 +10058,12 @@
       <c r="B306" s="2"/>
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
-      <c r="E306" s="32"/>
+      <c r="E306" s="33"/>
       <c r="F306" s="4"/>
       <c r="G306" s="4"/>
       <c r="I306" s="4"/>
       <c r="L306" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N306" s="4"/>
       <c r="O306" s="4"/>
@@ -10082,7 +10079,7 @@
       <c r="G307" s="4"/>
       <c r="I307" s="4"/>
       <c r="L307" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N307" s="4"/>
       <c r="O307" s="4"/>
@@ -10098,7 +10095,7 @@
       <c r="G308" s="4"/>
       <c r="I308" s="4"/>
       <c r="L308" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N308" s="4"/>
       <c r="O308" s="4"/>
@@ -10114,7 +10111,7 @@
       <c r="G309" s="4"/>
       <c r="I309" s="4"/>
       <c r="L309" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N309" s="4"/>
       <c r="O309" s="4"/>
@@ -10130,7 +10127,7 @@
       <c r="G310" s="4"/>
       <c r="I310" s="4"/>
       <c r="L310" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N310" s="4"/>
       <c r="O310" s="4"/>
@@ -10146,7 +10143,7 @@
       <c r="G311" s="4"/>
       <c r="I311" s="4"/>
       <c r="L311" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N311" s="4"/>
       <c r="O311" s="4"/>
@@ -10162,7 +10159,7 @@
       <c r="G312" s="4"/>
       <c r="I312" s="4"/>
       <c r="L312" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N312" s="4"/>
       <c r="O312" s="4"/>
@@ -10178,7 +10175,7 @@
       <c r="G313" s="4"/>
       <c r="I313" s="4"/>
       <c r="L313" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N313" s="4"/>
       <c r="O313" s="4"/>
@@ -10194,7 +10191,7 @@
       <c r="G314" s="4"/>
       <c r="I314" s="4"/>
       <c r="L314" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N314" s="4"/>
       <c r="O314" s="4"/>
@@ -10210,7 +10207,7 @@
       <c r="G315" s="4"/>
       <c r="I315" s="4"/>
       <c r="L315" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N315" s="4"/>
       <c r="O315" s="4"/>
@@ -10226,7 +10223,7 @@
       <c r="G316" s="4"/>
       <c r="I316" s="4"/>
       <c r="L316" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N316" s="4"/>
       <c r="O316" s="4"/>
@@ -10242,7 +10239,7 @@
       <c r="G317" s="4"/>
       <c r="I317" s="4"/>
       <c r="L317" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N317" s="4"/>
       <c r="O317" s="4"/>
@@ -10258,7 +10255,7 @@
       <c r="G318" s="4"/>
       <c r="I318" s="4"/>
       <c r="L318" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N318" s="4"/>
       <c r="O318" s="4"/>
@@ -10274,7 +10271,7 @@
       <c r="G319" s="4"/>
       <c r="I319" s="4"/>
       <c r="L319" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N319" s="4"/>
       <c r="O319" s="4"/>
@@ -10290,7 +10287,7 @@
       <c r="G320" s="4"/>
       <c r="I320" s="4"/>
       <c r="L320" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N320" s="4"/>
       <c r="O320" s="4"/>
@@ -10306,7 +10303,7 @@
       <c r="G321" s="4"/>
       <c r="I321" s="4"/>
       <c r="L321" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N321" s="4"/>
       <c r="O321" s="4"/>
@@ -10322,7 +10319,7 @@
       <c r="G322" s="4"/>
       <c r="I322" s="4"/>
       <c r="L322" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N322" s="4"/>
       <c r="O322" s="4"/>
@@ -10338,7 +10335,7 @@
       <c r="G323" s="4"/>
       <c r="I323" s="4"/>
       <c r="L323" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N323" s="4"/>
       <c r="O323" s="4"/>
@@ -10354,7 +10351,7 @@
       <c r="G324" s="4"/>
       <c r="I324" s="4"/>
       <c r="L324" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N324" s="4"/>
       <c r="O324" s="4"/>
@@ -10370,7 +10367,7 @@
       <c r="G325" s="4"/>
       <c r="I325" s="4"/>
       <c r="L325" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N325" s="4"/>
       <c r="O325" s="4"/>
@@ -10386,7 +10383,7 @@
       <c r="G326" s="4"/>
       <c r="I326" s="4"/>
       <c r="L326" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N326" s="4"/>
       <c r="O326" s="4"/>
@@ -10402,7 +10399,7 @@
       <c r="G327" s="4"/>
       <c r="I327" s="4"/>
       <c r="L327" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N327" s="4"/>
       <c r="O327" s="4"/>
@@ -10418,7 +10415,7 @@
       <c r="G328" s="4"/>
       <c r="I328" s="4"/>
       <c r="L328" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N328" s="4"/>
       <c r="O328" s="4"/>
@@ -10434,7 +10431,7 @@
       <c r="G329" s="4"/>
       <c r="I329" s="4"/>
       <c r="L329" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N329" s="4"/>
       <c r="O329" s="4"/>
@@ -10453,7 +10450,7 @@
       <c r="J330" s="24"/>
       <c r="K330" s="24"/>
       <c r="L330" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M330" s="24"/>
       <c r="N330" s="4"/>
@@ -10486,7 +10483,7 @@
       <c r="J331" s="4"/>
       <c r="K331" s="4"/>
       <c r="L331" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M331" s="4"/>
       <c r="N331" s="4"/>
@@ -10517,7 +10514,7 @@
       <c r="I332" s="4"/>
       <c r="J332" s="4"/>
       <c r="L332" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N332" s="4"/>
       <c r="O332" s="4"/>
@@ -10533,7 +10530,7 @@
       <c r="G333" s="4"/>
       <c r="I333" s="4"/>
       <c r="L333" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N333" s="4"/>
       <c r="O333" s="4"/>
@@ -10549,7 +10546,7 @@
       <c r="G334" s="4"/>
       <c r="I334" s="4"/>
       <c r="L334" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N334" s="4"/>
       <c r="O334" s="4"/>
@@ -10565,7 +10562,7 @@
       <c r="G335" s="4"/>
       <c r="I335" s="4"/>
       <c r="L335" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N335" s="4"/>
       <c r="O335" s="4"/>
@@ -10581,7 +10578,7 @@
       <c r="G336" s="4"/>
       <c r="I336" s="4"/>
       <c r="L336" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N336" s="4"/>
       <c r="O336" s="4"/>
@@ -10597,7 +10594,7 @@
       <c r="G337" s="4"/>
       <c r="I337" s="4"/>
       <c r="L337" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N337" s="4"/>
       <c r="O337" s="4"/>
@@ -10613,7 +10610,7 @@
       <c r="G338" s="4"/>
       <c r="I338" s="4"/>
       <c r="L338" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N338" s="4"/>
       <c r="O338" s="4"/>
@@ -10629,7 +10626,7 @@
       <c r="G339" s="4"/>
       <c r="I339" s="4"/>
       <c r="L339" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N339" s="4"/>
       <c r="O339" s="4"/>
@@ -10645,7 +10642,7 @@
       <c r="G340" s="4"/>
       <c r="I340" s="4"/>
       <c r="L340" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N340" s="4"/>
       <c r="O340" s="4"/>
@@ -10661,7 +10658,7 @@
       <c r="G341" s="4"/>
       <c r="I341" s="4"/>
       <c r="L341" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N341" s="4"/>
       <c r="O341" s="4"/>
@@ -10677,7 +10674,7 @@
       <c r="G342" s="4"/>
       <c r="I342" s="4"/>
       <c r="L342" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N342" s="4"/>
       <c r="O342" s="4"/>
@@ -10693,7 +10690,7 @@
       <c r="G343" s="4"/>
       <c r="I343" s="4"/>
       <c r="L343" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N343" s="4"/>
       <c r="O343" s="4"/>
@@ -10709,7 +10706,7 @@
       <c r="G344" s="4"/>
       <c r="I344" s="4"/>
       <c r="L344" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N344" s="4"/>
       <c r="O344" s="4"/>
@@ -10725,7 +10722,7 @@
       <c r="G345" s="4"/>
       <c r="I345" s="4"/>
       <c r="L345" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N345" s="4"/>
       <c r="O345" s="4"/>
@@ -10741,7 +10738,7 @@
       <c r="G346" s="4"/>
       <c r="I346" s="4"/>
       <c r="L346" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N346" s="4"/>
       <c r="O346" s="4"/>
@@ -10758,7 +10755,7 @@
       <c r="H347" s="4"/>
       <c r="I347" s="4"/>
       <c r="L347" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N347" s="4"/>
       <c r="O347" s="4"/>
@@ -10774,7 +10771,7 @@
       <c r="G348" s="4"/>
       <c r="I348" s="4"/>
       <c r="L348" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N348" s="4"/>
       <c r="O348" s="4"/>
@@ -10790,7 +10787,7 @@
       <c r="G349" s="4"/>
       <c r="I349" s="4"/>
       <c r="L349" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N349" s="4"/>
       <c r="O349" s="4"/>
@@ -10807,7 +10804,7 @@
       <c r="H350" s="4"/>
       <c r="I350" s="4"/>
       <c r="L350" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N350" s="4"/>
       <c r="O350" s="4"/>
@@ -10823,7 +10820,7 @@
       <c r="G351" s="4"/>
       <c r="I351" s="4"/>
       <c r="L351" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N351" s="4"/>
       <c r="O351" s="4"/>
@@ -10839,7 +10836,7 @@
       <c r="G352" s="4"/>
       <c r="I352" s="4"/>
       <c r="L352" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N352" s="4"/>
       <c r="O352" s="4"/>
@@ -10855,7 +10852,7 @@
       <c r="G353" s="4"/>
       <c r="I353" s="4"/>
       <c r="L353" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N353" s="4"/>
       <c r="O353" s="4"/>
@@ -10871,7 +10868,7 @@
       <c r="G354" s="4"/>
       <c r="I354" s="4"/>
       <c r="L354" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N354" s="4"/>
       <c r="O354" s="4"/>
@@ -10890,7 +10887,7 @@
       <c r="J355" s="11"/>
       <c r="K355" s="11"/>
       <c r="L355" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M355" s="11"/>
       <c r="N355" s="4"/>
@@ -10920,7 +10917,7 @@
       <c r="G356" s="4"/>
       <c r="I356" s="4"/>
       <c r="L356" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N356" s="4"/>
       <c r="O356" s="4"/>
@@ -10936,7 +10933,7 @@
       <c r="G357" s="4"/>
       <c r="I357" s="4"/>
       <c r="L357" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N357" s="4"/>
       <c r="O357" s="4"/>
@@ -10952,7 +10949,7 @@
       <c r="G358" s="4"/>
       <c r="I358" s="4"/>
       <c r="L358" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N358" s="4"/>
       <c r="O358" s="4"/>
@@ -10968,7 +10965,7 @@
       <c r="G359" s="4"/>
       <c r="I359" s="4"/>
       <c r="L359" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N359" s="4"/>
       <c r="O359" s="4"/>
@@ -10984,7 +10981,7 @@
       <c r="G360" s="4"/>
       <c r="I360" s="4"/>
       <c r="L360" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N360" s="4"/>
       <c r="O360" s="4"/>
@@ -11000,7 +10997,7 @@
       <c r="G361" s="4"/>
       <c r="I361" s="4"/>
       <c r="L361" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N361" s="4"/>
       <c r="O361" s="4"/>
@@ -11016,7 +11013,7 @@
       <c r="G362" s="4"/>
       <c r="I362" s="4"/>
       <c r="L362" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N362" s="4"/>
       <c r="O362" s="4"/>
@@ -11032,7 +11029,7 @@
       <c r="G363" s="4"/>
       <c r="I363" s="4"/>
       <c r="L363" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N363" s="4"/>
       <c r="O363" s="4"/>
@@ -11048,7 +11045,7 @@
       <c r="G364" s="4"/>
       <c r="I364" s="4"/>
       <c r="L364" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N364" s="4"/>
       <c r="O364" s="4"/>
@@ -11064,7 +11061,7 @@
       <c r="G365" s="4"/>
       <c r="I365" s="4"/>
       <c r="L365" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N365" s="4"/>
       <c r="O365" s="4"/>
@@ -11080,7 +11077,7 @@
       <c r="G366" s="4"/>
       <c r="I366" s="4"/>
       <c r="L366" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N366" s="4"/>
       <c r="O366" s="4"/>
@@ -11096,7 +11093,7 @@
       <c r="G367" s="4"/>
       <c r="I367" s="4"/>
       <c r="L367" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N367" s="4"/>
       <c r="O367" s="4"/>
@@ -11112,7 +11109,7 @@
       <c r="G368" s="4"/>
       <c r="I368" s="4"/>
       <c r="L368" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N368" s="4"/>
       <c r="O368" s="4"/>
@@ -11128,7 +11125,7 @@
       <c r="G369" s="4"/>
       <c r="I369" s="4"/>
       <c r="L369" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N369" s="4"/>
       <c r="O369" s="4"/>
@@ -11144,7 +11141,7 @@
       <c r="G370" s="4"/>
       <c r="I370" s="4"/>
       <c r="L370" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N370" s="4"/>
       <c r="O370" s="4"/>
@@ -11160,7 +11157,7 @@
       <c r="G371" s="4"/>
       <c r="I371" s="4"/>
       <c r="L371" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N371" s="4"/>
       <c r="O371" s="4"/>
@@ -11176,7 +11173,7 @@
       <c r="G372" s="4"/>
       <c r="I372" s="4"/>
       <c r="L372" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N372" s="4"/>
       <c r="O372" s="4"/>
@@ -11192,7 +11189,7 @@
       <c r="G373" s="4"/>
       <c r="I373" s="4"/>
       <c r="L373" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N373" s="4"/>
       <c r="O373" s="4"/>
@@ -11208,7 +11205,7 @@
       <c r="G374" s="4"/>
       <c r="I374" s="4"/>
       <c r="L374" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N374" s="4"/>
       <c r="O374" s="4"/>
@@ -11224,7 +11221,7 @@
       <c r="G375" s="4"/>
       <c r="I375" s="4"/>
       <c r="L375" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N375" s="4"/>
       <c r="O375" s="4"/>
@@ -11240,7 +11237,7 @@
       <c r="G376" s="4"/>
       <c r="I376" s="4"/>
       <c r="L376" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N376" s="4"/>
       <c r="O376" s="4"/>
@@ -11256,7 +11253,7 @@
       <c r="G377" s="4"/>
       <c r="I377" s="4"/>
       <c r="L377" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N377" s="4"/>
       <c r="O377" s="4"/>
@@ -11272,7 +11269,7 @@
       <c r="G378" s="4"/>
       <c r="I378" s="4"/>
       <c r="L378" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N378" s="4"/>
       <c r="O378" s="4"/>
@@ -11288,7 +11285,7 @@
       <c r="G379" s="4"/>
       <c r="I379" s="4"/>
       <c r="L379" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N379" s="4"/>
       <c r="O379" s="4"/>
@@ -11304,7 +11301,7 @@
       <c r="G380" s="4"/>
       <c r="I380" s="4"/>
       <c r="L380" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N380" s="4"/>
       <c r="O380" s="4"/>
@@ -11320,7 +11317,7 @@
       <c r="G381" s="4"/>
       <c r="I381" s="4"/>
       <c r="L381" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N381" s="4"/>
       <c r="O381" s="4"/>
@@ -11336,7 +11333,7 @@
       <c r="G382" s="4"/>
       <c r="I382" s="4"/>
       <c r="L382" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N382" s="4"/>
       <c r="O382" s="4"/>
@@ -11352,7 +11349,7 @@
       <c r="G383" s="4"/>
       <c r="I383" s="4"/>
       <c r="L383" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N383" s="4"/>
       <c r="O383" s="4"/>
@@ -11368,7 +11365,7 @@
       <c r="G384" s="4"/>
       <c r="I384" s="4"/>
       <c r="L384" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N384" s="4"/>
       <c r="O384" s="4"/>
@@ -11384,7 +11381,7 @@
       <c r="G385" s="4"/>
       <c r="I385" s="4"/>
       <c r="L385" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N385" s="4"/>
       <c r="O385" s="4"/>
@@ -11400,7 +11397,7 @@
       <c r="G386" s="4"/>
       <c r="I386" s="4"/>
       <c r="L386" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N386" s="4"/>
       <c r="O386" s="4"/>
@@ -11416,7 +11413,7 @@
       <c r="G387" s="4"/>
       <c r="I387" s="4"/>
       <c r="L387" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N387" s="4"/>
       <c r="O387" s="4"/>
@@ -11432,7 +11429,7 @@
       <c r="G388" s="4"/>
       <c r="I388" s="4"/>
       <c r="L388" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N388" s="4"/>
       <c r="O388" s="4"/>
@@ -11448,7 +11445,7 @@
       <c r="G389" s="4"/>
       <c r="I389" s="4"/>
       <c r="L389" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N389" s="4"/>
       <c r="O389" s="4"/>
@@ -11464,7 +11461,7 @@
       <c r="G390" s="4"/>
       <c r="I390" s="4"/>
       <c r="L390" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N390" s="4"/>
       <c r="O390" s="4"/>
@@ -11480,7 +11477,7 @@
       <c r="G391" s="4"/>
       <c r="I391" s="4"/>
       <c r="L391" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N391" s="4"/>
       <c r="O391" s="4"/>
@@ -11496,7 +11493,7 @@
       <c r="G392" s="4"/>
       <c r="I392" s="4"/>
       <c r="L392" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N392" s="4"/>
       <c r="O392" s="4"/>
@@ -11512,7 +11509,7 @@
       <c r="G393" s="4"/>
       <c r="I393" s="4"/>
       <c r="L393" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N393" s="4"/>
       <c r="O393" s="4"/>
@@ -11528,7 +11525,7 @@
       <c r="G394" s="4"/>
       <c r="I394" s="4"/>
       <c r="L394" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N394" s="4"/>
       <c r="O394" s="4"/>
@@ -11544,7 +11541,7 @@
       <c r="G395" s="4"/>
       <c r="I395" s="4"/>
       <c r="L395" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N395" s="4"/>
       <c r="O395" s="4"/>
@@ -11560,7 +11557,7 @@
       <c r="G396" s="4"/>
       <c r="I396" s="4"/>
       <c r="L396" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N396" s="4"/>
       <c r="O396" s="4"/>
@@ -11576,7 +11573,7 @@
       <c r="G397" s="4"/>
       <c r="I397" s="4"/>
       <c r="L397" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N397" s="4"/>
       <c r="O397" s="4"/>
@@ -11592,7 +11589,7 @@
       <c r="G398" s="4"/>
       <c r="I398" s="4"/>
       <c r="L398" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N398" s="4"/>
       <c r="O398" s="4"/>
@@ -11608,7 +11605,7 @@
       <c r="G399" s="4"/>
       <c r="I399" s="4"/>
       <c r="L399" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N399" s="4"/>
       <c r="O399" s="4"/>
@@ -11624,7 +11621,7 @@
       <c r="G400" s="4"/>
       <c r="I400" s="4"/>
       <c r="L400" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N400" s="4"/>
       <c r="O400" s="4"/>
@@ -11640,7 +11637,7 @@
       <c r="G401" s="4"/>
       <c r="I401" s="4"/>
       <c r="L401" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N401" s="4"/>
       <c r="O401" s="4"/>
@@ -11656,7 +11653,7 @@
       <c r="G402" s="4"/>
       <c r="I402" s="4"/>
       <c r="L402" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N402" s="4"/>
       <c r="O402" s="4"/>
@@ -11672,7 +11669,7 @@
       <c r="G403" s="4"/>
       <c r="I403" s="4"/>
       <c r="L403" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N403" s="4"/>
       <c r="O403" s="4"/>
@@ -11688,7 +11685,7 @@
       <c r="G404" s="4"/>
       <c r="I404" s="4"/>
       <c r="L404" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N404" s="4"/>
       <c r="O404" s="4"/>
@@ -11704,7 +11701,7 @@
       <c r="G405" s="4"/>
       <c r="I405" s="4"/>
       <c r="L405" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N405" s="4"/>
       <c r="O405" s="4"/>
